--- a/datos.xlsx
+++ b/datos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OACEVEDOD\Desktop\Jefe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OACEVEDOD\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9541749C-7026-4426-9468-F43457560B1C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2FAD8F-B67F-441D-812D-E81A83926EFD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,52 +28,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={8E3B43B7-4E50-49A0-BFFA-6EEC1658D79C}</author>
-    <author>tc={32851E12-2A14-423F-AF75-3D964D0C8E1F}</author>
-  </authors>
-  <commentList>
-    <comment ref="L5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    CAMBIO FECHA DE TERMINACIÓN PERO NO REPORTA ESTE AJUSTE EN LA PLATAFORMA</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    CAMBIO FECHA DE TERMINACION PERO NO REPORTA DICHO AJUSTE EN PLATAFORMA
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="239">
   <si>
     <t>PROYECTOS APROBADOS POR ASIGNACIÓN CON CARGO AL SISTEMA GENERAL DE REGALÍAS DEPARTAMENTO DE Antioquia - 2024-2026</t>
   </si>
@@ -169,9 +125,6 @@
     <t>26/02/2026</t>
   </si>
   <si>
-    <t>99,52</t>
-  </si>
-  <si>
     <t>SAN LUIS</t>
   </si>
   <si>
@@ -205,12 +158,6 @@
     <t>CONTRATADO EN EJECUCIÓN</t>
   </si>
   <si>
-    <t>25,22</t>
-  </si>
-  <si>
-    <t>27,22</t>
-  </si>
-  <si>
     <t>BRICEÑO</t>
   </si>
   <si>
@@ -229,15 +176,6 @@
     <t>23/08/2026</t>
   </si>
   <si>
-    <t>98,3</t>
-  </si>
-  <si>
-    <t>89,2</t>
-  </si>
-  <si>
-    <t>89,64</t>
-  </si>
-  <si>
     <t>TÁMESIS</t>
   </si>
   <si>
@@ -250,18 +188,12 @@
     <t>26/09/2025</t>
   </si>
   <si>
-    <t>98,69</t>
-  </si>
-  <si>
     <t>NARIÑO</t>
   </si>
   <si>
     <t>Mejoramiento de vías terciarias mediante la pavimentación en placa huella del tramo que conecta a Puente Linda con el Corregimiento de Puerto Venus en el municipio de Nariño Antioquia</t>
   </si>
   <si>
-    <t>98,41</t>
-  </si>
-  <si>
     <t>GIRALDO</t>
   </si>
   <si>
@@ -271,12 +203,6 @@
     <t>Construcción de placa huella productiva en la vía terciaria Águila-Roblar del municipio de Giraldo</t>
   </si>
   <si>
-    <t>100,01</t>
-  </si>
-  <si>
-    <t>62,65</t>
-  </si>
-  <si>
     <t>CAROLINA DEL PRÍNCIPE</t>
   </si>
   <si>
@@ -292,9 +218,6 @@
     <t>NO DEFINIDO</t>
   </si>
   <si>
-    <t>120,38</t>
-  </si>
-  <si>
     <t>ENTRERRÍOS</t>
   </si>
   <si>
@@ -310,27 +233,12 @@
     <t>28/11/2026</t>
   </si>
   <si>
-    <t>73,01</t>
-  </si>
-  <si>
-    <t>59,95</t>
-  </si>
-  <si>
-    <t>76,13</t>
-  </si>
-  <si>
-    <t>83,52</t>
-  </si>
-  <si>
     <t>ANDES</t>
   </si>
   <si>
     <t>Mejoramiento de la malla vial de 3 km mediante el sistema constructivo de placa huella en el corredor vial Andes - Santa Rita; en el municipio de Andes departamento de Antioquia</t>
   </si>
   <si>
-    <t>79,94</t>
-  </si>
-  <si>
     <t>COCORNÁ</t>
   </si>
   <si>
@@ -346,12 +254,6 @@
     <t>31/08/2026</t>
   </si>
   <si>
-    <t>97,04</t>
-  </si>
-  <si>
-    <t>60,54</t>
-  </si>
-  <si>
     <t>TITIRIBÍ</t>
   </si>
   <si>
@@ -373,15 +275,6 @@
     <t>31/07/2027</t>
   </si>
   <si>
-    <t>13,08</t>
-  </si>
-  <si>
-    <t>7,59</t>
-  </si>
-  <si>
-    <t>21,74</t>
-  </si>
-  <si>
     <t>SOPETRÁN</t>
   </si>
   <si>
@@ -394,21 +287,6 @@
     <t>29/09/2026</t>
   </si>
   <si>
-    <t>80,46</t>
-  </si>
-  <si>
-    <t>84,53</t>
-  </si>
-  <si>
-    <t>86,13</t>
-  </si>
-  <si>
-    <t>88,50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prorroga 90 días+ adición de recursos (obras complementarias) </t>
-  </si>
-  <si>
     <t>PUERTO TRIUNFO</t>
   </si>
   <si>
@@ -424,9 +302,6 @@
     <t>22/03/2026</t>
   </si>
   <si>
-    <t>99,95</t>
-  </si>
-  <si>
     <t>SAN JOSÉ DE LA MONTAÑA</t>
   </si>
   <si>
@@ -445,18 +320,6 @@
     <t>28/09/2026</t>
   </si>
   <si>
-    <t>64,74</t>
-  </si>
-  <si>
-    <t>22,45</t>
-  </si>
-  <si>
-    <t>87,62</t>
-  </si>
-  <si>
-    <t>97,2</t>
-  </si>
-  <si>
     <t>GÓMEZ PLATA</t>
   </si>
   <si>
@@ -487,18 +350,6 @@
     <t>30/09/2026</t>
   </si>
   <si>
-    <t>45,38</t>
-  </si>
-  <si>
-    <t>36,26</t>
-  </si>
-  <si>
-    <t>63,55</t>
-  </si>
-  <si>
-    <t>98,4</t>
-  </si>
-  <si>
     <t>DONMATÍAS</t>
   </si>
   <si>
@@ -511,12 +362,6 @@
     <t>27/07/2026</t>
   </si>
   <si>
-    <t>97,87</t>
-  </si>
-  <si>
-    <t>90,17</t>
-  </si>
-  <si>
     <t>MARINILLA</t>
   </si>
   <si>
@@ -526,15 +371,6 @@
     <t>22/09/2026</t>
   </si>
   <si>
-    <t>95,93</t>
-  </si>
-  <si>
-    <t>71,73</t>
-  </si>
-  <si>
-    <t>96,3</t>
-  </si>
-  <si>
     <t>SAN JUAN DE URABÁ</t>
   </si>
   <si>
@@ -544,30 +380,12 @@
     <t>Construccion de placa huella en la vía de acceso al corregimiento de Belén, municipio de San Juan de Urabá, departamento de Antioquia</t>
   </si>
   <si>
-    <t>37,27</t>
-  </si>
-  <si>
-    <t>66,47</t>
-  </si>
-  <si>
     <t>SAN RAFAEL</t>
   </si>
   <si>
     <t>Mejoramiento de vias terciarias en los sectores de Manila, La Luz, Chico y Bizcocho en el municipio de San Rafael, Antioquia</t>
   </si>
   <si>
-    <t>85,28</t>
-  </si>
-  <si>
-    <t>77,01</t>
-  </si>
-  <si>
-    <t>85,80</t>
-  </si>
-  <si>
-    <t>84,20</t>
-  </si>
-  <si>
     <t>Mejoramiento de la red vial de segundo orden mediante la construccion de un puente ubicado en la vÍa San fermín (ruta 25-Briceño) del departamento de Antioquia</t>
   </si>
   <si>
@@ -586,18 +404,6 @@
     <t>22/08/2026</t>
   </si>
   <si>
-    <t>98,97</t>
-  </si>
-  <si>
-    <t>98,25</t>
-  </si>
-  <si>
-    <t>99,98</t>
-  </si>
-  <si>
-    <t>48,6</t>
-  </si>
-  <si>
     <t>ANORÍ</t>
   </si>
   <si>
@@ -607,9 +413,6 @@
     <t>15/08/2026</t>
   </si>
   <si>
-    <t>83,9</t>
-  </si>
-  <si>
     <t>ITUANGO</t>
   </si>
   <si>
@@ -622,9 +425,6 @@
     <t>30/07/2027</t>
   </si>
   <si>
-    <t>0,68</t>
-  </si>
-  <si>
     <t>DEPARTAMENTO</t>
   </si>
   <si>
@@ -640,18 +440,6 @@
     <t>13/09/2026</t>
   </si>
   <si>
-    <t>82,86</t>
-  </si>
-  <si>
-    <t>62,88</t>
-  </si>
-  <si>
-    <t>96,46</t>
-  </si>
-  <si>
-    <t>83,30</t>
-  </si>
-  <si>
     <t>RIONEGRO</t>
   </si>
   <si>
@@ -673,33 +461,12 @@
     <t>18/08/2026</t>
   </si>
   <si>
-    <t>69,27</t>
-  </si>
-  <si>
-    <t>40,13</t>
-  </si>
-  <si>
-    <t>77,58</t>
-  </si>
-  <si>
-    <t>41,73</t>
-  </si>
-  <si>
     <t>Construcción de pavimento rígido en el área urbana del municipio de Cocorná Antioquia</t>
   </si>
   <si>
     <t>16/11/2026</t>
   </si>
   <si>
-    <t>60,71</t>
-  </si>
-  <si>
-    <t>84,45</t>
-  </si>
-  <si>
-    <t>99,55</t>
-  </si>
-  <si>
     <t>SANTO DOMINGO</t>
   </si>
   <si>
@@ -718,15 +485,6 @@
     <t>25/12/2026</t>
   </si>
   <si>
-    <t>56,27</t>
-  </si>
-  <si>
-    <t>68,52</t>
-  </si>
-  <si>
-    <t>77,99</t>
-  </si>
-  <si>
     <t>BETANIA</t>
   </si>
   <si>
@@ -736,12 +494,6 @@
     <t>15/11/2026</t>
   </si>
   <si>
-    <t>23,44</t>
-  </si>
-  <si>
-    <t>45,52</t>
-  </si>
-  <si>
     <t>SAN VICENTE FERRER</t>
   </si>
   <si>
@@ -751,78 +503,27 @@
     <t>17/10/2026</t>
   </si>
   <si>
-    <t>46,12</t>
-  </si>
-  <si>
-    <t>41,92</t>
-  </si>
-  <si>
-    <t>49,33</t>
-  </si>
-  <si>
-    <t>90,4</t>
-  </si>
-  <si>
     <t>HISPANIA</t>
   </si>
   <si>
     <t>Pavimentación mediante el sistema constructivo placa huella via terciaria San Juaquin vereda La Palamira del municipio de Hispania, Antioquía</t>
   </si>
   <si>
-    <t>45,49</t>
-  </si>
-  <si>
-    <t>45,88</t>
-  </si>
-  <si>
-    <t>58,40</t>
-  </si>
-  <si>
-    <t>73,71</t>
-  </si>
-  <si>
     <t>Mejoramientode la via de tercer orden Ye a La Bodega (Andes)-Buenas Aires-Puente Lata-Jericó en la subregión Suroeste del departamento de Antioquia</t>
   </si>
   <si>
     <t>31/03/2028</t>
   </si>
   <si>
-    <t>1,02</t>
-  </si>
-  <si>
-    <t>1,92</t>
-  </si>
-  <si>
-    <t>0,50</t>
-  </si>
-  <si>
-    <t>80,4</t>
-  </si>
-  <si>
     <t>TOLEDO</t>
   </si>
   <si>
     <t>Mejoramiento de vias terciarias mediante la construcción de placa huella vereda Helechales en la zona rural del municipio de Toledo, Antioquia</t>
   </si>
   <si>
-    <t>97,22</t>
-  </si>
-  <si>
-    <t>96,27</t>
-  </si>
-  <si>
-    <t>99,85</t>
-  </si>
-  <si>
     <t>Mejoramiento de vías mediante placa huella en la vereda Buenavista y Chorrillo en el municipio de Briceño, Antioquia</t>
   </si>
   <si>
-    <t>81,21</t>
-  </si>
-  <si>
-    <t>81,69</t>
-  </si>
-  <si>
     <t>GUATAPÉ</t>
   </si>
   <si>
@@ -832,54 +533,30 @@
     <t>24/01/2027</t>
   </si>
   <si>
-    <t>46,1</t>
-  </si>
-  <si>
-    <t>49,30</t>
-  </si>
-  <si>
     <t>Construcción de placa huella en la vía terciaria vereda El Encanto del municipio de Támesis del departamento de Antioquia</t>
   </si>
   <si>
     <t>28/07/2026</t>
   </si>
   <si>
-    <t>91,75</t>
-  </si>
-  <si>
     <t>Mejoramiento de las vías que conducen a las veredas El Llano y El Recreo del municipio de Nariño Antioquia</t>
   </si>
   <si>
     <t>22/11/2026</t>
   </si>
   <si>
-    <t>19,13</t>
-  </si>
-  <si>
-    <t>27,56</t>
-  </si>
-  <si>
     <t>HELICONIA</t>
   </si>
   <si>
     <t>Adecuación y Mejoramiento de la infraestructura vial del municipio de Heliconia, Antioquia</t>
   </si>
   <si>
-    <t>97,51</t>
-  </si>
-  <si>
-    <t>99,24</t>
-  </si>
-  <si>
     <t>CAMPAMENTO</t>
   </si>
   <si>
     <t>Pavimentación de via rural mediante contrucción de placa huella en la vereda El Limon del municipio de Campamento, Antioquia</t>
   </si>
   <si>
-    <t>99,49</t>
-  </si>
-  <si>
     <t>URRAO</t>
   </si>
   <si>
@@ -889,78 +566,33 @@
     <t>20/12/2026</t>
   </si>
   <si>
-    <t>31,83</t>
-  </si>
-  <si>
-    <t>35,69</t>
-  </si>
-  <si>
-    <t>60,19</t>
-  </si>
-  <si>
-    <t>38,06</t>
-  </si>
-  <si>
-    <t>79,6</t>
-  </si>
-  <si>
     <t>TARAZÁ</t>
   </si>
   <si>
     <t>Mejoramiento de vías de tercer orden mediante la intervención de puntos de atención prioritaria en el municipio de Tarazá del departamento de Antioquia</t>
   </si>
   <si>
-    <t>30,46</t>
-  </si>
-  <si>
     <t>TURBO</t>
   </si>
   <si>
     <t>Mejoramiento de la vía El Tres - San Pedro de Urabá (código: 62AN02) mediante la atención de un punto de atención prioritaria en el municipio de Turbo de la subregión Urabá del departamento de  Antioquia</t>
   </si>
   <si>
+    <t>28/04/2027</t>
+  </si>
+  <si>
     <t>CHIGORODÓ</t>
   </si>
   <si>
     <t>Transformación Urbanística de la Calle 97 y Vías Conexas para una Movilidad Segura en el Municipio de Chigorodó Antioquia</t>
   </si>
   <si>
-    <t>46,43</t>
-  </si>
-  <si>
-    <t>se necesito un ajuste que impidio el avance del proyecto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">el contratista se encuentra haciendo </t>
-  </si>
-  <si>
-    <t xml:space="preserve">la gobernacion aprobo un ajuste pero tienen un inconveniente de la piip con la migracion a gesproy, esta ayudando miladis con el cargue de la información, no migra la programacion y el ajuste de los nuevos </t>
-  </si>
-  <si>
-    <t>el proyecto sale con los valores antiguos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a hoy la ejecución esta aproximadamente en 46 y sube a aproximadamente a 58 </t>
-  </si>
-  <si>
     <t>ALEJANDRÍA</t>
   </si>
   <si>
     <t>Mejoramiento de vías del circuito productivo rural cafetero en el municipio de Alejandría Antioquia</t>
   </si>
   <si>
-    <t>86,08</t>
-  </si>
-  <si>
-    <t>51,1</t>
-  </si>
-  <si>
-    <t>96,48</t>
-  </si>
-  <si>
-    <t>91,56</t>
-  </si>
-  <si>
     <t>96,4</t>
   </si>
   <si>
@@ -970,18 +602,6 @@
     <t>26/03/2027</t>
   </si>
   <si>
-    <t>45,86</t>
-  </si>
-  <si>
-    <t>65,74</t>
-  </si>
-  <si>
-    <t>56,80</t>
-  </si>
-  <si>
-    <t>67,01</t>
-  </si>
-  <si>
     <t>SAN JERÓNIMO</t>
   </si>
   <si>
@@ -991,30 +611,9 @@
     <t>17/12/2026</t>
   </si>
   <si>
-    <t>28,56</t>
-  </si>
-  <si>
-    <t>44,26</t>
-  </si>
-  <si>
-    <t>47,61</t>
-  </si>
-  <si>
     <t>Mejoramiento de vías urbanas mediante la construcción de puentes vehiculares en los municipios de Rionegro y Cisneros del departamento de Antioquia</t>
   </si>
   <si>
-    <t>10,3</t>
-  </si>
-  <si>
-    <t>35,76</t>
-  </si>
-  <si>
-    <t>30,31</t>
-  </si>
-  <si>
-    <t>44,08</t>
-  </si>
-  <si>
     <t>CISNEROS</t>
   </si>
   <si>
@@ -1024,118 +623,67 @@
     <t>18/02/2027</t>
   </si>
   <si>
-    <t>16,66</t>
-  </si>
-  <si>
-    <t>31,53</t>
-  </si>
-  <si>
     <t>EL SANTUARIO</t>
   </si>
   <si>
     <t>Mejoramiento de vías terciarias en el municipio de El Santuario, Antioquia</t>
   </si>
   <si>
-    <t>14,94</t>
-  </si>
-  <si>
-    <t>19,34</t>
-  </si>
-  <si>
-    <t>27,90</t>
-  </si>
-  <si>
-    <t>30,04</t>
-  </si>
-  <si>
     <t>ANGOSTURA</t>
   </si>
   <si>
     <t>Mejoramiento de Vías Terciarias en el Municipio de Angostura Antioquia</t>
   </si>
   <si>
-    <t>19,09</t>
-  </si>
-  <si>
-    <t>36,66</t>
-  </si>
-  <si>
-    <t>57,61</t>
-  </si>
-  <si>
-    <t>63,05</t>
-  </si>
-  <si>
     <t>EL RETIRO</t>
   </si>
   <si>
     <t>Construcción de Placa Huella en la vía terciaria de la vereda Pantalio en el municipio de El Retiro Antioquia</t>
   </si>
   <si>
+    <t>MONTEBELLO</t>
+  </si>
+  <si>
+    <t>Mejoramiento de vías terciarias en las veredas La Camelia y el Tablazo del municipio de Montebello, Antioquia</t>
+  </si>
+  <si>
+    <t>78,6</t>
+  </si>
+  <si>
+    <t>ARGELIA</t>
+  </si>
+  <si>
+    <t>Mejoramiento de vías terciarias en el municipio de Argelia de María Antioquia</t>
+  </si>
+  <si>
+    <t>14/11/2026</t>
+  </si>
+  <si>
+    <t>Mejoramiento de la vía Bellavista - Sabanalarga Sector Patio Bonito en el municipio de Cisneros Antioquia</t>
+  </si>
+  <si>
+    <t>CÁCERES</t>
+  </si>
+  <si>
+    <t>Mejoramiento de Vías Rurales Mediante la Construcción de Placa Huella en el Municipio de Cáceres Antioquia</t>
+  </si>
+  <si>
+    <t>15/12/2026</t>
+  </si>
+  <si>
+    <t>ARMENIA MANTEQUILLA</t>
+  </si>
+  <si>
+    <t>Mejoramiento de vías terciarias en placa huella en la vereda la Horcona Municipio de Armenia Antioquia</t>
+  </si>
+  <si>
     <t>SIN CONTRATAR</t>
   </si>
   <si>
-    <t>MONTEBELLO</t>
-  </si>
-  <si>
-    <t>Mejoramiento de vías terciarias en las veredas La Camelia y el Tablazo del municipio de Montebello, Antioquia</t>
-  </si>
-  <si>
-    <t>78,6</t>
-  </si>
-  <si>
-    <t>ARGELIA</t>
-  </si>
-  <si>
-    <t>Mejoramiento de vías terciarias en el municipio de Argelia de María Antioquia</t>
-  </si>
-  <si>
-    <t>14/11/2026</t>
-  </si>
-  <si>
-    <t>47,67</t>
-  </si>
-  <si>
-    <t>46,93</t>
-  </si>
-  <si>
-    <t>51,93</t>
-  </si>
-  <si>
-    <t>63,72</t>
-  </si>
-  <si>
-    <t>Mejoramiento de la vía Bellavista - Sabanalarga Sector Patio Bonito en el municipio de Cisneros Antioquia</t>
-  </si>
-  <si>
-    <t>CÁCERES</t>
-  </si>
-  <si>
-    <t>Mejoramiento de Vías Rurales Mediante la Construcción de Placa Huella en el Municipio de Cáceres Antioquia</t>
-  </si>
-  <si>
-    <t>15/12/2026</t>
-  </si>
-  <si>
-    <t>45,06</t>
-  </si>
-  <si>
-    <t>63,83</t>
-  </si>
-  <si>
-    <t>ARMENIA MANTEQUILLA</t>
-  </si>
-  <si>
-    <t>Mejoramiento de vías terciarias en placa huella en la vereda la Horcona Municipio de Armenia Antioquia</t>
-  </si>
-  <si>
     <t>Construcción de placa huella para el mejoramiento de la vía que conduce al sector el Coco en el Municipio de Chigorodó Antioquia</t>
   </si>
   <si>
     <t>24/09/2026</t>
-  </si>
-  <si>
-    <t>35,73</t>
   </si>
   <si>
     <t>PUEBLORRICO</t>
@@ -1517,7 +1065,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1706,12 +1254,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="21" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1720,14 +1262,26 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -2042,11 +1596,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB121"/>
+  <dimension ref="A1:AC121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7" style="7" customWidth="1"/>
@@ -2066,37 +1620,38 @@
     <col min="21" max="16384" width="8.85546875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
-      <c r="A1" s="69" t="s">
+    <row r="1" spans="1:21">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
       <c r="I1" s="38"/>
       <c r="J1" s="38"/>
       <c r="K1" s="39"/>
       <c r="L1" s="38"/>
-      <c r="M1" s="69" t="s">
+      <c r="M1" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="69"/>
-      <c r="O1" s="69" t="s">
+      <c r="N1" s="70"/>
+      <c r="O1" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="69"/>
-      <c r="Q1" s="69" t="s">
+      <c r="P1" s="70"/>
+      <c r="Q1" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="69"/>
+      <c r="R1" s="70"/>
       <c r="S1" s="38"/>
       <c r="T1" s="38"/>
-    </row>
-    <row r="2" spans="1:20" s="28" customFormat="1" ht="54.6" customHeight="1">
+      <c r="U1" s="40"/>
+    </row>
+    <row r="2" spans="1:21" s="28" customFormat="1" ht="54.6" customHeight="1">
       <c r="A2" s="29" t="s">
         <v>4</v>
       </c>
@@ -2158,7 +1713,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="36.75" customHeight="1">
+    <row r="3" spans="1:21" ht="36.75" customHeight="1">
       <c r="A3" s="41">
         <v>2024</v>
       </c>
@@ -2192,7 +1747,7 @@
       <c r="K3" s="43">
         <v>45635</v>
       </c>
-      <c r="L3" s="68">
+      <c r="L3" s="72">
         <v>45788</v>
       </c>
       <c r="M3" s="44">
@@ -2215,8 +1770,9 @@
       <c r="T3" s="21">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U3" s="40"/>
+    </row>
+    <row r="4" spans="1:21" ht="36.75" customHeight="1">
       <c r="A4" s="41">
         <v>2024</v>
       </c>
@@ -2250,7 +1806,7 @@
       <c r="K4" s="43">
         <v>45637</v>
       </c>
-      <c r="L4" s="65" t="s">
+      <c r="L4" s="63" t="s">
         <v>30</v>
       </c>
       <c r="M4" s="22">
@@ -2262,14 +1818,14 @@
       <c r="O4" s="60">
         <v>100</v>
       </c>
-      <c r="P4" s="62" t="s">
-        <v>31</v>
+      <c r="P4" s="62">
+        <v>99.52</v>
       </c>
       <c r="Q4" s="62">
         <v>100</v>
       </c>
-      <c r="R4" s="62" t="s">
-        <v>31</v>
+      <c r="R4" s="62">
+        <v>99.52</v>
       </c>
       <c r="S4" s="57">
         <v>100</v>
@@ -2277,13 +1833,14 @@
       <c r="T4" s="21">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U4" s="40"/>
+    </row>
+    <row r="5" spans="1:21" ht="36.75" customHeight="1">
       <c r="A5" s="41">
         <v>2024</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="41" t="s">
         <v>21</v>
@@ -2295,7 +1852,7 @@
         <v>2024003050243</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G5" s="2">
         <v>4907167940</v>
@@ -2313,7 +1870,7 @@
         <v>45635</v>
       </c>
       <c r="L5" s="63" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M5" s="21">
         <v>99.25</v>
@@ -2330,21 +1887,22 @@
       <c r="Q5" s="60"/>
       <c r="R5" s="60"/>
       <c r="S5" s="57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T5" s="21">
         <v>100</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U5" s="40"/>
+    </row>
+    <row r="6" spans="1:21" ht="36.75" customHeight="1">
       <c r="A6" s="41">
         <v>2024</v>
       </c>
       <c r="B6" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="45" t="s">
         <v>36</v>
-      </c>
-      <c r="C6" s="45" t="s">
-        <v>37</v>
       </c>
       <c r="D6" s="36" t="s">
         <v>22</v>
@@ -2353,7 +1911,7 @@
         <v>2024053150037</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G6" s="2">
         <v>3945999620</v>
@@ -2371,7 +1929,7 @@
         <v>45635</v>
       </c>
       <c r="L6" s="63" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M6" s="21">
         <v>99.9</v>
@@ -2393,13 +1951,14 @@
       <c r="T6" s="21">
         <v>100</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U6" s="40"/>
+    </row>
+    <row r="7" spans="1:21" ht="36.75" customHeight="1">
       <c r="A7" s="41">
         <v>2024</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" s="41" t="s">
         <v>27</v>
@@ -2411,7 +1970,7 @@
         <v>2024003050241</v>
       </c>
       <c r="F7" s="36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G7" s="2">
         <v>4232130933.4000001</v>
@@ -2423,12 +1982,12 @@
         <v>24</v>
       </c>
       <c r="J7" s="57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K7" s="23">
         <v>45636</v>
       </c>
-      <c r="L7" s="66">
+      <c r="L7" s="64">
         <v>46336</v>
       </c>
       <c r="M7" s="21">
@@ -2437,14 +1996,14 @@
       <c r="N7" s="21">
         <v>58.62</v>
       </c>
-      <c r="O7" s="60" t="s">
-        <v>43</v>
+      <c r="O7" s="60">
+        <v>25.22</v>
       </c>
       <c r="P7" s="62">
         <v>60</v>
       </c>
-      <c r="Q7" s="62" t="s">
-        <v>44</v>
+      <c r="Q7" s="62">
+        <v>27.22</v>
       </c>
       <c r="R7" s="62">
         <v>60</v>
@@ -2455,16 +2014,17 @@
       <c r="T7" s="21">
         <v>35</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U7" s="40"/>
+    </row>
+    <row r="8" spans="1:21" ht="36.75" customHeight="1">
       <c r="A8" s="41">
         <v>2024</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" s="36" t="s">
         <v>22</v>
@@ -2473,7 +2033,7 @@
         <v>2024051070040</v>
       </c>
       <c r="F8" s="36" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G8" s="2">
         <v>1645755840</v>
@@ -2513,13 +2073,14 @@
       <c r="T8" s="21">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U8" s="40"/>
+    </row>
+    <row r="9" spans="1:21" ht="36.75" customHeight="1">
       <c r="A9" s="41">
         <v>2024</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C9" s="41" t="s">
         <v>21</v>
@@ -2531,7 +2092,7 @@
         <v>2024057560039</v>
       </c>
       <c r="F9" s="36" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G9" s="2">
         <v>4699883725</v>
@@ -2543,13 +2104,13 @@
         <v>24</v>
       </c>
       <c r="J9" s="57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K9" s="23">
         <v>45636</v>
       </c>
-      <c r="L9" s="65" t="s">
-        <v>50</v>
+      <c r="L9" s="63" t="s">
+        <v>47</v>
       </c>
       <c r="M9" s="21">
         <v>90.52</v>
@@ -2557,17 +2118,17 @@
       <c r="N9" s="21">
         <v>85.38</v>
       </c>
-      <c r="O9" s="60" t="s">
-        <v>51</v>
-      </c>
-      <c r="P9" s="62" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q9" s="62" t="s">
-        <v>51</v>
-      </c>
-      <c r="R9" s="62" t="s">
-        <v>53</v>
+      <c r="O9" s="60">
+        <v>98.3</v>
+      </c>
+      <c r="P9" s="62">
+        <v>89.2</v>
+      </c>
+      <c r="Q9" s="62">
+        <v>98.3</v>
+      </c>
+      <c r="R9" s="62">
+        <v>89.64</v>
       </c>
       <c r="S9" s="57">
         <v>100</v>
@@ -2575,16 +2136,17 @@
       <c r="T9" s="21">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U9" s="40"/>
+    </row>
+    <row r="10" spans="1:21" ht="36.75" customHeight="1">
       <c r="A10" s="41">
         <v>2024</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D10" s="36" t="s">
         <v>22</v>
@@ -2593,7 +2155,7 @@
         <v>2024057890040</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G10" s="2">
         <v>3035607509</v>
@@ -2610,8 +2172,8 @@
       <c r="K10" s="43">
         <v>45628</v>
       </c>
-      <c r="L10" s="65" t="s">
-        <v>57</v>
+      <c r="L10" s="63" t="s">
+        <v>51</v>
       </c>
       <c r="M10" s="21">
         <v>98.69</v>
@@ -2619,31 +2181,32 @@
       <c r="N10" s="21">
         <v>100</v>
       </c>
-      <c r="O10" s="60" t="s">
-        <v>58</v>
+      <c r="O10" s="60">
+        <v>98.69</v>
       </c>
       <c r="P10" s="62">
         <v>100</v>
       </c>
-      <c r="Q10" s="62" t="s">
-        <v>58</v>
+      <c r="Q10" s="62">
+        <v>98.69</v>
       </c>
       <c r="R10" s="62">
         <v>100</v>
       </c>
       <c r="S10" s="57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T10" s="21">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U10" s="40"/>
+    </row>
+    <row r="11" spans="1:21" ht="36.75" customHeight="1">
       <c r="A11" s="41">
         <v>2024</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C11" s="41" t="s">
         <v>21</v>
@@ -2655,7 +2218,7 @@
         <v>2024054830016</v>
       </c>
       <c r="F11" s="36" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G11" s="2">
         <v>2596905323</v>
@@ -2672,7 +2235,7 @@
       <c r="K11" s="43">
         <v>45636</v>
       </c>
-      <c r="L11" s="66">
+      <c r="L11" s="64">
         <v>45940</v>
       </c>
       <c r="M11" s="21">
@@ -2690,25 +2253,26 @@
       <c r="Q11" s="60">
         <v>100</v>
       </c>
-      <c r="R11" s="60" t="s">
-        <v>61</v>
+      <c r="R11" s="60">
+        <v>98.41</v>
       </c>
       <c r="S11" s="57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T11" s="21">
         <v>100</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U11" s="40"/>
+    </row>
+    <row r="12" spans="1:21" ht="36.75" customHeight="1">
       <c r="A12" s="41">
         <v>2024</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C12" s="41" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D12" s="36" t="s">
         <v>22</v>
@@ -2717,7 +2281,7 @@
         <v>2024003050236</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="G12" s="2">
         <v>1513619665</v>
@@ -2734,7 +2298,7 @@
       <c r="K12" s="43">
         <v>45618</v>
       </c>
-      <c r="L12" s="66">
+      <c r="L12" s="64">
         <v>45501</v>
       </c>
       <c r="M12" s="21">
@@ -2743,17 +2307,17 @@
       <c r="N12" s="21">
         <v>62.65</v>
       </c>
-      <c r="O12" s="60" t="s">
-        <v>65</v>
-      </c>
-      <c r="P12" s="62" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q12" s="62" t="s">
-        <v>65</v>
-      </c>
-      <c r="R12" s="62" t="s">
-        <v>66</v>
+      <c r="O12" s="60">
+        <v>100.01</v>
+      </c>
+      <c r="P12" s="62">
+        <v>62.65</v>
+      </c>
+      <c r="Q12" s="62">
+        <v>100.01</v>
+      </c>
+      <c r="R12" s="62">
+        <v>62.65</v>
       </c>
       <c r="S12" s="57">
         <v>90</v>
@@ -2761,16 +2325,17 @@
       <c r="T12" s="22">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U12" s="40"/>
+    </row>
+    <row r="13" spans="1:21" ht="36.75" customHeight="1">
       <c r="A13" s="41">
         <v>2024</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" s="36" t="s">
         <v>22</v>
@@ -2779,7 +2344,7 @@
         <v>2024003050238</v>
       </c>
       <c r="F13" s="36" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G13" s="2">
         <v>4622246270</v>
@@ -2797,7 +2362,7 @@
         <v>45635</v>
       </c>
       <c r="L13" s="63" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M13" s="21">
         <v>90.22</v>
@@ -2819,16 +2384,17 @@
       <c r="T13" s="21">
         <v>100</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U13" s="40"/>
+    </row>
+    <row r="14" spans="1:21" ht="36.75" customHeight="1">
       <c r="A14" s="45">
         <v>2024</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D14" s="36" t="s">
         <v>22</v>
@@ -2837,7 +2403,7 @@
         <v>2024003050244</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G14" s="3">
         <v>2177618498</v>
@@ -2849,13 +2415,13 @@
         <v>24</v>
       </c>
       <c r="J14" s="57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K14" s="23">
         <v>45636</v>
       </c>
-      <c r="L14" s="65" t="s">
-        <v>71</v>
+      <c r="L14" s="63" t="s">
+        <v>61</v>
       </c>
       <c r="M14" s="25">
         <v>0</v>
@@ -2866,31 +2432,32 @@
       <c r="O14" s="60">
         <v>0</v>
       </c>
-      <c r="P14" s="60" t="s">
-        <v>72</v>
+      <c r="P14" s="60">
+        <v>120.38</v>
       </c>
       <c r="Q14" s="60">
         <v>0</v>
       </c>
-      <c r="R14" s="60" t="s">
-        <v>72</v>
+      <c r="R14" s="60">
+        <v>120.38</v>
       </c>
       <c r="S14" s="57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T14" s="22">
         <v>100</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U14" s="40"/>
+    </row>
+    <row r="15" spans="1:21" ht="36.75" customHeight="1">
       <c r="A15" s="41">
         <v>2024</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" s="36" t="s">
         <v>22</v>
@@ -2899,7 +2466,7 @@
         <v>2024003050242</v>
       </c>
       <c r="F15" s="36" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G15" s="2">
         <v>2688840891</v>
@@ -2939,16 +2506,17 @@
       <c r="T15" s="21">
         <v>100</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U15" s="40"/>
+    </row>
+    <row r="16" spans="1:21" ht="36.75" customHeight="1">
       <c r="A16" s="41">
         <v>2024</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D16" s="36" t="s">
         <v>22</v>
@@ -2957,7 +2525,7 @@
         <v>2024003050245</v>
       </c>
       <c r="F16" s="36" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="G16" s="2">
         <v>6076769979</v>
@@ -2969,13 +2537,13 @@
         <v>24</v>
       </c>
       <c r="J16" s="57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K16" s="23">
         <v>45635</v>
       </c>
-      <c r="L16" s="65" t="s">
-        <v>77</v>
+      <c r="L16" s="63" t="s">
+        <v>66</v>
       </c>
       <c r="M16" s="21">
         <v>71.45</v>
@@ -2983,17 +2551,17 @@
       <c r="N16" s="21">
         <v>59.95</v>
       </c>
-      <c r="O16" s="60" t="s">
-        <v>78</v>
-      </c>
-      <c r="P16" s="60" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q16" s="60" t="s">
-        <v>80</v>
-      </c>
-      <c r="R16" s="60" t="s">
-        <v>81</v>
+      <c r="O16" s="60">
+        <v>73.010000000000005</v>
+      </c>
+      <c r="P16" s="60">
+        <v>59.95</v>
+      </c>
+      <c r="Q16" s="60">
+        <v>76.13</v>
+      </c>
+      <c r="R16" s="60">
+        <v>83.52</v>
       </c>
       <c r="S16" s="57">
         <v>100</v>
@@ -3001,16 +2569,17 @@
       <c r="T16" s="21">
         <v>81</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U16" s="40"/>
+    </row>
+    <row r="17" spans="1:21" ht="36.75" customHeight="1">
       <c r="A17" s="41">
         <v>2024</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D17" s="36" t="s">
         <v>22</v>
@@ -3019,7 +2588,7 @@
         <v>2024003050237</v>
       </c>
       <c r="F17" s="36" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="G17" s="2">
         <v>5449013721.6000004</v>
@@ -3036,7 +2605,7 @@
       <c r="K17" s="23">
         <v>45635</v>
       </c>
-      <c r="L17" s="66">
+      <c r="L17" s="64">
         <v>46083</v>
       </c>
       <c r="M17" s="21">
@@ -3048,14 +2617,14 @@
       <c r="O17" s="60">
         <v>100</v>
       </c>
-      <c r="P17" s="60" t="s">
-        <v>84</v>
+      <c r="P17" s="60">
+        <v>79.94</v>
       </c>
       <c r="Q17" s="60">
         <v>100</v>
       </c>
-      <c r="R17" s="60" t="s">
-        <v>84</v>
+      <c r="R17" s="60">
+        <v>79.94</v>
       </c>
       <c r="S17" s="57">
         <v>90</v>
@@ -3063,13 +2632,14 @@
       <c r="T17" s="21">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U17" s="40"/>
+    </row>
+    <row r="18" spans="1:21" ht="36.75" customHeight="1">
       <c r="A18" s="41">
         <v>2024</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="C18" s="45" t="s">
         <v>21</v>
@@ -3081,7 +2651,7 @@
         <v>2024051970041</v>
       </c>
       <c r="F18" s="36" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2">
         <v>3445926513</v>
@@ -3121,16 +2691,17 @@
       <c r="T18" s="21">
         <v>100</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U18" s="40"/>
+    </row>
+    <row r="19" spans="1:21" ht="36.75" customHeight="1">
       <c r="A19" s="41">
         <v>2025</v>
       </c>
       <c r="B19" s="46" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D19" s="36" t="s">
         <v>22</v>
@@ -3139,7 +2710,7 @@
         <v>2025003050003</v>
       </c>
       <c r="F19" s="36" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="G19" s="2">
         <v>5581655075</v>
@@ -3151,13 +2722,13 @@
         <v>24</v>
       </c>
       <c r="J19" s="57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K19" s="23">
         <v>45768</v>
       </c>
-      <c r="L19" s="65" t="s">
-        <v>89</v>
+      <c r="L19" s="63" t="s">
+        <v>73</v>
       </c>
       <c r="M19" s="22">
         <v>97</v>
@@ -3165,32 +2736,33 @@
       <c r="N19" s="22">
         <v>61</v>
       </c>
-      <c r="O19" s="60" t="s">
-        <v>90</v>
-      </c>
-      <c r="P19" s="60" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q19" s="60" t="s">
-        <v>90</v>
-      </c>
-      <c r="R19" s="60" t="s">
-        <v>91</v>
+      <c r="O19" s="60">
+        <v>97.04</v>
+      </c>
+      <c r="P19" s="60">
+        <v>60.54</v>
+      </c>
+      <c r="Q19" s="60">
+        <v>97.04</v>
+      </c>
+      <c r="R19" s="60">
+        <v>60.54</v>
       </c>
       <c r="S19" s="57">
         <v>77</v>
       </c>
       <c r="T19" s="22"/>
-    </row>
-    <row r="20" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U19" s="40"/>
+    </row>
+    <row r="20" spans="1:21" ht="36.75" customHeight="1">
       <c r="A20" s="41">
         <v>2025</v>
       </c>
       <c r="B20" s="46" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D20" s="36" t="s">
         <v>22</v>
@@ -3199,7 +2771,7 @@
         <v>2025003050008</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="G20" s="2">
         <v>2661301361.5999999</v>
@@ -3216,8 +2788,8 @@
       <c r="K20" s="43">
         <v>45818</v>
       </c>
-      <c r="L20" s="65" t="s">
-        <v>94</v>
+      <c r="L20" s="63" t="s">
+        <v>76</v>
       </c>
       <c r="M20" s="44">
         <v>100</v>
@@ -3238,30 +2810,31 @@
         <v>100</v>
       </c>
       <c r="S20" s="57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T20" s="44">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U20" s="40"/>
+    </row>
+    <row r="21" spans="1:21" ht="36.75" customHeight="1">
       <c r="A21" s="41">
         <v>2025</v>
       </c>
       <c r="B21" s="46" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D21" s="36" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="E21" s="37">
         <v>2025003050002</v>
       </c>
       <c r="F21" s="36" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="G21" s="2">
         <v>24272420632</v>
@@ -3270,16 +2843,16 @@
         <v>24272420632</v>
       </c>
       <c r="I21" s="21" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="J21" s="57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K21" s="23">
         <v>45805</v>
       </c>
-      <c r="L21" s="65" t="s">
-        <v>98</v>
+      <c r="L21" s="63" t="s">
+        <v>80</v>
       </c>
       <c r="M21" s="21">
         <v>7.59</v>
@@ -3287,41 +2860,42 @@
       <c r="N21" s="21">
         <v>3</v>
       </c>
-      <c r="O21" s="60" t="s">
-        <v>99</v>
-      </c>
-      <c r="P21" s="60" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q21" s="60" t="s">
-        <v>101</v>
-      </c>
-      <c r="R21" s="60" t="s">
-        <v>101</v>
+      <c r="O21" s="60">
+        <v>13.08</v>
+      </c>
+      <c r="P21" s="60">
+        <v>7.59</v>
+      </c>
+      <c r="Q21" s="60">
+        <v>21.74</v>
+      </c>
+      <c r="R21" s="60">
+        <v>21.74</v>
       </c>
       <c r="S21" s="57">
         <v>100</v>
       </c>
       <c r="T21" s="22"/>
-    </row>
-    <row r="22" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U21" s="40"/>
+    </row>
+    <row r="22" spans="1:21" ht="36.75" customHeight="1">
       <c r="A22" s="41">
         <v>2025</v>
       </c>
       <c r="B22" s="46" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="E22" s="47">
         <v>2025003050005</v>
       </c>
       <c r="F22" s="36" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="G22" s="2">
         <v>13746524997</v>
@@ -3333,13 +2907,13 @@
         <v>24</v>
       </c>
       <c r="J22" s="57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K22" s="23">
         <v>45811</v>
       </c>
-      <c r="L22" s="65" t="s">
-        <v>105</v>
+      <c r="L22" s="63" t="s">
+        <v>84</v>
       </c>
       <c r="M22" s="22">
         <v>75.34</v>
@@ -3347,34 +2921,33 @@
       <c r="N22" s="22">
         <v>66.150000000000006</v>
       </c>
-      <c r="O22" s="60" t="s">
-        <v>106</v>
-      </c>
-      <c r="P22" s="60" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q22" s="60" t="s">
-        <v>108</v>
-      </c>
-      <c r="R22" s="60" t="s">
-        <v>109</v>
+      <c r="O22" s="60">
+        <v>80.459999999999994</v>
+      </c>
+      <c r="P22" s="60">
+        <v>84.53</v>
+      </c>
+      <c r="Q22" s="60">
+        <v>86.13</v>
+      </c>
+      <c r="R22" s="60">
+        <v>88.5</v>
       </c>
       <c r="S22" s="57">
         <v>90</v>
       </c>
-      <c r="T22" s="44" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="36.75" customHeight="1">
+      <c r="T22" s="44"/>
+      <c r="U22" s="40"/>
+    </row>
+    <row r="23" spans="1:21" ht="36.75" customHeight="1">
       <c r="A23" s="41">
         <v>2025</v>
       </c>
       <c r="B23" s="46" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="C23" s="41" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="D23" s="36" t="s">
         <v>22</v>
@@ -3383,7 +2956,7 @@
         <v>2025003050011</v>
       </c>
       <c r="F23" s="36" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="G23" s="2">
         <v>4237507648</v>
@@ -3395,13 +2968,13 @@
         <v>24</v>
       </c>
       <c r="J23" s="58" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="K23" s="43">
         <v>45813</v>
       </c>
-      <c r="L23" s="65" t="s">
-        <v>115</v>
+      <c r="L23" s="63" t="s">
+        <v>89</v>
       </c>
       <c r="M23" s="44">
         <v>99.95</v>
@@ -3409,14 +2982,14 @@
       <c r="N23" s="44">
         <v>99.92</v>
       </c>
-      <c r="O23" s="60" t="s">
-        <v>116</v>
+      <c r="O23" s="60">
+        <v>99.95</v>
       </c>
       <c r="P23" s="60">
         <v>100</v>
       </c>
-      <c r="Q23" s="60" t="s">
-        <v>116</v>
+      <c r="Q23" s="60">
+        <v>99.95</v>
       </c>
       <c r="R23" s="60">
         <v>100</v>
@@ -3427,16 +3000,17 @@
       <c r="T23" s="44">
         <v>100</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U23" s="40"/>
+    </row>
+    <row r="24" spans="1:21" ht="36.75" customHeight="1">
       <c r="A24" s="41">
         <v>2025</v>
       </c>
       <c r="B24" s="46" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D24" s="36" t="s">
         <v>22</v>
@@ -3445,7 +3019,7 @@
         <v>2025003050014</v>
       </c>
       <c r="F24" s="36" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="G24" s="2">
         <v>1811206529</v>
@@ -3463,7 +3037,7 @@
         <v>45825</v>
       </c>
       <c r="L24" s="63" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="M24" s="44">
         <v>100</v>
@@ -3480,18 +3054,19 @@
       <c r="Q24" s="62"/>
       <c r="R24" s="62"/>
       <c r="S24" s="57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T24" s="44">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U24" s="40"/>
+    </row>
+    <row r="25" spans="1:21" ht="36.75" customHeight="1">
       <c r="A25" s="41">
         <v>2025</v>
       </c>
       <c r="B25" s="46" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="C25" s="41" t="s">
         <v>21</v>
@@ -3503,7 +3078,7 @@
         <v>2025003050012</v>
       </c>
       <c r="F25" s="36" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="G25" s="2">
         <v>4812305821</v>
@@ -3515,13 +3090,13 @@
         <v>24</v>
       </c>
       <c r="J25" s="57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K25" s="23">
         <v>45826</v>
       </c>
-      <c r="L25" s="65" t="s">
-        <v>122</v>
+      <c r="L25" s="63" t="s">
+        <v>95</v>
       </c>
       <c r="M25" s="22">
         <v>0</v>
@@ -3529,32 +3104,33 @@
       <c r="N25" s="22">
         <v>56.54</v>
       </c>
-      <c r="O25" s="60" t="s">
-        <v>123</v>
-      </c>
-      <c r="P25" s="60" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q25" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="R25" s="60" t="s">
-        <v>124</v>
-      </c>
-      <c r="S25" s="57" t="s">
-        <v>126</v>
+      <c r="O25" s="60">
+        <v>64.739999999999995</v>
+      </c>
+      <c r="P25" s="60">
+        <v>22.45</v>
+      </c>
+      <c r="Q25" s="60">
+        <v>87.62</v>
+      </c>
+      <c r="R25" s="60">
+        <v>22.45</v>
+      </c>
+      <c r="S25" s="57">
+        <v>97.2</v>
       </c>
       <c r="T25" s="22"/>
-    </row>
-    <row r="26" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U25" s="40"/>
+    </row>
+    <row r="26" spans="1:21" ht="36.75" customHeight="1">
       <c r="A26" s="41">
         <v>2025</v>
       </c>
       <c r="B26" s="46" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="C26" s="41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D26" s="36" t="s">
         <v>22</v>
@@ -3563,7 +3139,7 @@
         <v>2025003050015</v>
       </c>
       <c r="F26" s="36" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="G26" s="2">
         <v>4294044919</v>
@@ -3581,7 +3157,7 @@
         <v>45824</v>
       </c>
       <c r="L26" s="63" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="M26" s="44">
         <v>100</v>
@@ -3603,16 +3179,17 @@
       <c r="T26" s="21">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U26" s="40"/>
+    </row>
+    <row r="27" spans="1:21" ht="36.75" customHeight="1">
       <c r="A27" s="41">
         <v>2025</v>
       </c>
       <c r="B27" s="46" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="C27" s="41" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="D27" s="36" t="s">
         <v>22</v>
@@ -3621,7 +3198,7 @@
         <v>2025003050013</v>
       </c>
       <c r="F27" s="36" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="G27" s="2">
         <v>1999756329</v>
@@ -3638,8 +3215,8 @@
       <c r="K27" s="23">
         <v>45853</v>
       </c>
-      <c r="L27" s="65" t="s">
-        <v>133</v>
+      <c r="L27" s="63" t="s">
+        <v>102</v>
       </c>
       <c r="M27" s="22">
         <v>100</v>
@@ -3665,13 +3242,14 @@
       <c r="T27" s="44">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U27" s="40"/>
+    </row>
+    <row r="28" spans="1:21" ht="36.75" customHeight="1">
       <c r="A28" s="41">
         <v>2025</v>
       </c>
       <c r="B28" s="46" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="C28" s="41" t="s">
         <v>21</v>
@@ -3683,7 +3261,7 @@
         <v>2025003050022</v>
       </c>
       <c r="F28" s="36" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="G28" s="2">
         <v>4833319756</v>
@@ -3695,13 +3273,13 @@
         <v>24</v>
       </c>
       <c r="J28" s="57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K28" s="23">
         <v>45874</v>
       </c>
-      <c r="L28" s="65" t="s">
-        <v>136</v>
+      <c r="L28" s="63" t="s">
+        <v>105</v>
       </c>
       <c r="M28" s="44">
         <v>45.38</v>
@@ -3709,41 +3287,42 @@
       <c r="N28" s="44">
         <v>36.26</v>
       </c>
-      <c r="O28" s="60" t="s">
-        <v>137</v>
-      </c>
-      <c r="P28" s="60" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q28" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="R28" s="60" t="s">
-        <v>138</v>
-      </c>
-      <c r="S28" s="57" t="s">
-        <v>140</v>
+      <c r="O28" s="60">
+        <v>45.38</v>
+      </c>
+      <c r="P28" s="60">
+        <v>36.26</v>
+      </c>
+      <c r="Q28" s="60">
+        <v>63.55</v>
+      </c>
+      <c r="R28" s="60">
+        <v>36.26</v>
+      </c>
+      <c r="S28" s="57">
+        <v>98.4</v>
       </c>
       <c r="T28" s="44"/>
-    </row>
-    <row r="29" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U28" s="40"/>
+    </row>
+    <row r="29" spans="1:21" ht="36.75" customHeight="1">
       <c r="A29" s="41">
         <v>2025</v>
       </c>
       <c r="B29" s="46" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D29" s="36" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="E29" s="47">
         <v>2025003050017</v>
       </c>
       <c r="F29" s="36" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="G29" s="2">
         <v>5922191430</v>
@@ -3755,13 +3334,13 @@
         <v>24</v>
       </c>
       <c r="J29" s="57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K29" s="23">
         <v>45854</v>
       </c>
-      <c r="L29" s="65" t="s">
-        <v>144</v>
+      <c r="L29" s="63" t="s">
+        <v>109</v>
       </c>
       <c r="M29" s="22">
         <v>97.87</v>
@@ -3769,17 +3348,17 @@
       <c r="N29" s="22">
         <v>90.17</v>
       </c>
-      <c r="O29" s="60" t="s">
-        <v>145</v>
-      </c>
-      <c r="P29" s="60" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q29" s="60" t="s">
-        <v>145</v>
-      </c>
-      <c r="R29" s="60" t="s">
-        <v>146</v>
+      <c r="O29" s="60">
+        <v>97.87</v>
+      </c>
+      <c r="P29" s="60">
+        <v>90.17</v>
+      </c>
+      <c r="Q29" s="60">
+        <v>97.87</v>
+      </c>
+      <c r="R29" s="60">
+        <v>90.17</v>
       </c>
       <c r="S29" s="57">
         <v>77</v>
@@ -3787,13 +3366,14 @@
       <c r="T29" s="44">
         <v>100</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U29" s="40"/>
+    </row>
+    <row r="30" spans="1:21" ht="36.75" customHeight="1">
       <c r="A30" s="41">
         <v>2025</v>
       </c>
       <c r="B30" s="46" t="s">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="C30" s="41" t="s">
         <v>21</v>
@@ -3805,7 +3385,7 @@
         <v>2025003050020</v>
       </c>
       <c r="F30" s="36" t="s">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="G30" s="2">
         <v>4797586284</v>
@@ -3817,13 +3397,13 @@
         <v>24</v>
       </c>
       <c r="J30" s="57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K30" s="23">
         <v>45874</v>
       </c>
-      <c r="L30" s="65" t="s">
-        <v>149</v>
+      <c r="L30" s="63" t="s">
+        <v>112</v>
       </c>
       <c r="M30" s="44">
         <v>95.44</v>
@@ -3831,32 +3411,33 @@
       <c r="N30" s="44">
         <v>60.59</v>
       </c>
-      <c r="O30" s="60" t="s">
-        <v>150</v>
-      </c>
-      <c r="P30" s="60" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q30" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="R30" s="60" t="s">
-        <v>151</v>
+      <c r="O30" s="60">
+        <v>95.93</v>
+      </c>
+      <c r="P30" s="60">
+        <v>71.73</v>
+      </c>
+      <c r="Q30" s="60">
+        <v>96.3</v>
+      </c>
+      <c r="R30" s="60">
+        <v>71.73</v>
       </c>
       <c r="S30" s="57">
         <v>100</v>
       </c>
       <c r="T30" s="44"/>
-    </row>
-    <row r="31" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U30" s="40"/>
+    </row>
+    <row r="31" spans="1:21" ht="36.75" customHeight="1">
       <c r="A31" s="41">
         <v>2025</v>
       </c>
       <c r="B31" s="46" t="s">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="C31" s="41" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="D31" s="36" t="s">
         <v>22</v>
@@ -3865,7 +3446,7 @@
         <v>2025003050010</v>
       </c>
       <c r="F31" s="36" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="G31" s="2">
         <v>2479887333</v>
@@ -3877,13 +3458,13 @@
         <v>24</v>
       </c>
       <c r="J31" s="57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K31" s="23">
         <v>45874</v>
       </c>
-      <c r="L31" s="65" t="s">
-        <v>89</v>
+      <c r="L31" s="63" t="s">
+        <v>73</v>
       </c>
       <c r="M31" s="21">
         <v>37.270000000000003</v>
@@ -3891,17 +3472,17 @@
       <c r="N31" s="21">
         <v>41.96</v>
       </c>
-      <c r="O31" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="P31" s="60" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q31" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="R31" s="60" t="s">
-        <v>157</v>
+      <c r="O31" s="60">
+        <v>37.270000000000003</v>
+      </c>
+      <c r="P31" s="60">
+        <v>66.47</v>
+      </c>
+      <c r="Q31" s="60">
+        <v>37.270000000000003</v>
+      </c>
+      <c r="R31" s="60">
+        <v>66.47</v>
       </c>
       <c r="S31" s="57">
         <v>100</v>
@@ -3909,13 +3490,14 @@
       <c r="T31" s="44">
         <v>35</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U31" s="40"/>
+    </row>
+    <row r="32" spans="1:21" ht="36.75" customHeight="1">
       <c r="A32" s="41">
         <v>2025</v>
       </c>
       <c r="B32" s="46" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="C32" s="41" t="s">
         <v>21</v>
@@ -3927,7 +3509,7 @@
         <v>2025003050021</v>
       </c>
       <c r="F32" s="36" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="G32" s="2">
         <v>4847192489</v>
@@ -3939,12 +3521,12 @@
         <v>24</v>
       </c>
       <c r="J32" s="57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K32" s="23">
         <v>45909</v>
       </c>
-      <c r="L32" s="66">
+      <c r="L32" s="64">
         <v>46240</v>
       </c>
       <c r="M32" s="44">
@@ -3953,17 +3535,17 @@
       <c r="N32" s="44">
         <v>71</v>
       </c>
-      <c r="O32" s="60" t="s">
-        <v>160</v>
-      </c>
-      <c r="P32" s="60" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q32" s="60" t="s">
-        <v>162</v>
-      </c>
-      <c r="R32" s="60" t="s">
-        <v>163</v>
+      <c r="O32" s="60">
+        <v>85.28</v>
+      </c>
+      <c r="P32" s="60">
+        <v>77.010000000000005</v>
+      </c>
+      <c r="Q32" s="60">
+        <v>85.8</v>
+      </c>
+      <c r="R32" s="60">
+        <v>84.2</v>
       </c>
       <c r="S32" s="57">
         <v>100</v>
@@ -3971,25 +3553,26 @@
       <c r="T32" s="44">
         <v>100</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U32" s="40"/>
+    </row>
+    <row r="33" spans="1:21" ht="36.75" customHeight="1">
       <c r="A33" s="41">
         <v>2025</v>
       </c>
       <c r="B33" s="46" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C33" s="41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="E33" s="47">
         <v>2025003050018</v>
       </c>
       <c r="F33" s="36" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="G33" s="2">
         <v>2786298806</v>
@@ -3998,49 +3581,50 @@
         <v>2786298806</v>
       </c>
       <c r="I33" s="49" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="J33" s="57" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="K33" s="23">
         <v>45903</v>
       </c>
-      <c r="L33" s="65" t="s">
-        <v>166</v>
+      <c r="L33" s="63" t="s">
+        <v>120</v>
       </c>
       <c r="M33" s="60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N33" s="60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O33" s="60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P33" s="60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q33" s="60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R33" s="60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S33" s="57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T33" s="44"/>
-    </row>
-    <row r="34" spans="1:20" s="8" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U33" s="40"/>
+    </row>
+    <row r="34" spans="1:21" s="8" customFormat="1" ht="36.75" customHeight="1">
       <c r="A34" s="41">
         <v>2025</v>
       </c>
       <c r="B34" s="46" t="s">
-        <v>167</v>
+        <v>121</v>
       </c>
       <c r="C34" s="41" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D34" s="36" t="s">
         <v>22</v>
@@ -4049,7 +3633,7 @@
         <v>2025003050023</v>
       </c>
       <c r="F34" s="36" t="s">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="G34" s="2">
         <v>4842926067</v>
@@ -4061,13 +3645,13 @@
         <v>24</v>
       </c>
       <c r="J34" s="57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K34" s="23">
         <v>45944</v>
       </c>
-      <c r="L34" s="65" t="s">
-        <v>169</v>
+      <c r="L34" s="63" t="s">
+        <v>123</v>
       </c>
       <c r="M34" s="44">
         <v>93.11</v>
@@ -4075,29 +3659,30 @@
       <c r="N34" s="44">
         <v>75.33</v>
       </c>
-      <c r="O34" s="60" t="s">
-        <v>170</v>
-      </c>
-      <c r="P34" s="60" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q34" s="60" t="s">
-        <v>172</v>
-      </c>
-      <c r="R34" s="60" t="s">
-        <v>171</v>
-      </c>
-      <c r="S34" s="57" t="s">
-        <v>173</v>
+      <c r="O34" s="60">
+        <v>98.97</v>
+      </c>
+      <c r="P34" s="60">
+        <v>98.25</v>
+      </c>
+      <c r="Q34" s="60">
+        <v>99.98</v>
+      </c>
+      <c r="R34" s="60">
+        <v>98.25</v>
+      </c>
+      <c r="S34" s="57">
+        <v>48.6</v>
       </c>
       <c r="T34" s="44"/>
-    </row>
-    <row r="35" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U34" s="40"/>
+    </row>
+    <row r="35" spans="1:21" ht="36.75" customHeight="1">
       <c r="A35" s="41">
         <v>2025</v>
       </c>
       <c r="B35" s="46" t="s">
-        <v>174</v>
+        <v>124</v>
       </c>
       <c r="C35" s="41" t="s">
         <v>27</v>
@@ -4109,7 +3694,7 @@
         <v>2025003050028</v>
       </c>
       <c r="F35" s="36" t="s">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="G35" s="2">
         <v>4663630855</v>
@@ -4126,8 +3711,8 @@
       <c r="K35" s="23">
         <v>45936</v>
       </c>
-      <c r="L35" s="65" t="s">
-        <v>176</v>
+      <c r="L35" s="63" t="s">
+        <v>126</v>
       </c>
       <c r="M35" s="44">
         <v>78.69</v>
@@ -4138,38 +3723,39 @@
       <c r="O35" s="60">
         <v>95</v>
       </c>
-      <c r="P35" s="60" t="s">
-        <v>177</v>
+      <c r="P35" s="60">
+        <v>83.9</v>
       </c>
       <c r="Q35" s="60">
         <v>100</v>
       </c>
-      <c r="R35" s="60" t="s">
-        <v>177</v>
+      <c r="R35" s="60">
+        <v>83.9</v>
       </c>
       <c r="S35" s="57">
         <v>83.9</v>
       </c>
       <c r="T35" s="44"/>
-    </row>
-    <row r="36" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U35" s="40"/>
+    </row>
+    <row r="36" spans="1:21" ht="36.75" customHeight="1">
       <c r="A36" s="41">
         <v>2025</v>
       </c>
       <c r="B36" s="46" t="s">
-        <v>178</v>
+        <v>127</v>
       </c>
       <c r="C36" s="41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D36" s="36" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="E36" s="47">
         <v>2025003050024</v>
       </c>
       <c r="F36" s="36" t="s">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="G36" s="2">
         <v>14688946853</v>
@@ -4178,16 +3764,16 @@
         <v>14688946853</v>
       </c>
       <c r="I36" s="49" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="J36" s="57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K36" s="23">
         <v>45938</v>
       </c>
-      <c r="L36" s="65" t="s">
-        <v>181</v>
+      <c r="L36" s="63" t="s">
+        <v>130</v>
       </c>
       <c r="M36" s="44">
         <v>0</v>
@@ -4195,8 +3781,8 @@
       <c r="N36" s="44">
         <v>0</v>
       </c>
-      <c r="O36" s="60" t="s">
-        <v>182</v>
+      <c r="O36" s="60">
+        <v>0.68</v>
       </c>
       <c r="P36" s="60">
         <v>0</v>
@@ -4211,25 +3797,26 @@
         <v>0</v>
       </c>
       <c r="T36" s="44"/>
-    </row>
-    <row r="37" spans="1:20" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U36" s="40"/>
+    </row>
+    <row r="37" spans="1:21" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A37" s="41">
         <v>2025</v>
       </c>
       <c r="B37" s="46" t="s">
-        <v>183</v>
+        <v>131</v>
       </c>
       <c r="C37" s="41" t="s">
-        <v>184</v>
+        <v>132</v>
       </c>
       <c r="D37" s="36" t="s">
-        <v>185</v>
+        <v>133</v>
       </c>
       <c r="E37" s="47">
         <v>2025003050025</v>
       </c>
       <c r="F37" s="36" t="s">
-        <v>186</v>
+        <v>134</v>
       </c>
       <c r="G37" s="2">
         <v>5913699663</v>
@@ -4238,16 +3825,16 @@
         <v>5913699663</v>
       </c>
       <c r="I37" s="49" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="J37" s="57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K37" s="23">
         <v>45915</v>
       </c>
-      <c r="L37" s="65" t="s">
-        <v>187</v>
+      <c r="L37" s="63" t="s">
+        <v>135</v>
       </c>
       <c r="M37" s="44">
         <v>82.86</v>
@@ -4255,29 +3842,30 @@
       <c r="N37" s="44">
         <v>62.88</v>
       </c>
-      <c r="O37" s="60" t="s">
-        <v>188</v>
-      </c>
-      <c r="P37" s="62" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q37" s="62" t="s">
-        <v>190</v>
-      </c>
-      <c r="R37" s="62" t="s">
-        <v>191</v>
+      <c r="O37" s="60">
+        <v>82.86</v>
+      </c>
+      <c r="P37" s="62">
+        <v>62.88</v>
+      </c>
+      <c r="Q37" s="62">
+        <v>96.46</v>
+      </c>
+      <c r="R37" s="62">
+        <v>83.3</v>
       </c>
       <c r="S37" s="57">
         <v>100</v>
       </c>
       <c r="T37" s="44"/>
-    </row>
-    <row r="38" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U37" s="40"/>
+    </row>
+    <row r="38" spans="1:21" ht="36.75" customHeight="1">
       <c r="A38" s="41">
         <v>2025</v>
       </c>
       <c r="B38" s="46" t="s">
-        <v>192</v>
+        <v>136</v>
       </c>
       <c r="C38" s="41" t="s">
         <v>21</v>
@@ -4289,7 +3877,7 @@
         <v>2025003050035</v>
       </c>
       <c r="F38" s="36" t="s">
-        <v>193</v>
+        <v>137</v>
       </c>
       <c r="G38" s="2">
         <v>5248430707.1999998</v>
@@ -4301,13 +3889,13 @@
         <v>24</v>
       </c>
       <c r="J38" s="57" t="s">
-        <v>194</v>
+        <v>138</v>
       </c>
       <c r="K38" s="23">
         <v>45967</v>
       </c>
-      <c r="L38" s="65" t="s">
-        <v>71</v>
+      <c r="L38" s="63" t="s">
+        <v>61</v>
       </c>
       <c r="M38" s="44">
         <v>0</v>
@@ -4331,15 +3919,16 @@
         <v>0</v>
       </c>
       <c r="T38" s="44" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" ht="36.75" customHeight="1">
+        <v>139</v>
+      </c>
+      <c r="U38" s="40"/>
+    </row>
+    <row r="39" spans="1:21" ht="36.75" customHeight="1">
       <c r="A39" s="41">
         <v>2025</v>
       </c>
       <c r="B39" s="46" t="s">
-        <v>196</v>
+        <v>140</v>
       </c>
       <c r="C39" s="41" t="s">
         <v>21</v>
@@ -4351,7 +3940,7 @@
         <v>2025003050026</v>
       </c>
       <c r="F39" s="36" t="s">
-        <v>197</v>
+        <v>141</v>
       </c>
       <c r="G39" s="2">
         <v>3715229969</v>
@@ -4363,13 +3952,13 @@
         <v>24</v>
       </c>
       <c r="J39" s="57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K39" s="23">
         <v>45968</v>
       </c>
-      <c r="L39" s="65" t="s">
-        <v>198</v>
+      <c r="L39" s="63" t="s">
+        <v>142</v>
       </c>
       <c r="M39" s="44">
         <v>69.27</v>
@@ -4377,41 +3966,42 @@
       <c r="N39" s="44">
         <v>40.130000000000003</v>
       </c>
-      <c r="O39" s="60" t="s">
-        <v>199</v>
-      </c>
-      <c r="P39" s="62" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q39" s="62" t="s">
-        <v>201</v>
-      </c>
-      <c r="R39" s="62" t="s">
-        <v>202</v>
+      <c r="O39" s="60">
+        <v>69.27</v>
+      </c>
+      <c r="P39" s="62">
+        <v>40.130000000000003</v>
+      </c>
+      <c r="Q39" s="62">
+        <v>77.58</v>
+      </c>
+      <c r="R39" s="62">
+        <v>41.73</v>
       </c>
       <c r="S39" s="57">
         <v>100</v>
       </c>
       <c r="T39" s="44"/>
-    </row>
-    <row r="40" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U39" s="40"/>
+    </row>
+    <row r="40" spans="1:21" ht="36.75" customHeight="1">
       <c r="A40" s="41">
         <v>2025</v>
       </c>
       <c r="B40" s="46" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="C40" s="41" t="s">
         <v>21</v>
       </c>
       <c r="D40" s="36" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="E40" s="47">
         <v>2025003050034</v>
       </c>
       <c r="F40" s="36" t="s">
-        <v>203</v>
+        <v>143</v>
       </c>
       <c r="G40" s="2">
         <v>4782821867</v>
@@ -4423,13 +4013,13 @@
         <v>24</v>
       </c>
       <c r="J40" s="57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K40" s="23">
         <v>45973</v>
       </c>
-      <c r="L40" s="65" t="s">
-        <v>204</v>
+      <c r="L40" s="63" t="s">
+        <v>144</v>
       </c>
       <c r="M40" s="44">
         <v>60.71</v>
@@ -4437,14 +4027,14 @@
       <c r="N40" s="44">
         <v>84.45</v>
       </c>
-      <c r="O40" s="60" t="s">
-        <v>205</v>
-      </c>
-      <c r="P40" s="62" t="s">
-        <v>206</v>
-      </c>
-      <c r="Q40" s="62" t="s">
-        <v>207</v>
+      <c r="O40" s="60">
+        <v>60.71</v>
+      </c>
+      <c r="P40" s="62">
+        <v>84.45</v>
+      </c>
+      <c r="Q40" s="62">
+        <v>99.55</v>
       </c>
       <c r="R40" s="62">
         <v>100</v>
@@ -4453,13 +4043,14 @@
         <v>52</v>
       </c>
       <c r="T40" s="44"/>
-    </row>
-    <row r="41" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U40" s="40"/>
+    </row>
+    <row r="41" spans="1:21" ht="36.75" customHeight="1">
       <c r="A41" s="41">
         <v>2025</v>
       </c>
       <c r="B41" s="46" t="s">
-        <v>208</v>
+        <v>145</v>
       </c>
       <c r="C41" s="41" t="s">
         <v>27</v>
@@ -4471,7 +4062,7 @@
         <v>2025003050031</v>
       </c>
       <c r="F41" s="36" t="s">
-        <v>209</v>
+        <v>146</v>
       </c>
       <c r="G41" s="2">
         <v>2267187134</v>
@@ -4483,13 +4074,13 @@
         <v>24</v>
       </c>
       <c r="J41" s="59" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="K41" s="43">
         <v>45971</v>
       </c>
-      <c r="L41" s="65" t="s">
-        <v>210</v>
+      <c r="L41" s="63" t="s">
+        <v>147</v>
       </c>
       <c r="M41" s="44">
         <v>100</v>
@@ -4515,16 +4106,17 @@
       <c r="T41" s="44">
         <v>100</v>
       </c>
-    </row>
-    <row r="42" spans="1:20" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U41" s="40"/>
+    </row>
+    <row r="42" spans="1:21" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A42" s="41">
         <v>2025</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>211</v>
+        <v>148</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D42" s="36" t="s">
         <v>22</v>
@@ -4533,7 +4125,7 @@
         <v>2025003050032</v>
       </c>
       <c r="F42" s="36" t="s">
-        <v>212</v>
+        <v>149</v>
       </c>
       <c r="G42" s="2">
         <v>2068919343</v>
@@ -4545,13 +4137,13 @@
         <v>24</v>
       </c>
       <c r="J42" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K42" s="23">
         <v>46015</v>
       </c>
-      <c r="L42" s="65" t="s">
-        <v>213</v>
+      <c r="L42" s="63" t="s">
+        <v>150</v>
       </c>
       <c r="M42" s="44">
         <v>45.41</v>
@@ -4559,32 +4151,33 @@
       <c r="N42" s="44">
         <v>45</v>
       </c>
-      <c r="O42" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="P42" s="62" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q42" s="62" t="s">
-        <v>216</v>
-      </c>
-      <c r="R42" s="62" t="s">
-        <v>215</v>
+      <c r="O42" s="60">
+        <v>56.27</v>
+      </c>
+      <c r="P42" s="62">
+        <v>68.52</v>
+      </c>
+      <c r="Q42" s="62">
+        <v>77.989999999999995</v>
+      </c>
+      <c r="R42" s="62">
+        <v>68.52</v>
       </c>
       <c r="S42" s="57">
         <v>100</v>
       </c>
       <c r="T42" s="44"/>
-    </row>
-    <row r="43" spans="1:20" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U42" s="40"/>
+    </row>
+    <row r="43" spans="1:21" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A43" s="41">
         <v>2025</v>
       </c>
       <c r="B43" s="46" t="s">
-        <v>217</v>
+        <v>151</v>
       </c>
       <c r="C43" s="41" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D43" s="36" t="s">
         <v>22</v>
@@ -4593,7 +4186,7 @@
         <v>2025003050038</v>
       </c>
       <c r="F43" s="36" t="s">
-        <v>218</v>
+        <v>152</v>
       </c>
       <c r="G43" s="2">
         <v>2138705796</v>
@@ -4605,13 +4198,13 @@
         <v>24</v>
       </c>
       <c r="J43" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K43" s="23">
         <v>46001</v>
       </c>
-      <c r="L43" s="65" t="s">
-        <v>219</v>
+      <c r="L43" s="63" t="s">
+        <v>153</v>
       </c>
       <c r="M43" s="44">
         <v>23.44</v>
@@ -4619,17 +4212,17 @@
       <c r="N43" s="44">
         <v>45.52</v>
       </c>
-      <c r="O43" s="60" t="s">
-        <v>220</v>
-      </c>
-      <c r="P43" s="62" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q43" s="62" t="s">
-        <v>220</v>
-      </c>
-      <c r="R43" s="62" t="s">
-        <v>221</v>
+      <c r="O43" s="60">
+        <v>23.44</v>
+      </c>
+      <c r="P43" s="62">
+        <v>45.52</v>
+      </c>
+      <c r="Q43" s="62">
+        <v>23.44</v>
+      </c>
+      <c r="R43" s="62">
+        <v>45.52</v>
       </c>
       <c r="S43" s="57">
         <v>100</v>
@@ -4637,13 +4230,14 @@
       <c r="T43" s="44">
         <v>14</v>
       </c>
-    </row>
-    <row r="44" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U43" s="40"/>
+    </row>
+    <row r="44" spans="1:21" ht="36.75" customHeight="1">
       <c r="A44" s="41">
         <v>2025</v>
       </c>
       <c r="B44" s="46" t="s">
-        <v>222</v>
+        <v>154</v>
       </c>
       <c r="C44" s="41" t="s">
         <v>21</v>
@@ -4655,7 +4249,7 @@
         <v>2025003050046</v>
       </c>
       <c r="F44" s="36" t="s">
-        <v>223</v>
+        <v>155</v>
       </c>
       <c r="G44" s="2">
         <v>4319392762</v>
@@ -4667,13 +4261,13 @@
         <v>24</v>
       </c>
       <c r="J44" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K44" s="23">
         <v>46014</v>
       </c>
-      <c r="L44" s="65" t="s">
-        <v>224</v>
+      <c r="L44" s="63" t="s">
+        <v>156</v>
       </c>
       <c r="M44" s="44">
         <v>26.14</v>
@@ -4681,32 +4275,33 @@
       <c r="N44" s="44">
         <v>27.27</v>
       </c>
-      <c r="O44" s="60" t="s">
-        <v>225</v>
-      </c>
-      <c r="P44" s="62" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q44" s="62" t="s">
-        <v>227</v>
-      </c>
-      <c r="R44" s="62" t="s">
-        <v>225</v>
-      </c>
-      <c r="S44" s="57" t="s">
-        <v>228</v>
+      <c r="O44" s="60">
+        <v>46.12</v>
+      </c>
+      <c r="P44" s="62">
+        <v>41.92</v>
+      </c>
+      <c r="Q44" s="62">
+        <v>49.33</v>
+      </c>
+      <c r="R44" s="62">
+        <v>46.12</v>
+      </c>
+      <c r="S44" s="57">
+        <v>90.4</v>
       </c>
       <c r="T44" s="49"/>
-    </row>
-    <row r="45" spans="1:20" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U44" s="40"/>
+    </row>
+    <row r="45" spans="1:21" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A45" s="41">
         <v>2025</v>
       </c>
       <c r="B45" s="46" t="s">
-        <v>229</v>
+        <v>157</v>
       </c>
       <c r="C45" s="41" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D45" s="36" t="s">
         <v>22</v>
@@ -4715,7 +4310,7 @@
         <v>2025003050043</v>
       </c>
       <c r="F45" s="36" t="s">
-        <v>230</v>
+        <v>158</v>
       </c>
       <c r="G45" s="2">
         <v>2387040561</v>
@@ -4727,13 +4322,13 @@
         <v>24</v>
       </c>
       <c r="J45" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K45" s="23">
         <v>46011</v>
       </c>
-      <c r="L45" s="65" t="s">
-        <v>122</v>
+      <c r="L45" s="63" t="s">
+        <v>95</v>
       </c>
       <c r="M45" s="44">
         <v>31.59</v>
@@ -4741,41 +4336,42 @@
       <c r="N45" s="44">
         <v>45.88</v>
       </c>
-      <c r="O45" s="60" t="s">
-        <v>231</v>
-      </c>
-      <c r="P45" s="62" t="s">
-        <v>232</v>
-      </c>
-      <c r="Q45" s="62" t="s">
-        <v>233</v>
-      </c>
-      <c r="R45" s="62" t="s">
-        <v>234</v>
+      <c r="O45" s="60">
+        <v>45.49</v>
+      </c>
+      <c r="P45" s="62">
+        <v>45.88</v>
+      </c>
+      <c r="Q45" s="62">
+        <v>58.4</v>
+      </c>
+      <c r="R45" s="62">
+        <v>73.709999999999994</v>
       </c>
       <c r="S45" s="57">
         <v>60</v>
       </c>
       <c r="T45" s="44"/>
-    </row>
-    <row r="46" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U45" s="40"/>
+    </row>
+    <row r="46" spans="1:21" ht="36.75" customHeight="1">
       <c r="A46" s="41">
         <v>2025</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D46" s="36" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="E46" s="47">
         <v>2025003050027</v>
       </c>
       <c r="F46" s="36" t="s">
-        <v>235</v>
+        <v>159</v>
       </c>
       <c r="G46" s="2">
         <v>27387320782</v>
@@ -4784,16 +4380,16 @@
         <v>27387320782</v>
       </c>
       <c r="I46" s="49" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="J46" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K46" s="23">
         <v>46013</v>
       </c>
-      <c r="L46" s="65" t="s">
-        <v>236</v>
+      <c r="L46" s="63" t="s">
+        <v>160</v>
       </c>
       <c r="M46" s="44">
         <v>0</v>
@@ -4801,32 +4397,33 @@
       <c r="N46" s="44">
         <v>0</v>
       </c>
-      <c r="O46" s="60" t="s">
-        <v>237</v>
+      <c r="O46" s="60">
+        <v>1.02</v>
       </c>
       <c r="P46" s="62">
         <v>0</v>
       </c>
-      <c r="Q46" s="62" t="s">
-        <v>238</v>
-      </c>
-      <c r="R46" s="62" t="s">
-        <v>239</v>
-      </c>
-      <c r="S46" s="57" t="s">
-        <v>240</v>
+      <c r="Q46" s="62">
+        <v>1.92</v>
+      </c>
+      <c r="R46" s="62">
+        <v>0.5</v>
+      </c>
+      <c r="S46" s="57">
+        <v>80.400000000000006</v>
       </c>
       <c r="T46" s="44"/>
-    </row>
-    <row r="47" spans="1:20" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U46" s="40"/>
+    </row>
+    <row r="47" spans="1:21" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A47" s="41">
         <v>2025</v>
       </c>
       <c r="B47" s="46" t="s">
-        <v>241</v>
+        <v>161</v>
       </c>
       <c r="C47" s="41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D47" s="36" t="s">
         <v>22</v>
@@ -4835,7 +4432,7 @@
         <v>2025003050053</v>
       </c>
       <c r="F47" s="36" t="s">
-        <v>242</v>
+        <v>162</v>
       </c>
       <c r="G47" s="2">
         <v>2149409352</v>
@@ -4852,7 +4449,7 @@
       <c r="K47" s="23">
         <v>46014</v>
       </c>
-      <c r="L47" s="66">
+      <c r="L47" s="64">
         <v>46060</v>
       </c>
       <c r="M47" s="44">
@@ -4861,17 +4458,17 @@
       <c r="N47" s="44">
         <v>94.43</v>
       </c>
-      <c r="O47" s="60" t="s">
-        <v>243</v>
-      </c>
-      <c r="P47" s="62" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q47" s="62" t="s">
-        <v>243</v>
-      </c>
-      <c r="R47" s="62" t="s">
-        <v>245</v>
+      <c r="O47" s="60">
+        <v>97.22</v>
+      </c>
+      <c r="P47" s="62">
+        <v>96.27</v>
+      </c>
+      <c r="Q47" s="62">
+        <v>97.22</v>
+      </c>
+      <c r="R47" s="62">
+        <v>99.85</v>
       </c>
       <c r="S47" s="57">
         <v>100</v>
@@ -4879,16 +4476,17 @@
       <c r="T47" s="44">
         <v>100</v>
       </c>
-    </row>
-    <row r="48" spans="1:20" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U47" s="40"/>
+    </row>
+    <row r="48" spans="1:21" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A48" s="41">
         <v>2025</v>
       </c>
       <c r="B48" s="46" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C48" s="41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D48" s="36" t="s">
         <v>22</v>
@@ -4897,7 +4495,7 @@
         <v>2025003050051</v>
       </c>
       <c r="F48" s="36" t="s">
-        <v>246</v>
+        <v>163</v>
       </c>
       <c r="G48" s="2">
         <v>2264647460</v>
@@ -4914,7 +4512,7 @@
       <c r="K48" s="23">
         <v>46014</v>
       </c>
-      <c r="L48" s="66">
+      <c r="L48" s="64">
         <v>46332</v>
       </c>
       <c r="M48" s="44">
@@ -4926,14 +4524,14 @@
       <c r="O48" s="60">
         <v>100</v>
       </c>
-      <c r="P48" s="62" t="s">
-        <v>247</v>
+      <c r="P48" s="62">
+        <v>81.209999999999994</v>
       </c>
       <c r="Q48" s="60">
         <v>100</v>
       </c>
-      <c r="R48" s="62" t="s">
-        <v>248</v>
+      <c r="R48" s="62">
+        <v>81.69</v>
       </c>
       <c r="S48" s="57">
         <v>100</v>
@@ -4941,13 +4539,14 @@
       <c r="T48" s="44">
         <v>100</v>
       </c>
-    </row>
-    <row r="49" spans="1:28" s="9" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U48" s="40"/>
+    </row>
+    <row r="49" spans="1:29" s="9" customFormat="1" ht="36.75" customHeight="1">
       <c r="A49" s="45">
         <v>2025</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>249</v>
+        <v>164</v>
       </c>
       <c r="C49" s="45" t="s">
         <v>21</v>
@@ -4959,7 +4558,7 @@
         <v>2025003050056</v>
       </c>
       <c r="F49" s="36" t="s">
-        <v>250</v>
+        <v>165</v>
       </c>
       <c r="G49" s="3">
         <v>4431237626</v>
@@ -4971,13 +4570,13 @@
         <v>24</v>
       </c>
       <c r="J49" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K49" s="23">
         <v>46014</v>
       </c>
-      <c r="L49" s="65" t="s">
-        <v>251</v>
+      <c r="L49" s="63" t="s">
+        <v>166</v>
       </c>
       <c r="M49" s="44">
         <v>28.94</v>
@@ -4985,40 +4584,41 @@
       <c r="N49" s="44">
         <v>27.38</v>
       </c>
-      <c r="O49" s="60" t="s">
-        <v>252</v>
-      </c>
-      <c r="P49" s="62" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q49" s="62" t="s">
-        <v>253</v>
-      </c>
-      <c r="R49" s="62" t="s">
-        <v>252</v>
-      </c>
-      <c r="S49" s="57" t="s">
-        <v>126</v>
+      <c r="O49" s="60">
+        <v>46.1</v>
+      </c>
+      <c r="P49" s="62">
+        <v>46.1</v>
+      </c>
+      <c r="Q49" s="62">
+        <v>49.3</v>
+      </c>
+      <c r="R49" s="62">
+        <v>46.1</v>
+      </c>
+      <c r="S49" s="57">
+        <v>97.2</v>
       </c>
       <c r="T49" s="44"/>
-      <c r="U49" s="67"/>
-      <c r="V49" s="67"/>
-      <c r="W49" s="67"/>
-      <c r="X49" s="67"/>
-      <c r="Y49" s="67"/>
-      <c r="Z49" s="67"/>
-      <c r="AA49" s="67"/>
-      <c r="AB49" s="67"/>
-    </row>
-    <row r="50" spans="1:28" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U49" s="40"/>
+      <c r="V49" s="65"/>
+      <c r="W49" s="65"/>
+      <c r="X49" s="65"/>
+      <c r="Y49" s="65"/>
+      <c r="Z49" s="65"/>
+      <c r="AA49" s="65"/>
+      <c r="AB49" s="65"/>
+      <c r="AC49" s="65"/>
+    </row>
+    <row r="50" spans="1:29" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A50" s="41">
         <v>2025</v>
       </c>
       <c r="B50" s="46" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C50" s="41" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D50" s="36" t="s">
         <v>22</v>
@@ -5027,7 +4627,7 @@
         <v>2025003050044</v>
       </c>
       <c r="F50" s="36" t="s">
-        <v>254</v>
+        <v>167</v>
       </c>
       <c r="G50" s="2">
         <v>2808881690</v>
@@ -5044,8 +4644,8 @@
       <c r="K50" s="23">
         <v>46014</v>
       </c>
-      <c r="L50" s="65" t="s">
-        <v>255</v>
+      <c r="L50" s="63" t="s">
+        <v>168</v>
       </c>
       <c r="M50" s="44">
         <v>100</v>
@@ -5056,14 +4656,14 @@
       <c r="O50" s="60">
         <v>100</v>
       </c>
-      <c r="P50" s="62" t="s">
-        <v>256</v>
+      <c r="P50" s="62">
+        <v>91.75</v>
       </c>
       <c r="Q50" s="60">
         <v>100</v>
       </c>
-      <c r="R50" s="62" t="s">
-        <v>256</v>
+      <c r="R50" s="62">
+        <v>91.75</v>
       </c>
       <c r="S50" s="57">
         <v>100</v>
@@ -5079,13 +4679,14 @@
       <c r="Z50" s="40"/>
       <c r="AA50" s="40"/>
       <c r="AB50" s="40"/>
-    </row>
-    <row r="51" spans="1:28" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="AC50" s="40"/>
+    </row>
+    <row r="51" spans="1:29" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A51" s="41">
         <v>2025</v>
       </c>
       <c r="B51" s="46" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C51" s="41" t="s">
         <v>21</v>
@@ -5097,7 +4698,7 @@
         <v>2025003050045</v>
       </c>
       <c r="F51" s="36" t="s">
-        <v>257</v>
+        <v>169</v>
       </c>
       <c r="G51" s="2">
         <v>2357899973</v>
@@ -5109,13 +4710,13 @@
         <v>24</v>
       </c>
       <c r="J51" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K51" s="23">
         <v>46013</v>
       </c>
-      <c r="L51" s="65" t="s">
-        <v>258</v>
+      <c r="L51" s="63" t="s">
+        <v>170</v>
       </c>
       <c r="M51" s="44">
         <v>5.64</v>
@@ -5123,17 +4724,17 @@
       <c r="N51" s="44">
         <v>0</v>
       </c>
-      <c r="O51" s="60" t="s">
-        <v>259</v>
-      </c>
-      <c r="P51" s="62" t="s">
-        <v>260</v>
-      </c>
-      <c r="Q51" s="62" t="s">
-        <v>124</v>
-      </c>
-      <c r="R51" s="62" t="s">
-        <v>260</v>
+      <c r="O51" s="60">
+        <v>19.13</v>
+      </c>
+      <c r="P51" s="62">
+        <v>27.56</v>
+      </c>
+      <c r="Q51" s="62">
+        <v>22.45</v>
+      </c>
+      <c r="R51" s="62">
+        <v>27.56</v>
       </c>
       <c r="S51" s="57">
         <v>100</v>
@@ -5147,16 +4748,17 @@
       <c r="Z51" s="40"/>
       <c r="AA51" s="40"/>
       <c r="AB51" s="40"/>
-    </row>
-    <row r="52" spans="1:28" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="AC51" s="40"/>
+    </row>
+    <row r="52" spans="1:29" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A52" s="41">
         <v>2025</v>
       </c>
       <c r="B52" s="46" t="s">
-        <v>261</v>
+        <v>171</v>
       </c>
       <c r="C52" s="41" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D52" s="36" t="s">
         <v>22</v>
@@ -5165,7 +4767,7 @@
         <v>2025003050050</v>
       </c>
       <c r="F52" s="36" t="s">
-        <v>262</v>
+        <v>172</v>
       </c>
       <c r="G52" s="2">
         <v>1879328482</v>
@@ -5182,7 +4784,7 @@
       <c r="K52" s="23">
         <v>46014</v>
       </c>
-      <c r="L52" s="66">
+      <c r="L52" s="64">
         <v>46272</v>
       </c>
       <c r="M52" s="44">
@@ -5194,14 +4796,14 @@
       <c r="O52" s="60">
         <v>100</v>
       </c>
-      <c r="P52" s="62" t="s">
-        <v>263</v>
+      <c r="P52" s="62">
+        <v>97.51</v>
       </c>
       <c r="Q52" s="60">
         <v>100</v>
       </c>
-      <c r="R52" s="62" t="s">
-        <v>264</v>
+      <c r="R52" s="62">
+        <v>99.24</v>
       </c>
       <c r="S52" s="57">
         <v>100</v>
@@ -5217,16 +4819,17 @@
       <c r="Z52" s="40"/>
       <c r="AA52" s="40"/>
       <c r="AB52" s="40"/>
-    </row>
-    <row r="53" spans="1:28" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="AC52" s="40"/>
+    </row>
+    <row r="53" spans="1:29" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A53" s="41">
         <v>2025</v>
       </c>
       <c r="B53" s="46" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="C53" s="41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D53" s="36" t="s">
         <v>22</v>
@@ -5235,7 +4838,7 @@
         <v>2025003050049</v>
       </c>
       <c r="F53" s="36" t="s">
-        <v>266</v>
+        <v>174</v>
       </c>
       <c r="G53" s="2">
         <v>2156349509</v>
@@ -5252,7 +4855,7 @@
       <c r="K53" s="23">
         <v>46014</v>
       </c>
-      <c r="L53" s="66">
+      <c r="L53" s="64">
         <v>46333</v>
       </c>
       <c r="M53" s="49">
@@ -5264,8 +4867,8 @@
       <c r="O53" s="60">
         <v>100</v>
       </c>
-      <c r="P53" s="62" t="s">
-        <v>267</v>
+      <c r="P53" s="62">
+        <v>99.49</v>
       </c>
       <c r="Q53" s="62">
         <v>100</v>
@@ -5287,25 +4890,26 @@
       <c r="Z53" s="40"/>
       <c r="AA53" s="40"/>
       <c r="AB53" s="40"/>
-    </row>
-    <row r="54" spans="1:28" ht="36.75" customHeight="1">
+      <c r="AC53" s="40"/>
+    </row>
+    <row r="54" spans="1:29" ht="36.75" customHeight="1">
       <c r="A54" s="41">
         <v>2026</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>268</v>
+        <v>175</v>
       </c>
       <c r="C54" s="45" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D54" s="36" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="E54" s="47">
         <v>2025003050036</v>
       </c>
       <c r="F54" s="36" t="s">
-        <v>269</v>
+        <v>176</v>
       </c>
       <c r="G54" s="2">
         <v>14202451801</v>
@@ -5317,13 +4921,13 @@
         <v>24</v>
       </c>
       <c r="J54" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K54" s="23">
         <v>46031</v>
       </c>
-      <c r="L54" s="65" t="s">
-        <v>270</v>
+      <c r="L54" s="63" t="s">
+        <v>177</v>
       </c>
       <c r="M54" s="44">
         <v>13.9</v>
@@ -5331,20 +4935,20 @@
       <c r="N54" s="44">
         <v>35.69</v>
       </c>
-      <c r="O54" s="60" t="s">
-        <v>271</v>
-      </c>
-      <c r="P54" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q54" s="62" t="s">
-        <v>273</v>
-      </c>
-      <c r="R54" s="62" t="s">
-        <v>274</v>
-      </c>
-      <c r="S54" s="57" t="s">
-        <v>275</v>
+      <c r="O54" s="60">
+        <v>31.83</v>
+      </c>
+      <c r="P54" s="62">
+        <v>35.69</v>
+      </c>
+      <c r="Q54" s="62">
+        <v>60.19</v>
+      </c>
+      <c r="R54" s="62">
+        <v>38.06</v>
+      </c>
+      <c r="S54" s="57">
+        <v>79.599999999999994</v>
       </c>
       <c r="T54" s="44"/>
       <c r="U54" s="40"/>
@@ -5355,25 +4959,26 @@
       <c r="Z54" s="40"/>
       <c r="AA54" s="40"/>
       <c r="AB54" s="40"/>
-    </row>
-    <row r="55" spans="1:28" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="AC54" s="40"/>
+    </row>
+    <row r="55" spans="1:29" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A55" s="41">
         <v>2026</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>276</v>
+        <v>178</v>
       </c>
       <c r="C55" s="45" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="D55" s="36" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="E55" s="47">
         <v>2025003050040</v>
       </c>
       <c r="F55" s="36" t="s">
-        <v>277</v>
+        <v>179</v>
       </c>
       <c r="G55" s="2">
         <v>2540216819</v>
@@ -5385,25 +4990,25 @@
         <v>24</v>
       </c>
       <c r="J55" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K55" s="23">
         <v>46031</v>
       </c>
-      <c r="L55" s="66">
+      <c r="L55" s="64">
         <v>46276</v>
       </c>
       <c r="M55" s="51" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="N55" s="51" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O55" s="60">
         <v>19</v>
       </c>
-      <c r="P55" s="62" t="s">
-        <v>278</v>
+      <c r="P55" s="62">
+        <v>30.46</v>
       </c>
       <c r="Q55" s="60">
         <v>19</v>
@@ -5423,25 +5028,26 @@
       <c r="Z55" s="40"/>
       <c r="AA55" s="40"/>
       <c r="AB55" s="40"/>
-    </row>
-    <row r="56" spans="1:28" ht="36.75" customHeight="1">
+      <c r="AC55" s="40"/>
+    </row>
+    <row r="56" spans="1:29" ht="36.75" customHeight="1">
       <c r="A56" s="45">
         <v>2026</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>279</v>
+        <v>180</v>
       </c>
       <c r="C56" s="45" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="D56" s="36" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="E56" s="47">
         <v>2025003050039</v>
       </c>
       <c r="F56" s="36" t="s">
-        <v>280</v>
+        <v>181</v>
       </c>
       <c r="G56" s="48">
         <v>9381110055</v>
@@ -5453,34 +5059,34 @@
         <v>24</v>
       </c>
       <c r="J56" s="60" t="s">
-        <v>165</v>
+        <v>41</v>
       </c>
       <c r="K56" s="23">
         <v>46031</v>
       </c>
-      <c r="L56" s="65" t="s">
-        <v>71</v>
+      <c r="L56" s="66" t="s">
+        <v>182</v>
       </c>
       <c r="M56" s="44" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="N56" s="44" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O56" s="60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P56" s="62" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q56" s="60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R56" s="62">
         <v>35.840000000000003</v>
       </c>
       <c r="S56" s="57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T56" s="44"/>
       <c r="U56" s="40"/>
@@ -5491,25 +5097,26 @@
       <c r="Z56" s="40"/>
       <c r="AA56" s="40"/>
       <c r="AB56" s="40"/>
-    </row>
-    <row r="57" spans="1:28" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="AC56" s="40"/>
+    </row>
+    <row r="57" spans="1:29" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A57" s="45">
         <v>2026</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>281</v>
+        <v>183</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="D57" s="36" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="E57" s="47">
         <v>2025003050060</v>
       </c>
       <c r="F57" s="36" t="s">
-        <v>282</v>
+        <v>184</v>
       </c>
       <c r="G57" s="3">
         <v>5567719862</v>
@@ -5521,13 +5128,13 @@
         <v>24</v>
       </c>
       <c r="J57" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K57" s="23">
         <v>46048</v>
       </c>
-      <c r="L57" s="65" t="s">
-        <v>255</v>
+      <c r="L57" s="63" t="s">
+        <v>168</v>
       </c>
       <c r="M57" s="44">
         <v>15.02</v>
@@ -5535,14 +5142,14 @@
       <c r="N57" s="44">
         <v>30</v>
       </c>
-      <c r="O57" s="60" t="s">
-        <v>283</v>
+      <c r="O57" s="60">
+        <v>46.43</v>
       </c>
       <c r="P57" s="62">
         <v>30</v>
       </c>
-      <c r="Q57" s="60" t="s">
-        <v>283</v>
+      <c r="Q57" s="60">
+        <v>46.43</v>
       </c>
       <c r="R57" s="62">
         <v>30</v>
@@ -5551,31 +5158,22 @@
         <v>0</v>
       </c>
       <c r="T57" s="44"/>
-      <c r="U57" s="40" t="s">
-        <v>284</v>
-      </c>
-      <c r="V57" s="40" t="s">
-        <v>285</v>
-      </c>
-      <c r="W57" s="40" t="s">
-        <v>286</v>
-      </c>
-      <c r="X57" s="40" t="s">
-        <v>287</v>
-      </c>
+      <c r="U57" s="40"/>
+      <c r="V57" s="40"/>
+      <c r="W57" s="40"/>
+      <c r="X57" s="40"/>
       <c r="Y57" s="40"/>
       <c r="Z57" s="40"/>
       <c r="AA57" s="40"/>
-      <c r="AB57" s="40" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="58" spans="1:28" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="AB57" s="40"/>
+      <c r="AC57" s="40"/>
+    </row>
+    <row r="58" spans="1:29" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A58" s="45">
         <v>2026</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>289</v>
+        <v>185</v>
       </c>
       <c r="C58" s="45" t="s">
         <v>21</v>
@@ -5587,7 +5185,7 @@
         <v>2025003050047</v>
       </c>
       <c r="F58" s="36" t="s">
-        <v>290</v>
+        <v>186</v>
       </c>
       <c r="G58" s="48">
         <v>2577210949</v>
@@ -5599,12 +5197,12 @@
         <v>24</v>
       </c>
       <c r="J58" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K58" s="23">
         <v>46072</v>
       </c>
-      <c r="L58" s="66">
+      <c r="L58" s="64">
         <v>46242</v>
       </c>
       <c r="M58" s="44">
@@ -5613,20 +5211,20 @@
       <c r="N58" s="44">
         <v>45.92</v>
       </c>
-      <c r="O58" s="60" t="s">
-        <v>291</v>
-      </c>
-      <c r="P58" s="62" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q58" s="62" t="s">
-        <v>293</v>
-      </c>
-      <c r="R58" s="62" t="s">
-        <v>294</v>
+      <c r="O58" s="60">
+        <v>86.08</v>
+      </c>
+      <c r="P58" s="62">
+        <v>51.1</v>
+      </c>
+      <c r="Q58" s="62">
+        <v>96.48</v>
+      </c>
+      <c r="R58" s="62">
+        <v>91.56</v>
       </c>
       <c r="S58" s="57" t="s">
-        <v>295</v>
+        <v>187</v>
       </c>
       <c r="T58" s="44"/>
       <c r="U58" s="40"/>
@@ -5637,25 +5235,26 @@
       <c r="Z58" s="40"/>
       <c r="AA58" s="40"/>
       <c r="AB58" s="40"/>
-    </row>
-    <row r="59" spans="1:28" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="AC58" s="40"/>
+    </row>
+    <row r="59" spans="1:29" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A59" s="41">
         <v>2026</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>261</v>
+        <v>171</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D59" s="36" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="E59" s="47">
         <v>2025003050059</v>
       </c>
       <c r="F59" s="36" t="s">
-        <v>296</v>
+        <v>188</v>
       </c>
       <c r="G59" s="2">
         <v>6759815490</v>
@@ -5667,13 +5266,13 @@
         <v>24</v>
       </c>
       <c r="J59" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K59" s="23">
         <v>46077</v>
       </c>
-      <c r="L59" s="65" t="s">
-        <v>297</v>
+      <c r="L59" s="63" t="s">
+        <v>189</v>
       </c>
       <c r="M59" s="44">
         <v>39.979999999999997</v>
@@ -5681,17 +5280,17 @@
       <c r="N59" s="44">
         <v>54.89</v>
       </c>
-      <c r="O59" s="60" t="s">
-        <v>298</v>
-      </c>
-      <c r="P59" s="62" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q59" s="62" t="s">
-        <v>300</v>
-      </c>
-      <c r="R59" s="62" t="s">
-        <v>301</v>
+      <c r="O59" s="60">
+        <v>45.86</v>
+      </c>
+      <c r="P59" s="62">
+        <v>65.739999999999995</v>
+      </c>
+      <c r="Q59" s="62">
+        <v>56.8</v>
+      </c>
+      <c r="R59" s="67">
+        <v>70.2</v>
       </c>
       <c r="S59" s="57">
         <v>60</v>
@@ -5705,25 +5304,26 @@
       <c r="Z59" s="40"/>
       <c r="AA59" s="40"/>
       <c r="AB59" s="40"/>
-    </row>
-    <row r="60" spans="1:28" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="AC59" s="40"/>
+    </row>
+    <row r="60" spans="1:29" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A60" s="45">
         <v>2026</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>302</v>
+        <v>190</v>
       </c>
       <c r="C60" s="45" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D60" s="36" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="E60" s="47">
         <v>2025003050058</v>
       </c>
       <c r="F60" s="36" t="s">
-        <v>303</v>
+        <v>191</v>
       </c>
       <c r="G60" s="48">
         <v>1956028276</v>
@@ -5735,13 +5335,13 @@
         <v>24</v>
       </c>
       <c r="J60" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K60" s="23">
         <v>46073</v>
       </c>
-      <c r="L60" s="65" t="s">
-        <v>304</v>
+      <c r="L60" s="63" t="s">
+        <v>192</v>
       </c>
       <c r="M60" s="44">
         <v>6.94</v>
@@ -5749,17 +5349,17 @@
       <c r="N60" s="44">
         <v>25</v>
       </c>
-      <c r="O60" s="60" t="s">
-        <v>305</v>
-      </c>
-      <c r="P60" s="62" t="s">
-        <v>306</v>
-      </c>
-      <c r="Q60" s="62" t="s">
-        <v>307</v>
-      </c>
-      <c r="R60" s="62" t="s">
-        <v>306</v>
+      <c r="O60" s="60">
+        <v>28.56</v>
+      </c>
+      <c r="P60" s="62">
+        <v>44.26</v>
+      </c>
+      <c r="Q60" s="62">
+        <v>47.61</v>
+      </c>
+      <c r="R60" s="67">
+        <v>55.67</v>
       </c>
       <c r="S60" s="57">
         <v>60</v>
@@ -5773,25 +5373,26 @@
       <c r="Z60" s="40"/>
       <c r="AA60" s="40"/>
       <c r="AB60" s="40"/>
-    </row>
-    <row r="61" spans="1:28" ht="36.75" customHeight="1">
+      <c r="AC60" s="40"/>
+    </row>
+    <row r="61" spans="1:29" ht="36.75" customHeight="1">
       <c r="A61" s="45">
         <v>2026</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>192</v>
+        <v>136</v>
       </c>
       <c r="C61" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="E61" s="47">
         <v>2025003050037</v>
       </c>
       <c r="F61" s="36" t="s">
-        <v>308</v>
+        <v>193</v>
       </c>
       <c r="G61" s="2">
         <v>4919153330</v>
@@ -5803,12 +5404,12 @@
         <v>24</v>
       </c>
       <c r="J61" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K61" s="23">
         <v>46073</v>
       </c>
-      <c r="L61" s="66">
+      <c r="L61" s="64">
         <v>46367</v>
       </c>
       <c r="M61" s="44">
@@ -5817,17 +5418,17 @@
       <c r="N61" s="44">
         <v>29.54</v>
       </c>
-      <c r="O61" s="60" t="s">
-        <v>309</v>
-      </c>
-      <c r="P61" s="62" t="s">
-        <v>310</v>
-      </c>
-      <c r="Q61" s="62" t="s">
-        <v>311</v>
-      </c>
-      <c r="R61" s="62" t="s">
-        <v>312</v>
+      <c r="O61" s="60">
+        <v>10.3</v>
+      </c>
+      <c r="P61" s="62">
+        <v>35.76</v>
+      </c>
+      <c r="Q61" s="62">
+        <v>30.31</v>
+      </c>
+      <c r="R61" s="67">
+        <v>52.91</v>
       </c>
       <c r="S61" s="57">
         <v>60</v>
@@ -5841,25 +5442,26 @@
       <c r="Z61" s="40"/>
       <c r="AA61" s="40"/>
       <c r="AB61" s="40"/>
-    </row>
-    <row r="62" spans="1:28" ht="36.75" customHeight="1">
+      <c r="AC61" s="40"/>
+    </row>
+    <row r="62" spans="1:29" ht="36.75" customHeight="1">
       <c r="A62" s="45">
         <v>2026</v>
       </c>
       <c r="B62" s="36" t="s">
-        <v>313</v>
+        <v>194</v>
       </c>
       <c r="C62" s="50" t="s">
         <v>27</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="E62" s="47">
         <v>2025003050037</v>
       </c>
       <c r="F62" s="36" t="s">
-        <v>308</v>
+        <v>193</v>
       </c>
       <c r="G62" s="2">
         <v>4814470012</v>
@@ -5871,12 +5473,12 @@
         <v>24</v>
       </c>
       <c r="J62" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K62" s="23">
         <v>46073</v>
       </c>
-      <c r="L62" s="66">
+      <c r="L62" s="64">
         <v>46367</v>
       </c>
       <c r="M62" s="44">
@@ -5885,17 +5487,17 @@
       <c r="N62" s="44">
         <v>29.54</v>
       </c>
-      <c r="O62" s="60" t="s">
-        <v>309</v>
-      </c>
-      <c r="P62" s="62" t="s">
-        <v>310</v>
-      </c>
-      <c r="Q62" s="62" t="s">
-        <v>311</v>
-      </c>
-      <c r="R62" s="62" t="s">
-        <v>312</v>
+      <c r="O62" s="60">
+        <v>10.3</v>
+      </c>
+      <c r="P62" s="62">
+        <v>35.76</v>
+      </c>
+      <c r="Q62" s="62">
+        <v>30.31</v>
+      </c>
+      <c r="R62" s="67">
+        <v>52.91</v>
       </c>
       <c r="S62" s="57">
         <v>60</v>
@@ -5909,25 +5511,26 @@
       <c r="Z62" s="40"/>
       <c r="AA62" s="40"/>
       <c r="AB62" s="40"/>
-    </row>
-    <row r="63" spans="1:28" ht="36.75" customHeight="1">
+      <c r="AC62" s="40"/>
+    </row>
+    <row r="63" spans="1:29" ht="36.75" customHeight="1">
       <c r="A63" s="45">
         <v>2026</v>
       </c>
       <c r="B63" s="36" t="s">
-        <v>281</v>
+        <v>183</v>
       </c>
       <c r="C63" s="45" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="E63" s="47">
         <v>2026003050010</v>
       </c>
       <c r="F63" s="36" t="s">
-        <v>314</v>
+        <v>195</v>
       </c>
       <c r="G63" s="48">
         <v>8659084152</v>
@@ -5939,13 +5542,13 @@
         <v>24</v>
       </c>
       <c r="J63" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K63" s="23">
         <v>46105</v>
       </c>
-      <c r="L63" s="65" t="s">
-        <v>315</v>
+      <c r="L63" s="63" t="s">
+        <v>196</v>
       </c>
       <c r="M63" s="44">
         <v>8.81</v>
@@ -5953,17 +5556,17 @@
       <c r="N63" s="44">
         <v>36</v>
       </c>
-      <c r="O63" s="60" t="s">
-        <v>316</v>
+      <c r="O63" s="60">
+        <v>16.66</v>
       </c>
       <c r="P63" s="62">
         <v>37</v>
       </c>
-      <c r="Q63" s="62" t="s">
-        <v>317</v>
-      </c>
-      <c r="R63" s="62">
-        <v>37</v>
+      <c r="Q63" s="62">
+        <v>31.53</v>
+      </c>
+      <c r="R63" s="67">
+        <v>38</v>
       </c>
       <c r="S63" s="57">
         <v>100</v>
@@ -5977,13 +5580,14 @@
       <c r="Z63" s="40"/>
       <c r="AA63" s="40"/>
       <c r="AB63" s="40"/>
-    </row>
-    <row r="64" spans="1:28" ht="36.75" customHeight="1">
+      <c r="AC63" s="40"/>
+    </row>
+    <row r="64" spans="1:29" ht="36.75" customHeight="1">
       <c r="A64" s="45">
         <v>2026</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>318</v>
+        <v>197</v>
       </c>
       <c r="C64" s="45" t="s">
         <v>21</v>
@@ -5995,7 +5599,7 @@
         <v>2026003050009</v>
       </c>
       <c r="F64" s="36" t="s">
-        <v>319</v>
+        <v>198</v>
       </c>
       <c r="G64" s="48">
         <v>5112178665</v>
@@ -6007,12 +5611,12 @@
         <v>24</v>
       </c>
       <c r="J64" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K64" s="23">
         <v>46107</v>
       </c>
-      <c r="L64" s="66">
+      <c r="L64" s="64">
         <v>46480</v>
       </c>
       <c r="M64" s="44">
@@ -6021,17 +5625,17 @@
       <c r="N64" s="44">
         <v>18.21</v>
       </c>
-      <c r="O64" s="60" t="s">
-        <v>320</v>
-      </c>
-      <c r="P64" s="62" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q64" s="62" t="s">
-        <v>322</v>
-      </c>
-      <c r="R64" s="62" t="s">
-        <v>323</v>
+      <c r="O64" s="60">
+        <v>14.94</v>
+      </c>
+      <c r="P64" s="62">
+        <v>19.34</v>
+      </c>
+      <c r="Q64" s="62">
+        <v>27.9</v>
+      </c>
+      <c r="R64" s="67">
+        <v>31.13</v>
       </c>
       <c r="S64" s="57">
         <v>100</v>
@@ -6045,16 +5649,17 @@
       <c r="Z64" s="40"/>
       <c r="AA64" s="40"/>
       <c r="AB64" s="40"/>
-    </row>
-    <row r="65" spans="1:20" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="AC64" s="40"/>
+    </row>
+    <row r="65" spans="1:21" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A65" s="45">
         <v>2026</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>324</v>
+        <v>199</v>
       </c>
       <c r="C65" s="45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D65" s="17" t="s">
         <v>22</v>
@@ -6063,7 +5668,7 @@
         <v>2025003050057</v>
       </c>
       <c r="F65" s="36" t="s">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="G65" s="2">
         <v>2205897938</v>
@@ -6075,39 +5680,44 @@
         <v>24</v>
       </c>
       <c r="J65" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K65" s="23">
         <v>46299</v>
       </c>
-      <c r="L65" s="66">
+      <c r="L65" s="64">
         <v>46245</v>
       </c>
-      <c r="M65" s="44"/>
-      <c r="N65" s="44"/>
-      <c r="O65" s="60" t="s">
-        <v>326</v>
-      </c>
-      <c r="P65" s="62" t="s">
-        <v>327</v>
-      </c>
-      <c r="Q65" s="62" t="s">
-        <v>328</v>
-      </c>
-      <c r="R65" s="62" t="s">
-        <v>329</v>
+      <c r="M65" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="N65" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="O65" s="60">
+        <v>19.09</v>
+      </c>
+      <c r="P65" s="62">
+        <v>36.659999999999997</v>
+      </c>
+      <c r="Q65" s="62">
+        <v>57.61</v>
+      </c>
+      <c r="R65" s="67">
+        <v>76.37</v>
       </c>
       <c r="S65" s="57">
         <v>100</v>
       </c>
       <c r="T65" s="44"/>
-    </row>
-    <row r="66" spans="1:20" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U65" s="40"/>
+    </row>
+    <row r="66" spans="1:21" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A66" s="45">
         <v>2026</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>330</v>
+        <v>201</v>
       </c>
       <c r="C66" s="45" t="s">
         <v>21</v>
@@ -6119,7 +5729,7 @@
         <v>2025003050052</v>
       </c>
       <c r="F66" s="36" t="s">
-        <v>331</v>
+        <v>202</v>
       </c>
       <c r="G66" s="2">
         <v>1865730932</v>
@@ -6130,43 +5740,48 @@
       <c r="I66" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="J66" s="60" t="s">
-        <v>332</v>
+      <c r="J66" s="68" t="s">
+        <v>119</v>
       </c>
       <c r="K66" s="23">
         <v>46132</v>
       </c>
-      <c r="L66" s="65" t="s">
-        <v>71</v>
-      </c>
-      <c r="M66" s="44"/>
-      <c r="N66" s="44"/>
+      <c r="L66" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="M66" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="N66" s="44" t="s">
+        <v>34</v>
+      </c>
       <c r="O66" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P66" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q66" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R66" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S66" s="57">
         <v>100</v>
       </c>
       <c r="T66" s="44"/>
-    </row>
-    <row r="67" spans="1:20" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U66" s="40"/>
+    </row>
+    <row r="67" spans="1:21" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A67" s="45">
         <v>2026</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>333</v>
+        <v>203</v>
       </c>
       <c r="C67" s="45" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D67" s="17" t="s">
         <v>22</v>
@@ -6175,7 +5790,7 @@
         <v>2026003050017</v>
       </c>
       <c r="F67" s="36" t="s">
-        <v>334</v>
+        <v>204</v>
       </c>
       <c r="G67" s="3">
         <v>2177276654</v>
@@ -6186,44 +5801,45 @@
       <c r="I67" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J67" s="60" t="s">
-        <v>332</v>
+      <c r="J67" s="68" t="s">
+        <v>119</v>
       </c>
       <c r="K67" s="23">
         <v>46147</v>
       </c>
-      <c r="L67" s="65" t="s">
-        <v>71</v>
+      <c r="L67" s="63" t="s">
+        <v>61</v>
       </c>
       <c r="M67" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N67" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O67" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P67" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q67" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="R67" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
+      </c>
+      <c r="R67" s="69">
+        <v>45.33</v>
       </c>
       <c r="S67" s="57" t="s">
-        <v>335</v>
+        <v>205</v>
       </c>
       <c r="T67" s="44"/>
-    </row>
-    <row r="68" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U67" s="40"/>
+    </row>
+    <row r="68" spans="1:21" ht="36.75" customHeight="1">
       <c r="A68" s="45">
         <v>2026</v>
       </c>
       <c r="B68" s="36" t="s">
-        <v>336</v>
+        <v>206</v>
       </c>
       <c r="C68" s="45" t="s">
         <v>21</v>
@@ -6235,7 +5851,7 @@
         <v>2026003050018</v>
       </c>
       <c r="F68" s="36" t="s">
-        <v>337</v>
+        <v>207</v>
       </c>
       <c r="G68" s="48">
         <v>8022406899</v>
@@ -6247,13 +5863,13 @@
         <v>24</v>
       </c>
       <c r="J68" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K68" s="23">
         <v>46129</v>
       </c>
-      <c r="L68" s="65" t="s">
-        <v>338</v>
+      <c r="L68" s="63" t="s">
+        <v>208</v>
       </c>
       <c r="M68" s="44">
         <v>15.5</v>
@@ -6261,29 +5877,30 @@
       <c r="N68" s="44">
         <v>46.93</v>
       </c>
-      <c r="O68" s="60" t="s">
-        <v>339</v>
-      </c>
-      <c r="P68" s="62" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q68" s="62" t="s">
-        <v>341</v>
-      </c>
-      <c r="R68" s="62" t="s">
-        <v>342</v>
+      <c r="O68" s="60">
+        <v>47.67</v>
+      </c>
+      <c r="P68" s="62">
+        <v>46.93</v>
+      </c>
+      <c r="Q68" s="62">
+        <v>51.93</v>
+      </c>
+      <c r="R68" s="62">
+        <v>63.72</v>
       </c>
       <c r="S68" s="57">
         <v>100</v>
       </c>
       <c r="T68" s="44"/>
-    </row>
-    <row r="69" spans="1:20" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U68" s="40"/>
+    </row>
+    <row r="69" spans="1:21" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A69" s="45">
         <v>2026</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>313</v>
+        <v>194</v>
       </c>
       <c r="C69" s="45" t="s">
         <v>27</v>
@@ -6295,7 +5912,7 @@
         <v>2026003050021</v>
       </c>
       <c r="F69" s="36" t="s">
-        <v>343</v>
+        <v>209</v>
       </c>
       <c r="G69" s="2">
         <v>2356550945</v>
@@ -6307,46 +5924,47 @@
         <v>24</v>
       </c>
       <c r="J69" s="60" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="K69" s="23">
         <v>46149</v>
       </c>
-      <c r="L69" s="65" t="s">
-        <v>71</v>
+      <c r="L69" s="63" t="s">
+        <v>61</v>
       </c>
       <c r="M69" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N69" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O69" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P69" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q69" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R69" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S69" s="57">
         <v>75</v>
       </c>
       <c r="T69" s="44"/>
-    </row>
-    <row r="70" spans="1:20" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U69" s="40"/>
+    </row>
+    <row r="70" spans="1:21" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A70" s="45">
         <v>2026</v>
       </c>
       <c r="B70" s="46" t="s">
-        <v>344</v>
+        <v>210</v>
       </c>
       <c r="C70" s="41" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="D70" s="36" t="s">
         <v>22</v>
@@ -6355,7 +5973,7 @@
         <v>2026003050005</v>
       </c>
       <c r="F70" s="36" t="s">
-        <v>345</v>
+        <v>211</v>
       </c>
       <c r="G70" s="42">
         <v>2126428620</v>
@@ -6367,46 +5985,47 @@
         <v>24</v>
       </c>
       <c r="J70" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K70" s="23">
         <v>46191</v>
       </c>
-      <c r="L70" s="65" t="s">
-        <v>346</v>
+      <c r="L70" s="63" t="s">
+        <v>212</v>
       </c>
       <c r="M70" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N70" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O70" s="60">
         <v>11</v>
       </c>
-      <c r="P70" s="62" t="s">
-        <v>347</v>
+      <c r="P70" s="62">
+        <v>45.06</v>
       </c>
       <c r="Q70" s="62">
         <v>43</v>
       </c>
-      <c r="R70" s="62" t="s">
-        <v>348</v>
+      <c r="R70" s="67">
+        <v>68.260000000000005</v>
       </c>
       <c r="S70" s="57">
         <v>100</v>
       </c>
       <c r="T70" s="44"/>
-    </row>
-    <row r="71" spans="1:20" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U70" s="40"/>
+    </row>
+    <row r="71" spans="1:21" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A71" s="45">
         <v>2026</v>
       </c>
       <c r="B71" s="36" t="s">
-        <v>349</v>
+        <v>213</v>
       </c>
       <c r="C71" s="45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D71" s="36" t="s">
         <v>22</v>
@@ -6415,7 +6034,7 @@
         <v>2026003050006</v>
       </c>
       <c r="F71" s="36" t="s">
-        <v>350</v>
+        <v>214</v>
       </c>
       <c r="G71" s="2">
         <v>2495192913</v>
@@ -6427,46 +6046,47 @@
         <v>24</v>
       </c>
       <c r="J71" s="60" t="s">
-        <v>332</v>
+        <v>215</v>
       </c>
       <c r="K71" s="23">
         <v>46170</v>
       </c>
-      <c r="L71" s="65" t="s">
-        <v>71</v>
+      <c r="L71" s="63" t="s">
+        <v>61</v>
       </c>
       <c r="M71" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N71" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O71" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P71" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q71" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R71" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S71" s="57">
         <v>100</v>
       </c>
       <c r="T71" s="44"/>
-    </row>
-    <row r="72" spans="1:20" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U71" s="40"/>
+    </row>
+    <row r="72" spans="1:21" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A72" s="45">
         <v>2026</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>281</v>
+        <v>183</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>22</v>
@@ -6475,7 +6095,7 @@
         <v>2026003050011</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>351</v>
+        <v>216</v>
       </c>
       <c r="G72" s="15">
         <v>2095882218</v>
@@ -6487,55 +6107,56 @@
         <v>24</v>
       </c>
       <c r="J72" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K72" s="23">
         <v>46132</v>
       </c>
-      <c r="L72" s="65" t="s">
-        <v>352</v>
+      <c r="L72" s="63" t="s">
+        <v>217</v>
       </c>
       <c r="M72" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N72" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O72" s="60">
         <v>0</v>
       </c>
-      <c r="P72" s="62" t="s">
-        <v>353</v>
+      <c r="P72" s="62">
+        <v>35.729999999999997</v>
       </c>
       <c r="Q72" s="60">
         <v>0</v>
       </c>
-      <c r="R72" s="62" t="s">
-        <v>353</v>
+      <c r="R72" s="62">
+        <v>35.729999999999997</v>
       </c>
       <c r="S72" s="57">
         <v>40</v>
       </c>
       <c r="T72" s="44"/>
-    </row>
-    <row r="73" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U72" s="40"/>
+    </row>
+    <row r="73" spans="1:21" ht="36.75" customHeight="1">
       <c r="A73" s="45">
         <v>2026</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>354</v>
+        <v>218</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="E73" s="55">
         <v>2026003050014</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>355</v>
+        <v>219</v>
       </c>
       <c r="G73" s="10">
         <v>5482855957</v>
@@ -6546,56 +6167,57 @@
       <c r="I73" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="J73" s="60" t="s">
-        <v>332</v>
+      <c r="J73" s="68" t="s">
+        <v>119</v>
       </c>
       <c r="K73" s="23">
         <v>46189</v>
       </c>
-      <c r="L73" s="65" t="s">
-        <v>71</v>
+      <c r="L73" s="63" t="s">
+        <v>61</v>
       </c>
       <c r="M73" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N73" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O73" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P73" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q73" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R73" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S73" s="57">
         <v>100</v>
       </c>
       <c r="T73" s="44"/>
-    </row>
-    <row r="74" spans="1:20" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U73" s="40"/>
+    </row>
+    <row r="74" spans="1:21" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A74" s="45">
         <v>2026</v>
       </c>
       <c r="B74" s="36" t="s">
-        <v>357</v>
+        <v>221</v>
       </c>
       <c r="C74" s="45" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="E74" s="47">
         <v>2026003050008</v>
       </c>
       <c r="F74" s="36" t="s">
-        <v>358</v>
+        <v>222</v>
       </c>
       <c r="G74" s="2">
         <v>2300078297</v>
@@ -6607,19 +6229,19 @@
         <v>24</v>
       </c>
       <c r="J74" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K74" s="23">
         <v>46175</v>
       </c>
-      <c r="L74" s="65" t="s">
-        <v>359</v>
+      <c r="L74" s="63" t="s">
+        <v>223</v>
       </c>
       <c r="M74" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N74" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O74" s="60">
         <v>0</v>
@@ -6637,25 +6259,26 @@
         <v>100</v>
       </c>
       <c r="T74" s="44"/>
-    </row>
-    <row r="75" spans="1:20" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U74" s="40"/>
+    </row>
+    <row r="75" spans="1:21" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A75" s="45">
         <v>2026</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>360</v>
+        <v>224</v>
       </c>
       <c r="C75" s="45" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D75" s="17" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="E75" s="47">
         <v>2026003050002</v>
       </c>
       <c r="F75" s="36" t="s">
-        <v>361</v>
+        <v>225</v>
       </c>
       <c r="G75" s="48">
         <v>1408385533</v>
@@ -6667,55 +6290,56 @@
         <v>24</v>
       </c>
       <c r="J75" s="60" t="s">
-        <v>332</v>
+        <v>215</v>
       </c>
       <c r="K75" s="23">
         <v>46185</v>
       </c>
-      <c r="L75" s="65" t="s">
-        <v>356</v>
+      <c r="L75" s="63" t="s">
+        <v>61</v>
       </c>
       <c r="M75" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N75" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O75" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P75" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q75" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R75" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S75" s="57">
         <v>100</v>
       </c>
       <c r="T75" s="44"/>
-    </row>
-    <row r="76" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U75" s="40"/>
+    </row>
+    <row r="76" spans="1:21" ht="36.75" customHeight="1">
       <c r="A76" s="45">
         <v>2026</v>
       </c>
       <c r="B76" s="36" t="s">
-        <v>362</v>
+        <v>226</v>
       </c>
       <c r="C76" s="50" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="E76" s="47">
         <v>2026003050020</v>
       </c>
       <c r="F76" s="36" t="s">
-        <v>363</v>
+        <v>227</v>
       </c>
       <c r="G76" s="48">
         <v>8105380232</v>
@@ -6727,55 +6351,56 @@
         <v>24</v>
       </c>
       <c r="J76" s="60" t="s">
-        <v>332</v>
+        <v>215</v>
       </c>
       <c r="K76" s="23">
         <v>46185</v>
       </c>
-      <c r="L76" s="65" t="s">
-        <v>356</v>
+      <c r="L76" s="63" t="s">
+        <v>61</v>
       </c>
       <c r="M76" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N76" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O76" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P76" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q76" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R76" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S76" s="57">
         <v>100</v>
       </c>
       <c r="T76" s="44"/>
-    </row>
-    <row r="77" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U76" s="40"/>
+    </row>
+    <row r="77" spans="1:21" ht="36.75" customHeight="1">
       <c r="A77" s="45">
         <v>2026</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>211</v>
+        <v>148</v>
       </c>
       <c r="C77" s="50" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="E77" s="47">
         <v>2026003050020</v>
       </c>
       <c r="F77" s="36" t="s">
-        <v>363</v>
+        <v>227</v>
       </c>
       <c r="G77" s="2">
         <v>4333614485</v>
@@ -6787,55 +6412,56 @@
         <v>24</v>
       </c>
       <c r="J77" s="60" t="s">
-        <v>332</v>
+        <v>215</v>
       </c>
       <c r="K77" s="23">
         <v>46185</v>
       </c>
-      <c r="L77" s="65" t="s">
-        <v>356</v>
+      <c r="L77" s="63" t="s">
+        <v>220</v>
       </c>
       <c r="M77" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N77" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O77" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P77" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q77" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R77" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S77" s="57">
         <v>100</v>
       </c>
       <c r="T77" s="44"/>
-    </row>
-    <row r="78" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U77" s="40"/>
+    </row>
+    <row r="78" spans="1:21" ht="36.75" customHeight="1">
       <c r="A78" s="45">
         <v>2026</v>
       </c>
       <c r="B78" s="36" t="s">
-        <v>241</v>
+        <v>161</v>
       </c>
       <c r="C78" s="50" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D78" s="17" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="E78" s="47">
         <v>2026003050015</v>
       </c>
       <c r="F78" s="36" t="s">
-        <v>364</v>
+        <v>228</v>
       </c>
       <c r="G78" s="2">
         <v>3806958402</v>
@@ -6847,55 +6473,56 @@
         <v>24</v>
       </c>
       <c r="J78" s="60" t="s">
-        <v>332</v>
+        <v>215</v>
       </c>
       <c r="K78" s="23">
         <v>46185</v>
       </c>
-      <c r="L78" s="65" t="s">
-        <v>356</v>
+      <c r="L78" s="63" t="s">
+        <v>220</v>
       </c>
       <c r="M78" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N78" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O78" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P78" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q78" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R78" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S78" s="57">
         <v>100</v>
       </c>
       <c r="T78" s="44"/>
-    </row>
-    <row r="79" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U78" s="40"/>
+    </row>
+    <row r="79" spans="1:21" ht="36.75" customHeight="1">
       <c r="A79" s="45">
         <v>2026</v>
       </c>
       <c r="B79" s="36" t="s">
-        <v>365</v>
+        <v>229</v>
       </c>
       <c r="C79" s="50" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D79" s="17" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="E79" s="47">
         <v>2026003050015</v>
       </c>
       <c r="F79" s="36" t="s">
-        <v>364</v>
+        <v>228</v>
       </c>
       <c r="G79" s="2">
         <v>2044483403</v>
@@ -6907,55 +6534,56 @@
         <v>24</v>
       </c>
       <c r="J79" s="60" t="s">
-        <v>332</v>
+        <v>215</v>
       </c>
       <c r="K79" s="23">
         <v>46185</v>
       </c>
-      <c r="L79" s="65" t="s">
-        <v>356</v>
+      <c r="L79" s="63" t="s">
+        <v>220</v>
       </c>
       <c r="M79" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N79" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O79" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P79" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q79" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R79" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S79" s="57">
         <v>100</v>
       </c>
       <c r="T79" s="44"/>
-    </row>
-    <row r="80" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U79" s="40"/>
+    </row>
+    <row r="80" spans="1:21" ht="36.75" customHeight="1">
       <c r="A80" s="45">
         <v>2026</v>
       </c>
       <c r="B80" s="36" t="s">
-        <v>366</v>
+        <v>230</v>
       </c>
       <c r="C80" s="45" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="E80" s="47">
         <v>2026003050025</v>
       </c>
       <c r="F80" s="36" t="s">
-        <v>367</v>
+        <v>231</v>
       </c>
       <c r="G80" s="2">
         <v>3738220582</v>
@@ -6967,46 +6595,47 @@
         <v>24</v>
       </c>
       <c r="J80" s="60" t="s">
-        <v>332</v>
+        <v>215</v>
       </c>
       <c r="K80" s="23">
         <v>46185</v>
       </c>
-      <c r="L80" s="65" t="s">
-        <v>356</v>
+      <c r="L80" s="63" t="s">
+        <v>220</v>
       </c>
       <c r="M80" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N80" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O80" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P80" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q80" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R80" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S80" s="57">
         <v>100</v>
       </c>
       <c r="T80" s="44"/>
-    </row>
-    <row r="81" spans="1:20" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U80" s="40"/>
+    </row>
+    <row r="81" spans="1:21" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A81" s="45">
         <v>2026</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>368</v>
+        <v>232</v>
       </c>
       <c r="C81" s="45" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="D81" s="36" t="s">
         <v>22</v>
@@ -7015,7 +6644,7 @@
         <v>2026003050016</v>
       </c>
       <c r="F81" s="36" t="s">
-        <v>369</v>
+        <v>233</v>
       </c>
       <c r="G81" s="3">
         <v>2343812951</v>
@@ -7027,53 +6656,56 @@
         <v>24</v>
       </c>
       <c r="J81" s="60" t="s">
-        <v>47</v>
-      </c>
-      <c r="K81" s="23"/>
-      <c r="L81" s="65" t="s">
-        <v>47</v>
+        <v>215</v>
+      </c>
+      <c r="K81" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="L81" s="63" t="s">
+        <v>44</v>
       </c>
       <c r="M81" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N81" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O81" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P81" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q81" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R81" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S81" s="57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T81" s="44"/>
-    </row>
-    <row r="82" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U81" s="40"/>
+    </row>
+    <row r="82" spans="1:21" ht="36.75" customHeight="1">
       <c r="A82" s="45">
         <v>2026</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>370</v>
+        <v>234</v>
       </c>
       <c r="C82" s="45" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="D82" s="36" t="s">
-        <v>371</v>
+        <v>235</v>
       </c>
       <c r="E82" s="47">
         <v>2026003050022</v>
       </c>
       <c r="F82" s="36" t="s">
-        <v>372</v>
+        <v>236</v>
       </c>
       <c r="G82" s="48">
         <v>6654540000</v>
@@ -7085,55 +6717,56 @@
         <v>24</v>
       </c>
       <c r="J82" s="60" t="s">
-        <v>332</v>
-      </c>
-      <c r="K82" s="66">
+        <v>215</v>
+      </c>
+      <c r="K82" s="64">
         <v>46239</v>
       </c>
-      <c r="L82" s="65" t="s">
-        <v>356</v>
+      <c r="L82" s="63" t="s">
+        <v>220</v>
       </c>
       <c r="M82" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N82" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O82" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P82" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q82" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R82" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S82" s="57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T82" s="44"/>
-    </row>
-    <row r="83" spans="1:20" ht="36.75" customHeight="1">
+      <c r="U82" s="40"/>
+    </row>
+    <row r="83" spans="1:21" ht="36.75" customHeight="1">
       <c r="A83" s="45">
         <v>2026</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>279</v>
+        <v>180</v>
       </c>
       <c r="C83" s="45" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="D83" s="36" t="s">
-        <v>373</v>
+        <v>237</v>
       </c>
       <c r="E83" s="47">
         <v>2026003050019</v>
       </c>
       <c r="F83" s="36" t="s">
-        <v>374</v>
+        <v>238</v>
       </c>
       <c r="G83" s="48">
         <v>8154980500</v>
@@ -7145,38 +6778,39 @@
         <v>24</v>
       </c>
       <c r="J83" s="60" t="s">
-        <v>332</v>
-      </c>
-      <c r="K83" s="66">
+        <v>215</v>
+      </c>
+      <c r="K83" s="64">
         <v>46212</v>
       </c>
-      <c r="L83" s="65" t="s">
-        <v>356</v>
+      <c r="L83" s="63" t="s">
+        <v>220</v>
       </c>
       <c r="M83" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N83" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O83" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P83" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q83" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R83" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S83" s="57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T83" s="44"/>
-    </row>
-    <row r="84" spans="1:20" s="14" customFormat="1">
+      <c r="U83" s="40"/>
+    </row>
+    <row r="84" spans="1:21" s="14" customFormat="1">
       <c r="A84" s="40"/>
       <c r="B84" s="52"/>
       <c r="C84" s="40"/>
@@ -7203,8 +6837,9 @@
       <c r="R84" s="38"/>
       <c r="S84" s="38"/>
       <c r="T84" s="38"/>
-    </row>
-    <row r="85" spans="1:20" s="14" customFormat="1">
+      <c r="U84" s="40"/>
+    </row>
+    <row r="85" spans="1:21" s="14" customFormat="1">
       <c r="A85" s="40"/>
       <c r="B85" s="52"/>
       <c r="C85" s="40"/>
@@ -7225,8 +6860,9 @@
       <c r="R85" s="38"/>
       <c r="S85" s="38"/>
       <c r="T85" s="38"/>
-    </row>
-    <row r="86" spans="1:20" s="14" customFormat="1">
+      <c r="U85" s="40"/>
+    </row>
+    <row r="86" spans="1:21" s="14" customFormat="1">
       <c r="A86" s="40"/>
       <c r="B86" s="52"/>
       <c r="C86" s="40"/>
@@ -7247,8 +6883,9 @@
       <c r="R86" s="38"/>
       <c r="S86" s="38"/>
       <c r="T86" s="38"/>
-    </row>
-    <row r="87" spans="1:20" s="14" customFormat="1">
+      <c r="U86" s="40"/>
+    </row>
+    <row r="87" spans="1:21" s="14" customFormat="1">
       <c r="A87" s="40"/>
       <c r="B87" s="52"/>
       <c r="C87" s="40"/>
@@ -7269,8 +6906,9 @@
       <c r="R87" s="38"/>
       <c r="S87" s="38"/>
       <c r="T87" s="38"/>
-    </row>
-    <row r="88" spans="1:20" s="14" customFormat="1">
+      <c r="U87" s="40"/>
+    </row>
+    <row r="88" spans="1:21" s="14" customFormat="1">
       <c r="A88" s="40"/>
       <c r="B88" s="52"/>
       <c r="C88" s="40"/>
@@ -7291,8 +6929,9 @@
       <c r="R88" s="38"/>
       <c r="S88" s="38"/>
       <c r="T88" s="38"/>
-    </row>
-    <row r="89" spans="1:20" s="14" customFormat="1">
+      <c r="U88" s="40"/>
+    </row>
+    <row r="89" spans="1:21" s="14" customFormat="1">
       <c r="A89" s="40"/>
       <c r="B89" s="52"/>
       <c r="C89" s="40"/>
@@ -7313,8 +6952,9 @@
       <c r="R89" s="38"/>
       <c r="S89" s="38"/>
       <c r="T89" s="38"/>
-    </row>
-    <row r="90" spans="1:20" s="14" customFormat="1">
+      <c r="U89" s="40"/>
+    </row>
+    <row r="90" spans="1:21" s="14" customFormat="1">
       <c r="A90" s="40"/>
       <c r="B90" s="52"/>
       <c r="C90" s="40"/>
@@ -7335,8 +6975,9 @@
       <c r="R90" s="38"/>
       <c r="S90" s="38"/>
       <c r="T90" s="38"/>
-    </row>
-    <row r="91" spans="1:20" s="14" customFormat="1">
+      <c r="U90" s="40"/>
+    </row>
+    <row r="91" spans="1:21" s="14" customFormat="1">
       <c r="A91" s="40"/>
       <c r="B91" s="52"/>
       <c r="C91" s="40"/>
@@ -7357,8 +6998,9 @@
       <c r="R91" s="38"/>
       <c r="S91" s="38"/>
       <c r="T91" s="38"/>
-    </row>
-    <row r="92" spans="1:20" s="14" customFormat="1">
+      <c r="U91" s="40"/>
+    </row>
+    <row r="92" spans="1:21" s="14" customFormat="1">
       <c r="A92" s="40"/>
       <c r="B92" s="52"/>
       <c r="C92" s="40"/>
@@ -7379,8 +7021,9 @@
       <c r="R92" s="38"/>
       <c r="S92" s="38"/>
       <c r="T92" s="38"/>
-    </row>
-    <row r="93" spans="1:20" s="14" customFormat="1">
+      <c r="U92" s="40"/>
+    </row>
+    <row r="93" spans="1:21" s="14" customFormat="1">
       <c r="A93" s="40"/>
       <c r="B93" s="52"/>
       <c r="C93" s="40"/>
@@ -7401,8 +7044,9 @@
       <c r="R93" s="38"/>
       <c r="S93" s="38"/>
       <c r="T93" s="38"/>
-    </row>
-    <row r="94" spans="1:20" s="14" customFormat="1">
+      <c r="U93" s="40"/>
+    </row>
+    <row r="94" spans="1:21" s="14" customFormat="1">
       <c r="A94" s="40"/>
       <c r="B94" s="52"/>
       <c r="C94" s="40"/>
@@ -7423,8 +7067,9 @@
       <c r="R94" s="38"/>
       <c r="S94" s="38"/>
       <c r="T94" s="38"/>
-    </row>
-    <row r="95" spans="1:20">
+      <c r="U94" s="40"/>
+    </row>
+    <row r="95" spans="1:21">
       <c r="A95" s="40"/>
       <c r="B95" s="52"/>
       <c r="C95" s="40"/>
@@ -7445,8 +7090,9 @@
       <c r="R95" s="38"/>
       <c r="S95" s="38"/>
       <c r="T95" s="38"/>
-    </row>
-    <row r="96" spans="1:20">
+      <c r="U95" s="40"/>
+    </row>
+    <row r="96" spans="1:21">
       <c r="A96" s="40"/>
       <c r="B96" s="52"/>
       <c r="C96" s="40"/>
@@ -7467,6 +7113,7 @@
       <c r="R96" s="38"/>
       <c r="S96" s="38"/>
       <c r="T96" s="38"/>
+      <c r="U96" s="40"/>
     </row>
     <row r="97" spans="2:5">
       <c r="B97" s="52"/>
@@ -7633,6 +7280,5 @@
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="41" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OACEVEDOD\Desktop\Jefe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85595A4C-7F1F-4EF2-BD33-80351162063B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3EA6055-752D-4A28-90F3-F3AC130BC988}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="APROBADOS 2024-2025-2026" sheetId="18" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'APROBADOS 2024-2025-2026'!$A$2:$U$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'APROBADOS 2024-2025-2026'!$A$2:$V$85</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'APROBADOS 2024-2025-2026'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -35,7 +35,7 @@
     <author>tc={32851E12-2A14-423F-AF75-3D964D0C8E1F}</author>
   </authors>
   <commentList>
-    <comment ref="M5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="N5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -51,7 +51,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+    <comment ref="N9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="283">
   <si>
     <t>PROYECTOS APROBADOS POR ASIGNACIÓN CON CARGO AL SISTEMA GENERAL DE REGALÍAS DEPARTAMENTO DE Antioquia - 2024-2026</t>
   </si>
@@ -745,18 +745,12 @@
     <t>17/12/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">PUENTE VEHICULAR LOS ESTUDIANTES </t>
-  </si>
-  <si>
     <t>Mejoramiento de vías urbanas mediante la construcción de puentes vehiculares en los municipios de Rionegro y Cisneros del departamento de Antioquia</t>
   </si>
   <si>
     <t>CISNEROS</t>
   </si>
   <si>
-    <t>PUENTE VEHICULAR</t>
-  </si>
-  <si>
     <t>0,8 KM PAV VIAS URB PARQUE TERM TTE</t>
   </si>
   <si>
@@ -844,9 +838,6 @@
     <t>URAMITA</t>
   </si>
   <si>
-    <t>PAVIMENTACIÓN URBANA</t>
-  </si>
-  <si>
     <t>Pavimentación y Adecuación de Vía en el Barrio el Socorro y La Copa en la Zona Urbana del Municipio de Uramita Antioquia</t>
   </si>
   <si>
@@ -923,6 +914,16 @@
   </si>
   <si>
     <t>Construcción de Alcantarillado Residual Vía Centro de Salud Don Bosco de Currulao en el Distrito de Turbo, Antioquia</t>
+  </si>
+  <si>
+    <t>Alcance
+Valor</t>
+  </si>
+  <si>
+    <t>0,54 KM PAVIMENTACIÓN URBANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 PUENTE VEHICULAR LOS ESTUDIANTES </t>
   </si>
 </sst>
 </file>
@@ -932,7 +933,7 @@
   <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="[$$-240A]\ #,##0.00"/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1321,10 +1322,10 @@
     <xf numFmtId="1" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1770,31 +1771,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD121"/>
+  <dimension ref="A1:AE121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7" style="7" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" style="12" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="7" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" style="12" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" style="12" customWidth="1"/>
-    <col min="6" max="6" width="21.28515625" style="11" customWidth="1"/>
-    <col min="7" max="7" width="56.28515625" style="12" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" style="13" customWidth="1"/>
-    <col min="9" max="9" width="23" style="13" customWidth="1"/>
-    <col min="10" max="10" width="27.85546875" style="20" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="20" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="21" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="20" customWidth="1"/>
-    <col min="14" max="20" width="11.42578125" style="20" customWidth="1"/>
-    <col min="21" max="21" width="12.42578125" style="20" customWidth="1"/>
-    <col min="22" max="16384" width="8.85546875" style="7"/>
+    <col min="3" max="4" width="17.28515625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" style="12" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" style="12" customWidth="1"/>
+    <col min="7" max="7" width="21.28515625" style="11" customWidth="1"/>
+    <col min="8" max="8" width="56.28515625" style="12" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" style="13" customWidth="1"/>
+    <col min="10" max="10" width="23" style="13" customWidth="1"/>
+    <col min="11" max="11" width="27.85546875" style="20" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="20" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="21" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="20" customWidth="1"/>
+    <col min="15" max="21" width="11.42578125" style="20" customWidth="1"/>
+    <col min="22" max="22" width="12.42578125" style="20" customWidth="1"/>
+    <col min="23" max="16384" width="8.85546875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:23">
       <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
@@ -1803,30 +1804,31 @@
       <c r="D1" s="70"/>
       <c r="E1" s="70"/>
       <c r="F1" s="70"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
       <c r="I1" s="70"/>
-      <c r="J1" s="39"/>
+      <c r="J1" s="70"/>
       <c r="K1" s="39"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="70" t="s">
+      <c r="L1" s="39"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="O1" s="70"/>
-      <c r="P1" s="70" t="s">
+      <c r="P1" s="70"/>
+      <c r="Q1" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="70"/>
-      <c r="R1" s="70" t="s">
+      <c r="R1" s="70"/>
+      <c r="S1" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="S1" s="70"/>
-      <c r="T1" s="39"/>
+      <c r="T1" s="70"/>
       <c r="U1" s="39"/>
-      <c r="V1" s="41"/>
-    </row>
-    <row r="2" spans="1:22" s="29" customFormat="1" ht="54.6" customHeight="1">
+      <c r="V1" s="39"/>
+      <c r="W1" s="41"/>
+    </row>
+    <row r="2" spans="1:23" s="29" customFormat="1" ht="54.6" customHeight="1">
       <c r="A2" s="30" t="s">
         <v>4</v>
       </c>
@@ -1837,61 +1839,64 @@
         <v>6</v>
       </c>
       <c r="D2" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="E2" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="F2" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="G2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="H2" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="I2" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="31" t="s">
+      <c r="J2" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="32" t="s">
+      <c r="K2" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="32" t="s">
+      <c r="L2" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="M2" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="34" t="s">
+      <c r="N2" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="32" t="s">
+      <c r="O2" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="32" t="s">
+      <c r="P2" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="32" t="s">
+      <c r="Q2" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="32" t="s">
+      <c r="R2" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="32" t="s">
+      <c r="S2" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="32" t="s">
+      <c r="T2" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="32" t="s">
+      <c r="U2" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="U2" s="35" t="s">
+      <c r="V2" s="35" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="36.75" customHeight="1">
+    <row r="3" spans="1:23" ht="36.75" customHeight="1">
       <c r="A3" s="42">
         <v>2024</v>
       </c>
@@ -1901,59 +1906,63 @@
       <c r="C3" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="D3" s="42">
+        <f>IF(ISNUMBER(E3),E3,IFERROR(VALUE(LEFT(E3,FIND(" ",E3)-1)),1))</f>
+        <v>4</v>
+      </c>
+      <c r="E3" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="F3" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G3" s="1">
         <v>2024003050239</v>
       </c>
-      <c r="G3" s="37" t="s">
+      <c r="H3" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="2">
         <v>7046140299</v>
       </c>
-      <c r="I3" s="2">
+      <c r="J3" s="2">
         <v>5636912239</v>
       </c>
-      <c r="J3" s="22" t="s">
+      <c r="K3" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="57" t="s">
+      <c r="L3" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="44">
+      <c r="M3" s="44">
         <v>45635</v>
       </c>
-      <c r="M3" s="69">
+      <c r="N3" s="69">
         <v>45788</v>
       </c>
-      <c r="N3" s="45">
+      <c r="O3" s="45">
         <v>99.45</v>
       </c>
-      <c r="O3" s="45">
+      <c r="P3" s="45">
         <v>99.87</v>
       </c>
-      <c r="P3" s="22">
-        <v>100</v>
-      </c>
-      <c r="Q3" s="45">
+      <c r="Q3" s="22">
+        <v>100</v>
+      </c>
+      <c r="R3" s="45">
         <v>99.87</v>
       </c>
-      <c r="R3" s="62"/>
       <c r="S3" s="62"/>
-      <c r="T3" s="57" t="s">
+      <c r="T3" s="62"/>
+      <c r="U3" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="U3" s="22">
-        <v>100</v>
-      </c>
-      <c r="V3" s="41"/>
-    </row>
-    <row r="4" spans="1:22" ht="36.75" customHeight="1">
+      <c r="V3" s="22">
+        <v>100</v>
+      </c>
+      <c r="W3" s="41"/>
+    </row>
+    <row r="4" spans="1:23" ht="36.75" customHeight="1">
       <c r="A4" s="42">
         <v>2024</v>
       </c>
@@ -1963,63 +1972,67 @@
       <c r="C4" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="42">
+        <f t="shared" ref="D4:D67" si="0">IF(ISNUMBER(E4),E4,IFERROR(VALUE(LEFT(E4,FIND(" ",E4)-1)),1))</f>
+        <v>2</v>
+      </c>
+      <c r="E4" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="37" t="s">
+      <c r="F4" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="38">
+      <c r="G4" s="38">
         <v>2024003050246</v>
       </c>
-      <c r="G4" s="37" t="s">
+      <c r="H4" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <v>4078127896</v>
       </c>
-      <c r="I4" s="2">
+      <c r="J4" s="2">
         <v>3262502317</v>
       </c>
-      <c r="J4" s="22" t="s">
+      <c r="K4" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="58" t="s">
+      <c r="L4" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="L4" s="44">
+      <c r="M4" s="44">
         <v>45637</v>
       </c>
-      <c r="M4" s="66" t="s">
+      <c r="N4" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="N4" s="23">
-        <v>100</v>
-      </c>
       <c r="O4" s="23">
+        <v>100</v>
+      </c>
+      <c r="P4" s="23">
         <v>99.52</v>
       </c>
-      <c r="P4" s="61">
-        <v>100</v>
-      </c>
-      <c r="Q4" s="63">
+      <c r="Q4" s="61">
+        <v>100</v>
+      </c>
+      <c r="R4" s="63">
         <v>99.52</v>
       </c>
-      <c r="R4" s="63">
-        <v>100</v>
-      </c>
       <c r="S4" s="63">
+        <v>100</v>
+      </c>
+      <c r="T4" s="63">
         <v>99.52</v>
       </c>
-      <c r="T4" s="58">
-        <v>100</v>
-      </c>
-      <c r="U4" s="22">
-        <v>100</v>
-      </c>
-      <c r="V4" s="41"/>
-    </row>
-    <row r="5" spans="1:22" ht="36.75" customHeight="1">
+      <c r="U4" s="58">
+        <v>100</v>
+      </c>
+      <c r="V4" s="22">
+        <v>100</v>
+      </c>
+      <c r="W4" s="41"/>
+    </row>
+    <row r="5" spans="1:23" ht="36.75" customHeight="1">
       <c r="A5" s="42">
         <v>2024</v>
       </c>
@@ -2029,59 +2042,63 @@
       <c r="C5" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="42">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E5" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="37" t="s">
+      <c r="F5" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
         <v>2024003050243</v>
       </c>
-      <c r="G5" s="37" t="s">
+      <c r="H5" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <v>4907167940</v>
       </c>
-      <c r="I5" s="2">
+      <c r="J5" s="2">
         <v>4047973265</v>
       </c>
-      <c r="J5" s="22" t="s">
+      <c r="K5" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="58" t="s">
+      <c r="L5" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="L5" s="44">
+      <c r="M5" s="44">
         <v>45635</v>
       </c>
-      <c r="M5" s="64" t="s">
+      <c r="N5" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="22">
+      <c r="O5" s="22">
         <v>99.25</v>
       </c>
-      <c r="O5" s="22">
+      <c r="P5" s="22">
         <v>99.97</v>
       </c>
-      <c r="P5" s="61">
+      <c r="Q5" s="61">
         <v>89</v>
       </c>
-      <c r="Q5" s="61">
-        <v>100</v>
-      </c>
-      <c r="R5" s="61"/>
+      <c r="R5" s="61">
+        <v>100</v>
+      </c>
       <c r="S5" s="61"/>
-      <c r="T5" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="U5" s="22">
-        <v>100</v>
-      </c>
-      <c r="V5" s="41"/>
-    </row>
-    <row r="6" spans="1:22" ht="36.75" customHeight="1">
+      <c r="T5" s="61"/>
+      <c r="U5" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="V5" s="22">
+        <v>100</v>
+      </c>
+      <c r="W5" s="41"/>
+    </row>
+    <row r="6" spans="1:23" ht="36.75" customHeight="1">
       <c r="A6" s="42">
         <v>2024</v>
       </c>
@@ -2091,59 +2108,63 @@
       <c r="C6" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="37" t="s">
+      <c r="D6" s="42">
+        <f t="shared" si="0"/>
+        <v>1.8660000000000001</v>
+      </c>
+      <c r="E6" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="F6" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>2024053150037</v>
       </c>
-      <c r="G6" s="37" t="s">
+      <c r="H6" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <v>3945999620</v>
       </c>
-      <c r="I6" s="2">
+      <c r="J6" s="2">
         <v>3156799696</v>
       </c>
-      <c r="J6" s="22" t="s">
+      <c r="K6" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="58" t="s">
+      <c r="L6" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="L6" s="44">
+      <c r="M6" s="44">
         <v>45635</v>
       </c>
-      <c r="M6" s="64" t="s">
+      <c r="N6" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="N6" s="22">
+      <c r="O6" s="22">
         <v>99.9</v>
       </c>
-      <c r="O6" s="22">
-        <v>100</v>
-      </c>
       <c r="P6" s="22">
         <v>100</v>
       </c>
       <c r="Q6" s="22">
         <v>100</v>
       </c>
-      <c r="R6" s="61"/>
+      <c r="R6" s="22">
+        <v>100</v>
+      </c>
       <c r="S6" s="61"/>
-      <c r="T6" s="58" t="s">
+      <c r="T6" s="61"/>
+      <c r="U6" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="U6" s="22">
-        <v>100</v>
-      </c>
-      <c r="V6" s="41"/>
-    </row>
-    <row r="7" spans="1:22" ht="36.75" customHeight="1">
+      <c r="V6" s="22">
+        <v>100</v>
+      </c>
+      <c r="W6" s="41"/>
+    </row>
+    <row r="7" spans="1:23" ht="36.75" customHeight="1">
       <c r="A7" s="42">
         <v>2024</v>
       </c>
@@ -2153,63 +2174,67 @@
       <c r="C7" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="37" t="s">
+      <c r="D7" s="42">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E7" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="F7" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="38">
+      <c r="G7" s="38">
         <v>2024003050241</v>
       </c>
-      <c r="G7" s="37" t="s">
+      <c r="H7" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>4232130933.4000001</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>3385704746.4000001</v>
       </c>
-      <c r="J7" s="22" t="s">
+      <c r="K7" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K7" s="58" t="s">
+      <c r="L7" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="L7" s="24">
+      <c r="M7" s="24">
         <v>45636</v>
       </c>
-      <c r="M7" s="67">
+      <c r="N7" s="67">
         <v>46336</v>
       </c>
-      <c r="N7" s="22">
+      <c r="O7" s="22">
         <v>21.71</v>
       </c>
-      <c r="O7" s="22">
+      <c r="P7" s="22">
         <v>58.62</v>
       </c>
-      <c r="P7" s="61">
+      <c r="Q7" s="61">
         <v>25.22</v>
       </c>
-      <c r="Q7" s="63">
+      <c r="R7" s="63">
         <v>60</v>
       </c>
-      <c r="R7" s="63">
+      <c r="S7" s="63">
         <v>27.22</v>
       </c>
-      <c r="S7" s="63">
+      <c r="T7" s="63">
         <v>60</v>
       </c>
-      <c r="T7" s="58">
-        <v>100</v>
-      </c>
-      <c r="U7" s="22">
+      <c r="U7" s="58">
+        <v>100</v>
+      </c>
+      <c r="V7" s="22">
         <v>35</v>
       </c>
-      <c r="V7" s="41"/>
-    </row>
-    <row r="8" spans="1:22" ht="36.75" customHeight="1">
+      <c r="W7" s="41"/>
+    </row>
+    <row r="8" spans="1:23" ht="36.75" customHeight="1">
       <c r="A8" s="42">
         <v>2024</v>
       </c>
@@ -2219,39 +2244,40 @@
       <c r="C8" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="D8" s="42">
+        <f t="shared" si="0"/>
+        <v>0.78200000000000003</v>
+      </c>
+      <c r="E8" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="37" t="s">
+      <c r="F8" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
         <v>2024051070040</v>
       </c>
-      <c r="G8" s="37" t="s">
+      <c r="H8" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="2">
         <v>1645755840</v>
       </c>
-      <c r="I8" s="2">
+      <c r="J8" s="2">
         <v>1316604672</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="K8" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="58" t="s">
+      <c r="L8" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="L8" s="44">
+      <c r="M8" s="44">
         <v>45636</v>
       </c>
-      <c r="M8" s="65">
+      <c r="N8" s="65">
         <v>45995</v>
       </c>
-      <c r="N8" s="22">
-        <v>100</v>
-      </c>
       <c r="O8" s="22">
         <v>100</v>
       </c>
@@ -2261,17 +2287,20 @@
       <c r="Q8" s="22">
         <v>100</v>
       </c>
-      <c r="R8" s="63"/>
+      <c r="R8" s="22">
+        <v>100</v>
+      </c>
       <c r="S8" s="63"/>
-      <c r="T8" s="58" t="s">
+      <c r="T8" s="63"/>
+      <c r="U8" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="U8" s="22">
-        <v>100</v>
-      </c>
-      <c r="V8" s="41"/>
-    </row>
-    <row r="9" spans="1:22" ht="36.75" customHeight="1">
+      <c r="V8" s="22">
+        <v>100</v>
+      </c>
+      <c r="W8" s="41"/>
+    </row>
+    <row r="9" spans="1:23" ht="36.75" customHeight="1">
       <c r="A9" s="42">
         <v>2024</v>
       </c>
@@ -2281,63 +2310,67 @@
       <c r="C9" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="D9" s="42">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E9" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="F9" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="38">
+      <c r="G9" s="38">
         <v>2024057560039</v>
       </c>
-      <c r="G9" s="37" t="s">
+      <c r="H9" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="H9" s="2">
+      <c r="I9" s="2">
         <v>4699883725</v>
       </c>
-      <c r="I9" s="2">
+      <c r="J9" s="2">
         <v>3759906980</v>
       </c>
-      <c r="J9" s="22" t="s">
+      <c r="K9" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K9" s="58" t="s">
+      <c r="L9" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="24">
+      <c r="M9" s="24">
         <v>45636</v>
       </c>
-      <c r="M9" s="66" t="s">
+      <c r="N9" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="N9" s="22">
+      <c r="O9" s="22">
         <v>90.52</v>
       </c>
-      <c r="O9" s="22">
+      <c r="P9" s="22">
         <v>85.38</v>
       </c>
-      <c r="P9" s="61">
+      <c r="Q9" s="61">
         <v>98.3</v>
       </c>
-      <c r="Q9" s="63">
+      <c r="R9" s="63">
         <v>89.2</v>
       </c>
-      <c r="R9" s="63">
+      <c r="S9" s="63">
         <v>98.3</v>
       </c>
-      <c r="S9" s="63">
+      <c r="T9" s="63">
         <v>89.64</v>
       </c>
-      <c r="T9" s="58">
-        <v>100</v>
-      </c>
-      <c r="U9" s="22">
-        <v>100</v>
-      </c>
-      <c r="V9" s="41"/>
-    </row>
-    <row r="10" spans="1:22" ht="36.75" customHeight="1">
+      <c r="U9" s="58">
+        <v>100</v>
+      </c>
+      <c r="V9" s="22">
+        <v>100</v>
+      </c>
+      <c r="W9" s="41"/>
+    </row>
+    <row r="10" spans="1:23" ht="36.75" customHeight="1">
       <c r="A10" s="42">
         <v>2024</v>
       </c>
@@ -2347,63 +2380,67 @@
       <c r="C10" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="D10" s="42">
+        <f t="shared" si="0"/>
+        <v>1.3</v>
+      </c>
+      <c r="E10" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="F10" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="38">
+      <c r="G10" s="38">
         <v>2024057890040</v>
       </c>
-      <c r="G10" s="37" t="s">
+      <c r="H10" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="H10" s="2">
+      <c r="I10" s="2">
         <v>3035607509</v>
       </c>
-      <c r="I10" s="2">
+      <c r="J10" s="2">
         <v>2428486007.1999998</v>
       </c>
-      <c r="J10" s="22" t="s">
+      <c r="K10" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="58" t="s">
+      <c r="L10" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="L10" s="44">
+      <c r="M10" s="44">
         <v>45628</v>
       </c>
-      <c r="M10" s="66" t="s">
+      <c r="N10" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="N10" s="22">
+      <c r="O10" s="22">
         <v>98.69</v>
       </c>
-      <c r="O10" s="22">
-        <v>100</v>
-      </c>
-      <c r="P10" s="61">
+      <c r="P10" s="22">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="61">
         <v>98.69</v>
       </c>
-      <c r="Q10" s="63">
-        <v>100</v>
-      </c>
       <c r="R10" s="63">
+        <v>100</v>
+      </c>
+      <c r="S10" s="63">
         <v>98.69</v>
       </c>
-      <c r="S10" s="63">
-        <v>100</v>
-      </c>
-      <c r="T10" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="U10" s="22">
-        <v>100</v>
-      </c>
-      <c r="V10" s="41"/>
-    </row>
-    <row r="11" spans="1:22" ht="36.75" customHeight="1">
+      <c r="T10" s="63">
+        <v>100</v>
+      </c>
+      <c r="U10" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="V10" s="22">
+        <v>100</v>
+      </c>
+      <c r="W10" s="41"/>
+    </row>
+    <row r="11" spans="1:23" ht="36.75" customHeight="1">
       <c r="A11" s="42">
         <v>2024</v>
       </c>
@@ -2413,63 +2450,67 @@
       <c r="C11" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="37" t="s">
+      <c r="D11" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E11" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E11" s="37" t="s">
+      <c r="F11" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="38">
+      <c r="G11" s="38">
         <v>2024054830016</v>
       </c>
-      <c r="G11" s="37" t="s">
+      <c r="H11" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="H11" s="2">
+      <c r="I11" s="2">
         <v>2596905323</v>
       </c>
-      <c r="I11" s="2">
+      <c r="J11" s="2">
         <v>2077524258</v>
       </c>
-      <c r="J11" s="22" t="s">
+      <c r="K11" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="58" t="s">
+      <c r="L11" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="L11" s="44">
+      <c r="M11" s="44">
         <v>45636</v>
       </c>
-      <c r="M11" s="67">
+      <c r="N11" s="67">
         <v>45940</v>
       </c>
-      <c r="N11" s="22">
-        <v>100</v>
-      </c>
       <c r="O11" s="22">
+        <v>100</v>
+      </c>
+      <c r="P11" s="22">
         <v>89.24</v>
       </c>
-      <c r="P11" s="61">
+      <c r="Q11" s="61">
         <v>71</v>
       </c>
-      <c r="Q11" s="61">
+      <c r="R11" s="61">
         <v>90</v>
       </c>
-      <c r="R11" s="61">
-        <v>100</v>
-      </c>
       <c r="S11" s="61">
+        <v>100</v>
+      </c>
+      <c r="T11" s="61">
         <v>98.41</v>
       </c>
-      <c r="T11" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="U11" s="22">
-        <v>100</v>
-      </c>
-      <c r="V11" s="41"/>
-    </row>
-    <row r="12" spans="1:22" ht="36.75" customHeight="1">
+      <c r="U11" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="V11" s="22">
+        <v>100</v>
+      </c>
+      <c r="W11" s="41"/>
+    </row>
+    <row r="12" spans="1:23" ht="36.75" customHeight="1">
       <c r="A12" s="42">
         <v>2024</v>
       </c>
@@ -2479,63 +2520,67 @@
       <c r="C12" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="37" t="s">
+      <c r="D12" s="42">
+        <f t="shared" si="0"/>
+        <v>0.95</v>
+      </c>
+      <c r="E12" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="37" t="s">
+      <c r="F12" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="38">
+      <c r="G12" s="38">
         <v>2024003050236</v>
       </c>
-      <c r="G12" s="37" t="s">
+      <c r="H12" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="H12" s="2">
+      <c r="I12" s="2">
         <v>1513619665</v>
       </c>
-      <c r="I12" s="2">
+      <c r="J12" s="2">
         <v>1210895732</v>
       </c>
-      <c r="J12" s="22" t="s">
+      <c r="K12" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K12" s="58" t="s">
+      <c r="L12" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="L12" s="44">
+      <c r="M12" s="44">
         <v>45618</v>
       </c>
-      <c r="M12" s="67">
+      <c r="N12" s="67">
         <v>45501</v>
       </c>
-      <c r="N12" s="22">
-        <v>100</v>
-      </c>
       <c r="O12" s="22">
+        <v>100</v>
+      </c>
+      <c r="P12" s="22">
         <v>62.65</v>
       </c>
-      <c r="P12" s="61">
+      <c r="Q12" s="61">
         <v>100.01</v>
       </c>
-      <c r="Q12" s="63">
+      <c r="R12" s="63">
         <v>62.65</v>
       </c>
-      <c r="R12" s="63">
+      <c r="S12" s="63">
         <v>100.01</v>
       </c>
-      <c r="S12" s="63">
+      <c r="T12" s="63">
         <v>62.65</v>
       </c>
-      <c r="T12" s="58">
+      <c r="U12" s="58">
         <v>90</v>
       </c>
-      <c r="U12" s="23">
-        <v>100</v>
-      </c>
-      <c r="V12" s="41"/>
-    </row>
-    <row r="13" spans="1:22" ht="36.75" customHeight="1">
+      <c r="V12" s="23">
+        <v>100</v>
+      </c>
+      <c r="W12" s="41"/>
+    </row>
+    <row r="13" spans="1:23" ht="36.75" customHeight="1">
       <c r="A13" s="42">
         <v>2024</v>
       </c>
@@ -2545,59 +2590,63 @@
       <c r="C13" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="37" t="s">
+      <c r="D13" s="42">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E13" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="37" t="s">
+      <c r="F13" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="38">
+      <c r="G13" s="38">
         <v>2024003050238</v>
       </c>
-      <c r="G13" s="37" t="s">
+      <c r="H13" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="H13" s="2">
+      <c r="I13" s="2">
         <v>4622246270</v>
       </c>
-      <c r="I13" s="2">
+      <c r="J13" s="2">
         <v>3697797016</v>
       </c>
-      <c r="J13" s="22" t="s">
+      <c r="K13" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K13" s="58" t="s">
+      <c r="L13" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="L13" s="44">
+      <c r="M13" s="44">
         <v>45635</v>
       </c>
-      <c r="M13" s="64" t="s">
+      <c r="N13" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="N13" s="22">
+      <c r="O13" s="22">
         <v>90.22</v>
       </c>
-      <c r="O13" s="22">
-        <v>100</v>
-      </c>
       <c r="P13" s="22">
         <v>100</v>
       </c>
       <c r="Q13" s="22">
         <v>100</v>
       </c>
-      <c r="R13" s="61"/>
+      <c r="R13" s="22">
+        <v>100</v>
+      </c>
       <c r="S13" s="61"/>
-      <c r="T13" s="58" t="s">
+      <c r="T13" s="61"/>
+      <c r="U13" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="U13" s="22">
-        <v>100</v>
-      </c>
-      <c r="V13" s="41"/>
-    </row>
-    <row r="14" spans="1:22" ht="36.75" customHeight="1">
+      <c r="V13" s="22">
+        <v>100</v>
+      </c>
+      <c r="W13" s="41"/>
+    </row>
+    <row r="14" spans="1:23" ht="36.75" customHeight="1">
       <c r="A14" s="46">
         <v>2024</v>
       </c>
@@ -2607,63 +2656,67 @@
       <c r="C14" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E14" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="37" t="s">
+      <c r="F14" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="38">
+      <c r="G14" s="38">
         <v>2024003050244</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="H14" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2177618498</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1742094798.4000001</v>
       </c>
-      <c r="J14" s="23" t="s">
+      <c r="K14" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="58" t="s">
+      <c r="L14" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="L14" s="24">
+      <c r="M14" s="24">
         <v>45636</v>
       </c>
-      <c r="M14" s="66" t="s">
+      <c r="N14" s="66" t="s">
         <v>69</v>
       </c>
-      <c r="N14" s="26">
+      <c r="O14" s="26">
         <v>0</v>
       </c>
-      <c r="O14" s="26">
+      <c r="P14" s="26">
         <v>120</v>
       </c>
-      <c r="P14" s="61">
+      <c r="Q14" s="61">
         <v>0</v>
       </c>
-      <c r="Q14" s="61">
+      <c r="R14" s="61">
         <v>120.38</v>
       </c>
-      <c r="R14" s="61">
+      <c r="S14" s="61">
         <v>0</v>
       </c>
-      <c r="S14" s="61">
+      <c r="T14" s="61">
         <v>120.38</v>
       </c>
-      <c r="T14" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="U14" s="23">
-        <v>100</v>
-      </c>
-      <c r="V14" s="41"/>
-    </row>
-    <row r="15" spans="1:22" ht="36.75" customHeight="1">
+      <c r="U14" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="V14" s="23">
+        <v>100</v>
+      </c>
+      <c r="W14" s="41"/>
+    </row>
+    <row r="15" spans="1:23" ht="36.75" customHeight="1">
       <c r="A15" s="42">
         <v>2024</v>
       </c>
@@ -2673,59 +2726,63 @@
       <c r="C15" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="37" t="s">
+      <c r="D15" s="42">
+        <f t="shared" si="0"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E15" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="F15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="1">
+      <c r="G15" s="1">
         <v>2024003050242</v>
       </c>
-      <c r="G15" s="37" t="s">
+      <c r="H15" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="H15" s="2">
+      <c r="I15" s="2">
         <v>2688840891</v>
       </c>
-      <c r="I15" s="2">
+      <c r="J15" s="2">
         <v>2151072713</v>
       </c>
-      <c r="J15" s="22" t="s">
+      <c r="K15" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K15" s="58" t="s">
+      <c r="L15" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="L15" s="44">
+      <c r="M15" s="44">
         <v>45637</v>
       </c>
-      <c r="M15" s="65">
+      <c r="N15" s="65">
         <v>45698</v>
       </c>
-      <c r="N15" s="22">
-        <v>100</v>
-      </c>
       <c r="O15" s="22">
+        <v>100</v>
+      </c>
+      <c r="P15" s="22">
         <v>99.99</v>
       </c>
-      <c r="P15" s="22">
-        <v>100</v>
-      </c>
       <c r="Q15" s="22">
+        <v>100</v>
+      </c>
+      <c r="R15" s="22">
         <v>99.99</v>
       </c>
-      <c r="R15" s="61"/>
       <c r="S15" s="61"/>
-      <c r="T15" s="58" t="s">
+      <c r="T15" s="61"/>
+      <c r="U15" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="U15" s="22">
-        <v>100</v>
-      </c>
-      <c r="V15" s="41"/>
-    </row>
-    <row r="16" spans="1:22" ht="36.75" customHeight="1">
+      <c r="V15" s="22">
+        <v>100</v>
+      </c>
+      <c r="W15" s="41"/>
+    </row>
+    <row r="16" spans="1:23" ht="36.75" customHeight="1">
       <c r="A16" s="42">
         <v>2024</v>
       </c>
@@ -2735,63 +2792,67 @@
       <c r="C16" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="37" t="s">
+      <c r="D16" s="42">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="E16" s="37" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="37" t="s">
+      <c r="F16" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F16" s="38">
+      <c r="G16" s="38">
         <v>2024003050245</v>
       </c>
-      <c r="G16" s="37" t="s">
+      <c r="H16" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="H16" s="2">
+      <c r="I16" s="2">
         <v>6076769979</v>
       </c>
-      <c r="I16" s="2">
+      <c r="J16" s="2">
         <v>4861415983</v>
       </c>
-      <c r="J16" s="22" t="s">
+      <c r="K16" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K16" s="58" t="s">
+      <c r="L16" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="L16" s="24">
+      <c r="M16" s="24">
         <v>45635</v>
       </c>
-      <c r="M16" s="66" t="s">
+      <c r="N16" s="66" t="s">
         <v>76</v>
       </c>
-      <c r="N16" s="22">
+      <c r="O16" s="22">
         <v>71.45</v>
       </c>
-      <c r="O16" s="22">
+      <c r="P16" s="22">
         <v>59.95</v>
       </c>
-      <c r="P16" s="61">
+      <c r="Q16" s="61">
         <v>73.010000000000005</v>
       </c>
-      <c r="Q16" s="61">
+      <c r="R16" s="61">
         <v>59.95</v>
       </c>
-      <c r="R16" s="61">
+      <c r="S16" s="61">
         <v>76.13</v>
       </c>
-      <c r="S16" s="61">
+      <c r="T16" s="61">
         <v>83.52</v>
       </c>
-      <c r="T16" s="58">
-        <v>100</v>
-      </c>
-      <c r="U16" s="22">
+      <c r="U16" s="58">
+        <v>100</v>
+      </c>
+      <c r="V16" s="22">
         <v>81</v>
       </c>
-      <c r="V16" s="41"/>
-    </row>
-    <row r="17" spans="1:22" ht="36.75" customHeight="1">
+      <c r="W16" s="41"/>
+    </row>
+    <row r="17" spans="1:23" ht="36.75" customHeight="1">
       <c r="A17" s="42">
         <v>2024</v>
       </c>
@@ -2801,63 +2862,67 @@
       <c r="C17" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="37" t="s">
+      <c r="D17" s="42">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="E17" s="37" t="s">
         <v>74</v>
       </c>
-      <c r="E17" s="37" t="s">
+      <c r="F17" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="38">
+      <c r="G17" s="38">
         <v>2024003050237</v>
       </c>
-      <c r="G17" s="37" t="s">
+      <c r="H17" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="H17" s="2">
+      <c r="I17" s="2">
         <v>5449013721.6000004</v>
       </c>
-      <c r="I17" s="2">
+      <c r="J17" s="2">
         <v>4359210977.6000004</v>
       </c>
-      <c r="J17" s="22" t="s">
+      <c r="K17" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K17" s="58" t="s">
+      <c r="L17" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="L17" s="24">
+      <c r="M17" s="24">
         <v>45635</v>
       </c>
-      <c r="M17" s="67">
+      <c r="N17" s="67">
         <v>46083</v>
       </c>
-      <c r="N17" s="22">
-        <v>100</v>
-      </c>
       <c r="O17" s="22">
+        <v>100</v>
+      </c>
+      <c r="P17" s="22">
         <v>79.94</v>
       </c>
-      <c r="P17" s="61">
-        <v>100</v>
-      </c>
       <c r="Q17" s="61">
+        <v>100</v>
+      </c>
+      <c r="R17" s="61">
         <v>79.94</v>
       </c>
-      <c r="R17" s="61">
-        <v>100</v>
-      </c>
       <c r="S17" s="61">
+        <v>100</v>
+      </c>
+      <c r="T17" s="61">
         <v>79.94</v>
       </c>
-      <c r="T17" s="58">
+      <c r="U17" s="58">
         <v>90</v>
       </c>
-      <c r="U17" s="22">
-        <v>100</v>
-      </c>
-      <c r="V17" s="41"/>
-    </row>
-    <row r="18" spans="1:22" ht="36.75" customHeight="1">
+      <c r="V17" s="22">
+        <v>100</v>
+      </c>
+      <c r="W17" s="41"/>
+    </row>
+    <row r="18" spans="1:23" ht="36.75" customHeight="1">
       <c r="A18" s="42">
         <v>2024</v>
       </c>
@@ -2867,59 +2932,63 @@
       <c r="C18" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="37" t="s">
+      <c r="D18" s="42">
+        <f t="shared" si="0"/>
+        <v>1.5</v>
+      </c>
+      <c r="E18" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="E18" s="37" t="s">
+      <c r="F18" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="38">
+      <c r="G18" s="38">
         <v>2024051970041</v>
       </c>
-      <c r="G18" s="37" t="s">
+      <c r="H18" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="H18" s="2">
+      <c r="I18" s="2">
         <v>3445926513</v>
       </c>
-      <c r="I18" s="2">
+      <c r="J18" s="2">
         <v>2756741210</v>
       </c>
-      <c r="J18" s="22" t="s">
+      <c r="K18" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K18" s="58" t="s">
+      <c r="L18" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="L18" s="44">
+      <c r="M18" s="44">
         <v>45636</v>
       </c>
-      <c r="M18" s="65">
+      <c r="N18" s="65">
         <v>45908</v>
       </c>
-      <c r="N18" s="22">
+      <c r="O18" s="22">
         <v>96.56</v>
       </c>
-      <c r="O18" s="22">
+      <c r="P18" s="22">
         <v>99.99</v>
       </c>
-      <c r="P18" s="22">
-        <v>100</v>
-      </c>
       <c r="Q18" s="22">
+        <v>100</v>
+      </c>
+      <c r="R18" s="22">
         <v>99.99</v>
       </c>
-      <c r="R18" s="61"/>
       <c r="S18" s="61"/>
-      <c r="T18" s="58" t="s">
+      <c r="T18" s="61"/>
+      <c r="U18" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="U18" s="22">
-        <v>100</v>
-      </c>
-      <c r="V18" s="41"/>
-    </row>
-    <row r="19" spans="1:22" ht="36.75" customHeight="1">
+      <c r="V18" s="22">
+        <v>100</v>
+      </c>
+      <c r="W18" s="41"/>
+    </row>
+    <row r="19" spans="1:23" ht="36.75" customHeight="1">
       <c r="A19" s="42">
         <v>2025</v>
       </c>
@@ -2929,61 +2998,65 @@
       <c r="C19" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="37" t="s">
+      <c r="D19" s="42">
+        <f t="shared" si="0"/>
+        <v>3.5</v>
+      </c>
+      <c r="E19" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="E19" s="37" t="s">
+      <c r="F19" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="38">
+      <c r="G19" s="38">
         <v>2025003050003</v>
       </c>
-      <c r="G19" s="37" t="s">
+      <c r="H19" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="H19" s="2">
+      <c r="I19" s="2">
         <v>5581655075</v>
       </c>
-      <c r="I19" s="49">
+      <c r="J19" s="49">
         <v>4519742225</v>
       </c>
-      <c r="J19" s="22" t="s">
+      <c r="K19" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K19" s="58" t="s">
+      <c r="L19" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="L19" s="24">
+      <c r="M19" s="24">
         <v>45768</v>
       </c>
-      <c r="M19" s="66" t="s">
+      <c r="N19" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="N19" s="23">
+      <c r="O19" s="23">
         <v>97</v>
       </c>
-      <c r="O19" s="23">
+      <c r="P19" s="23">
         <v>61</v>
       </c>
-      <c r="P19" s="61">
+      <c r="Q19" s="61">
         <v>97.04</v>
       </c>
-      <c r="Q19" s="61">
+      <c r="R19" s="61">
         <v>60.54</v>
       </c>
-      <c r="R19" s="61">
+      <c r="S19" s="61">
         <v>97.04</v>
       </c>
-      <c r="S19" s="61">
+      <c r="T19" s="61">
         <v>60.54</v>
       </c>
-      <c r="T19" s="58">
+      <c r="U19" s="58">
         <v>77</v>
       </c>
-      <c r="U19" s="23"/>
-      <c r="V19" s="41"/>
-    </row>
-    <row r="20" spans="1:22" ht="36.75" customHeight="1">
+      <c r="V19" s="23"/>
+      <c r="W19" s="41"/>
+    </row>
+    <row r="20" spans="1:23" ht="36.75" customHeight="1">
       <c r="A20" s="42">
         <v>2025</v>
       </c>
@@ -2993,43 +3066,44 @@
       <c r="C20" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="37" t="s">
+      <c r="D20" s="42">
+        <f t="shared" si="0"/>
+        <v>1.2</v>
+      </c>
+      <c r="E20" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="E20" s="37" t="s">
+      <c r="F20" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="38">
+      <c r="G20" s="38">
         <v>2025003050008</v>
       </c>
-      <c r="G20" s="37" t="s">
+      <c r="H20" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="H20" s="2">
+      <c r="I20" s="2">
         <v>2661301361.5999999</v>
       </c>
-      <c r="I20" s="49">
+      <c r="J20" s="49">
         <v>2129041089.5999999</v>
       </c>
-      <c r="J20" s="22" t="s">
+      <c r="K20" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K20" s="58" t="s">
+      <c r="L20" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="L20" s="44">
+      <c r="M20" s="44">
         <v>45818</v>
       </c>
-      <c r="M20" s="66" t="s">
+      <c r="N20" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="N20" s="45">
-        <v>100</v>
-      </c>
       <c r="O20" s="45">
         <v>100</v>
       </c>
-      <c r="P20" s="61">
+      <c r="P20" s="45">
         <v>100</v>
       </c>
       <c r="Q20" s="61">
@@ -3041,15 +3115,18 @@
       <c r="S20" s="61">
         <v>100</v>
       </c>
-      <c r="T20" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="U20" s="45">
-        <v>100</v>
-      </c>
-      <c r="V20" s="41"/>
-    </row>
-    <row r="21" spans="1:22" ht="36.75" customHeight="1">
+      <c r="T20" s="61">
+        <v>100</v>
+      </c>
+      <c r="U20" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="V20" s="45">
+        <v>100</v>
+      </c>
+      <c r="W20" s="41"/>
+    </row>
+    <row r="21" spans="1:23" ht="36.75" hidden="1" customHeight="1">
       <c r="A21" s="42">
         <v>2025</v>
       </c>
@@ -3059,61 +3136,65 @@
       <c r="C21" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="37" t="s">
+      <c r="D21" s="42">
+        <f t="shared" si="0"/>
+        <v>6.9</v>
+      </c>
+      <c r="E21" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="E21" s="37" t="s">
+      <c r="F21" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="F21" s="38">
+      <c r="G21" s="38">
         <v>2025003050002</v>
       </c>
-      <c r="G21" s="37" t="s">
+      <c r="H21" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="H21" s="2">
+      <c r="I21" s="2">
         <v>24272420632</v>
       </c>
-      <c r="I21" s="49">
+      <c r="J21" s="49">
         <v>24272420632</v>
       </c>
-      <c r="J21" s="22" t="s">
+      <c r="K21" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="K21" s="58" t="s">
+      <c r="L21" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="L21" s="24">
+      <c r="M21" s="24">
         <v>45805</v>
       </c>
-      <c r="M21" s="66" t="s">
+      <c r="N21" s="66" t="s">
         <v>94</v>
       </c>
-      <c r="N21" s="22">
+      <c r="O21" s="22">
         <v>7.59</v>
       </c>
-      <c r="O21" s="22">
+      <c r="P21" s="22">
         <v>3</v>
       </c>
-      <c r="P21" s="61">
+      <c r="Q21" s="61">
         <v>13.08</v>
       </c>
-      <c r="Q21" s="61">
+      <c r="R21" s="61">
         <v>7.59</v>
-      </c>
-      <c r="R21" s="61">
-        <v>21.74</v>
       </c>
       <c r="S21" s="61">
         <v>21.74</v>
       </c>
-      <c r="T21" s="58">
-        <v>100</v>
-      </c>
-      <c r="U21" s="23"/>
-      <c r="V21" s="41"/>
-    </row>
-    <row r="22" spans="1:22" ht="36.75" customHeight="1">
+      <c r="T21" s="61">
+        <v>21.74</v>
+      </c>
+      <c r="U21" s="58">
+        <v>100</v>
+      </c>
+      <c r="V21" s="23"/>
+      <c r="W21" s="41"/>
+    </row>
+    <row r="22" spans="1:23" ht="36.75" hidden="1" customHeight="1">
       <c r="A22" s="42">
         <v>2025</v>
       </c>
@@ -3123,61 +3204,65 @@
       <c r="C22" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="37" t="s">
+      <c r="D22" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E22" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="E22" s="37" t="s">
+      <c r="F22" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="F22" s="48">
+      <c r="G22" s="48">
         <v>2025003050005</v>
       </c>
-      <c r="G22" s="37" t="s">
+      <c r="H22" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="H22" s="2">
+      <c r="I22" s="2">
         <v>13746524997</v>
       </c>
-      <c r="I22" s="49">
+      <c r="J22" s="49">
         <v>12746524997</v>
       </c>
-      <c r="J22" s="50" t="s">
+      <c r="K22" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K22" s="58" t="s">
+      <c r="L22" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="L22" s="24">
+      <c r="M22" s="24">
         <v>45811</v>
       </c>
-      <c r="M22" s="66" t="s">
+      <c r="N22" s="66" t="s">
         <v>99</v>
       </c>
-      <c r="N22" s="23">
+      <c r="O22" s="23">
         <v>75.34</v>
       </c>
-      <c r="O22" s="23">
+      <c r="P22" s="23">
         <v>66.150000000000006</v>
       </c>
-      <c r="P22" s="61">
+      <c r="Q22" s="61">
         <v>80.459999999999994</v>
       </c>
-      <c r="Q22" s="61">
+      <c r="R22" s="61">
         <v>84.53</v>
       </c>
-      <c r="R22" s="61">
+      <c r="S22" s="61">
         <v>86.13</v>
       </c>
-      <c r="S22" s="61">
+      <c r="T22" s="61">
         <v>88.5</v>
       </c>
-      <c r="T22" s="58">
+      <c r="U22" s="58">
         <v>90</v>
       </c>
-      <c r="U22" s="45"/>
-      <c r="V22" s="41"/>
-    </row>
-    <row r="23" spans="1:22" ht="36.75" customHeight="1">
+      <c r="V22" s="45"/>
+      <c r="W22" s="41"/>
+    </row>
+    <row r="23" spans="1:23" ht="36.75" customHeight="1">
       <c r="A23" s="42">
         <v>2025</v>
       </c>
@@ -3187,63 +3272,67 @@
       <c r="C23" s="42" t="s">
         <v>101</v>
       </c>
-      <c r="D23" s="37" t="s">
+      <c r="D23" s="42">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E23" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="E23" s="37" t="s">
+      <c r="F23" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="38">
+      <c r="G23" s="38">
         <v>2025003050011</v>
       </c>
-      <c r="G23" s="37" t="s">
+      <c r="H23" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="H23" s="2">
+      <c r="I23" s="2">
         <v>4237507648</v>
       </c>
-      <c r="I23" s="49">
+      <c r="J23" s="49">
         <v>3390006119</v>
       </c>
-      <c r="J23" s="22" t="s">
+      <c r="K23" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K23" s="59" t="s">
+      <c r="L23" s="59" t="s">
         <v>103</v>
       </c>
-      <c r="L23" s="44">
+      <c r="M23" s="44">
         <v>45813</v>
       </c>
-      <c r="M23" s="66" t="s">
+      <c r="N23" s="66" t="s">
         <v>104</v>
       </c>
-      <c r="N23" s="45">
+      <c r="O23" s="45">
         <v>99.95</v>
       </c>
-      <c r="O23" s="45">
+      <c r="P23" s="45">
         <v>99.92</v>
       </c>
-      <c r="P23" s="61">
+      <c r="Q23" s="61">
         <v>99.95</v>
       </c>
-      <c r="Q23" s="61">
-        <v>100</v>
-      </c>
       <c r="R23" s="61">
+        <v>100</v>
+      </c>
+      <c r="S23" s="61">
         <v>99.95</v>
       </c>
-      <c r="S23" s="61">
-        <v>100</v>
-      </c>
-      <c r="T23" s="58">
+      <c r="T23" s="61">
+        <v>100</v>
+      </c>
+      <c r="U23" s="58">
         <v>89</v>
       </c>
-      <c r="U23" s="45">
-        <v>100</v>
-      </c>
-      <c r="V23" s="41"/>
-    </row>
-    <row r="24" spans="1:22" ht="36.75" customHeight="1">
+      <c r="V23" s="45">
+        <v>100</v>
+      </c>
+      <c r="W23" s="41"/>
+    </row>
+    <row r="24" spans="1:23" ht="36.75" customHeight="1">
       <c r="A24" s="42">
         <v>2025</v>
       </c>
@@ -3253,59 +3342,63 @@
       <c r="C24" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="37" t="s">
+      <c r="D24" s="42">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+      <c r="E24" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="E24" s="37" t="s">
+      <c r="F24" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F24" s="36">
+      <c r="G24" s="36">
         <v>2025003050014</v>
       </c>
-      <c r="G24" s="37" t="s">
+      <c r="H24" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="H24" s="2">
+      <c r="I24" s="2">
         <v>1811206529</v>
       </c>
-      <c r="I24" s="49">
+      <c r="J24" s="49">
         <v>1448965223</v>
       </c>
-      <c r="J24" s="22" t="s">
+      <c r="K24" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K24" s="58" t="s">
+      <c r="L24" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="L24" s="44">
+      <c r="M24" s="44">
         <v>45825</v>
       </c>
-      <c r="M24" s="64" t="s">
+      <c r="N24" s="64" t="s">
         <v>108</v>
       </c>
-      <c r="N24" s="45">
-        <v>100</v>
-      </c>
       <c r="O24" s="45">
         <v>100</v>
       </c>
-      <c r="P24" s="61">
-        <v>100</v>
-      </c>
-      <c r="Q24" s="63">
-        <v>100</v>
-      </c>
-      <c r="R24" s="63"/>
+      <c r="P24" s="45">
+        <v>100</v>
+      </c>
+      <c r="Q24" s="61">
+        <v>100</v>
+      </c>
+      <c r="R24" s="63">
+        <v>100</v>
+      </c>
       <c r="S24" s="63"/>
-      <c r="T24" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="U24" s="45">
-        <v>100</v>
-      </c>
-      <c r="V24" s="41"/>
-    </row>
-    <row r="25" spans="1:22" ht="36.75" customHeight="1">
+      <c r="T24" s="63"/>
+      <c r="U24" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="V24" s="45">
+        <v>100</v>
+      </c>
+      <c r="W24" s="41"/>
+    </row>
+    <row r="25" spans="1:23" ht="36.75" customHeight="1">
       <c r="A25" s="42">
         <v>2025</v>
       </c>
@@ -3315,61 +3408,65 @@
       <c r="C25" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="D25" s="37" t="s">
+      <c r="D25" s="42">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E25" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="E25" s="37" t="s">
+      <c r="F25" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F25" s="38">
+      <c r="G25" s="38">
         <v>2025003050012</v>
       </c>
-      <c r="G25" s="37" t="s">
+      <c r="H25" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="H25" s="2">
+      <c r="I25" s="2">
         <v>4812305821</v>
       </c>
-      <c r="I25" s="49">
+      <c r="J25" s="49">
         <v>3849844657</v>
       </c>
-      <c r="J25" s="22" t="s">
+      <c r="K25" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K25" s="58" t="s">
+      <c r="L25" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="L25" s="24">
+      <c r="M25" s="24">
         <v>45826</v>
       </c>
-      <c r="M25" s="66" t="s">
+      <c r="N25" s="66" t="s">
         <v>111</v>
       </c>
-      <c r="N25" s="23">
+      <c r="O25" s="23">
         <v>0</v>
       </c>
-      <c r="O25" s="23">
+      <c r="P25" s="23">
         <v>56.54</v>
       </c>
-      <c r="P25" s="61">
+      <c r="Q25" s="61">
         <v>64.739999999999995</v>
       </c>
-      <c r="Q25" s="61">
+      <c r="R25" s="61">
         <v>22.45</v>
       </c>
-      <c r="R25" s="61">
+      <c r="S25" s="61">
         <v>87.62</v>
       </c>
-      <c r="S25" s="61">
+      <c r="T25" s="61">
         <v>22.45</v>
       </c>
-      <c r="T25" s="58">
+      <c r="U25" s="58">
         <v>97.2</v>
       </c>
-      <c r="U25" s="23"/>
-      <c r="V25" s="41"/>
-    </row>
-    <row r="26" spans="1:22" ht="36.75" customHeight="1">
+      <c r="V25" s="23"/>
+      <c r="W25" s="41"/>
+    </row>
+    <row r="26" spans="1:23" ht="36.75" customHeight="1">
       <c r="A26" s="42">
         <v>2025</v>
       </c>
@@ -3379,39 +3476,40 @@
       <c r="C26" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="D26" s="37" t="s">
+      <c r="D26" s="42">
+        <f t="shared" si="0"/>
+        <v>1.9</v>
+      </c>
+      <c r="E26" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="E26" s="37" t="s">
+      <c r="F26" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F26" s="36">
+      <c r="G26" s="36">
         <v>2025003050015</v>
       </c>
-      <c r="G26" s="37" t="s">
+      <c r="H26" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="H26" s="2">
+      <c r="I26" s="2">
         <v>4294044919</v>
       </c>
-      <c r="I26" s="49">
+      <c r="J26" s="49">
         <v>3435235935.1999998</v>
       </c>
-      <c r="J26" s="22" t="s">
+      <c r="K26" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K26" s="58" t="s">
+      <c r="L26" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="L26" s="44">
+      <c r="M26" s="44">
         <v>45824</v>
       </c>
-      <c r="M26" s="64" t="s">
+      <c r="N26" s="64" t="s">
         <v>115</v>
       </c>
-      <c r="N26" s="45">
-        <v>100</v>
-      </c>
       <c r="O26" s="45">
         <v>100</v>
       </c>
@@ -3421,17 +3519,20 @@
       <c r="Q26" s="45">
         <v>100</v>
       </c>
-      <c r="R26" s="63"/>
+      <c r="R26" s="45">
+        <v>100</v>
+      </c>
       <c r="S26" s="63"/>
-      <c r="T26" s="58" t="s">
+      <c r="T26" s="63"/>
+      <c r="U26" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="U26" s="22">
-        <v>100</v>
-      </c>
-      <c r="V26" s="41"/>
-    </row>
-    <row r="27" spans="1:22" ht="36.75" customHeight="1">
+      <c r="V26" s="22">
+        <v>100</v>
+      </c>
+      <c r="W26" s="41"/>
+    </row>
+    <row r="27" spans="1:23" ht="36.75" customHeight="1">
       <c r="A27" s="42">
         <v>2025</v>
       </c>
@@ -3441,63 +3542,67 @@
       <c r="C27" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="D27" s="37" t="s">
+      <c r="D27" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E27" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E27" s="37" t="s">
+      <c r="F27" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F27" s="48">
+      <c r="G27" s="48">
         <v>2025003050013</v>
       </c>
-      <c r="G27" s="37" t="s">
+      <c r="H27" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="H27" s="2">
+      <c r="I27" s="2">
         <v>1999756329</v>
       </c>
-      <c r="I27" s="43">
+      <c r="J27" s="43">
         <v>1599805063</v>
       </c>
-      <c r="J27" s="50" t="s">
+      <c r="K27" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K27" s="58" t="s">
+      <c r="L27" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="L27" s="24">
+      <c r="M27" s="24">
         <v>45853</v>
       </c>
-      <c r="M27" s="66" t="s">
+      <c r="N27" s="66" t="s">
         <v>119</v>
       </c>
-      <c r="N27" s="23">
-        <v>100</v>
-      </c>
       <c r="O27" s="23">
+        <v>100</v>
+      </c>
+      <c r="P27" s="23">
         <v>76.47</v>
       </c>
-      <c r="P27" s="61">
-        <v>100</v>
-      </c>
       <c r="Q27" s="61">
+        <v>100</v>
+      </c>
+      <c r="R27" s="61">
         <v>80</v>
       </c>
-      <c r="R27" s="61">
-        <v>100</v>
-      </c>
       <c r="S27" s="61">
+        <v>100</v>
+      </c>
+      <c r="T27" s="61">
         <v>80</v>
       </c>
-      <c r="T27" s="58">
+      <c r="U27" s="58">
         <v>90</v>
       </c>
-      <c r="U27" s="45">
-        <v>100</v>
-      </c>
-      <c r="V27" s="41"/>
-    </row>
-    <row r="28" spans="1:22" ht="36.75" customHeight="1">
+      <c r="V27" s="45">
+        <v>100</v>
+      </c>
+      <c r="W27" s="41"/>
+    </row>
+    <row r="28" spans="1:23" ht="36.75" customHeight="1">
       <c r="A28" s="42">
         <v>2025</v>
       </c>
@@ -3507,61 +3612,65 @@
       <c r="C28" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="D28" s="37" t="s">
+      <c r="D28" s="42">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E28" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="E28" s="37" t="s">
+      <c r="F28" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F28" s="48">
+      <c r="G28" s="48">
         <v>2025003050022</v>
       </c>
-      <c r="G28" s="37" t="s">
+      <c r="H28" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="H28" s="2">
+      <c r="I28" s="2">
         <v>4833319756</v>
       </c>
-      <c r="I28" s="43">
+      <c r="J28" s="43">
         <v>3866655805</v>
       </c>
-      <c r="J28" s="50" t="s">
+      <c r="K28" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K28" s="58" t="s">
+      <c r="L28" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="L28" s="24">
+      <c r="M28" s="24">
         <v>45874</v>
       </c>
-      <c r="M28" s="66" t="s">
+      <c r="N28" s="66" t="s">
         <v>122</v>
       </c>
-      <c r="N28" s="45">
+      <c r="O28" s="45">
         <v>45.38</v>
       </c>
-      <c r="O28" s="45">
+      <c r="P28" s="45">
         <v>36.26</v>
       </c>
-      <c r="P28" s="61">
+      <c r="Q28" s="61">
         <v>45.38</v>
       </c>
-      <c r="Q28" s="61">
+      <c r="R28" s="61">
         <v>36.26</v>
       </c>
-      <c r="R28" s="61">
+      <c r="S28" s="61">
         <v>63.55</v>
       </c>
-      <c r="S28" s="61">
+      <c r="T28" s="61">
         <v>36.26</v>
       </c>
-      <c r="T28" s="58">
+      <c r="U28" s="58">
         <v>98.4</v>
       </c>
-      <c r="U28" s="45"/>
-      <c r="V28" s="41"/>
-    </row>
-    <row r="29" spans="1:22" ht="36.75" customHeight="1">
+      <c r="V28" s="45"/>
+      <c r="W28" s="41"/>
+    </row>
+    <row r="29" spans="1:23" ht="36.75" hidden="1" customHeight="1">
       <c r="A29" s="42">
         <v>2025</v>
       </c>
@@ -3571,63 +3680,67 @@
       <c r="C29" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="D29" s="37" t="s">
+      <c r="D29" s="42">
+        <f t="shared" si="0"/>
+        <v>1.95</v>
+      </c>
+      <c r="E29" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="E29" s="37" t="s">
+      <c r="F29" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="F29" s="48">
+      <c r="G29" s="48">
         <v>2025003050017</v>
       </c>
-      <c r="G29" s="37" t="s">
+      <c r="H29" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="H29" s="2">
+      <c r="I29" s="2">
         <v>5922191430</v>
       </c>
-      <c r="I29" s="43">
+      <c r="J29" s="43">
         <v>4922191430</v>
       </c>
-      <c r="J29" s="50" t="s">
+      <c r="K29" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K29" s="58" t="s">
+      <c r="L29" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="L29" s="24">
+      <c r="M29" s="24">
         <v>45854</v>
       </c>
-      <c r="M29" s="66" t="s">
+      <c r="N29" s="66" t="s">
         <v>127</v>
       </c>
-      <c r="N29" s="23">
+      <c r="O29" s="23">
         <v>97.87</v>
       </c>
-      <c r="O29" s="23">
+      <c r="P29" s="23">
         <v>90.17</v>
       </c>
-      <c r="P29" s="61">
+      <c r="Q29" s="61">
         <v>97.87</v>
       </c>
-      <c r="Q29" s="61">
+      <c r="R29" s="61">
         <v>90.17</v>
       </c>
-      <c r="R29" s="61">
+      <c r="S29" s="61">
         <v>97.87</v>
       </c>
-      <c r="S29" s="61">
+      <c r="T29" s="61">
         <v>90.17</v>
       </c>
-      <c r="T29" s="58">
+      <c r="U29" s="58">
         <v>77</v>
       </c>
-      <c r="U29" s="45">
-        <v>100</v>
-      </c>
-      <c r="V29" s="41"/>
-    </row>
-    <row r="30" spans="1:22" ht="36.75" customHeight="1">
+      <c r="V29" s="45">
+        <v>100</v>
+      </c>
+      <c r="W29" s="41"/>
+    </row>
+    <row r="30" spans="1:23" ht="36.75" customHeight="1">
       <c r="A30" s="42">
         <v>2025</v>
       </c>
@@ -3637,61 +3750,65 @@
       <c r="C30" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="37" t="s">
+      <c r="D30" s="42">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E30" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="E30" s="37" t="s">
+      <c r="F30" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F30" s="48">
+      <c r="G30" s="48">
         <v>2025003050020</v>
       </c>
-      <c r="G30" s="37" t="s">
+      <c r="H30" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="H30" s="2">
+      <c r="I30" s="2">
         <v>4797586284</v>
       </c>
-      <c r="I30" s="43">
+      <c r="J30" s="43">
         <v>3838069027</v>
       </c>
-      <c r="J30" s="50" t="s">
+      <c r="K30" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K30" s="58" t="s">
+      <c r="L30" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="L30" s="24">
+      <c r="M30" s="24">
         <v>45874</v>
       </c>
-      <c r="M30" s="66" t="s">
+      <c r="N30" s="66" t="s">
         <v>130</v>
       </c>
-      <c r="N30" s="45">
+      <c r="O30" s="45">
         <v>95.44</v>
       </c>
-      <c r="O30" s="45">
+      <c r="P30" s="45">
         <v>60.59</v>
       </c>
-      <c r="P30" s="61">
+      <c r="Q30" s="61">
         <v>95.93</v>
       </c>
-      <c r="Q30" s="61">
+      <c r="R30" s="61">
         <v>71.73</v>
       </c>
-      <c r="R30" s="61">
+      <c r="S30" s="61">
         <v>96.3</v>
       </c>
-      <c r="S30" s="61">
+      <c r="T30" s="61">
         <v>71.73</v>
       </c>
-      <c r="T30" s="58">
-        <v>100</v>
-      </c>
-      <c r="U30" s="45"/>
-      <c r="V30" s="41"/>
-    </row>
-    <row r="31" spans="1:22" ht="36.75" customHeight="1">
+      <c r="U30" s="58">
+        <v>100</v>
+      </c>
+      <c r="V30" s="45"/>
+      <c r="W30" s="41"/>
+    </row>
+    <row r="31" spans="1:23" ht="36.75" customHeight="1">
       <c r="A31" s="42">
         <v>2025</v>
       </c>
@@ -3701,63 +3818,67 @@
       <c r="C31" s="42" t="s">
         <v>132</v>
       </c>
-      <c r="D31" s="37" t="s">
+      <c r="D31" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E31" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E31" s="37" t="s">
+      <c r="F31" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F31" s="48">
+      <c r="G31" s="48">
         <v>2025003050010</v>
       </c>
-      <c r="G31" s="37" t="s">
+      <c r="H31" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="H31" s="2">
+      <c r="I31" s="2">
         <v>2479887333</v>
       </c>
-      <c r="I31" s="43">
+      <c r="J31" s="43">
         <v>1983909866</v>
       </c>
-      <c r="J31" s="50" t="s">
+      <c r="K31" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K31" s="58" t="s">
+      <c r="L31" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="L31" s="24">
+      <c r="M31" s="24">
         <v>45874</v>
       </c>
-      <c r="M31" s="66" t="s">
+      <c r="N31" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="N31" s="22">
+      <c r="O31" s="22">
         <v>37.270000000000003</v>
       </c>
-      <c r="O31" s="22">
+      <c r="P31" s="22">
         <v>41.96</v>
       </c>
-      <c r="P31" s="61">
+      <c r="Q31" s="61">
         <v>37.270000000000003</v>
       </c>
-      <c r="Q31" s="61">
+      <c r="R31" s="61">
         <v>66.47</v>
       </c>
-      <c r="R31" s="61">
+      <c r="S31" s="61">
         <v>37.270000000000003</v>
       </c>
-      <c r="S31" s="61">
+      <c r="T31" s="61">
         <v>66.47</v>
       </c>
-      <c r="T31" s="58">
-        <v>100</v>
-      </c>
-      <c r="U31" s="45">
+      <c r="U31" s="58">
+        <v>100</v>
+      </c>
+      <c r="V31" s="45">
         <v>35</v>
       </c>
-      <c r="V31" s="41"/>
-    </row>
-    <row r="32" spans="1:22" ht="36.75" customHeight="1">
+      <c r="W31" s="41"/>
+    </row>
+    <row r="32" spans="1:23" ht="36.75" customHeight="1">
       <c r="A32" s="42">
         <v>2025</v>
       </c>
@@ -3767,63 +3888,67 @@
       <c r="C32" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="D32" s="37" t="s">
+      <c r="D32" s="42">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E32" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="E32" s="37" t="s">
+      <c r="F32" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F32" s="48">
+      <c r="G32" s="48">
         <v>2025003050021</v>
       </c>
-      <c r="G32" s="37" t="s">
+      <c r="H32" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="H32" s="2">
+      <c r="I32" s="2">
         <v>4847192489</v>
       </c>
-      <c r="I32" s="43">
+      <c r="J32" s="43">
         <v>3877753992</v>
       </c>
-      <c r="J32" s="50" t="s">
+      <c r="K32" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K32" s="58" t="s">
+      <c r="L32" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="L32" s="24">
+      <c r="M32" s="24">
         <v>45909</v>
       </c>
-      <c r="M32" s="67">
+      <c r="N32" s="67">
         <v>46240</v>
       </c>
-      <c r="N32" s="45">
+      <c r="O32" s="45">
         <v>84</v>
       </c>
-      <c r="O32" s="45">
+      <c r="P32" s="45">
         <v>71</v>
       </c>
-      <c r="P32" s="61">
+      <c r="Q32" s="61">
         <v>85.28</v>
       </c>
-      <c r="Q32" s="61">
+      <c r="R32" s="61">
         <v>77.010000000000005</v>
       </c>
-      <c r="R32" s="61">
+      <c r="S32" s="61">
         <v>85.8</v>
       </c>
-      <c r="S32" s="61">
+      <c r="T32" s="61">
         <v>84.2</v>
       </c>
-      <c r="T32" s="58">
-        <v>100</v>
-      </c>
-      <c r="U32" s="45">
-        <v>100</v>
-      </c>
-      <c r="V32" s="41"/>
-    </row>
-    <row r="33" spans="1:22" ht="36.75" customHeight="1">
+      <c r="U32" s="58">
+        <v>100</v>
+      </c>
+      <c r="V32" s="45">
+        <v>100</v>
+      </c>
+      <c r="W32" s="41"/>
+    </row>
+    <row r="33" spans="1:23" ht="36.75" hidden="1" customHeight="1">
       <c r="A33" s="42">
         <v>2025</v>
       </c>
@@ -3833,39 +3958,40 @@
       <c r="C33" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="D33" s="37" t="s">
+      <c r="D33" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E33" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="E33" s="37" t="s">
+      <c r="F33" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="F33" s="48">
+      <c r="G33" s="48">
         <v>2025003050018</v>
       </c>
-      <c r="G33" s="37" t="s">
+      <c r="H33" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="H33" s="2">
+      <c r="I33" s="2">
         <v>2786298806</v>
       </c>
-      <c r="I33" s="43">
+      <c r="J33" s="43">
         <v>2786298806</v>
       </c>
-      <c r="J33" s="50" t="s">
+      <c r="K33" s="50" t="s">
         <v>93</v>
       </c>
-      <c r="K33" s="58" t="s">
+      <c r="L33" s="58" t="s">
         <v>138</v>
       </c>
-      <c r="L33" s="24">
+      <c r="M33" s="24">
         <v>45903</v>
       </c>
-      <c r="M33" s="66" t="s">
+      <c r="N33" s="66" t="s">
         <v>139</v>
       </c>
-      <c r="N33" s="61" t="s">
-        <v>37</v>
-      </c>
       <c r="O33" s="61" t="s">
         <v>37</v>
       </c>
@@ -3881,13 +4007,16 @@
       <c r="S33" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="T33" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="U33" s="45"/>
-      <c r="V33" s="41"/>
-    </row>
-    <row r="34" spans="1:22" s="8" customFormat="1" ht="36.75" customHeight="1">
+      <c r="T33" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="U33" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="V33" s="45"/>
+      <c r="W33" s="41"/>
+    </row>
+    <row r="34" spans="1:23" s="8" customFormat="1" ht="36.75" customHeight="1">
       <c r="A34" s="42">
         <v>2025</v>
       </c>
@@ -3897,61 +4026,65 @@
       <c r="C34" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="D34" s="37" t="s">
+      <c r="D34" s="42">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E34" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="37" t="s">
+      <c r="F34" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F34" s="48">
+      <c r="G34" s="48">
         <v>2025003050023</v>
       </c>
-      <c r="G34" s="37" t="s">
+      <c r="H34" s="37" t="s">
         <v>141</v>
       </c>
-      <c r="H34" s="2">
+      <c r="I34" s="2">
         <v>4842926067</v>
       </c>
-      <c r="I34" s="43">
+      <c r="J34" s="43">
         <v>4842926067</v>
       </c>
-      <c r="J34" s="50" t="s">
+      <c r="K34" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K34" s="58" t="s">
+      <c r="L34" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="L34" s="24">
+      <c r="M34" s="24">
         <v>45944</v>
       </c>
-      <c r="M34" s="66" t="s">
+      <c r="N34" s="66" t="s">
         <v>142</v>
       </c>
-      <c r="N34" s="45">
+      <c r="O34" s="45">
         <v>93.11</v>
       </c>
-      <c r="O34" s="45">
+      <c r="P34" s="45">
         <v>75.33</v>
       </c>
-      <c r="P34" s="61">
+      <c r="Q34" s="61">
         <v>98.97</v>
       </c>
-      <c r="Q34" s="61">
+      <c r="R34" s="61">
         <v>98.25</v>
       </c>
-      <c r="R34" s="61">
+      <c r="S34" s="61">
         <v>99.98</v>
       </c>
-      <c r="S34" s="61">
+      <c r="T34" s="61">
         <v>98.25</v>
       </c>
-      <c r="T34" s="58">
+      <c r="U34" s="58">
         <v>48.6</v>
       </c>
-      <c r="U34" s="45"/>
-      <c r="V34" s="41"/>
-    </row>
-    <row r="35" spans="1:22" ht="36.75" customHeight="1">
+      <c r="V34" s="45"/>
+      <c r="W34" s="41"/>
+    </row>
+    <row r="35" spans="1:23" ht="36.75" customHeight="1">
       <c r="A35" s="42">
         <v>2025</v>
       </c>
@@ -3961,61 +4094,65 @@
       <c r="C35" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="D35" s="37" t="s">
+      <c r="D35" s="42">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E35" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="37" t="s">
+      <c r="F35" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F35" s="48">
+      <c r="G35" s="48">
         <v>2025003050028</v>
       </c>
-      <c r="G35" s="37" t="s">
+      <c r="H35" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="H35" s="2">
+      <c r="I35" s="2">
         <v>4663630855</v>
       </c>
-      <c r="I35" s="43">
+      <c r="J35" s="43">
         <v>3730904684</v>
       </c>
-      <c r="J35" s="50" t="s">
+      <c r="K35" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K35" s="58" t="s">
+      <c r="L35" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="L35" s="24">
+      <c r="M35" s="24">
         <v>45936</v>
       </c>
-      <c r="M35" s="66" t="s">
+      <c r="N35" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="N35" s="45">
+      <c r="O35" s="45">
         <v>78.69</v>
       </c>
-      <c r="O35" s="45">
+      <c r="P35" s="45">
         <v>69.48</v>
       </c>
-      <c r="P35" s="61">
+      <c r="Q35" s="61">
         <v>95</v>
       </c>
-      <c r="Q35" s="61">
+      <c r="R35" s="61">
         <v>83.9</v>
       </c>
-      <c r="R35" s="61">
-        <v>100</v>
-      </c>
       <c r="S35" s="61">
+        <v>100</v>
+      </c>
+      <c r="T35" s="61">
         <v>83.9</v>
       </c>
-      <c r="T35" s="58">
+      <c r="U35" s="58">
         <v>83.9</v>
       </c>
-      <c r="U35" s="45"/>
-      <c r="V35" s="41"/>
-    </row>
-    <row r="36" spans="1:22" ht="36.75" customHeight="1">
+      <c r="V35" s="45"/>
+      <c r="W35" s="41"/>
+    </row>
+    <row r="36" spans="1:23" ht="36.75" hidden="1" customHeight="1">
       <c r="A36" s="42">
         <v>2025</v>
       </c>
@@ -4025,61 +4162,65 @@
       <c r="C36" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="D36" s="37" t="s">
+      <c r="D36" s="42">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="E36" s="37" t="s">
         <v>147</v>
       </c>
-      <c r="E36" s="37" t="s">
+      <c r="F36" s="37" t="s">
         <v>148</v>
       </c>
-      <c r="F36" s="48">
+      <c r="G36" s="48">
         <v>2025003050024</v>
       </c>
-      <c r="G36" s="37" t="s">
+      <c r="H36" s="37" t="s">
         <v>149</v>
       </c>
-      <c r="H36" s="2">
+      <c r="I36" s="2">
         <v>14688946853</v>
       </c>
-      <c r="I36" s="43">
+      <c r="J36" s="43">
         <v>14688946853</v>
       </c>
-      <c r="J36" s="50" t="s">
+      <c r="K36" s="50" t="s">
         <v>93</v>
       </c>
-      <c r="K36" s="58" t="s">
+      <c r="L36" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="L36" s="24">
+      <c r="M36" s="24">
         <v>45938</v>
       </c>
-      <c r="M36" s="66" t="s">
+      <c r="N36" s="66" t="s">
         <v>150</v>
-      </c>
-      <c r="N36" s="45">
-        <v>0</v>
       </c>
       <c r="O36" s="45">
         <v>0</v>
       </c>
-      <c r="P36" s="61">
+      <c r="P36" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="61">
         <v>0.68</v>
       </c>
-      <c r="Q36" s="61">
+      <c r="R36" s="61">
         <v>0</v>
       </c>
-      <c r="R36" s="61">
+      <c r="S36" s="61">
         <v>2.2200000000000002</v>
       </c>
-      <c r="S36" s="61">
+      <c r="T36" s="61">
         <v>0.68</v>
       </c>
-      <c r="T36" s="58">
+      <c r="U36" s="58">
         <v>0</v>
       </c>
-      <c r="U36" s="45"/>
-      <c r="V36" s="41"/>
-    </row>
-    <row r="37" spans="1:22" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="V36" s="45"/>
+      <c r="W36" s="41"/>
+    </row>
+    <row r="37" spans="1:23" s="14" customFormat="1" ht="36.75" hidden="1" customHeight="1">
       <c r="A37" s="42">
         <v>2025</v>
       </c>
@@ -4089,61 +4230,65 @@
       <c r="C37" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="D37" s="37" t="s">
+      <c r="D37" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E37" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="E37" s="37" t="s">
+      <c r="F37" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="F37" s="48">
+      <c r="G37" s="48">
         <v>2025003050025</v>
       </c>
-      <c r="G37" s="37" t="s">
+      <c r="H37" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H37" s="2">
+      <c r="I37" s="2">
         <v>5913699663</v>
       </c>
-      <c r="I37" s="43">
+      <c r="J37" s="43">
         <v>5913699663</v>
       </c>
-      <c r="J37" s="50" t="s">
+      <c r="K37" s="50" t="s">
         <v>93</v>
       </c>
-      <c r="K37" s="58" t="s">
+      <c r="L37" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="L37" s="24">
+      <c r="M37" s="24">
         <v>45915</v>
       </c>
-      <c r="M37" s="66" t="s">
+      <c r="N37" s="66" t="s">
         <v>156</v>
       </c>
-      <c r="N37" s="45">
+      <c r="O37" s="45">
         <v>82.86</v>
       </c>
-      <c r="O37" s="45">
+      <c r="P37" s="45">
         <v>62.88</v>
       </c>
-      <c r="P37" s="61">
+      <c r="Q37" s="61">
         <v>82.86</v>
       </c>
-      <c r="Q37" s="63">
+      <c r="R37" s="63">
         <v>62.88</v>
       </c>
-      <c r="R37" s="63">
+      <c r="S37" s="63">
         <v>96.46</v>
       </c>
-      <c r="S37" s="63">
+      <c r="T37" s="63">
         <v>83.3</v>
       </c>
-      <c r="T37" s="58">
-        <v>100</v>
-      </c>
-      <c r="U37" s="45"/>
-      <c r="V37" s="41"/>
-    </row>
-    <row r="38" spans="1:22" ht="36.75" customHeight="1">
+      <c r="U37" s="58">
+        <v>100</v>
+      </c>
+      <c r="V37" s="45"/>
+      <c r="W37" s="41"/>
+    </row>
+    <row r="38" spans="1:23" ht="36.75" hidden="1" customHeight="1">
       <c r="A38" s="42">
         <v>2025</v>
       </c>
@@ -4153,46 +4298,47 @@
       <c r="C38" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="D38" s="37" t="s">
+      <c r="D38" s="42">
+        <f t="shared" si="0"/>
+        <v>2.65</v>
+      </c>
+      <c r="E38" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="E38" s="37" t="s">
+      <c r="F38" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F38" s="48">
+      <c r="G38" s="48">
         <v>2025003050035</v>
       </c>
-      <c r="G38" s="37" t="s">
+      <c r="H38" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>5248430707.1999998</v>
       </c>
-      <c r="I38" s="49">
+      <c r="J38" s="49">
         <v>4198744565.5999999</v>
       </c>
-      <c r="J38" s="50" t="s">
+      <c r="K38" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K38" s="58" t="s">
+      <c r="L38" s="58" t="s">
         <v>160</v>
       </c>
-      <c r="L38" s="24">
+      <c r="M38" s="24">
         <v>45967</v>
       </c>
-      <c r="M38" s="66" t="s">
+      <c r="N38" s="66" t="s">
         <v>69</v>
-      </c>
-      <c r="N38" s="45">
-        <v>0</v>
       </c>
       <c r="O38" s="45">
         <v>0</v>
       </c>
-      <c r="P38" s="61">
+      <c r="P38" s="45">
         <v>0</v>
       </c>
-      <c r="Q38" s="63">
+      <c r="Q38" s="61">
         <v>0</v>
       </c>
       <c r="R38" s="63">
@@ -4201,15 +4347,18 @@
       <c r="S38" s="63">
         <v>0</v>
       </c>
-      <c r="T38" s="58">
+      <c r="T38" s="63">
         <v>0</v>
       </c>
-      <c r="U38" s="45" t="s">
+      <c r="U38" s="58">
+        <v>0</v>
+      </c>
+      <c r="V38" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="V38" s="41"/>
-    </row>
-    <row r="39" spans="1:22" ht="36.75" customHeight="1">
+      <c r="W38" s="41"/>
+    </row>
+    <row r="39" spans="1:23" ht="36.75" customHeight="1">
       <c r="A39" s="42">
         <v>2025</v>
       </c>
@@ -4219,61 +4368,65 @@
       <c r="C39" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="D39" s="37" t="s">
+      <c r="D39" s="42">
+        <f t="shared" si="0"/>
+        <v>1.63</v>
+      </c>
+      <c r="E39" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="E39" s="37" t="s">
+      <c r="F39" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F39" s="48">
+      <c r="G39" s="48">
         <v>2025003050026</v>
       </c>
-      <c r="G39" s="37" t="s">
+      <c r="H39" s="37" t="s">
         <v>164</v>
       </c>
-      <c r="H39" s="2">
+      <c r="I39" s="2">
         <v>3715229969</v>
       </c>
-      <c r="I39" s="3">
+      <c r="J39" s="3">
         <v>2972183975</v>
       </c>
-      <c r="J39" s="50" t="s">
+      <c r="K39" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K39" s="58" t="s">
+      <c r="L39" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="L39" s="24">
+      <c r="M39" s="24">
         <v>45968</v>
       </c>
-      <c r="M39" s="66" t="s">
+      <c r="N39" s="66" t="s">
         <v>165</v>
       </c>
-      <c r="N39" s="45">
+      <c r="O39" s="45">
         <v>69.27</v>
       </c>
-      <c r="O39" s="45">
+      <c r="P39" s="45">
         <v>40.130000000000003</v>
       </c>
-      <c r="P39" s="61">
+      <c r="Q39" s="61">
         <v>69.27</v>
       </c>
-      <c r="Q39" s="63">
+      <c r="R39" s="63">
         <v>40.130000000000003</v>
       </c>
-      <c r="R39" s="63">
+      <c r="S39" s="63">
         <v>77.58</v>
       </c>
-      <c r="S39" s="63">
+      <c r="T39" s="63">
         <v>41.73</v>
       </c>
-      <c r="T39" s="58">
-        <v>100</v>
-      </c>
-      <c r="U39" s="45"/>
-      <c r="V39" s="41"/>
-    </row>
-    <row r="40" spans="1:22" ht="36.75" customHeight="1">
+      <c r="U39" s="58">
+        <v>100</v>
+      </c>
+      <c r="V39" s="45"/>
+      <c r="W39" s="41"/>
+    </row>
+    <row r="40" spans="1:23" ht="36.75" hidden="1" customHeight="1">
       <c r="A40" s="42">
         <v>2025</v>
       </c>
@@ -4283,61 +4436,65 @@
       <c r="C40" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="D40" s="37" t="s">
+      <c r="D40" s="42">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E40" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="E40" s="37" t="s">
+      <c r="F40" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="F40" s="48">
+      <c r="G40" s="48">
         <v>2025003050034</v>
       </c>
-      <c r="G40" s="37" t="s">
+      <c r="H40" s="37" t="s">
         <v>167</v>
       </c>
-      <c r="H40" s="2">
+      <c r="I40" s="2">
         <v>4782821867</v>
       </c>
-      <c r="I40" s="49">
+      <c r="J40" s="49">
         <v>4682821867</v>
       </c>
-      <c r="J40" s="50" t="s">
+      <c r="K40" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K40" s="58" t="s">
+      <c r="L40" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="L40" s="24">
+      <c r="M40" s="24">
         <v>45973</v>
       </c>
-      <c r="M40" s="66" t="s">
+      <c r="N40" s="66" t="s">
         <v>168</v>
       </c>
-      <c r="N40" s="45">
+      <c r="O40" s="45">
         <v>60.71</v>
       </c>
-      <c r="O40" s="45">
+      <c r="P40" s="45">
         <v>84.45</v>
       </c>
-      <c r="P40" s="61">
+      <c r="Q40" s="61">
         <v>60.71</v>
       </c>
-      <c r="Q40" s="63">
+      <c r="R40" s="63">
         <v>84.45</v>
       </c>
-      <c r="R40" s="63">
+      <c r="S40" s="63">
         <v>99.55</v>
       </c>
-      <c r="S40" s="63">
-        <v>100</v>
-      </c>
-      <c r="T40" s="58">
+      <c r="T40" s="63">
+        <v>100</v>
+      </c>
+      <c r="U40" s="58">
         <v>52</v>
       </c>
-      <c r="U40" s="45"/>
-      <c r="V40" s="41"/>
-    </row>
-    <row r="41" spans="1:22" ht="36.75" customHeight="1">
+      <c r="V40" s="45"/>
+      <c r="W40" s="41"/>
+    </row>
+    <row r="41" spans="1:23" ht="36.75" customHeight="1">
       <c r="A41" s="42">
         <v>2025</v>
       </c>
@@ -4347,46 +4504,47 @@
       <c r="C41" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="D41" s="37" t="s">
+      <c r="D41" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E41" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E41" s="37" t="s">
+      <c r="F41" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F41" s="48">
+      <c r="G41" s="48">
         <v>2025003050031</v>
       </c>
-      <c r="G41" s="37" t="s">
+      <c r="H41" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="H41" s="2">
+      <c r="I41" s="2">
         <v>2267187134</v>
       </c>
-      <c r="I41" s="2">
+      <c r="J41" s="2">
         <v>1500000000</v>
       </c>
-      <c r="J41" s="50" t="s">
+      <c r="K41" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K41" s="60" t="s">
+      <c r="L41" s="60" t="s">
         <v>103</v>
       </c>
-      <c r="L41" s="44">
+      <c r="M41" s="44">
         <v>45971</v>
       </c>
-      <c r="M41" s="66" t="s">
+      <c r="N41" s="66" t="s">
         <v>171</v>
       </c>
-      <c r="N41" s="45">
-        <v>100</v>
-      </c>
       <c r="O41" s="45">
+        <v>100</v>
+      </c>
+      <c r="P41" s="45">
         <v>96.43</v>
       </c>
-      <c r="P41" s="61">
-        <v>100</v>
-      </c>
-      <c r="Q41" s="63">
+      <c r="Q41" s="61">
         <v>100</v>
       </c>
       <c r="R41" s="63">
@@ -4395,15 +4553,18 @@
       <c r="S41" s="63">
         <v>100</v>
       </c>
-      <c r="T41" s="58">
+      <c r="T41" s="63">
+        <v>100</v>
+      </c>
+      <c r="U41" s="58">
         <v>89</v>
       </c>
-      <c r="U41" s="45">
-        <v>100</v>
-      </c>
-      <c r="V41" s="41"/>
-    </row>
-    <row r="42" spans="1:22" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="V41" s="45">
+        <v>100</v>
+      </c>
+      <c r="W41" s="41"/>
+    </row>
+    <row r="42" spans="1:23" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A42" s="42">
         <v>2025</v>
       </c>
@@ -4413,61 +4574,65 @@
       <c r="C42" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D42" s="37" t="s">
+      <c r="D42" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E42" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E42" s="37" t="s">
+      <c r="F42" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F42" s="48">
+      <c r="G42" s="48">
         <v>2025003050032</v>
       </c>
-      <c r="G42" s="37" t="s">
+      <c r="H42" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="H42" s="2">
+      <c r="I42" s="2">
         <v>2068919343</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1654822441</v>
       </c>
-      <c r="J42" s="50" t="s">
+      <c r="K42" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K42" s="61" t="s">
+      <c r="L42" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="L42" s="24">
+      <c r="M42" s="24">
         <v>46015</v>
       </c>
-      <c r="M42" s="66" t="s">
+      <c r="N42" s="66" t="s">
         <v>174</v>
       </c>
-      <c r="N42" s="45">
+      <c r="O42" s="45">
         <v>45.41</v>
       </c>
-      <c r="O42" s="45">
+      <c r="P42" s="45">
         <v>45</v>
       </c>
-      <c r="P42" s="61">
+      <c r="Q42" s="61">
         <v>56.27</v>
       </c>
-      <c r="Q42" s="63">
+      <c r="R42" s="63">
         <v>68.52</v>
       </c>
-      <c r="R42" s="63">
+      <c r="S42" s="63">
         <v>77.989999999999995</v>
       </c>
-      <c r="S42" s="63">
+      <c r="T42" s="63">
         <v>68.52</v>
       </c>
-      <c r="T42" s="58">
-        <v>100</v>
-      </c>
-      <c r="U42" s="45"/>
-      <c r="V42" s="41"/>
-    </row>
-    <row r="43" spans="1:22" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U42" s="58">
+        <v>100</v>
+      </c>
+      <c r="V42" s="45"/>
+      <c r="W42" s="41"/>
+    </row>
+    <row r="43" spans="1:23" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A43" s="42">
         <v>2025</v>
       </c>
@@ -4477,63 +4642,67 @@
       <c r="C43" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="D43" s="37" t="s">
+      <c r="D43" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E43" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E43" s="37" t="s">
+      <c r="F43" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="48">
+      <c r="G43" s="48">
         <v>2025003050038</v>
       </c>
-      <c r="G43" s="37" t="s">
+      <c r="H43" s="37" t="s">
         <v>176</v>
       </c>
-      <c r="H43" s="2">
+      <c r="I43" s="2">
         <v>2138705796</v>
       </c>
-      <c r="I43" s="43">
+      <c r="J43" s="43">
         <v>1500000000</v>
       </c>
-      <c r="J43" s="50" t="s">
+      <c r="K43" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K43" s="61" t="s">
+      <c r="L43" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="L43" s="24">
+      <c r="M43" s="24">
         <v>46001</v>
       </c>
-      <c r="M43" s="66" t="s">
+      <c r="N43" s="66" t="s">
         <v>177</v>
       </c>
-      <c r="N43" s="45">
+      <c r="O43" s="45">
         <v>23.44</v>
       </c>
-      <c r="O43" s="45">
+      <c r="P43" s="45">
         <v>45.52</v>
       </c>
-      <c r="P43" s="61">
+      <c r="Q43" s="61">
         <v>23.44</v>
       </c>
-      <c r="Q43" s="63">
+      <c r="R43" s="63">
         <v>45.52</v>
       </c>
-      <c r="R43" s="63">
+      <c r="S43" s="63">
         <v>23.44</v>
       </c>
-      <c r="S43" s="63">
+      <c r="T43" s="63">
         <v>45.52</v>
       </c>
-      <c r="T43" s="58">
-        <v>100</v>
-      </c>
-      <c r="U43" s="45">
+      <c r="U43" s="58">
+        <v>100</v>
+      </c>
+      <c r="V43" s="45">
         <v>14</v>
       </c>
-      <c r="V43" s="41"/>
-    </row>
-    <row r="44" spans="1:22" ht="36.75" customHeight="1">
+      <c r="W43" s="41"/>
+    </row>
+    <row r="44" spans="1:23" ht="36.75" customHeight="1">
       <c r="A44" s="42">
         <v>2025</v>
       </c>
@@ -4543,61 +4712,65 @@
       <c r="C44" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="D44" s="37" t="s">
+      <c r="D44" s="42">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E44" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="E44" s="37" t="s">
+      <c r="F44" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F44" s="48">
+      <c r="G44" s="48">
         <v>2025003050046</v>
       </c>
-      <c r="G44" s="37" t="s">
+      <c r="H44" s="37" t="s">
         <v>179</v>
       </c>
-      <c r="H44" s="2">
+      <c r="I44" s="2">
         <v>4319392762</v>
       </c>
-      <c r="I44" s="2">
+      <c r="J44" s="2">
         <v>3414414209</v>
       </c>
-      <c r="J44" s="50" t="s">
+      <c r="K44" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K44" s="61" t="s">
+      <c r="L44" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="L44" s="24">
+      <c r="M44" s="24">
         <v>46014</v>
       </c>
-      <c r="M44" s="66" t="s">
+      <c r="N44" s="66" t="s">
         <v>180</v>
       </c>
-      <c r="N44" s="45">
+      <c r="O44" s="45">
         <v>26.14</v>
       </c>
-      <c r="O44" s="45">
+      <c r="P44" s="45">
         <v>27.27</v>
       </c>
-      <c r="P44" s="61">
+      <c r="Q44" s="61">
         <v>46.12</v>
       </c>
-      <c r="Q44" s="63">
+      <c r="R44" s="63">
         <v>41.92</v>
       </c>
-      <c r="R44" s="63">
+      <c r="S44" s="63">
         <v>49.33</v>
       </c>
-      <c r="S44" s="63">
+      <c r="T44" s="63">
         <v>46.12</v>
       </c>
-      <c r="T44" s="58">
+      <c r="U44" s="58">
         <v>90.4</v>
       </c>
-      <c r="U44" s="50"/>
-      <c r="V44" s="41"/>
-    </row>
-    <row r="45" spans="1:22" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="V44" s="50"/>
+      <c r="W44" s="41"/>
+    </row>
+    <row r="45" spans="1:23" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A45" s="42">
         <v>2025</v>
       </c>
@@ -4607,61 +4780,65 @@
       <c r="C45" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="D45" s="37" t="s">
+      <c r="D45" s="42">
+        <f t="shared" si="0"/>
+        <v>1.5</v>
+      </c>
+      <c r="E45" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="E45" s="37" t="s">
+      <c r="F45" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F45" s="48">
+      <c r="G45" s="48">
         <v>2025003050043</v>
       </c>
-      <c r="G45" s="37" t="s">
+      <c r="H45" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="H45" s="2">
+      <c r="I45" s="2">
         <v>2387040561</v>
       </c>
-      <c r="I45" s="43">
+      <c r="J45" s="43">
         <v>1500000000</v>
       </c>
-      <c r="J45" s="50" t="s">
+      <c r="K45" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K45" s="61" t="s">
+      <c r="L45" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="L45" s="24">
+      <c r="M45" s="24">
         <v>46011</v>
       </c>
-      <c r="M45" s="66" t="s">
+      <c r="N45" s="66" t="s">
         <v>111</v>
       </c>
-      <c r="N45" s="45">
+      <c r="O45" s="45">
         <v>31.59</v>
       </c>
-      <c r="O45" s="45">
+      <c r="P45" s="45">
         <v>45.88</v>
       </c>
-      <c r="P45" s="61">
+      <c r="Q45" s="61">
         <v>45.49</v>
       </c>
-      <c r="Q45" s="63">
+      <c r="R45" s="63">
         <v>45.88</v>
       </c>
-      <c r="R45" s="63">
+      <c r="S45" s="63">
         <v>58.4</v>
       </c>
-      <c r="S45" s="63">
+      <c r="T45" s="63">
         <v>73.709999999999994</v>
       </c>
-      <c r="T45" s="58">
+      <c r="U45" s="58">
         <v>60</v>
       </c>
-      <c r="U45" s="45"/>
-      <c r="V45" s="41"/>
-    </row>
-    <row r="46" spans="1:22" ht="36.75" customHeight="1">
+      <c r="V45" s="45"/>
+      <c r="W45" s="41"/>
+    </row>
+    <row r="46" spans="1:23" ht="36.75" hidden="1" customHeight="1">
       <c r="A46" s="42">
         <v>2025</v>
       </c>
@@ -4671,61 +4848,65 @@
       <c r="C46" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D46" s="37" t="s">
+      <c r="D46" s="42">
+        <f t="shared" si="0"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E46" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="E46" s="37" t="s">
+      <c r="F46" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="F46" s="48">
+      <c r="G46" s="48">
         <v>2025003050027</v>
       </c>
-      <c r="G46" s="37" t="s">
+      <c r="H46" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="H46" s="2">
+      <c r="I46" s="2">
         <v>27387320782</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>27387320782</v>
       </c>
-      <c r="J46" s="50" t="s">
+      <c r="K46" s="50" t="s">
         <v>93</v>
       </c>
-      <c r="K46" s="61" t="s">
+      <c r="L46" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="L46" s="24">
+      <c r="M46" s="24">
         <v>46013</v>
       </c>
-      <c r="M46" s="66" t="s">
+      <c r="N46" s="66" t="s">
         <v>185</v>
-      </c>
-      <c r="N46" s="45">
-        <v>0</v>
       </c>
       <c r="O46" s="45">
         <v>0</v>
       </c>
-      <c r="P46" s="61">
+      <c r="P46" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="61">
         <v>1.02</v>
       </c>
-      <c r="Q46" s="63">
+      <c r="R46" s="63">
         <v>0</v>
       </c>
-      <c r="R46" s="63">
+      <c r="S46" s="63">
         <v>1.92</v>
       </c>
-      <c r="S46" s="63">
+      <c r="T46" s="63">
         <v>0.5</v>
       </c>
-      <c r="T46" s="58">
+      <c r="U46" s="58">
         <v>80.400000000000006</v>
       </c>
-      <c r="U46" s="45"/>
-      <c r="V46" s="41"/>
-    </row>
-    <row r="47" spans="1:22" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="V46" s="45"/>
+      <c r="W46" s="41"/>
+    </row>
+    <row r="47" spans="1:23" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A47" s="42">
         <v>2025</v>
       </c>
@@ -4735,63 +4916,67 @@
       <c r="C47" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="37" t="s">
+      <c r="D47" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E47" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E47" s="37" t="s">
+      <c r="F47" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F47" s="48">
+      <c r="G47" s="48">
         <v>2025003050053</v>
       </c>
-      <c r="G47" s="37" t="s">
+      <c r="H47" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="H47" s="2">
+      <c r="I47" s="2">
         <v>2149409352</v>
       </c>
-      <c r="I47" s="43">
+      <c r="J47" s="43">
         <v>1500000000</v>
       </c>
-      <c r="J47" s="50" t="s">
+      <c r="K47" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K47" s="58" t="s">
+      <c r="L47" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="L47" s="24">
+      <c r="M47" s="24">
         <v>46014</v>
       </c>
-      <c r="M47" s="67">
+      <c r="N47" s="67">
         <v>46060</v>
       </c>
-      <c r="N47" s="45">
+      <c r="O47" s="45">
         <v>97.2</v>
       </c>
-      <c r="O47" s="45">
+      <c r="P47" s="45">
         <v>94.43</v>
       </c>
-      <c r="P47" s="61">
+      <c r="Q47" s="61">
         <v>97.22</v>
       </c>
-      <c r="Q47" s="63">
+      <c r="R47" s="63">
         <v>96.27</v>
       </c>
-      <c r="R47" s="63">
+      <c r="S47" s="63">
         <v>97.22</v>
       </c>
-      <c r="S47" s="63">
+      <c r="T47" s="63">
         <v>99.85</v>
       </c>
-      <c r="T47" s="58">
-        <v>100</v>
-      </c>
-      <c r="U47" s="45">
-        <v>100</v>
-      </c>
-      <c r="V47" s="41"/>
-    </row>
-    <row r="48" spans="1:22" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U47" s="58">
+        <v>100</v>
+      </c>
+      <c r="V47" s="45">
+        <v>100</v>
+      </c>
+      <c r="W47" s="41"/>
+    </row>
+    <row r="48" spans="1:23" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A48" s="42">
         <v>2025</v>
       </c>
@@ -4801,63 +4986,67 @@
       <c r="C48" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="D48" s="37" t="s">
+      <c r="D48" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E48" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E48" s="37" t="s">
+      <c r="F48" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F48" s="48">
+      <c r="G48" s="48">
         <v>2025003050051</v>
       </c>
-      <c r="G48" s="37" t="s">
+      <c r="H48" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="H48" s="2">
+      <c r="I48" s="2">
         <v>2264647460</v>
       </c>
-      <c r="I48" s="49">
+      <c r="J48" s="49">
         <v>1750000000</v>
       </c>
-      <c r="J48" s="50" t="s">
+      <c r="K48" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K48" s="58" t="s">
+      <c r="L48" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="L48" s="24">
+      <c r="M48" s="24">
         <v>46014</v>
       </c>
-      <c r="M48" s="67">
+      <c r="N48" s="67">
         <v>46332</v>
       </c>
-      <c r="N48" s="45">
-        <v>100</v>
-      </c>
       <c r="O48" s="45">
+        <v>100</v>
+      </c>
+      <c r="P48" s="45">
         <v>78.69</v>
       </c>
-      <c r="P48" s="61">
-        <v>100</v>
-      </c>
-      <c r="Q48" s="63">
+      <c r="Q48" s="61">
+        <v>100</v>
+      </c>
+      <c r="R48" s="63">
         <v>81.209999999999994</v>
       </c>
-      <c r="R48" s="61">
-        <v>100</v>
-      </c>
-      <c r="S48" s="63">
+      <c r="S48" s="61">
+        <v>100</v>
+      </c>
+      <c r="T48" s="63">
         <v>81.69</v>
       </c>
-      <c r="T48" s="58">
-        <v>100</v>
-      </c>
-      <c r="U48" s="45">
-        <v>100</v>
-      </c>
-      <c r="V48" s="41"/>
-    </row>
-    <row r="49" spans="1:30" s="9" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U48" s="58">
+        <v>100</v>
+      </c>
+      <c r="V48" s="45">
+        <v>100</v>
+      </c>
+      <c r="W48" s="41"/>
+    </row>
+    <row r="49" spans="1:31" s="9" customFormat="1" ht="36.75" customHeight="1">
       <c r="A49" s="46">
         <v>2025</v>
       </c>
@@ -4867,60 +5056,63 @@
       <c r="C49" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="D49" s="37" t="s">
+      <c r="D49" s="42">
+        <f t="shared" si="0"/>
+        <v>1.73</v>
+      </c>
+      <c r="E49" s="37" t="s">
         <v>190</v>
       </c>
-      <c r="E49" s="37" t="s">
+      <c r="F49" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F49" s="48">
+      <c r="G49" s="48">
         <v>2025003050056</v>
       </c>
-      <c r="G49" s="37" t="s">
+      <c r="H49" s="37" t="s">
         <v>191</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4431237626</v>
       </c>
-      <c r="I49" s="49">
+      <c r="J49" s="49">
         <v>4431237626</v>
       </c>
-      <c r="J49" s="45" t="s">
+      <c r="K49" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="K49" s="61" t="s">
+      <c r="L49" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="L49" s="24">
+      <c r="M49" s="24">
         <v>46014</v>
       </c>
-      <c r="M49" s="66" t="s">
+      <c r="N49" s="66" t="s">
         <v>192</v>
       </c>
-      <c r="N49" s="45">
+      <c r="O49" s="45">
         <v>28.94</v>
       </c>
-      <c r="O49" s="45">
+      <c r="P49" s="45">
         <v>27.38</v>
       </c>
-      <c r="P49" s="61">
+      <c r="Q49" s="61">
         <v>46.1</v>
       </c>
-      <c r="Q49" s="63">
+      <c r="R49" s="63">
         <v>46.1</v>
       </c>
-      <c r="R49" s="63">
+      <c r="S49" s="63">
         <v>49.3</v>
       </c>
-      <c r="S49" s="63">
+      <c r="T49" s="63">
         <v>46.1</v>
       </c>
-      <c r="T49" s="58">
+      <c r="U49" s="58">
         <v>97.2</v>
       </c>
-      <c r="U49" s="45"/>
-      <c r="V49" s="41"/>
-      <c r="W49" s="68"/>
+      <c r="V49" s="45"/>
+      <c r="W49" s="41"/>
       <c r="X49" s="68"/>
       <c r="Y49" s="68"/>
       <c r="Z49" s="68"/>
@@ -4928,8 +5120,9 @@
       <c r="AB49" s="68"/>
       <c r="AC49" s="68"/>
       <c r="AD49" s="68"/>
-    </row>
-    <row r="50" spans="1:30" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="AE49" s="68"/>
+    </row>
+    <row r="50" spans="1:31" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A50" s="42">
         <v>2025</v>
       </c>
@@ -4939,61 +5132,64 @@
       <c r="C50" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="D50" s="37" t="s">
+      <c r="D50" s="42">
+        <f t="shared" si="0"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E50" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="E50" s="37" t="s">
+      <c r="F50" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F50" s="48">
+      <c r="G50" s="48">
         <v>2025003050044</v>
       </c>
-      <c r="G50" s="37" t="s">
+      <c r="H50" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="H50" s="2">
+      <c r="I50" s="2">
         <v>2808881690</v>
       </c>
-      <c r="I50" s="43">
+      <c r="J50" s="43">
         <v>2708881690</v>
       </c>
-      <c r="J50" s="50" t="s">
+      <c r="K50" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K50" s="61" t="s">
+      <c r="L50" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="L50" s="24">
+      <c r="M50" s="24">
         <v>46014</v>
       </c>
-      <c r="M50" s="66" t="s">
+      <c r="N50" s="66" t="s">
         <v>194</v>
       </c>
-      <c r="N50" s="45">
-        <v>100</v>
-      </c>
       <c r="O50" s="45">
+        <v>100</v>
+      </c>
+      <c r="P50" s="45">
         <v>91.75</v>
       </c>
-      <c r="P50" s="61">
-        <v>100</v>
-      </c>
-      <c r="Q50" s="63">
+      <c r="Q50" s="61">
+        <v>100</v>
+      </c>
+      <c r="R50" s="63">
         <v>91.75</v>
       </c>
-      <c r="R50" s="61">
-        <v>100</v>
-      </c>
-      <c r="S50" s="63">
+      <c r="S50" s="61">
+        <v>100</v>
+      </c>
+      <c r="T50" s="63">
         <v>91.75</v>
       </c>
-      <c r="T50" s="58">
-        <v>100</v>
-      </c>
-      <c r="U50" s="45">
-        <v>100</v>
-      </c>
-      <c r="V50" s="41"/>
+      <c r="U50" s="58">
+        <v>100</v>
+      </c>
+      <c r="V50" s="45">
+        <v>100</v>
+      </c>
       <c r="W50" s="41"/>
       <c r="X50" s="41"/>
       <c r="Y50" s="41"/>
@@ -5002,8 +5198,9 @@
       <c r="AB50" s="41"/>
       <c r="AC50" s="41"/>
       <c r="AD50" s="41"/>
-    </row>
-    <row r="51" spans="1:30" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="AE50" s="41"/>
+    </row>
+    <row r="51" spans="1:31" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A51" s="42">
         <v>2025</v>
       </c>
@@ -5013,59 +5210,62 @@
       <c r="C51" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="D51" s="37" t="s">
+      <c r="D51" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E51" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E51" s="37" t="s">
+      <c r="F51" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F51" s="48">
+      <c r="G51" s="48">
         <v>2025003050045</v>
       </c>
-      <c r="G51" s="37" t="s">
+      <c r="H51" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="H51" s="2">
+      <c r="I51" s="2">
         <v>2357899973</v>
       </c>
-      <c r="I51" s="43">
+      <c r="J51" s="43">
         <v>1680000000</v>
       </c>
-      <c r="J51" s="50" t="s">
+      <c r="K51" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K51" s="61" t="s">
+      <c r="L51" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="L51" s="24">
+      <c r="M51" s="24">
         <v>46013</v>
       </c>
-      <c r="M51" s="66" t="s">
+      <c r="N51" s="66" t="s">
         <v>196</v>
       </c>
-      <c r="N51" s="45">
+      <c r="O51" s="45">
         <v>5.64</v>
       </c>
-      <c r="O51" s="45">
+      <c r="P51" s="45">
         <v>0</v>
       </c>
-      <c r="P51" s="61">
+      <c r="Q51" s="61">
         <v>19.13</v>
       </c>
-      <c r="Q51" s="63">
+      <c r="R51" s="63">
         <v>27.56</v>
       </c>
-      <c r="R51" s="63">
+      <c r="S51" s="63">
         <v>22.45</v>
       </c>
-      <c r="S51" s="63">
+      <c r="T51" s="63">
         <v>27.56</v>
       </c>
-      <c r="T51" s="58">
-        <v>100</v>
-      </c>
-      <c r="U51" s="45"/>
-      <c r="V51" s="41"/>
+      <c r="U51" s="58">
+        <v>100</v>
+      </c>
+      <c r="V51" s="45"/>
       <c r="W51" s="41"/>
       <c r="X51" s="41"/>
       <c r="Y51" s="41"/>
@@ -5074,8 +5274,9 @@
       <c r="AB51" s="41"/>
       <c r="AC51" s="41"/>
       <c r="AD51" s="41"/>
-    </row>
-    <row r="52" spans="1:30" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="AE51" s="41"/>
+    </row>
+    <row r="52" spans="1:31" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A52" s="42">
         <v>2025</v>
       </c>
@@ -5085,61 +5286,64 @@
       <c r="C52" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="37" t="s">
+      <c r="D52" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E52" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E52" s="37" t="s">
+      <c r="F52" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F52" s="48">
+      <c r="G52" s="48">
         <v>2025003050050</v>
       </c>
-      <c r="G52" s="37" t="s">
+      <c r="H52" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="H52" s="2">
+      <c r="I52" s="2">
         <v>1879328482</v>
       </c>
-      <c r="I52" s="43">
+      <c r="J52" s="43">
         <v>1500000000</v>
       </c>
-      <c r="J52" s="50" t="s">
+      <c r="K52" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K52" s="58" t="s">
+      <c r="L52" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="L52" s="24">
+      <c r="M52" s="24">
         <v>46014</v>
       </c>
-      <c r="M52" s="67">
+      <c r="N52" s="67">
         <v>46272</v>
       </c>
-      <c r="N52" s="45">
-        <v>100</v>
-      </c>
       <c r="O52" s="45">
+        <v>100</v>
+      </c>
+      <c r="P52" s="45">
         <v>87.72</v>
       </c>
-      <c r="P52" s="61">
-        <v>100</v>
-      </c>
-      <c r="Q52" s="63">
+      <c r="Q52" s="61">
+        <v>100</v>
+      </c>
+      <c r="R52" s="63">
         <v>97.51</v>
       </c>
-      <c r="R52" s="61">
-        <v>100</v>
-      </c>
-      <c r="S52" s="63">
+      <c r="S52" s="61">
+        <v>100</v>
+      </c>
+      <c r="T52" s="63">
         <v>99.24</v>
       </c>
-      <c r="T52" s="58">
-        <v>100</v>
-      </c>
-      <c r="U52" s="45">
-        <v>100</v>
-      </c>
-      <c r="V52" s="41"/>
+      <c r="U52" s="58">
+        <v>100</v>
+      </c>
+      <c r="V52" s="45">
+        <v>100</v>
+      </c>
       <c r="W52" s="41"/>
       <c r="X52" s="41"/>
       <c r="Y52" s="41"/>
@@ -5148,8 +5352,9 @@
       <c r="AB52" s="41"/>
       <c r="AC52" s="41"/>
       <c r="AD52" s="41"/>
-    </row>
-    <row r="53" spans="1:30" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="AE52" s="41"/>
+    </row>
+    <row r="53" spans="1:31" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A53" s="42">
         <v>2025</v>
       </c>
@@ -5159,61 +5364,64 @@
       <c r="C53" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="D53" s="37" t="s">
+      <c r="D53" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E53" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E53" s="37" t="s">
+      <c r="F53" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F53" s="48">
+      <c r="G53" s="48">
         <v>2025003050049</v>
       </c>
-      <c r="G53" s="37" t="s">
+      <c r="H53" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="H53" s="2">
+      <c r="I53" s="2">
         <v>2156349509</v>
       </c>
-      <c r="I53" s="43">
+      <c r="J53" s="43">
         <v>1500000000</v>
       </c>
-      <c r="J53" s="50" t="s">
+      <c r="K53" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K53" s="58" t="s">
+      <c r="L53" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="L53" s="24">
+      <c r="M53" s="24">
         <v>46014</v>
       </c>
-      <c r="M53" s="67">
+      <c r="N53" s="67">
         <v>46333</v>
       </c>
-      <c r="N53" s="50">
-        <v>100</v>
-      </c>
       <c r="O53" s="50">
+        <v>100</v>
+      </c>
+      <c r="P53" s="50">
         <v>94.73</v>
       </c>
-      <c r="P53" s="61">
-        <v>100</v>
-      </c>
-      <c r="Q53" s="63">
+      <c r="Q53" s="61">
+        <v>100</v>
+      </c>
+      <c r="R53" s="63">
         <v>99.49</v>
       </c>
-      <c r="R53" s="63">
-        <v>100</v>
-      </c>
       <c r="S53" s="63">
         <v>100</v>
       </c>
-      <c r="T53" s="58">
-        <v>100</v>
-      </c>
-      <c r="U53" s="45">
-        <v>100</v>
-      </c>
-      <c r="V53" s="41"/>
+      <c r="T53" s="63">
+        <v>100</v>
+      </c>
+      <c r="U53" s="58">
+        <v>100</v>
+      </c>
+      <c r="V53" s="45">
+        <v>100</v>
+      </c>
       <c r="W53" s="41"/>
       <c r="X53" s="41"/>
       <c r="Y53" s="41"/>
@@ -5222,8 +5430,9 @@
       <c r="AB53" s="41"/>
       <c r="AC53" s="41"/>
       <c r="AD53" s="41"/>
-    </row>
-    <row r="54" spans="1:30" ht="36.75" customHeight="1">
+      <c r="AE53" s="41"/>
+    </row>
+    <row r="54" spans="1:31" ht="36.75" hidden="1" customHeight="1">
       <c r="A54" s="42">
         <v>2026</v>
       </c>
@@ -5233,59 +5442,62 @@
       <c r="C54" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="D54" s="37" t="s">
+      <c r="D54" s="42">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E54" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="E54" s="37" t="s">
+      <c r="F54" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="F54" s="48">
+      <c r="G54" s="48">
         <v>2025003050036</v>
       </c>
-      <c r="G54" s="37" t="s">
+      <c r="H54" s="37" t="s">
         <v>203</v>
-      </c>
-      <c r="H54" s="2">
-        <v>14202451801</v>
       </c>
       <c r="I54" s="2">
         <v>14202451801</v>
       </c>
-      <c r="J54" s="50" t="s">
+      <c r="J54" s="2">
+        <v>14202451801</v>
+      </c>
+      <c r="K54" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K54" s="61" t="s">
+      <c r="L54" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="L54" s="24">
+      <c r="M54" s="24">
         <v>46031</v>
       </c>
-      <c r="M54" s="66" t="s">
+      <c r="N54" s="66" t="s">
         <v>204</v>
       </c>
-      <c r="N54" s="45">
+      <c r="O54" s="45">
         <v>13.9</v>
       </c>
-      <c r="O54" s="45">
+      <c r="P54" s="45">
         <v>35.69</v>
       </c>
-      <c r="P54" s="61">
+      <c r="Q54" s="61">
         <v>31.83</v>
       </c>
-      <c r="Q54" s="63">
+      <c r="R54" s="63">
         <v>35.69</v>
       </c>
-      <c r="R54" s="63">
+      <c r="S54" s="63">
         <v>60.19</v>
       </c>
-      <c r="S54" s="63">
+      <c r="T54" s="63">
         <v>38.06</v>
       </c>
-      <c r="T54" s="58">
+      <c r="U54" s="58">
         <v>79.599999999999994</v>
       </c>
-      <c r="U54" s="45"/>
-      <c r="V54" s="41"/>
+      <c r="V54" s="45"/>
       <c r="W54" s="41"/>
       <c r="X54" s="41"/>
       <c r="Y54" s="41"/>
@@ -5294,8 +5506,9 @@
       <c r="AB54" s="41"/>
       <c r="AC54" s="41"/>
       <c r="AD54" s="41"/>
-    </row>
-    <row r="55" spans="1:30" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="AE54" s="41"/>
+    </row>
+    <row r="55" spans="1:31" s="14" customFormat="1" ht="36.75" hidden="1" customHeight="1">
       <c r="A55" s="42">
         <v>2026</v>
       </c>
@@ -5305,59 +5518,62 @@
       <c r="C55" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="D55" s="37" t="s">
+      <c r="D55" s="42">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E55" s="37" t="s">
         <v>206</v>
       </c>
-      <c r="E55" s="37" t="s">
+      <c r="F55" s="37" t="s">
         <v>148</v>
       </c>
-      <c r="F55" s="48">
+      <c r="G55" s="48">
         <v>2025003050040</v>
       </c>
-      <c r="G55" s="37" t="s">
+      <c r="H55" s="37" t="s">
         <v>207</v>
-      </c>
-      <c r="H55" s="2">
-        <v>2540216819</v>
       </c>
       <c r="I55" s="2">
         <v>2540216819</v>
       </c>
-      <c r="J55" s="50" t="s">
+      <c r="J55" s="2">
+        <v>2540216819</v>
+      </c>
+      <c r="K55" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K55" s="61" t="s">
+      <c r="L55" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="L55" s="24">
+      <c r="M55" s="24">
         <v>46031</v>
       </c>
-      <c r="M55" s="67">
+      <c r="N55" s="67">
         <v>46276</v>
-      </c>
-      <c r="N55" s="52" t="s">
-        <v>49</v>
       </c>
       <c r="O55" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="P55" s="61">
+      <c r="P55" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q55" s="61">
         <v>19</v>
       </c>
-      <c r="Q55" s="63">
+      <c r="R55" s="63">
         <v>30.46</v>
       </c>
-      <c r="R55" s="61">
+      <c r="S55" s="61">
         <v>19</v>
       </c>
-      <c r="S55" s="63">
+      <c r="T55" s="63">
         <v>35.57</v>
       </c>
-      <c r="T55" s="58">
-        <v>100</v>
-      </c>
-      <c r="U55" s="45"/>
-      <c r="V55" s="41"/>
+      <c r="U55" s="58">
+        <v>100</v>
+      </c>
+      <c r="V55" s="45"/>
       <c r="W55" s="41"/>
       <c r="X55" s="41"/>
       <c r="Y55" s="41"/>
@@ -5366,8 +5582,9 @@
       <c r="AB55" s="41"/>
       <c r="AC55" s="41"/>
       <c r="AD55" s="41"/>
-    </row>
-    <row r="56" spans="1:30" ht="36.75" customHeight="1">
+      <c r="AE55" s="41"/>
+    </row>
+    <row r="56" spans="1:31" ht="36.75" hidden="1" customHeight="1">
       <c r="A56" s="46">
         <v>2026</v>
       </c>
@@ -5377,59 +5594,62 @@
       <c r="C56" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="D56" s="37" t="s">
+      <c r="D56" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E56" s="37" t="s">
         <v>209</v>
       </c>
-      <c r="E56" s="37" t="s">
+      <c r="F56" s="37" t="s">
         <v>148</v>
       </c>
-      <c r="F56" s="48">
+      <c r="G56" s="48">
         <v>2025003050039</v>
       </c>
-      <c r="G56" s="37" t="s">
+      <c r="H56" s="37" t="s">
         <v>210</v>
-      </c>
-      <c r="H56" s="49">
-        <v>9381110055</v>
       </c>
       <c r="I56" s="49">
         <v>9381110055</v>
       </c>
-      <c r="J56" s="50" t="s">
+      <c r="J56" s="49">
+        <v>9381110055</v>
+      </c>
+      <c r="K56" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K56" s="61" t="s">
+      <c r="L56" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="L56" s="24">
+      <c r="M56" s="24">
         <v>46031</v>
       </c>
-      <c r="M56" s="66" t="s">
+      <c r="N56" s="66" t="s">
         <v>211</v>
-      </c>
-      <c r="N56" s="45" t="s">
-        <v>49</v>
       </c>
       <c r="O56" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="P56" s="61" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q56" s="63" t="s">
-        <v>37</v>
-      </c>
-      <c r="R56" s="61" t="s">
-        <v>37</v>
-      </c>
-      <c r="S56" s="63">
+      <c r="P56" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q56" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="R56" s="63" t="s">
+        <v>37</v>
+      </c>
+      <c r="S56" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="T56" s="63">
         <v>35.840000000000003</v>
       </c>
-      <c r="T56" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="U56" s="45"/>
-      <c r="V56" s="41"/>
+      <c r="U56" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="V56" s="45"/>
       <c r="W56" s="41"/>
       <c r="X56" s="41"/>
       <c r="Y56" s="41"/>
@@ -5438,8 +5658,9 @@
       <c r="AB56" s="41"/>
       <c r="AC56" s="41"/>
       <c r="AD56" s="41"/>
-    </row>
-    <row r="57" spans="1:30" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="AE56" s="41"/>
+    </row>
+    <row r="57" spans="1:31" s="14" customFormat="1" ht="36.75" hidden="1" customHeight="1">
       <c r="A57" s="46">
         <v>2026</v>
       </c>
@@ -5449,59 +5670,62 @@
       <c r="C57" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="D57" s="37" t="s">
+      <c r="D57" s="42">
+        <f t="shared" si="0"/>
+        <v>1.07</v>
+      </c>
+      <c r="E57" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="E57" s="37" t="s">
+      <c r="F57" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="F57" s="48">
+      <c r="G57" s="48">
         <v>2025003050060</v>
       </c>
-      <c r="G57" s="37" t="s">
+      <c r="H57" s="37" t="s">
         <v>214</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5567719862</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2783859931</v>
       </c>
-      <c r="J57" s="50" t="s">
+      <c r="K57" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K57" s="61" t="s">
+      <c r="L57" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="L57" s="24">
+      <c r="M57" s="24">
         <v>46048</v>
       </c>
-      <c r="M57" s="66" t="s">
+      <c r="N57" s="66" t="s">
         <v>194</v>
       </c>
-      <c r="N57" s="45">
+      <c r="O57" s="45">
         <v>15.02</v>
       </c>
-      <c r="O57" s="45">
+      <c r="P57" s="45">
         <v>30</v>
       </c>
-      <c r="P57" s="61">
+      <c r="Q57" s="61">
         <v>46.43</v>
       </c>
-      <c r="Q57" s="63">
+      <c r="R57" s="63">
         <v>30</v>
       </c>
-      <c r="R57" s="61">
+      <c r="S57" s="61">
         <v>46.43</v>
       </c>
-      <c r="S57" s="63">
+      <c r="T57" s="63">
         <v>30</v>
       </c>
-      <c r="T57" s="58">
+      <c r="U57" s="58">
         <v>0</v>
       </c>
-      <c r="U57" s="45"/>
-      <c r="V57" s="41"/>
+      <c r="V57" s="45"/>
       <c r="W57" s="41"/>
       <c r="X57" s="41"/>
       <c r="Y57" s="41"/>
@@ -5510,8 +5734,9 @@
       <c r="AB57" s="41"/>
       <c r="AC57" s="41"/>
       <c r="AD57" s="41"/>
-    </row>
-    <row r="58" spans="1:30" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="AE57" s="41"/>
+    </row>
+    <row r="58" spans="1:31" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A58" s="46">
         <v>2026</v>
       </c>
@@ -5521,59 +5746,62 @@
       <c r="C58" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="D58" s="37" t="s">
+      <c r="D58" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E58" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E58" s="37" t="s">
+      <c r="F58" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F58" s="48">
+      <c r="G58" s="48">
         <v>2025003050047</v>
       </c>
-      <c r="G58" s="37" t="s">
+      <c r="H58" s="37" t="s">
         <v>216</v>
       </c>
-      <c r="H58" s="49">
+      <c r="I58" s="49">
         <v>2577210949</v>
       </c>
-      <c r="I58" s="49">
+      <c r="J58" s="49">
         <v>2557210949</v>
       </c>
-      <c r="J58" s="50" t="s">
+      <c r="K58" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K58" s="61" t="s">
+      <c r="L58" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="L58" s="24">
+      <c r="M58" s="24">
         <v>46072</v>
       </c>
-      <c r="M58" s="67">
+      <c r="N58" s="67">
         <v>46242</v>
       </c>
-      <c r="N58" s="45">
+      <c r="O58" s="45">
         <v>47.59</v>
       </c>
-      <c r="O58" s="45">
+      <c r="P58" s="45">
         <v>45.92</v>
       </c>
-      <c r="P58" s="61">
+      <c r="Q58" s="61">
         <v>86.08</v>
       </c>
-      <c r="Q58" s="63">
+      <c r="R58" s="63">
         <v>51.1</v>
       </c>
-      <c r="R58" s="63">
+      <c r="S58" s="63">
         <v>96.48</v>
       </c>
-      <c r="S58" s="63">
+      <c r="T58" s="63">
         <v>91.56</v>
       </c>
-      <c r="T58" s="58">
+      <c r="U58" s="58">
         <v>96.4</v>
       </c>
-      <c r="U58" s="45"/>
-      <c r="V58" s="41"/>
+      <c r="V58" s="45"/>
       <c r="W58" s="41"/>
       <c r="X58" s="41"/>
       <c r="Y58" s="41"/>
@@ -5582,8 +5810,9 @@
       <c r="AB58" s="41"/>
       <c r="AC58" s="41"/>
       <c r="AD58" s="41"/>
-    </row>
-    <row r="59" spans="1:30" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="AE58" s="41"/>
+    </row>
+    <row r="59" spans="1:31" s="14" customFormat="1" ht="36.75" hidden="1" customHeight="1">
       <c r="A59" s="42">
         <v>2026</v>
       </c>
@@ -5593,59 +5822,62 @@
       <c r="C59" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="D59" s="37" t="s">
+      <c r="D59" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E59" s="37" t="s">
         <v>209</v>
       </c>
-      <c r="E59" s="37" t="s">
+      <c r="F59" s="37" t="s">
         <v>148</v>
       </c>
-      <c r="F59" s="48">
+      <c r="G59" s="48">
         <v>2025003050059</v>
       </c>
-      <c r="G59" s="37" t="s">
+      <c r="H59" s="37" t="s">
         <v>217</v>
-      </c>
-      <c r="H59" s="2">
-        <v>6759815490</v>
       </c>
       <c r="I59" s="2">
         <v>6759815490</v>
       </c>
-      <c r="J59" s="27" t="s">
+      <c r="J59" s="2">
+        <v>6759815490</v>
+      </c>
+      <c r="K59" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="K59" s="61" t="s">
+      <c r="L59" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="L59" s="24">
+      <c r="M59" s="24">
         <v>46077</v>
       </c>
-      <c r="M59" s="66" t="s">
+      <c r="N59" s="66" t="s">
         <v>218</v>
       </c>
-      <c r="N59" s="45">
+      <c r="O59" s="45">
         <v>39.979999999999997</v>
       </c>
-      <c r="O59" s="45">
+      <c r="P59" s="45">
         <v>54.89</v>
       </c>
-      <c r="P59" s="61">
+      <c r="Q59" s="61">
         <v>45.86</v>
       </c>
-      <c r="Q59" s="63">
+      <c r="R59" s="63">
         <v>65.739999999999995</v>
       </c>
-      <c r="R59" s="63">
+      <c r="S59" s="63">
         <v>56.8</v>
       </c>
-      <c r="S59" s="63">
+      <c r="T59" s="63">
         <v>70.2</v>
       </c>
-      <c r="T59" s="58">
+      <c r="U59" s="58">
         <v>60</v>
       </c>
-      <c r="U59" s="45"/>
-      <c r="V59" s="41"/>
+      <c r="V59" s="45"/>
       <c r="W59" s="41"/>
       <c r="X59" s="41"/>
       <c r="Y59" s="41"/>
@@ -5654,8 +5886,9 @@
       <c r="AB59" s="41"/>
       <c r="AC59" s="41"/>
       <c r="AD59" s="41"/>
-    </row>
-    <row r="60" spans="1:30" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="AE59" s="41"/>
+    </row>
+    <row r="60" spans="1:31" s="14" customFormat="1" ht="36.75" hidden="1" customHeight="1">
       <c r="A60" s="46">
         <v>2026</v>
       </c>
@@ -5665,59 +5898,62 @@
       <c r="C60" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="D60" s="37" t="s">
+      <c r="D60" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E60" s="37" t="s">
         <v>220</v>
       </c>
-      <c r="E60" s="37" t="s">
+      <c r="F60" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="F60" s="48">
+      <c r="G60" s="48">
         <v>2025003050058</v>
       </c>
-      <c r="G60" s="37" t="s">
+      <c r="H60" s="37" t="s">
         <v>221</v>
-      </c>
-      <c r="H60" s="49">
-        <v>1956028276</v>
       </c>
       <c r="I60" s="49">
         <v>1956028276</v>
       </c>
-      <c r="J60" s="28" t="s">
+      <c r="J60" s="49">
+        <v>1956028276</v>
+      </c>
+      <c r="K60" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="K60" s="61" t="s">
+      <c r="L60" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="L60" s="24">
+      <c r="M60" s="24">
         <v>46073</v>
       </c>
-      <c r="M60" s="66" t="s">
+      <c r="N60" s="66" t="s">
         <v>222</v>
       </c>
-      <c r="N60" s="45">
+      <c r="O60" s="45">
         <v>6.94</v>
       </c>
-      <c r="O60" s="45">
+      <c r="P60" s="45">
         <v>25</v>
       </c>
-      <c r="P60" s="61">
+      <c r="Q60" s="61">
         <v>28.56</v>
       </c>
-      <c r="Q60" s="63">
+      <c r="R60" s="63">
         <v>44.26</v>
       </c>
-      <c r="R60" s="63">
+      <c r="S60" s="63">
         <v>47.61</v>
       </c>
-      <c r="S60" s="63">
+      <c r="T60" s="63">
         <v>55.67</v>
       </c>
-      <c r="T60" s="58">
+      <c r="U60" s="58">
         <v>60</v>
       </c>
-      <c r="U60" s="45"/>
-      <c r="V60" s="41"/>
+      <c r="V60" s="45"/>
       <c r="W60" s="41"/>
       <c r="X60" s="41"/>
       <c r="Y60" s="41"/>
@@ -5726,8 +5962,9 @@
       <c r="AB60" s="41"/>
       <c r="AC60" s="41"/>
       <c r="AD60" s="41"/>
-    </row>
-    <row r="61" spans="1:30" ht="36.75" customHeight="1">
+      <c r="AE60" s="41"/>
+    </row>
+    <row r="61" spans="1:31" ht="36.75" hidden="1" customHeight="1">
       <c r="A61" s="46">
         <v>2026</v>
       </c>
@@ -5737,59 +5974,62 @@
       <c r="C61" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="D61" s="17" t="s">
+      <c r="D61" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E61" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="F61" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="G61" s="48">
+        <v>2025003050037</v>
+      </c>
+      <c r="H61" s="37" t="s">
         <v>223</v>
-      </c>
-      <c r="E61" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="F61" s="48">
-        <v>2025003050037</v>
-      </c>
-      <c r="G61" s="37" t="s">
-        <v>224</v>
-      </c>
-      <c r="H61" s="2">
-        <v>4919153330</v>
       </c>
       <c r="I61" s="2">
         <v>4919153330</v>
       </c>
-      <c r="J61" s="28" t="s">
+      <c r="J61" s="2">
+        <v>4919153330</v>
+      </c>
+      <c r="K61" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="K61" s="61" t="s">
+      <c r="L61" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="L61" s="24">
+      <c r="M61" s="24">
         <v>46073</v>
       </c>
-      <c r="M61" s="67">
+      <c r="N61" s="67">
         <v>46367</v>
       </c>
-      <c r="N61" s="45">
+      <c r="O61" s="45">
         <v>6.37</v>
       </c>
-      <c r="O61" s="45">
+      <c r="P61" s="45">
         <v>29.54</v>
       </c>
-      <c r="P61" s="61">
+      <c r="Q61" s="61">
         <v>10.3</v>
       </c>
-      <c r="Q61" s="63">
+      <c r="R61" s="63">
         <v>35.76</v>
       </c>
-      <c r="R61" s="63">
+      <c r="S61" s="63">
         <v>30.31</v>
       </c>
-      <c r="S61" s="63">
+      <c r="T61" s="63">
         <v>52.91</v>
       </c>
-      <c r="T61" s="58">
+      <c r="U61" s="58">
         <v>60</v>
       </c>
-      <c r="U61" s="45"/>
-      <c r="V61" s="41"/>
+      <c r="V61" s="45"/>
       <c r="W61" s="41"/>
       <c r="X61" s="41"/>
       <c r="Y61" s="41"/>
@@ -5798,70 +6038,74 @@
       <c r="AB61" s="41"/>
       <c r="AC61" s="41"/>
       <c r="AD61" s="41"/>
-    </row>
-    <row r="62" spans="1:30" ht="36.75" customHeight="1">
+      <c r="AE61" s="41"/>
+    </row>
+    <row r="62" spans="1:31" ht="36.75" hidden="1" customHeight="1">
       <c r="A62" s="46">
         <v>2026</v>
       </c>
       <c r="B62" s="37" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C62" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="D62" s="17" t="s">
-        <v>226</v>
+      <c r="D62" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E62" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="F62" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="F62" s="48">
+      <c r="G62" s="48">
         <v>2025003050037</v>
       </c>
-      <c r="G62" s="37" t="s">
-        <v>224</v>
-      </c>
-      <c r="H62" s="2">
-        <v>4814470012</v>
+      <c r="H62" s="37" t="s">
+        <v>223</v>
       </c>
       <c r="I62" s="2">
         <v>4814470012</v>
       </c>
-      <c r="J62" s="28" t="s">
+      <c r="J62" s="2">
+        <v>4814470012</v>
+      </c>
+      <c r="K62" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="K62" s="61" t="s">
+      <c r="L62" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="L62" s="24">
+      <c r="M62" s="24">
         <v>46073</v>
       </c>
-      <c r="M62" s="67">
+      <c r="N62" s="67">
         <v>46367</v>
       </c>
-      <c r="N62" s="45">
+      <c r="O62" s="45">
         <v>6.37</v>
       </c>
-      <c r="O62" s="45">
+      <c r="P62" s="45">
         <v>29.54</v>
       </c>
-      <c r="P62" s="61">
+      <c r="Q62" s="61">
         <v>10.3</v>
       </c>
-      <c r="Q62" s="63">
+      <c r="R62" s="63">
         <v>35.76</v>
       </c>
-      <c r="R62" s="63">
+      <c r="S62" s="63">
         <v>30.31</v>
       </c>
-      <c r="S62" s="63">
+      <c r="T62" s="63">
         <v>52.91</v>
       </c>
-      <c r="T62" s="58">
+      <c r="U62" s="58">
         <v>60</v>
       </c>
-      <c r="U62" s="45"/>
-      <c r="V62" s="41"/>
+      <c r="V62" s="45"/>
       <c r="W62" s="41"/>
       <c r="X62" s="41"/>
       <c r="Y62" s="41"/>
@@ -5870,8 +6114,9 @@
       <c r="AB62" s="41"/>
       <c r="AC62" s="41"/>
       <c r="AD62" s="41"/>
-    </row>
-    <row r="63" spans="1:30" ht="36.75" customHeight="1">
+      <c r="AE62" s="41"/>
+    </row>
+    <row r="63" spans="1:31" ht="36.75" hidden="1" customHeight="1">
       <c r="A63" s="46">
         <v>2026</v>
       </c>
@@ -5881,59 +6126,62 @@
       <c r="C63" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="D63" s="37" t="s">
+      <c r="D63" s="42">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="E63" s="37" t="s">
+        <v>225</v>
+      </c>
+      <c r="F63" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="G63" s="48">
+        <v>2026003050010</v>
+      </c>
+      <c r="H63" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="I63" s="49">
+        <v>8659084152</v>
+      </c>
+      <c r="J63" s="49">
+        <v>7659084152</v>
+      </c>
+      <c r="K63" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="L63" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="M63" s="24">
+        <v>46105</v>
+      </c>
+      <c r="N63" s="66" t="s">
         <v>227</v>
       </c>
-      <c r="E63" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="F63" s="48">
-        <v>2026003050010</v>
-      </c>
-      <c r="G63" s="37" t="s">
-        <v>228</v>
-      </c>
-      <c r="H63" s="49">
-        <v>8659084152</v>
-      </c>
-      <c r="I63" s="49">
-        <v>7659084152</v>
-      </c>
-      <c r="J63" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="K63" s="61" t="s">
-        <v>45</v>
-      </c>
-      <c r="L63" s="24">
-        <v>46105</v>
-      </c>
-      <c r="M63" s="66" t="s">
-        <v>229</v>
-      </c>
-      <c r="N63" s="45">
+      <c r="O63" s="45">
         <v>8.81</v>
       </c>
-      <c r="O63" s="45">
+      <c r="P63" s="45">
         <v>36</v>
       </c>
-      <c r="P63" s="61">
+      <c r="Q63" s="61">
         <v>16.66</v>
       </c>
-      <c r="Q63" s="63">
-        <v>37</v>
-      </c>
       <c r="R63" s="63">
+        <v>37</v>
+      </c>
+      <c r="S63" s="63">
         <v>31.53</v>
       </c>
-      <c r="S63" s="63">
+      <c r="T63" s="63">
         <v>38</v>
       </c>
-      <c r="T63" s="58">
-        <v>100</v>
-      </c>
-      <c r="U63" s="45"/>
-      <c r="V63" s="41"/>
+      <c r="U63" s="58">
+        <v>100</v>
+      </c>
+      <c r="V63" s="45"/>
       <c r="W63" s="41"/>
       <c r="X63" s="41"/>
       <c r="Y63" s="41"/>
@@ -5942,70 +6190,74 @@
       <c r="AB63" s="41"/>
       <c r="AC63" s="41"/>
       <c r="AD63" s="41"/>
-    </row>
-    <row r="64" spans="1:30" ht="36.75" customHeight="1">
+      <c r="AE63" s="41"/>
+    </row>
+    <row r="64" spans="1:31" ht="36.75" customHeight="1">
       <c r="A64" s="46">
         <v>2026</v>
       </c>
       <c r="B64" s="37" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C64" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="D64" s="37" t="s">
+      <c r="D64" s="42">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E64" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="E64" s="17" t="s">
+      <c r="F64" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="F64" s="48">
+      <c r="G64" s="48">
         <v>2026003050009</v>
       </c>
-      <c r="G64" s="37" t="s">
-        <v>231</v>
-      </c>
-      <c r="H64" s="49">
+      <c r="H64" s="37" t="s">
+        <v>229</v>
+      </c>
+      <c r="I64" s="49">
         <v>5112178665</v>
       </c>
-      <c r="I64" s="49">
+      <c r="J64" s="49">
         <v>4500000000</v>
       </c>
-      <c r="J64" s="50" t="s">
+      <c r="K64" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K64" s="61" t="s">
+      <c r="L64" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="L64" s="24">
+      <c r="M64" s="24">
         <v>46107</v>
       </c>
-      <c r="M64" s="67">
+      <c r="N64" s="67">
         <v>46480</v>
       </c>
-      <c r="N64" s="45">
+      <c r="O64" s="45">
         <v>4.78</v>
       </c>
-      <c r="O64" s="45">
+      <c r="P64" s="45">
         <v>18.21</v>
       </c>
-      <c r="P64" s="61">
+      <c r="Q64" s="61">
         <v>14.94</v>
       </c>
-      <c r="Q64" s="63">
+      <c r="R64" s="63">
         <v>19.34</v>
       </c>
-      <c r="R64" s="63">
+      <c r="S64" s="63">
         <v>27.9</v>
       </c>
-      <c r="S64" s="63">
+      <c r="T64" s="63">
         <v>31.13</v>
       </c>
-      <c r="T64" s="58">
-        <v>100</v>
-      </c>
-      <c r="U64" s="45"/>
-      <c r="V64" s="41"/>
+      <c r="U64" s="58">
+        <v>100</v>
+      </c>
+      <c r="V64" s="45"/>
       <c r="W64" s="41"/>
       <c r="X64" s="41"/>
       <c r="Y64" s="41"/>
@@ -6014,114 +6266,120 @@
       <c r="AB64" s="41"/>
       <c r="AC64" s="41"/>
       <c r="AD64" s="41"/>
-    </row>
-    <row r="65" spans="1:22" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="AE64" s="41"/>
+    </row>
+    <row r="65" spans="1:23" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A65" s="46">
         <v>2026</v>
       </c>
       <c r="B65" s="37" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C65" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="17" t="s">
+      <c r="D65" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E65" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="E65" s="17" t="s">
+      <c r="F65" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="F65" s="48">
+      <c r="G65" s="48">
         <v>2025003050057</v>
       </c>
-      <c r="G65" s="37" t="s">
-        <v>233</v>
-      </c>
-      <c r="H65" s="2">
+      <c r="H65" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="I65" s="2">
         <v>2205897938</v>
       </c>
-      <c r="I65" s="49">
+      <c r="J65" s="49">
         <v>1500000000</v>
       </c>
-      <c r="J65" s="50" t="s">
+      <c r="K65" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K65" s="61" t="s">
+      <c r="L65" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="L65" s="24">
+      <c r="M65" s="24">
         <v>46299</v>
       </c>
-      <c r="M65" s="67">
+      <c r="N65" s="67">
         <v>46245</v>
       </c>
-      <c r="N65" s="45" t="s">
-        <v>37</v>
-      </c>
       <c r="O65" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="P65" s="61">
+      <c r="P65" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q65" s="61">
         <v>19.09</v>
       </c>
-      <c r="Q65" s="63">
+      <c r="R65" s="63">
         <v>36.659999999999997</v>
       </c>
-      <c r="R65" s="63">
+      <c r="S65" s="63">
         <v>57.61</v>
       </c>
-      <c r="S65" s="63">
+      <c r="T65" s="63">
         <v>76.37</v>
       </c>
-      <c r="T65" s="58">
-        <v>100</v>
-      </c>
-      <c r="U65" s="45"/>
-      <c r="V65" s="41"/>
-    </row>
-    <row r="66" spans="1:22" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U65" s="58">
+        <v>100</v>
+      </c>
+      <c r="V65" s="45"/>
+      <c r="W65" s="41"/>
+    </row>
+    <row r="66" spans="1:23" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A66" s="46">
         <v>2026</v>
       </c>
       <c r="B66" s="37" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C66" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="D66" s="37" t="s">
+      <c r="D66" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E66" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E66" s="17" t="s">
+      <c r="F66" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="F66" s="48">
+      <c r="G66" s="48">
         <v>2025003050052</v>
       </c>
-      <c r="G66" s="37" t="s">
-        <v>235</v>
-      </c>
-      <c r="H66" s="2">
+      <c r="H66" s="37" t="s">
+        <v>233</v>
+      </c>
+      <c r="I66" s="2">
         <v>1865730932</v>
       </c>
-      <c r="I66" s="2">
+      <c r="J66" s="2">
         <v>1500000000</v>
       </c>
-      <c r="J66" s="50" t="s">
+      <c r="K66" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K66" s="61" t="s">
+      <c r="L66" s="61" t="s">
         <v>138</v>
       </c>
-      <c r="L66" s="24">
+      <c r="M66" s="24">
         <v>46132</v>
       </c>
-      <c r="M66" s="66" t="s">
+      <c r="N66" s="66" t="s">
         <v>69</v>
       </c>
-      <c r="N66" s="45" t="s">
-        <v>37</v>
-      </c>
       <c r="O66" s="45" t="s">
         <v>37</v>
       </c>
@@ -6137,55 +6395,59 @@
       <c r="S66" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="T66" s="58">
-        <v>100</v>
-      </c>
-      <c r="U66" s="45"/>
-      <c r="V66" s="41"/>
-    </row>
-    <row r="67" spans="1:22" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="T66" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="U66" s="58">
+        <v>100</v>
+      </c>
+      <c r="V66" s="45"/>
+      <c r="W66" s="41"/>
+    </row>
+    <row r="67" spans="1:23" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A67" s="46">
         <v>2026</v>
       </c>
       <c r="B67" s="37" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C67" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="D67" s="37" t="s">
+      <c r="D67" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E67" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E67" s="17" t="s">
+      <c r="F67" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="F67" s="48">
+      <c r="G67" s="48">
         <v>2026003050017</v>
       </c>
-      <c r="G67" s="37" t="s">
-        <v>237</v>
-      </c>
-      <c r="H67" s="3">
+      <c r="H67" s="37" t="s">
+        <v>235</v>
+      </c>
+      <c r="I67" s="3">
         <v>2177276654</v>
       </c>
-      <c r="I67" s="3">
+      <c r="J67" s="3">
         <v>1677276654</v>
       </c>
-      <c r="J67" s="45" t="s">
+      <c r="K67" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="K67" s="61" t="s">
+      <c r="L67" s="61" t="s">
         <v>138</v>
       </c>
-      <c r="L67" s="24">
+      <c r="M67" s="24">
         <v>46147</v>
       </c>
-      <c r="M67" s="66" t="s">
+      <c r="N67" s="66" t="s">
         <v>69</v>
       </c>
-      <c r="N67" s="45" t="s">
-        <v>37</v>
-      </c>
       <c r="O67" s="45" t="s">
         <v>37</v>
       </c>
@@ -6198,122 +6460,130 @@
       <c r="R67" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="S67" s="45">
+      <c r="S67" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="T67" s="45">
         <v>45.33</v>
       </c>
-      <c r="T67" s="58">
+      <c r="U67" s="58">
         <v>78.599999999999994</v>
       </c>
-      <c r="U67" s="45"/>
-      <c r="V67" s="41"/>
-    </row>
-    <row r="68" spans="1:22" ht="36.75" customHeight="1">
+      <c r="V67" s="45"/>
+      <c r="W67" s="41"/>
+    </row>
+    <row r="68" spans="1:23" ht="36.75" customHeight="1">
       <c r="A68" s="46">
         <v>2026</v>
       </c>
       <c r="B68" s="37" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C68" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="D68" s="37" t="s">
+      <c r="D68" s="42">
+        <f t="shared" ref="D68:D83" si="1">IF(ISNUMBER(E68),E68,IFERROR(VALUE(LEFT(E68,FIND(" ",E68)-1)),1))</f>
+        <v>3</v>
+      </c>
+      <c r="E68" s="37" t="s">
         <v>74</v>
       </c>
-      <c r="E68" s="17" t="s">
+      <c r="F68" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="F68" s="48">
+      <c r="G68" s="48">
         <v>2026003050018</v>
       </c>
-      <c r="G68" s="37" t="s">
-        <v>239</v>
-      </c>
-      <c r="H68" s="49">
-        <v>8022406899</v>
+      <c r="H68" s="37" t="s">
+        <v>237</v>
       </c>
       <c r="I68" s="49">
         <v>8022406899</v>
       </c>
-      <c r="J68" s="50" t="s">
+      <c r="J68" s="49">
+        <v>8022406899</v>
+      </c>
+      <c r="K68" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K68" s="61" t="s">
+      <c r="L68" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="L68" s="24">
+      <c r="M68" s="24">
         <v>46129</v>
       </c>
-      <c r="M68" s="66" t="s">
-        <v>240</v>
-      </c>
-      <c r="N68" s="45">
+      <c r="N68" s="66" t="s">
+        <v>238</v>
+      </c>
+      <c r="O68" s="45">
         <v>15.5</v>
       </c>
-      <c r="O68" s="45">
+      <c r="P68" s="45">
         <v>46.93</v>
       </c>
-      <c r="P68" s="61">
+      <c r="Q68" s="61">
         <v>47.67</v>
       </c>
-      <c r="Q68" s="63">
+      <c r="R68" s="63">
         <v>46.93</v>
       </c>
-      <c r="R68" s="63">
+      <c r="S68" s="63">
         <v>51.93</v>
       </c>
-      <c r="S68" s="63">
+      <c r="T68" s="63">
         <v>63.72</v>
       </c>
-      <c r="T68" s="58">
-        <v>100</v>
-      </c>
-      <c r="U68" s="45"/>
-      <c r="V68" s="41"/>
-    </row>
-    <row r="69" spans="1:22" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U68" s="58">
+        <v>100</v>
+      </c>
+      <c r="V68" s="45"/>
+      <c r="W68" s="41"/>
+    </row>
+    <row r="69" spans="1:23" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A69" s="46">
         <v>2026</v>
       </c>
       <c r="B69" s="37" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C69" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="D69" s="37" t="s">
+      <c r="D69" s="42">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E69" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E69" s="37" t="s">
+      <c r="F69" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F69" s="48">
+      <c r="G69" s="48">
         <v>2026003050021</v>
       </c>
-      <c r="G69" s="37" t="s">
-        <v>241</v>
-      </c>
-      <c r="H69" s="2">
+      <c r="H69" s="37" t="s">
+        <v>239</v>
+      </c>
+      <c r="I69" s="2">
         <v>2356550945</v>
       </c>
-      <c r="I69" s="2">
+      <c r="J69" s="2">
         <v>1768550945</v>
       </c>
-      <c r="J69" s="50" t="s">
+      <c r="K69" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K69" s="61" t="s">
+      <c r="L69" s="61" t="s">
         <v>138</v>
       </c>
-      <c r="L69" s="24">
+      <c r="M69" s="24">
         <v>46149</v>
       </c>
-      <c r="M69" s="66" t="s">
+      <c r="N69" s="66" t="s">
         <v>69</v>
       </c>
-      <c r="N69" s="45" t="s">
-        <v>37</v>
-      </c>
       <c r="O69" s="45" t="s">
         <v>37</v>
       </c>
@@ -6329,119 +6599,127 @@
       <c r="S69" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="T69" s="58">
+      <c r="T69" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="U69" s="58">
         <v>75</v>
       </c>
-      <c r="U69" s="45"/>
-      <c r="V69" s="41"/>
-    </row>
-    <row r="70" spans="1:22" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="V69" s="45"/>
+      <c r="W69" s="41"/>
+    </row>
+    <row r="70" spans="1:23" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A70" s="46">
         <v>2026</v>
       </c>
       <c r="B70" s="47" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C70" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="D70" s="37" t="s">
+      <c r="D70" s="42">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E70" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E70" s="37" t="s">
+      <c r="F70" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F70" s="48">
+      <c r="G70" s="48">
         <v>2026003050005</v>
       </c>
-      <c r="G70" s="37" t="s">
-        <v>243</v>
-      </c>
-      <c r="H70" s="43">
+      <c r="H70" s="37" t="s">
+        <v>241</v>
+      </c>
+      <c r="I70" s="43">
         <v>2126428620</v>
       </c>
-      <c r="I70" s="43">
+      <c r="J70" s="43">
         <v>1821081885</v>
       </c>
-      <c r="J70" s="50" t="s">
+      <c r="K70" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K70" s="61" t="s">
+      <c r="L70" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="L70" s="24">
+      <c r="M70" s="24">
         <v>46191</v>
       </c>
-      <c r="M70" s="66" t="s">
-        <v>244</v>
-      </c>
-      <c r="N70" s="45" t="s">
-        <v>37</v>
+      <c r="N70" s="66" t="s">
+        <v>242</v>
       </c>
       <c r="O70" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="P70" s="61">
+      <c r="P70" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q70" s="61">
         <v>11</v>
       </c>
-      <c r="Q70" s="63">
+      <c r="R70" s="63">
         <v>45.06</v>
       </c>
-      <c r="R70" s="63">
+      <c r="S70" s="63">
         <v>43</v>
       </c>
-      <c r="S70" s="63">
+      <c r="T70" s="63">
         <v>68.260000000000005</v>
       </c>
-      <c r="T70" s="58">
-        <v>100</v>
-      </c>
-      <c r="U70" s="45"/>
-      <c r="V70" s="41"/>
-    </row>
-    <row r="71" spans="1:22" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="U70" s="58">
+        <v>100</v>
+      </c>
+      <c r="V70" s="45"/>
+      <c r="W70" s="41"/>
+    </row>
+    <row r="71" spans="1:23" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A71" s="46">
         <v>2026</v>
       </c>
       <c r="B71" s="37" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C71" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="D71" s="37" t="s">
+      <c r="D71" s="42">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E71" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E71" s="37" t="s">
+      <c r="F71" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F71" s="48">
+      <c r="G71" s="48">
         <v>2026003050006</v>
       </c>
-      <c r="G71" s="37" t="s">
-        <v>246</v>
-      </c>
-      <c r="H71" s="2">
+      <c r="H71" s="37" t="s">
+        <v>244</v>
+      </c>
+      <c r="I71" s="2">
         <v>2495192913</v>
       </c>
-      <c r="I71" s="49">
+      <c r="J71" s="49">
         <v>2490192913</v>
       </c>
-      <c r="J71" s="50" t="s">
+      <c r="K71" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K71" s="61" t="s">
-        <v>247</v>
-      </c>
-      <c r="L71" s="24">
+      <c r="L71" s="61" t="s">
+        <v>245</v>
+      </c>
+      <c r="M71" s="24">
         <v>46170</v>
       </c>
-      <c r="M71" s="66" t="s">
+      <c r="N71" s="66" t="s">
         <v>69</v>
       </c>
-      <c r="N71" s="45" t="s">
-        <v>37</v>
-      </c>
       <c r="O71" s="45" t="s">
         <v>37</v>
       </c>
@@ -6457,13 +6735,16 @@
       <c r="S71" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="T71" s="58">
-        <v>100</v>
-      </c>
-      <c r="U71" s="45"/>
-      <c r="V71" s="41"/>
-    </row>
-    <row r="72" spans="1:22" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="T71" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="U71" s="58">
+        <v>100</v>
+      </c>
+      <c r="V71" s="45"/>
+      <c r="W71" s="41"/>
+    </row>
+    <row r="72" spans="1:23" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A72" s="46">
         <v>2026</v>
       </c>
@@ -6473,103 +6754,108 @@
       <c r="C72" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D72" s="6" t="s">
+      <c r="D72" s="42">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G72" s="56">
+        <v>2026003050011</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="I72" s="15">
+        <v>2095882218</v>
+      </c>
+      <c r="J72" s="49">
+        <v>1995882218</v>
+      </c>
+      <c r="K72" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="L72" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="M72" s="24">
+        <v>46132</v>
+      </c>
+      <c r="N72" s="66" t="s">
         <v>248</v>
       </c>
-      <c r="E72" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F72" s="56">
-        <v>2026003050011</v>
-      </c>
-      <c r="G72" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="H72" s="15">
-        <v>2095882218</v>
-      </c>
-      <c r="I72" s="49">
-        <v>1995882218</v>
-      </c>
-      <c r="J72" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="K72" s="61" t="s">
-        <v>45</v>
-      </c>
-      <c r="L72" s="24">
-        <v>46132</v>
-      </c>
-      <c r="M72" s="66" t="s">
-        <v>250</v>
-      </c>
-      <c r="N72" s="45" t="s">
-        <v>37</v>
-      </c>
       <c r="O72" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="P72" s="61">
+      <c r="P72" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q72" s="61">
         <v>0</v>
       </c>
-      <c r="Q72" s="63">
+      <c r="R72" s="63">
         <v>35.729999999999997</v>
       </c>
-      <c r="R72" s="61">
+      <c r="S72" s="61">
         <v>0</v>
       </c>
-      <c r="S72" s="63">
+      <c r="T72" s="63">
         <v>35.729999999999997</v>
       </c>
-      <c r="T72" s="58">
+      <c r="U72" s="58">
         <v>40</v>
       </c>
-      <c r="U72" s="45"/>
-      <c r="V72" s="41"/>
-    </row>
-    <row r="73" spans="1:22" ht="36.75" customHeight="1">
+      <c r="V72" s="45"/>
+      <c r="W72" s="41"/>
+    </row>
+    <row r="73" spans="1:23" ht="36.75" hidden="1" customHeight="1">
       <c r="A73" s="46">
         <v>2026</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D73" s="6" t="s">
-        <v>252</v>
+      <c r="D73" s="42">
+        <f t="shared" si="1"/>
+        <v>0.98</v>
       </c>
       <c r="E73" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="F73" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="F73" s="56">
+      <c r="G73" s="56">
         <v>2026003050014</v>
       </c>
-      <c r="G73" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="H73" s="10">
+      <c r="H73" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="I73" s="10">
         <v>5482855957</v>
       </c>
-      <c r="I73" s="2">
+      <c r="J73" s="2">
         <v>4386284766</v>
       </c>
-      <c r="J73" s="50" t="s">
+      <c r="K73" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K73" s="61" t="s">
+      <c r="L73" s="61" t="s">
         <v>138</v>
       </c>
-      <c r="L73" s="24">
+      <c r="M73" s="24">
         <v>46189</v>
       </c>
-      <c r="M73" s="66" t="s">
+      <c r="N73" s="66" t="s">
         <v>69</v>
       </c>
-      <c r="N73" s="45" t="s">
-        <v>37</v>
-      </c>
       <c r="O73" s="45" t="s">
         <v>37</v>
       </c>
@@ -6585,62 +6871,66 @@
       <c r="S73" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="T73" s="58">
-        <v>100</v>
-      </c>
-      <c r="U73" s="45"/>
-      <c r="V73" s="41"/>
-    </row>
-    <row r="74" spans="1:22" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="T73" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="U73" s="58">
+        <v>100</v>
+      </c>
+      <c r="V73" s="45"/>
+      <c r="W73" s="41"/>
+    </row>
+    <row r="74" spans="1:23" s="14" customFormat="1" ht="36.75" hidden="1" customHeight="1">
       <c r="A74" s="46">
         <v>2026</v>
       </c>
       <c r="B74" s="37" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C74" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="D74" s="17" t="s">
-        <v>256</v>
-      </c>
-      <c r="E74" s="6" t="s">
+      <c r="D74" s="42">
+        <f t="shared" si="1"/>
+        <v>0.54</v>
+      </c>
+      <c r="E74" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="F74" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="F74" s="48">
+      <c r="G74" s="48">
         <v>2026003050008</v>
       </c>
-      <c r="G74" s="37" t="s">
-        <v>257</v>
-      </c>
-      <c r="H74" s="2">
+      <c r="H74" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="I74" s="2">
         <v>2300078297</v>
       </c>
-      <c r="I74" s="49">
+      <c r="J74" s="49">
         <v>2250078297</v>
       </c>
-      <c r="J74" s="50" t="s">
+      <c r="K74" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K74" s="61" t="s">
+      <c r="L74" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="L74" s="24">
+      <c r="M74" s="24">
         <v>46175</v>
       </c>
-      <c r="M74" s="66" t="s">
-        <v>258</v>
-      </c>
-      <c r="N74" s="45" t="s">
-        <v>37</v>
+      <c r="N74" s="66" t="s">
+        <v>255</v>
       </c>
       <c r="O74" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="P74" s="61">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="63">
+      <c r="P74" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q74" s="61">
         <v>0</v>
       </c>
       <c r="R74" s="63">
@@ -6649,55 +6939,59 @@
       <c r="S74" s="63">
         <v>0</v>
       </c>
-      <c r="T74" s="58">
-        <v>100</v>
-      </c>
-      <c r="U74" s="45"/>
-      <c r="V74" s="41"/>
-    </row>
-    <row r="75" spans="1:22" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="T74" s="63">
+        <v>0</v>
+      </c>
+      <c r="U74" s="58">
+        <v>100</v>
+      </c>
+      <c r="V74" s="45"/>
+      <c r="W74" s="41"/>
+    </row>
+    <row r="75" spans="1:23" s="14" customFormat="1" ht="36.75" hidden="1" customHeight="1">
       <c r="A75" s="46">
         <v>2026</v>
       </c>
       <c r="B75" s="37" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C75" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="D75" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="E75" s="17" t="s">
+      <c r="D75" s="42">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E75" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="F75" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="F75" s="48">
+      <c r="G75" s="48">
         <v>2026003050002</v>
       </c>
-      <c r="G75" s="37" t="s">
-        <v>261</v>
-      </c>
-      <c r="H75" s="49">
-        <v>1408385533</v>
+      <c r="H75" s="37" t="s">
+        <v>258</v>
       </c>
       <c r="I75" s="49">
         <v>1408385533</v>
       </c>
-      <c r="J75" s="50" t="s">
+      <c r="J75" s="49">
+        <v>1408385533</v>
+      </c>
+      <c r="K75" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K75" s="61" t="s">
-        <v>247</v>
-      </c>
-      <c r="L75" s="24">
+      <c r="L75" s="61" t="s">
+        <v>245</v>
+      </c>
+      <c r="M75" s="24">
         <v>46185</v>
       </c>
-      <c r="M75" s="66" t="s">
+      <c r="N75" s="66" t="s">
         <v>69</v>
       </c>
-      <c r="N75" s="45" t="s">
-        <v>37</v>
-      </c>
       <c r="O75" s="45" t="s">
         <v>37</v>
       </c>
@@ -6713,55 +7007,59 @@
       <c r="S75" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="T75" s="58">
-        <v>100</v>
-      </c>
-      <c r="U75" s="45"/>
-      <c r="V75" s="41"/>
-    </row>
-    <row r="76" spans="1:22" ht="36.75" customHeight="1">
+      <c r="T75" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="U75" s="58">
+        <v>100</v>
+      </c>
+      <c r="V75" s="45"/>
+      <c r="W75" s="41"/>
+    </row>
+    <row r="76" spans="1:23" ht="36.75" hidden="1" customHeight="1">
       <c r="A76" s="46">
         <v>2026</v>
       </c>
       <c r="B76" s="37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C76" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="D76" s="17" t="s">
-        <v>263</v>
+      <c r="D76" s="42">
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="E76" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="F76" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="F76" s="48">
+      <c r="G76" s="48">
         <v>2026003050020</v>
       </c>
-      <c r="G76" s="37" t="s">
-        <v>264</v>
-      </c>
-      <c r="H76" s="49">
-        <v>8105380232</v>
+      <c r="H76" s="37" t="s">
+        <v>261</v>
       </c>
       <c r="I76" s="49">
         <v>8105380232</v>
       </c>
-      <c r="J76" s="50" t="s">
+      <c r="J76" s="49">
+        <v>8105380232</v>
+      </c>
+      <c r="K76" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K76" s="61" t="s">
-        <v>247</v>
-      </c>
-      <c r="L76" s="24">
+      <c r="L76" s="61" t="s">
+        <v>245</v>
+      </c>
+      <c r="M76" s="24">
         <v>46185</v>
       </c>
-      <c r="M76" s="66" t="s">
+      <c r="N76" s="66" t="s">
         <v>69</v>
       </c>
-      <c r="N76" s="45" t="s">
-        <v>37</v>
-      </c>
       <c r="O76" s="45" t="s">
         <v>37</v>
       </c>
@@ -6777,13 +7075,16 @@
       <c r="S76" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="T76" s="58">
-        <v>100</v>
-      </c>
-      <c r="U76" s="45"/>
-      <c r="V76" s="41"/>
-    </row>
-    <row r="77" spans="1:22" ht="36.75" customHeight="1">
+      <c r="T76" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="U76" s="58">
+        <v>100</v>
+      </c>
+      <c r="V76" s="45"/>
+      <c r="W76" s="41"/>
+    </row>
+    <row r="77" spans="1:23" ht="36.75" hidden="1" customHeight="1">
       <c r="A77" s="46">
         <v>2026</v>
       </c>
@@ -6793,38 +7094,39 @@
       <c r="C77" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="D77" s="17" t="s">
-        <v>265</v>
+      <c r="D77" s="42">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E77" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="F77" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="F77" s="48">
+      <c r="G77" s="48">
         <v>2026003050020</v>
       </c>
-      <c r="G77" s="37" t="s">
-        <v>264</v>
-      </c>
-      <c r="H77" s="2">
-        <v>4333614485</v>
+      <c r="H77" s="37" t="s">
+        <v>261</v>
       </c>
       <c r="I77" s="2">
         <v>4333614485</v>
       </c>
-      <c r="J77" s="50" t="s">
+      <c r="J77" s="2">
+        <v>4333614485</v>
+      </c>
+      <c r="K77" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K77" s="61" t="s">
-        <v>247</v>
-      </c>
-      <c r="L77" s="24">
+      <c r="L77" s="61" t="s">
+        <v>245</v>
+      </c>
+      <c r="M77" s="24">
         <v>46185</v>
       </c>
-      <c r="M77" s="66" t="s">
-        <v>254</v>
-      </c>
-      <c r="N77" s="45" t="s">
-        <v>37</v>
+      <c r="N77" s="66" t="s">
+        <v>252</v>
       </c>
       <c r="O77" s="45" t="s">
         <v>37</v>
@@ -6841,13 +7143,16 @@
       <c r="S77" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="T77" s="58">
-        <v>100</v>
-      </c>
-      <c r="U77" s="45"/>
-      <c r="V77" s="41"/>
-    </row>
-    <row r="78" spans="1:22" ht="36.75" customHeight="1">
+      <c r="T77" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="U77" s="58">
+        <v>100</v>
+      </c>
+      <c r="V77" s="45"/>
+      <c r="W77" s="41"/>
+    </row>
+    <row r="78" spans="1:23" ht="36.75" hidden="1" customHeight="1">
       <c r="A78" s="46">
         <v>2026</v>
       </c>
@@ -6857,38 +7162,39 @@
       <c r="C78" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="D78" s="17" t="s">
-        <v>266</v>
+      <c r="D78" s="42">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E78" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="F78" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="F78" s="48">
+      <c r="G78" s="48">
         <v>2026003050015</v>
       </c>
-      <c r="G78" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="H78" s="2">
-        <v>3806958402</v>
+      <c r="H78" s="37" t="s">
+        <v>264</v>
       </c>
       <c r="I78" s="2">
         <v>3806958402</v>
       </c>
-      <c r="J78" s="50" t="s">
+      <c r="J78" s="2">
+        <v>3806958402</v>
+      </c>
+      <c r="K78" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K78" s="61" t="s">
-        <v>247</v>
-      </c>
-      <c r="L78" s="24">
+      <c r="L78" s="61" t="s">
+        <v>245</v>
+      </c>
+      <c r="M78" s="24">
         <v>46185</v>
       </c>
-      <c r="M78" s="66" t="s">
-        <v>254</v>
-      </c>
-      <c r="N78" s="45" t="s">
-        <v>37</v>
+      <c r="N78" s="66" t="s">
+        <v>252</v>
       </c>
       <c r="O78" s="45" t="s">
         <v>37</v>
@@ -6905,54 +7211,58 @@
       <c r="S78" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="T78" s="58">
-        <v>100</v>
-      </c>
-      <c r="U78" s="45"/>
-      <c r="V78" s="41"/>
-    </row>
-    <row r="79" spans="1:22" ht="36.75" customHeight="1">
+      <c r="T78" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="U78" s="58">
+        <v>100</v>
+      </c>
+      <c r="V78" s="45"/>
+      <c r="W78" s="41"/>
+    </row>
+    <row r="79" spans="1:23" ht="36.75" hidden="1" customHeight="1">
       <c r="A79" s="46">
         <v>2026</v>
       </c>
       <c r="B79" s="37" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C79" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="D79" s="17" t="s">
-        <v>269</v>
+      <c r="D79" s="42">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E79" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="F79" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="F79" s="48">
+      <c r="G79" s="48">
         <v>2026003050015</v>
       </c>
-      <c r="G79" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="H79" s="2">
-        <v>2044483403</v>
+      <c r="H79" s="37" t="s">
+        <v>264</v>
       </c>
       <c r="I79" s="2">
         <v>2044483403</v>
       </c>
-      <c r="J79" s="50" t="s">
+      <c r="J79" s="2">
+        <v>2044483403</v>
+      </c>
+      <c r="K79" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K79" s="61" t="s">
-        <v>247</v>
-      </c>
-      <c r="L79" s="24">
+      <c r="L79" s="61" t="s">
+        <v>245</v>
+      </c>
+      <c r="M79" s="24">
         <v>46185</v>
       </c>
-      <c r="M79" s="66" t="s">
-        <v>254</v>
-      </c>
-      <c r="N79" s="45" t="s">
-        <v>37</v>
+      <c r="N79" s="66" t="s">
+        <v>252</v>
       </c>
       <c r="O79" s="45" t="s">
         <v>37</v>
@@ -6969,54 +7279,58 @@
       <c r="S79" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="T79" s="58">
-        <v>100</v>
-      </c>
-      <c r="U79" s="45"/>
-      <c r="V79" s="41"/>
-    </row>
-    <row r="80" spans="1:22" ht="36.75" customHeight="1">
+      <c r="T79" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="U79" s="58">
+        <v>100</v>
+      </c>
+      <c r="V79" s="45"/>
+      <c r="W79" s="41"/>
+    </row>
+    <row r="80" spans="1:23" ht="36.75" hidden="1" customHeight="1">
       <c r="A80" s="46">
         <v>2026</v>
       </c>
       <c r="B80" s="37" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C80" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="D80" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="E80" s="17" t="s">
+      <c r="D80" s="42">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="E80" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="F80" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="F80" s="48">
+      <c r="G80" s="48">
         <v>2026003050025</v>
       </c>
-      <c r="G80" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="H80" s="2">
-        <v>3738220582</v>
+      <c r="H80" s="37" t="s">
+        <v>269</v>
       </c>
       <c r="I80" s="2">
         <v>3738220582</v>
       </c>
-      <c r="J80" s="50" t="s">
+      <c r="J80" s="2">
+        <v>3738220582</v>
+      </c>
+      <c r="K80" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K80" s="61" t="s">
-        <v>247</v>
-      </c>
-      <c r="L80" s="24">
+      <c r="L80" s="61" t="s">
+        <v>245</v>
+      </c>
+      <c r="M80" s="24">
         <v>46185</v>
       </c>
-      <c r="M80" s="66" t="s">
-        <v>254</v>
-      </c>
-      <c r="N80" s="45" t="s">
-        <v>37</v>
+      <c r="N80" s="66" t="s">
+        <v>252</v>
       </c>
       <c r="O80" s="45" t="s">
         <v>37</v>
@@ -7033,53 +7347,57 @@
       <c r="S80" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="T80" s="58">
-        <v>100</v>
-      </c>
-      <c r="U80" s="45"/>
-      <c r="V80" s="41"/>
-    </row>
-    <row r="81" spans="1:22" s="14" customFormat="1" ht="36.75" customHeight="1">
+      <c r="T80" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="U80" s="58">
+        <v>100</v>
+      </c>
+      <c r="V80" s="45"/>
+      <c r="W80" s="41"/>
+    </row>
+    <row r="81" spans="1:23" s="14" customFormat="1" ht="36.75" customHeight="1">
       <c r="A81" s="46">
         <v>2026</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C81" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="D81" s="37" t="s">
-        <v>274</v>
+      <c r="D81" s="42">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E81" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="F81" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F81" s="48">
+      <c r="G81" s="48">
         <v>2026003050016</v>
       </c>
-      <c r="G81" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="H81" s="37" t="s">
+        <v>272</v>
+      </c>
+      <c r="I81" s="3">
         <v>2343812951</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1875050361</v>
       </c>
-      <c r="J81" s="45" t="s">
+      <c r="K81" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="K81" s="61" t="s">
+      <c r="L81" s="61" t="s">
         <v>49</v>
       </c>
-      <c r="L81" s="24"/>
-      <c r="M81" s="66" t="s">
+      <c r="M81" s="24"/>
+      <c r="N81" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="N81" s="45" t="s">
-        <v>37</v>
-      </c>
       <c r="O81" s="45" t="s">
         <v>37</v>
       </c>
@@ -7095,54 +7413,58 @@
       <c r="S81" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="T81" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="U81" s="45"/>
-      <c r="V81" s="41"/>
-    </row>
-    <row r="82" spans="1:22" ht="36.75" customHeight="1">
+      <c r="T81" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="U81" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="V81" s="45"/>
+      <c r="W81" s="41"/>
+    </row>
+    <row r="82" spans="1:23" ht="36.75" hidden="1" customHeight="1">
       <c r="A82" s="46">
         <v>2026</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C82" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="D82" s="37" t="s">
-        <v>277</v>
+      <c r="D82" s="42">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E82" s="37" t="s">
-        <v>278</v>
-      </c>
-      <c r="F82" s="48">
+        <v>274</v>
+      </c>
+      <c r="F82" s="37" t="s">
+        <v>275</v>
+      </c>
+      <c r="G82" s="48">
         <v>2026003050022</v>
       </c>
-      <c r="G82" s="37" t="s">
-        <v>279</v>
-      </c>
-      <c r="H82" s="49">
-        <v>6654540000</v>
+      <c r="H82" s="37" t="s">
+        <v>276</v>
       </c>
       <c r="I82" s="49">
         <v>6654540000</v>
       </c>
-      <c r="J82" s="50" t="s">
+      <c r="J82" s="49">
+        <v>6654540000</v>
+      </c>
+      <c r="K82" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K82" s="61" t="s">
-        <v>247</v>
-      </c>
-      <c r="L82" s="67">
+      <c r="L82" s="61" t="s">
+        <v>245</v>
+      </c>
+      <c r="M82" s="67">
         <v>46239</v>
       </c>
-      <c r="M82" s="66" t="s">
-        <v>254</v>
-      </c>
-      <c r="N82" s="45" t="s">
-        <v>37</v>
+      <c r="N82" s="66" t="s">
+        <v>252</v>
       </c>
       <c r="O82" s="45" t="s">
         <v>37</v>
@@ -7159,13 +7481,16 @@
       <c r="S82" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="T82" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="U82" s="45"/>
-      <c r="V82" s="41"/>
-    </row>
-    <row r="83" spans="1:22" ht="36.75" customHeight="1">
+      <c r="T82" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="U82" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="V82" s="45"/>
+      <c r="W82" s="41"/>
+    </row>
+    <row r="83" spans="1:23" ht="36.75" hidden="1" customHeight="1">
       <c r="A83" s="46">
         <v>2026</v>
       </c>
@@ -7175,38 +7500,39 @@
       <c r="C83" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="D83" s="37" t="s">
-        <v>280</v>
+      <c r="D83" s="42">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E83" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="F83" s="48">
+        <v>277</v>
+      </c>
+      <c r="F83" s="37" t="s">
+        <v>278</v>
+      </c>
+      <c r="G83" s="48">
         <v>2026003050019</v>
       </c>
-      <c r="G83" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="H83" s="49">
+      <c r="H83" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="I83" s="49">
         <v>8154980500</v>
       </c>
-      <c r="I83" s="49">
+      <c r="J83" s="49">
         <v>8054980500</v>
       </c>
-      <c r="J83" s="50" t="s">
+      <c r="K83" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K83" s="61" t="s">
-        <v>247</v>
-      </c>
-      <c r="L83" s="67">
+      <c r="L83" s="61" t="s">
+        <v>245</v>
+      </c>
+      <c r="M83" s="67">
         <v>46212</v>
       </c>
-      <c r="M83" s="66" t="s">
-        <v>254</v>
-      </c>
-      <c r="N83" s="45" t="s">
-        <v>37</v>
+      <c r="N83" s="66" t="s">
+        <v>252</v>
       </c>
       <c r="O83" s="45" t="s">
         <v>37</v>
@@ -7223,32 +7549,35 @@
       <c r="S83" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="T83" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="U83" s="45"/>
-      <c r="V83" s="41"/>
-    </row>
-    <row r="84" spans="1:22" s="14" customFormat="1">
+      <c r="T83" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="U83" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="V83" s="45"/>
+      <c r="W83" s="41"/>
+    </row>
+    <row r="84" spans="1:23" s="14" customFormat="1" hidden="1">
       <c r="A84" s="41"/>
       <c r="B84" s="53"/>
       <c r="C84" s="41"/>
-      <c r="D84" s="53"/>
-      <c r="E84" s="19"/>
-      <c r="F84" s="54"/>
-      <c r="G84" s="41"/>
-      <c r="H84" s="16">
-        <f>SUM(H3:H83)</f>
-        <v>391925077355.80005</v>
-      </c>
+      <c r="D84" s="41"/>
+      <c r="E84" s="53"/>
+      <c r="F84" s="19"/>
+      <c r="G84" s="54"/>
+      <c r="H84" s="41"/>
       <c r="I84" s="16">
         <f>SUM(I3:I83)</f>
+        <v>391925077355.80005</v>
+      </c>
+      <c r="J84" s="16">
+        <f>SUM(J3:J83)</f>
         <v>351081780790</v>
       </c>
-      <c r="J84" s="39"/>
       <c r="K84" s="39"/>
-      <c r="L84" s="40"/>
-      <c r="M84" s="39"/>
+      <c r="L84" s="39"/>
+      <c r="M84" s="40"/>
       <c r="N84" s="39"/>
       <c r="O84" s="39"/>
       <c r="P84" s="39"/>
@@ -7257,22 +7586,23 @@
       <c r="S84" s="39"/>
       <c r="T84" s="39"/>
       <c r="U84" s="39"/>
-      <c r="V84" s="41"/>
-    </row>
-    <row r="85" spans="1:22" s="14" customFormat="1">
+      <c r="V84" s="39"/>
+      <c r="W84" s="41"/>
+    </row>
+    <row r="85" spans="1:23" s="14" customFormat="1" hidden="1">
       <c r="A85" s="41"/>
       <c r="B85" s="53"/>
       <c r="C85" s="41"/>
-      <c r="D85" s="53"/>
-      <c r="E85" s="19"/>
-      <c r="F85" s="54"/>
-      <c r="G85" s="41"/>
-      <c r="H85" s="55"/>
+      <c r="D85" s="41"/>
+      <c r="E85" s="53"/>
+      <c r="F85" s="19"/>
+      <c r="G85" s="54"/>
+      <c r="H85" s="41"/>
       <c r="I85" s="55"/>
-      <c r="J85" s="39"/>
+      <c r="J85" s="55"/>
       <c r="K85" s="39"/>
-      <c r="L85" s="40"/>
-      <c r="M85" s="39"/>
+      <c r="L85" s="39"/>
+      <c r="M85" s="40"/>
       <c r="N85" s="39"/>
       <c r="O85" s="39"/>
       <c r="P85" s="39"/>
@@ -7281,22 +7611,23 @@
       <c r="S85" s="39"/>
       <c r="T85" s="39"/>
       <c r="U85" s="39"/>
-      <c r="V85" s="41"/>
-    </row>
-    <row r="86" spans="1:22" s="14" customFormat="1">
+      <c r="V85" s="39"/>
+      <c r="W85" s="41"/>
+    </row>
+    <row r="86" spans="1:23" s="14" customFormat="1">
       <c r="A86" s="41"/>
       <c r="B86" s="53"/>
       <c r="C86" s="41"/>
-      <c r="D86" s="53"/>
-      <c r="E86" s="19"/>
-      <c r="F86" s="54"/>
-      <c r="G86" s="41"/>
-      <c r="H86" s="55"/>
+      <c r="D86" s="41"/>
+      <c r="E86" s="53"/>
+      <c r="F86" s="19"/>
+      <c r="G86" s="54"/>
+      <c r="H86" s="41"/>
       <c r="I86" s="55"/>
-      <c r="J86" s="39"/>
+      <c r="J86" s="55"/>
       <c r="K86" s="39"/>
-      <c r="L86" s="40"/>
-      <c r="M86" s="39"/>
+      <c r="L86" s="39"/>
+      <c r="M86" s="40"/>
       <c r="N86" s="39"/>
       <c r="O86" s="39"/>
       <c r="P86" s="39"/>
@@ -7305,22 +7636,23 @@
       <c r="S86" s="39"/>
       <c r="T86" s="39"/>
       <c r="U86" s="39"/>
-      <c r="V86" s="41"/>
-    </row>
-    <row r="87" spans="1:22" s="14" customFormat="1">
+      <c r="V86" s="39"/>
+      <c r="W86" s="41"/>
+    </row>
+    <row r="87" spans="1:23" s="14" customFormat="1">
       <c r="A87" s="41"/>
       <c r="B87" s="53"/>
       <c r="C87" s="41"/>
-      <c r="D87" s="53"/>
-      <c r="E87" s="19"/>
-      <c r="F87" s="54"/>
-      <c r="G87" s="41"/>
-      <c r="H87" s="55"/>
+      <c r="D87" s="41"/>
+      <c r="E87" s="53"/>
+      <c r="F87" s="19"/>
+      <c r="G87" s="54"/>
+      <c r="H87" s="41"/>
       <c r="I87" s="55"/>
-      <c r="J87" s="39"/>
+      <c r="J87" s="55"/>
       <c r="K87" s="39"/>
-      <c r="L87" s="40"/>
-      <c r="M87" s="39"/>
+      <c r="L87" s="39"/>
+      <c r="M87" s="40"/>
       <c r="N87" s="39"/>
       <c r="O87" s="39"/>
       <c r="P87" s="39"/>
@@ -7329,22 +7661,23 @@
       <c r="S87" s="39"/>
       <c r="T87" s="39"/>
       <c r="U87" s="39"/>
-      <c r="V87" s="41"/>
-    </row>
-    <row r="88" spans="1:22" s="14" customFormat="1">
+      <c r="V87" s="39"/>
+      <c r="W87" s="41"/>
+    </row>
+    <row r="88" spans="1:23" s="14" customFormat="1">
       <c r="A88" s="41"/>
       <c r="B88" s="53"/>
       <c r="C88" s="41"/>
-      <c r="D88" s="53"/>
-      <c r="E88" s="19"/>
-      <c r="F88" s="54"/>
-      <c r="G88" s="41"/>
-      <c r="H88" s="55"/>
+      <c r="D88" s="41"/>
+      <c r="E88" s="53"/>
+      <c r="F88" s="19"/>
+      <c r="G88" s="54"/>
+      <c r="H88" s="41"/>
       <c r="I88" s="55"/>
-      <c r="J88" s="39"/>
+      <c r="J88" s="55"/>
       <c r="K88" s="39"/>
-      <c r="L88" s="40"/>
-      <c r="M88" s="39"/>
+      <c r="L88" s="39"/>
+      <c r="M88" s="40"/>
       <c r="N88" s="39"/>
       <c r="O88" s="39"/>
       <c r="P88" s="39"/>
@@ -7353,22 +7686,23 @@
       <c r="S88" s="39"/>
       <c r="T88" s="39"/>
       <c r="U88" s="39"/>
-      <c r="V88" s="41"/>
-    </row>
-    <row r="89" spans="1:22" s="14" customFormat="1">
+      <c r="V88" s="39"/>
+      <c r="W88" s="41"/>
+    </row>
+    <row r="89" spans="1:23" s="14" customFormat="1">
       <c r="A89" s="41"/>
       <c r="B89" s="53"/>
       <c r="C89" s="41"/>
-      <c r="D89" s="53"/>
-      <c r="E89" s="19"/>
-      <c r="F89" s="54"/>
-      <c r="G89" s="41"/>
-      <c r="H89" s="55"/>
+      <c r="D89" s="41"/>
+      <c r="E89" s="53"/>
+      <c r="F89" s="19"/>
+      <c r="G89" s="54"/>
+      <c r="H89" s="41"/>
       <c r="I89" s="55"/>
-      <c r="J89" s="39"/>
+      <c r="J89" s="55"/>
       <c r="K89" s="39"/>
-      <c r="L89" s="40"/>
-      <c r="M89" s="39"/>
+      <c r="L89" s="39"/>
+      <c r="M89" s="40"/>
       <c r="N89" s="39"/>
       <c r="O89" s="39"/>
       <c r="P89" s="39"/>
@@ -7377,22 +7711,23 @@
       <c r="S89" s="39"/>
       <c r="T89" s="39"/>
       <c r="U89" s="39"/>
-      <c r="V89" s="41"/>
-    </row>
-    <row r="90" spans="1:22" s="14" customFormat="1">
+      <c r="V89" s="39"/>
+      <c r="W89" s="41"/>
+    </row>
+    <row r="90" spans="1:23" s="14" customFormat="1">
       <c r="A90" s="41"/>
       <c r="B90" s="53"/>
       <c r="C90" s="41"/>
-      <c r="D90" s="53"/>
-      <c r="E90" s="19"/>
-      <c r="F90" s="54"/>
-      <c r="G90" s="41"/>
-      <c r="H90" s="55"/>
+      <c r="D90" s="41"/>
+      <c r="E90" s="53"/>
+      <c r="F90" s="19"/>
+      <c r="G90" s="54"/>
+      <c r="H90" s="41"/>
       <c r="I90" s="55"/>
-      <c r="J90" s="39"/>
+      <c r="J90" s="55"/>
       <c r="K90" s="39"/>
-      <c r="L90" s="40"/>
-      <c r="M90" s="39"/>
+      <c r="L90" s="39"/>
+      <c r="M90" s="40"/>
       <c r="N90" s="39"/>
       <c r="O90" s="39"/>
       <c r="P90" s="39"/>
@@ -7401,22 +7736,23 @@
       <c r="S90" s="39"/>
       <c r="T90" s="39"/>
       <c r="U90" s="39"/>
-      <c r="V90" s="41"/>
-    </row>
-    <row r="91" spans="1:22" s="14" customFormat="1">
+      <c r="V90" s="39"/>
+      <c r="W90" s="41"/>
+    </row>
+    <row r="91" spans="1:23" s="14" customFormat="1">
       <c r="A91" s="41"/>
       <c r="B91" s="53"/>
       <c r="C91" s="41"/>
-      <c r="D91" s="53"/>
-      <c r="E91" s="19"/>
-      <c r="F91" s="54"/>
-      <c r="G91" s="41"/>
-      <c r="H91" s="55"/>
+      <c r="D91" s="41"/>
+      <c r="E91" s="53"/>
+      <c r="F91" s="19"/>
+      <c r="G91" s="54"/>
+      <c r="H91" s="41"/>
       <c r="I91" s="55"/>
-      <c r="J91" s="39"/>
+      <c r="J91" s="55"/>
       <c r="K91" s="39"/>
-      <c r="L91" s="40"/>
-      <c r="M91" s="39"/>
+      <c r="L91" s="39"/>
+      <c r="M91" s="40"/>
       <c r="N91" s="39"/>
       <c r="O91" s="39"/>
       <c r="P91" s="39"/>
@@ -7425,22 +7761,23 @@
       <c r="S91" s="39"/>
       <c r="T91" s="39"/>
       <c r="U91" s="39"/>
-      <c r="V91" s="41"/>
-    </row>
-    <row r="92" spans="1:22" s="14" customFormat="1">
+      <c r="V91" s="39"/>
+      <c r="W91" s="41"/>
+    </row>
+    <row r="92" spans="1:23" s="14" customFormat="1">
       <c r="A92" s="41"/>
       <c r="B92" s="53"/>
       <c r="C92" s="41"/>
-      <c r="D92" s="53"/>
-      <c r="E92" s="19"/>
-      <c r="F92" s="54"/>
-      <c r="G92" s="41"/>
-      <c r="H92" s="55"/>
+      <c r="D92" s="41"/>
+      <c r="E92" s="53"/>
+      <c r="F92" s="19"/>
+      <c r="G92" s="54"/>
+      <c r="H92" s="41"/>
       <c r="I92" s="55"/>
-      <c r="J92" s="39"/>
+      <c r="J92" s="55"/>
       <c r="K92" s="39"/>
-      <c r="L92" s="40"/>
-      <c r="M92" s="39"/>
+      <c r="L92" s="39"/>
+      <c r="M92" s="40"/>
       <c r="N92" s="39"/>
       <c r="O92" s="39"/>
       <c r="P92" s="39"/>
@@ -7449,22 +7786,23 @@
       <c r="S92" s="39"/>
       <c r="T92" s="39"/>
       <c r="U92" s="39"/>
-      <c r="V92" s="41"/>
-    </row>
-    <row r="93" spans="1:22" s="14" customFormat="1">
+      <c r="V92" s="39"/>
+      <c r="W92" s="41"/>
+    </row>
+    <row r="93" spans="1:23" s="14" customFormat="1">
       <c r="A93" s="41"/>
       <c r="B93" s="53"/>
       <c r="C93" s="41"/>
-      <c r="D93" s="53"/>
-      <c r="E93" s="19"/>
-      <c r="F93" s="54"/>
-      <c r="G93" s="41"/>
-      <c r="H93" s="55"/>
+      <c r="D93" s="41"/>
+      <c r="E93" s="53"/>
+      <c r="F93" s="19"/>
+      <c r="G93" s="54"/>
+      <c r="H93" s="41"/>
       <c r="I93" s="55"/>
-      <c r="J93" s="39"/>
+      <c r="J93" s="55"/>
       <c r="K93" s="39"/>
-      <c r="L93" s="40"/>
-      <c r="M93" s="39"/>
+      <c r="L93" s="39"/>
+      <c r="M93" s="40"/>
       <c r="N93" s="39"/>
       <c r="O93" s="39"/>
       <c r="P93" s="39"/>
@@ -7473,22 +7811,23 @@
       <c r="S93" s="39"/>
       <c r="T93" s="39"/>
       <c r="U93" s="39"/>
-      <c r="V93" s="41"/>
-    </row>
-    <row r="94" spans="1:22" s="14" customFormat="1">
+      <c r="V93" s="39"/>
+      <c r="W93" s="41"/>
+    </row>
+    <row r="94" spans="1:23" s="14" customFormat="1">
       <c r="A94" s="41"/>
       <c r="B94" s="53"/>
       <c r="C94" s="41"/>
-      <c r="D94" s="53"/>
-      <c r="E94" s="19"/>
-      <c r="F94" s="54"/>
-      <c r="G94" s="41"/>
-      <c r="H94" s="55"/>
+      <c r="D94" s="41"/>
+      <c r="E94" s="53"/>
+      <c r="F94" s="19"/>
+      <c r="G94" s="54"/>
+      <c r="H94" s="41"/>
       <c r="I94" s="55"/>
-      <c r="J94" s="39"/>
+      <c r="J94" s="55"/>
       <c r="K94" s="39"/>
-      <c r="L94" s="40"/>
-      <c r="M94" s="39"/>
+      <c r="L94" s="39"/>
+      <c r="M94" s="40"/>
       <c r="N94" s="39"/>
       <c r="O94" s="39"/>
       <c r="P94" s="39"/>
@@ -7497,22 +7836,23 @@
       <c r="S94" s="39"/>
       <c r="T94" s="39"/>
       <c r="U94" s="39"/>
-      <c r="V94" s="41"/>
-    </row>
-    <row r="95" spans="1:22">
+      <c r="V94" s="39"/>
+      <c r="W94" s="41"/>
+    </row>
+    <row r="95" spans="1:23">
       <c r="A95" s="41"/>
       <c r="B95" s="53"/>
       <c r="C95" s="41"/>
-      <c r="D95" s="53"/>
+      <c r="D95" s="41"/>
       <c r="E95" s="53"/>
-      <c r="F95" s="54"/>
-      <c r="G95" s="53"/>
-      <c r="H95" s="55"/>
+      <c r="F95" s="53"/>
+      <c r="G95" s="54"/>
+      <c r="H95" s="53"/>
       <c r="I95" s="55"/>
-      <c r="J95" s="39"/>
+      <c r="J95" s="55"/>
       <c r="K95" s="39"/>
-      <c r="L95" s="40"/>
-      <c r="M95" s="39"/>
+      <c r="L95" s="39"/>
+      <c r="M95" s="40"/>
       <c r="N95" s="39"/>
       <c r="O95" s="39"/>
       <c r="P95" s="39"/>
@@ -7521,22 +7861,23 @@
       <c r="S95" s="39"/>
       <c r="T95" s="39"/>
       <c r="U95" s="39"/>
-      <c r="V95" s="41"/>
-    </row>
-    <row r="96" spans="1:22">
+      <c r="V95" s="39"/>
+      <c r="W95" s="41"/>
+    </row>
+    <row r="96" spans="1:23">
       <c r="A96" s="41"/>
       <c r="B96" s="53"/>
       <c r="C96" s="41"/>
-      <c r="D96" s="53"/>
+      <c r="D96" s="41"/>
       <c r="E96" s="53"/>
-      <c r="F96" s="54"/>
-      <c r="G96" s="53"/>
-      <c r="H96" s="55"/>
+      <c r="F96" s="53"/>
+      <c r="G96" s="54"/>
+      <c r="H96" s="53"/>
       <c r="I96" s="55"/>
-      <c r="J96" s="39"/>
+      <c r="J96" s="55"/>
       <c r="K96" s="39"/>
-      <c r="L96" s="40"/>
-      <c r="M96" s="39"/>
+      <c r="L96" s="39"/>
+      <c r="M96" s="40"/>
       <c r="N96" s="39"/>
       <c r="O96" s="39"/>
       <c r="P96" s="39"/>
@@ -7545,194 +7886,233 @@
       <c r="S96" s="39"/>
       <c r="T96" s="39"/>
       <c r="U96" s="39"/>
-      <c r="V96" s="41"/>
-    </row>
-    <row r="97" spans="2:6">
+      <c r="V96" s="39"/>
+      <c r="W96" s="41"/>
+    </row>
+    <row r="97" spans="2:7">
       <c r="B97" s="53"/>
       <c r="C97" s="41"/>
-      <c r="D97" s="53"/>
+      <c r="D97" s="41"/>
       <c r="E97" s="53"/>
-      <c r="F97" s="54"/>
-    </row>
-    <row r="98" spans="2:6">
+      <c r="F97" s="53"/>
+      <c r="G97" s="54"/>
+    </row>
+    <row r="98" spans="2:7">
       <c r="B98" s="53"/>
       <c r="C98" s="41"/>
-      <c r="D98" s="53"/>
+      <c r="D98" s="41"/>
       <c r="E98" s="53"/>
-      <c r="F98" s="54"/>
-    </row>
-    <row r="99" spans="2:6">
+      <c r="F98" s="53"/>
+      <c r="G98" s="54"/>
+    </row>
+    <row r="99" spans="2:7">
       <c r="B99" s="53"/>
       <c r="C99" s="41"/>
-      <c r="D99" s="53"/>
+      <c r="D99" s="41"/>
       <c r="E99" s="53"/>
-      <c r="F99" s="54"/>
-    </row>
-    <row r="100" spans="2:6">
+      <c r="F99" s="53"/>
+      <c r="G99" s="54"/>
+    </row>
+    <row r="100" spans="2:7">
       <c r="B100" s="53"/>
       <c r="C100" s="41"/>
-      <c r="D100" s="53"/>
+      <c r="D100" s="41"/>
       <c r="E100" s="53"/>
-      <c r="F100" s="54"/>
-    </row>
-    <row r="101" spans="2:6">
+      <c r="F100" s="53"/>
+      <c r="G100" s="54"/>
+    </row>
+    <row r="101" spans="2:7">
       <c r="B101" s="53"/>
       <c r="C101" s="41"/>
-      <c r="D101" s="53"/>
+      <c r="D101" s="41"/>
       <c r="E101" s="53"/>
-      <c r="F101" s="54"/>
-    </row>
-    <row r="102" spans="2:6">
+      <c r="F101" s="53"/>
+      <c r="G101" s="54"/>
+    </row>
+    <row r="102" spans="2:7">
       <c r="B102" s="53"/>
       <c r="C102" s="41"/>
-      <c r="D102" s="53"/>
+      <c r="D102" s="41"/>
       <c r="E102" s="53"/>
-      <c r="F102" s="54"/>
-    </row>
-    <row r="103" spans="2:6">
+      <c r="F102" s="53"/>
+      <c r="G102" s="54"/>
+    </row>
+    <row r="103" spans="2:7">
       <c r="B103" s="53"/>
       <c r="C103" s="41"/>
-      <c r="D103" s="53"/>
+      <c r="D103" s="41"/>
       <c r="E103" s="53"/>
-      <c r="F103" s="54"/>
-    </row>
-    <row r="104" spans="2:6">
+      <c r="F103" s="53"/>
+      <c r="G103" s="54"/>
+    </row>
+    <row r="104" spans="2:7">
       <c r="B104" s="53"/>
       <c r="C104" s="41"/>
-      <c r="D104" s="53"/>
+      <c r="D104" s="41"/>
       <c r="E104" s="53"/>
-      <c r="F104" s="54"/>
-    </row>
-    <row r="105" spans="2:6">
+      <c r="F104" s="53"/>
+      <c r="G104" s="54"/>
+    </row>
+    <row r="105" spans="2:7">
       <c r="B105" s="53"/>
       <c r="C105" s="41"/>
-      <c r="D105" s="53"/>
+      <c r="D105" s="41"/>
       <c r="E105" s="53"/>
-      <c r="F105" s="54"/>
-    </row>
-    <row r="106" spans="2:6">
+      <c r="F105" s="53"/>
+      <c r="G105" s="54"/>
+    </row>
+    <row r="106" spans="2:7">
       <c r="B106" s="53"/>
       <c r="C106" s="41"/>
-      <c r="D106" s="53"/>
+      <c r="D106" s="41"/>
       <c r="E106" s="53"/>
-      <c r="F106" s="54"/>
-    </row>
-    <row r="107" spans="2:6">
+      <c r="F106" s="53"/>
+      <c r="G106" s="54"/>
+    </row>
+    <row r="107" spans="2:7">
       <c r="B107" s="53"/>
       <c r="C107" s="41"/>
-      <c r="D107" s="53"/>
+      <c r="D107" s="41"/>
       <c r="E107" s="53"/>
-      <c r="F107" s="54"/>
-    </row>
-    <row r="108" spans="2:6">
+      <c r="F107" s="53"/>
+      <c r="G107" s="54"/>
+    </row>
+    <row r="108" spans="2:7">
       <c r="B108" s="53"/>
       <c r="C108" s="41"/>
-      <c r="D108" s="53"/>
+      <c r="D108" s="41"/>
       <c r="E108" s="53"/>
-      <c r="F108" s="54"/>
-    </row>
-    <row r="109" spans="2:6">
+      <c r="F108" s="53"/>
+      <c r="G108" s="54"/>
+    </row>
+    <row r="109" spans="2:7">
       <c r="B109" s="53"/>
       <c r="C109" s="41"/>
-      <c r="D109" s="53"/>
+      <c r="D109" s="41"/>
       <c r="E109" s="53"/>
-      <c r="F109" s="54"/>
-    </row>
-    <row r="110" spans="2:6">
+      <c r="F109" s="53"/>
+      <c r="G109" s="54"/>
+    </row>
+    <row r="110" spans="2:7">
       <c r="B110" s="53"/>
       <c r="C110" s="41"/>
-      <c r="D110" s="53"/>
+      <c r="D110" s="41"/>
       <c r="E110" s="53"/>
-      <c r="F110" s="54"/>
-    </row>
-    <row r="111" spans="2:6">
+      <c r="F110" s="53"/>
+      <c r="G110" s="54"/>
+    </row>
+    <row r="111" spans="2:7">
       <c r="B111" s="53"/>
       <c r="C111" s="41"/>
-      <c r="D111" s="53"/>
+      <c r="D111" s="41"/>
       <c r="E111" s="53"/>
-      <c r="F111" s="54"/>
-    </row>
-    <row r="112" spans="2:6">
+      <c r="F111" s="53"/>
+      <c r="G111" s="54"/>
+    </row>
+    <row r="112" spans="2:7">
       <c r="B112" s="53"/>
       <c r="C112" s="41"/>
-      <c r="D112" s="53"/>
+      <c r="D112" s="41"/>
       <c r="E112" s="53"/>
-      <c r="F112" s="54"/>
-    </row>
-    <row r="113" spans="2:6">
+      <c r="F112" s="53"/>
+      <c r="G112" s="54"/>
+    </row>
+    <row r="113" spans="2:7">
       <c r="B113" s="53"/>
       <c r="C113" s="41"/>
-      <c r="D113" s="53"/>
+      <c r="D113" s="41"/>
       <c r="E113" s="53"/>
-      <c r="F113" s="54"/>
-    </row>
-    <row r="114" spans="2:6">
+      <c r="F113" s="53"/>
+      <c r="G113" s="54"/>
+    </row>
+    <row r="114" spans="2:7">
       <c r="B114" s="53"/>
       <c r="C114" s="41"/>
-      <c r="D114" s="53"/>
+      <c r="D114" s="41"/>
       <c r="E114" s="53"/>
-      <c r="F114" s="54"/>
-    </row>
-    <row r="115" spans="2:6">
+      <c r="F114" s="53"/>
+      <c r="G114" s="54"/>
+    </row>
+    <row r="115" spans="2:7">
       <c r="B115" s="53"/>
       <c r="C115" s="41"/>
-      <c r="D115" s="53"/>
+      <c r="D115" s="41"/>
       <c r="E115" s="53"/>
-      <c r="F115" s="54"/>
-    </row>
-    <row r="116" spans="2:6">
+      <c r="F115" s="53"/>
+      <c r="G115" s="54"/>
+    </row>
+    <row r="116" spans="2:7">
       <c r="B116" s="53"/>
       <c r="C116" s="41"/>
-      <c r="D116" s="53"/>
+      <c r="D116" s="41"/>
       <c r="E116" s="53"/>
-      <c r="F116" s="54"/>
-    </row>
-    <row r="117" spans="2:6">
+      <c r="F116" s="53"/>
+      <c r="G116" s="54"/>
+    </row>
+    <row r="117" spans="2:7">
       <c r="B117" s="53"/>
       <c r="C117" s="41"/>
-      <c r="D117" s="53"/>
+      <c r="D117" s="41"/>
       <c r="E117" s="53"/>
-      <c r="F117" s="54"/>
-    </row>
-    <row r="118" spans="2:6">
+      <c r="F117" s="53"/>
+      <c r="G117" s="54"/>
+    </row>
+    <row r="118" spans="2:7">
       <c r="B118" s="53"/>
       <c r="C118" s="41"/>
-      <c r="D118" s="53"/>
+      <c r="D118" s="41"/>
       <c r="E118" s="53"/>
-      <c r="F118" s="54"/>
-    </row>
-    <row r="119" spans="2:6">
+      <c r="F118" s="53"/>
+      <c r="G118" s="54"/>
+    </row>
+    <row r="119" spans="2:7">
       <c r="B119" s="53"/>
       <c r="C119" s="41"/>
-      <c r="D119" s="53"/>
+      <c r="D119" s="41"/>
       <c r="E119" s="53"/>
-      <c r="F119" s="54"/>
-    </row>
-    <row r="120" spans="2:6">
+      <c r="F119" s="53"/>
+      <c r="G119" s="54"/>
+    </row>
+    <row r="120" spans="2:7">
       <c r="B120" s="53"/>
       <c r="C120" s="41"/>
-      <c r="D120" s="53"/>
+      <c r="D120" s="41"/>
       <c r="E120" s="53"/>
-      <c r="F120" s="54"/>
-    </row>
-    <row r="121" spans="2:6">
+      <c r="F120" s="53"/>
+      <c r="G120" s="54"/>
+    </row>
+    <row r="121" spans="2:7">
       <c r="B121" s="53"/>
       <c r="C121" s="41"/>
-      <c r="D121" s="53"/>
+      <c r="D121" s="41"/>
       <c r="E121" s="53"/>
-      <c r="F121" s="54"/>
+      <c r="F121" s="53"/>
+      <c r="G121" s="54"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:U85" xr:uid="{00000000-0001-0000-0200-000000000000}">
-    <sortState ref="A3:U85">
+  <autoFilter ref="A2:V85" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="PLACA HUELLA"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="21">
+      <filters blank="1">
+        <filter val="100"/>
+        <filter val="14"/>
+        <filter val="35"/>
+        <filter val="81"/>
+      </filters>
+    </filterColumn>
+    <sortState ref="A3:V85">
       <sortCondition ref="A2:A85"/>
     </sortState>
   </autoFilter>
   <mergeCells count="4">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OACEVEDOD\Desktop\Jefe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9436FC23-ED6D-4DBB-91F2-60B459749F9D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E7B927-9F53-4CF7-894B-D3C737BD7EBD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="277">
   <si>
     <t>PROYECTOS APROBADOS POR ASIGNACIÓN CON CARGO AL SISTEMA GENERAL DE REGALÍAS DEPARTAMENTO DE Antioquia - 2024-2026</t>
   </si>
@@ -207,9 +207,6 @@
     <t>Norte</t>
   </si>
   <si>
-    <t>1.866 KM PLACA HUELLA</t>
-  </si>
-  <si>
     <t>Mejoramiento de vías terciarias en el municipio de Guadalupe Antioquia</t>
   </si>
   <si>
@@ -231,9 +228,6 @@
     <t>BRICEÑO</t>
   </si>
   <si>
-    <t>0.782 KM PLACA HUELLA</t>
-  </si>
-  <si>
     <t>Mejoramiento de la vía terciaria que comunica la vereda El Roblal y el Sector la Ye en el municipio de Briceño Antioquia</t>
   </si>
   <si>
@@ -261,9 +255,6 @@
     <t>Suroeste</t>
   </si>
   <si>
-    <t>1.3 KM PLACA HUELLA</t>
-  </si>
-  <si>
     <t>Construcción de placa huella de la vía terciaria El Hacha - La Alacena en el Municipio de Támesis del departamento de Antioquia</t>
   </si>
   <si>
@@ -288,9 +279,6 @@
     <t>Occidente</t>
   </si>
   <si>
-    <t>0.95 KM PLACA HUELLA</t>
-  </si>
-  <si>
     <t>Construcción de placa huella productiva en la vía terciaria Águila-Roblar del municipio de Giraldo</t>
   </si>
   <si>
@@ -322,9 +310,6 @@
   </si>
   <si>
     <t>ENTRERRÍOS</t>
-  </si>
-  <si>
-    <t>1.1 KM PLACA HUELLA</t>
   </si>
   <si>
     <t>Pavimentación tipo placa huella en vías rurales del municipio de Entrerríos Antioquia</t>
@@ -911,6 +896,18 @@
   </si>
   <si>
     <t>0,54 KM DE PAVIMENTACIÓN URBANA</t>
+  </si>
+  <si>
+    <t>1,866 KM PLACA HUELLA</t>
+  </si>
+  <si>
+    <t>0,782 KM PLACA HUELLA</t>
+  </si>
+  <si>
+    <t>1,3 KM PLACA HUELLA</t>
+  </si>
+  <si>
+    <t>0,95 KM PLACA HUELLA</t>
   </si>
 </sst>
 </file>
@@ -924,11 +921,18 @@
     <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1223,258 +1227,261 @@
   </borders>
   <cellStyleXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="13" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="14" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="13" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="18" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="14" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="15" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="12" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -1870,7 +1877,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E2" s="31" t="s">
         <v>7</v>
@@ -2201,10 +2208,10 @@
       </c>
       <c r="D6" s="74">
         <f>IF(ISNUMBER(E6),E6,IFERROR(VALUE(LEFT(E6,FIND(" ",E6)-1)),1))</f>
-        <v>1866</v>
+        <v>1.8660000000000001</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>43</v>
+        <v>273</v>
       </c>
       <c r="F6" s="38" t="s">
         <v>27</v>
@@ -2213,7 +2220,7 @@
         <v>2024053150037</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I6" s="3">
         <v>3945999620</v>
@@ -2273,7 +2280,7 @@
         <v>2024</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" s="44" t="s">
         <v>33</v>
@@ -2292,7 +2299,7 @@
         <v>2024003050241</v>
       </c>
       <c r="H7" s="38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I7" s="3">
         <v>4232130933.4000001</v>
@@ -2307,7 +2314,7 @@
         <v>30</v>
       </c>
       <c r="M7" s="60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N7" s="25">
         <v>45636</v>
@@ -2322,13 +2329,13 @@
         <v>58.62</v>
       </c>
       <c r="R7" s="63" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S7" s="66">
         <v>60</v>
       </c>
       <c r="T7" s="66" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U7" s="66">
         <v>60</v>
@@ -2360,17 +2367,17 @@
         <v>2024</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8" s="44" t="s">
         <v>42</v>
       </c>
       <c r="D8" s="74">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E8" s="38" t="s">
-        <v>51</v>
+        <v>0.78200000000000003</v>
+      </c>
+      <c r="E8" s="80" t="s">
+        <v>274</v>
       </c>
       <c r="F8" s="38" t="s">
         <v>27</v>
@@ -2379,7 +2386,7 @@
         <v>2024051070040</v>
       </c>
       <c r="H8" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I8" s="3">
         <v>1645755840</v>
@@ -2443,7 +2450,7 @@
         <v>2024</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C9" s="44" t="s">
         <v>25</v>
@@ -2462,7 +2469,7 @@
         <v>2024057560039</v>
       </c>
       <c r="H9" s="38" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I9" s="3">
         <v>4699883725</v>
@@ -2477,7 +2484,7 @@
         <v>30</v>
       </c>
       <c r="M9" s="60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N9" s="25">
         <v>45636</v>
@@ -2492,16 +2499,16 @@
         <v>85.38</v>
       </c>
       <c r="R9" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="S9" s="66" t="s">
+        <v>55</v>
+      </c>
+      <c r="T9" s="66" t="s">
+        <v>54</v>
+      </c>
+      <c r="U9" s="66" t="s">
         <v>56</v>
-      </c>
-      <c r="S9" s="66" t="s">
-        <v>57</v>
-      </c>
-      <c r="T9" s="66" t="s">
-        <v>56</v>
-      </c>
-      <c r="U9" s="66" t="s">
-        <v>58</v>
       </c>
       <c r="V9" s="24">
         <v>100</v>
@@ -2530,17 +2537,17 @@
         <v>2024</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D10" s="74">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E10" s="38" t="s">
-        <v>61</v>
+        <f>IF(ISNUMBER(E10),E10,IFERROR(VALUE(LEFT(E10,FIND(" ",E10)-1)),1))</f>
+        <v>1.3</v>
+      </c>
+      <c r="E10" s="80" t="s">
+        <v>275</v>
       </c>
       <c r="F10" s="38" t="s">
         <v>27</v>
@@ -2549,7 +2556,7 @@
         <v>2024057890040</v>
       </c>
       <c r="H10" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I10" s="3">
         <v>3035607509</v>
@@ -2579,13 +2586,13 @@
         <v>100</v>
       </c>
       <c r="R10" s="63" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="S10" s="66">
         <v>100</v>
       </c>
       <c r="T10" s="66" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="U10" s="66">
         <v>100</v>
@@ -2617,7 +2624,7 @@
         <v>2024</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C11" s="44" t="s">
         <v>25</v>
@@ -2627,7 +2634,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F11" s="38" t="s">
         <v>27</v>
@@ -2636,7 +2643,7 @@
         <v>2024054830016</v>
       </c>
       <c r="H11" s="38" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I11" s="3">
         <v>2596905323</v>
@@ -2675,7 +2682,7 @@
         <v>100</v>
       </c>
       <c r="U11" s="63" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="V11" s="23">
         <v>71</v>
@@ -2704,17 +2711,17 @@
         <v>2024</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D12" s="74">
         <f>IF(ISNUMBER(E12),E12,IFERROR(VALUE(LEFT(E12,FIND(" ",E12)-1)),1))</f>
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>70</v>
+        <v>276</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>27</v>
@@ -2723,7 +2730,7 @@
         <v>2024003050236</v>
       </c>
       <c r="H12" s="38" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I12" s="3">
         <v>1513619665</v>
@@ -2732,7 +2739,7 @@
         <v>1210895732</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="L12" s="23" t="s">
         <v>30</v>
@@ -2753,16 +2760,16 @@
         <v>62.65</v>
       </c>
       <c r="R12" s="63" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="S12" s="66" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="T12" s="66" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U12" s="66" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="V12" s="23">
         <v>51</v>
@@ -2791,7 +2798,7 @@
         <v>2024</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C13" s="48" t="s">
         <v>42</v>
@@ -2810,7 +2817,7 @@
         <v>2024003050238</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I13" s="3">
         <v>4622246270</v>
@@ -2819,7 +2826,7 @@
         <v>3697797016</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="L13" s="23" t="s">
         <v>30</v>
@@ -2870,17 +2877,17 @@
         <v>2024</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C14" s="48" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D14" s="74">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>27</v>
@@ -2889,7 +2896,7 @@
         <v>2024003050244</v>
       </c>
       <c r="H14" s="38" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I14" s="4">
         <v>2177618498</v>
@@ -2904,13 +2911,13 @@
         <v>30</v>
       </c>
       <c r="M14" s="60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N14" s="25">
         <v>45636</v>
       </c>
       <c r="O14" s="68" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="P14" s="27">
         <v>0</v>
@@ -2922,13 +2929,13 @@
         <v>0</v>
       </c>
       <c r="S14" s="63" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="T14" s="63">
         <v>0</v>
       </c>
       <c r="U14" s="63" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="V14" s="27">
         <v>0</v>
@@ -2957,17 +2964,17 @@
         <v>2024</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C15" s="44" t="s">
         <v>42</v>
       </c>
       <c r="D15" s="74">
         <f>IF(ISNUMBER(E15),E15,IFERROR(VALUE(LEFT(E15,FIND(" ",E15)-1)),1))</f>
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="F15" s="38" t="s">
         <v>27</v>
@@ -2976,7 +2983,7 @@
         <v>2024003050242</v>
       </c>
       <c r="H15" s="38" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I15" s="3">
         <v>2688840891</v>
@@ -3014,7 +3021,7 @@
       <c r="T15" s="63"/>
       <c r="U15" s="63"/>
       <c r="V15" s="23" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="W15" s="23">
         <v>100</v>
@@ -3040,7 +3047,7 @@
         <v>2024</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C16" s="44" t="s">
         <v>42</v>
@@ -3050,7 +3057,7 @@
         <v>3</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>27</v>
@@ -3059,7 +3066,7 @@
         <v>2024003050245</v>
       </c>
       <c r="H16" s="38" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="I16" s="3">
         <v>6076769979</v>
@@ -3074,7 +3081,7 @@
         <v>30</v>
       </c>
       <c r="M16" s="60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N16" s="25">
         <v>45635</v>
@@ -3089,16 +3096,16 @@
         <v>59.95</v>
       </c>
       <c r="R16" s="63" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="S16" s="63" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="T16" s="63" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="U16" s="63" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="V16" s="24">
         <v>50</v>
@@ -3127,17 +3134,17 @@
         <v>2024</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D17" s="74">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F17" s="38" t="s">
         <v>27</v>
@@ -3146,7 +3153,7 @@
         <v>2024003050237</v>
       </c>
       <c r="H17" s="38" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I17" s="3">
         <v>5449013721.6000004</v>
@@ -3179,13 +3186,13 @@
         <v>100</v>
       </c>
       <c r="S17" s="63" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="T17" s="63">
         <v>100</v>
       </c>
       <c r="U17" s="63" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="V17" s="23">
         <v>100</v>
@@ -3214,7 +3221,7 @@
         <v>2024</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C18" s="48" t="s">
         <v>25</v>
@@ -3224,7 +3231,7 @@
         <v>1.5</v>
       </c>
       <c r="E18" s="38" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F18" s="38" t="s">
         <v>27</v>
@@ -3233,7 +3240,7 @@
         <v>2024051970041</v>
       </c>
       <c r="H18" s="38" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="I18" s="3">
         <v>3445926513</v>
@@ -3293,26 +3300,26 @@
         <v>2024</v>
       </c>
       <c r="B19" s="49" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C19" s="44" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D19" s="74">
         <f t="shared" si="0"/>
         <v>320</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F19" s="38" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G19" s="40">
         <v>20243201010075</v>
       </c>
       <c r="H19" s="38" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I19" s="3">
         <v>15664988520</v>
@@ -3324,10 +3331,10 @@
         <v>0.2</v>
       </c>
       <c r="L19" s="23" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="M19" s="60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N19" s="46">
         <v>45652</v>
@@ -3370,17 +3377,17 @@
         <v>2025</v>
       </c>
       <c r="B20" s="49" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C20" s="44" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D20" s="74">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
       <c r="E20" s="38" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="F20" s="38" t="s">
         <v>27</v>
@@ -3389,7 +3396,7 @@
         <v>2025003050003</v>
       </c>
       <c r="H20" s="38" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I20" s="3">
         <v>5581655075</v>
@@ -3404,7 +3411,7 @@
         <v>30</v>
       </c>
       <c r="M20" s="60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N20" s="25">
         <v>45768</v>
@@ -3455,17 +3462,17 @@
         <v>2025</v>
       </c>
       <c r="B21" s="49" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C21" s="44" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D21" s="74">
         <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
       <c r="E21" s="38" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="F21" s="38" t="s">
         <v>27</v>
@@ -3474,7 +3481,7 @@
         <v>2025003050008</v>
       </c>
       <c r="H21" s="38" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="I21" s="3">
         <v>2661301361.5999999</v>
@@ -3542,26 +3549,26 @@
         <v>2025</v>
       </c>
       <c r="B22" s="49" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C22" s="44" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D22" s="75">
         <f t="shared" si="0"/>
         <v>6.9</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G22" s="40">
         <v>2025003050002</v>
       </c>
       <c r="H22" s="38" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="I22" s="3">
         <v>24272420632</v>
@@ -3573,10 +3580,10 @@
         <v>29</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="M22" s="60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N22" s="25">
         <v>45805</v>
@@ -3627,26 +3634,26 @@
         <v>2025</v>
       </c>
       <c r="B23" s="49" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C23" s="44" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D23" s="75">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E23" s="38" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G23" s="50">
         <v>2025003050005</v>
       </c>
       <c r="H23" s="38" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="I23" s="3">
         <v>13746524997</v>
@@ -3661,7 +3668,7 @@
         <v>30</v>
       </c>
       <c r="M23" s="60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N23" s="25">
         <v>45811</v>
@@ -3688,7 +3695,7 @@
         <v>88.5</v>
       </c>
       <c r="V23" s="24" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="W23" s="24">
         <v>90</v>
@@ -3697,7 +3704,7 @@
         <v>90</v>
       </c>
       <c r="Y23" s="47" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="Z23" s="43"/>
       <c r="AA23" s="43"/>
@@ -3714,10 +3721,10 @@
         <v>2025</v>
       </c>
       <c r="B24" s="49" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C24" s="44" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D24" s="74">
         <f t="shared" si="0"/>
@@ -3733,7 +3740,7 @@
         <v>2025003050011</v>
       </c>
       <c r="H24" s="38" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="I24" s="3">
         <v>4237507648</v>
@@ -3748,7 +3755,7 @@
         <v>30</v>
       </c>
       <c r="M24" s="61" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="N24" s="46">
         <v>45813</v>
@@ -3801,7 +3808,7 @@
         <v>2025</v>
       </c>
       <c r="B25" s="49" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C25" s="44" t="s">
         <v>42</v>
@@ -3811,7 +3818,7 @@
         <v>0.75</v>
       </c>
       <c r="E25" s="38" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F25" s="38" t="s">
         <v>27</v>
@@ -3820,7 +3827,7 @@
         <v>2025003050014</v>
       </c>
       <c r="H25" s="38" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="I25" s="3">
         <v>1811206529</v>
@@ -3884,7 +3891,7 @@
         <v>2025</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C26" s="44" t="s">
         <v>25</v>
@@ -3903,7 +3910,7 @@
         <v>2025003050012</v>
       </c>
       <c r="H26" s="38" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="I26" s="3">
         <v>4812305821</v>
@@ -3918,7 +3925,7 @@
         <v>30</v>
       </c>
       <c r="M26" s="60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N26" s="25">
         <v>45826</v>
@@ -3951,7 +3958,7 @@
         <v>100</v>
       </c>
       <c r="X26" s="60" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="Y26" s="24"/>
       <c r="Z26" s="43"/>
@@ -3969,7 +3976,7 @@
         <v>2025</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C27" s="44" t="s">
         <v>42</v>
@@ -3979,7 +3986,7 @@
         <v>1.9</v>
       </c>
       <c r="E27" s="38" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="F27" s="38" t="s">
         <v>27</v>
@@ -3988,7 +3995,7 @@
         <v>2025003050015</v>
       </c>
       <c r="H27" s="38" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="I27" s="3">
         <v>4294044919</v>
@@ -4052,17 +4059,17 @@
         <v>2025</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C28" s="44" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D28" s="74">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F28" s="38" t="s">
         <v>27</v>
@@ -4071,7 +4078,7 @@
         <v>2025003050013</v>
       </c>
       <c r="H28" s="38" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I28" s="3">
         <v>1999756329</v>
@@ -4139,7 +4146,7 @@
         <v>2025</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C29" s="44" t="s">
         <v>25</v>
@@ -4158,7 +4165,7 @@
         <v>2025003050022</v>
       </c>
       <c r="H29" s="38" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I29" s="3">
         <v>4833319756</v>
@@ -4173,7 +4180,7 @@
         <v>30</v>
       </c>
       <c r="M29" s="60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N29" s="25">
         <v>45874</v>
@@ -4206,7 +4213,7 @@
         <v>100</v>
       </c>
       <c r="X29" s="60" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="Y29" s="47"/>
       <c r="Z29" s="43"/>
@@ -4224,7 +4231,7 @@
         <v>2025</v>
       </c>
       <c r="B30" s="49" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C30" s="44" t="s">
         <v>42</v>
@@ -4234,16 +4241,16 @@
         <v>1.95</v>
       </c>
       <c r="E30" s="38" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="F30" s="38" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="G30" s="50">
         <v>2025003050017</v>
       </c>
       <c r="H30" s="38" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I30" s="3">
         <v>5922191430</v>
@@ -4258,7 +4265,7 @@
         <v>30</v>
       </c>
       <c r="M30" s="60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N30" s="25">
         <v>45854</v>
@@ -4311,7 +4318,7 @@
         <v>2025</v>
       </c>
       <c r="B31" s="49" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C31" s="44" t="s">
         <v>25</v>
@@ -4330,7 +4337,7 @@
         <v>2025003050020</v>
       </c>
       <c r="H31" s="38" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I31" s="3">
         <v>4797586284</v>
@@ -4345,7 +4352,7 @@
         <v>30</v>
       </c>
       <c r="M31" s="60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N31" s="25">
         <v>45874</v>
@@ -4396,17 +4403,17 @@
         <v>2025</v>
       </c>
       <c r="B32" s="49" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C32" s="44" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D32" s="74">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E32" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F32" s="38" t="s">
         <v>27</v>
@@ -4415,7 +4422,7 @@
         <v>2025003050010</v>
       </c>
       <c r="H32" s="38" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I32" s="3">
         <v>2479887333</v>
@@ -4430,7 +4437,7 @@
         <v>30</v>
       </c>
       <c r="M32" s="60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N32" s="25">
         <v>45874</v>
@@ -4483,7 +4490,7 @@
         <v>2025</v>
       </c>
       <c r="B33" s="49" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C33" s="44" t="s">
         <v>25</v>
@@ -4502,7 +4509,7 @@
         <v>2025003050021</v>
       </c>
       <c r="H33" s="38" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="I33" s="3">
         <v>4847192489</v>
@@ -4517,7 +4524,7 @@
         <v>30</v>
       </c>
       <c r="M33" s="60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N33" s="25">
         <v>45909</v>
@@ -4570,7 +4577,7 @@
         <v>2025</v>
       </c>
       <c r="B34" s="49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34" s="44" t="s">
         <v>42</v>
@@ -4580,16 +4587,16 @@
         <v>1</v>
       </c>
       <c r="E34" s="38" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G34" s="50">
         <v>2025003050018</v>
       </c>
       <c r="H34" s="38" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="I34" s="3">
         <v>2786298806</v>
@@ -4601,10 +4608,10 @@
         <v>29</v>
       </c>
       <c r="L34" s="52" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="M34" s="60" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="N34" s="25">
         <v>45903</v>
@@ -4655,10 +4662,10 @@
         <v>2025</v>
       </c>
       <c r="B35" s="49" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C35" s="44" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D35" s="74">
         <f t="shared" si="0"/>
@@ -4674,7 +4681,7 @@
         <v>2025003050023</v>
       </c>
       <c r="H35" s="38" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I35" s="3">
         <v>4842926067</v>
@@ -4740,7 +4747,7 @@
         <v>2025</v>
       </c>
       <c r="B36" s="49" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C36" s="44" t="s">
         <v>33</v>
@@ -4759,7 +4766,7 @@
         <v>2025003050028</v>
       </c>
       <c r="H36" s="38" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="I36" s="3">
         <v>4663630855</v>
@@ -4825,7 +4832,7 @@
         <v>2025</v>
       </c>
       <c r="B37" s="49" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C37" s="44" t="s">
         <v>42</v>
@@ -4835,16 +4842,16 @@
         <v>4</v>
       </c>
       <c r="E37" s="38" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F37" s="38" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G37" s="50">
         <v>2025003050024</v>
       </c>
       <c r="H37" s="38" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I37" s="3">
         <v>14688946853</v>
@@ -4856,10 +4863,10 @@
         <v>29</v>
       </c>
       <c r="L37" s="52" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="M37" s="60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N37" s="25">
         <v>45938</v>
@@ -4910,26 +4917,26 @@
         <v>2025</v>
       </c>
       <c r="B38" s="49" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C38" s="44" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D38" s="75">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E38" s="38" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F38" s="38" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G38" s="50">
         <v>2025003050025</v>
       </c>
       <c r="H38" s="38" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I38" s="3">
         <v>5913699663</v>
@@ -4938,13 +4945,13 @@
         <v>5913699663</v>
       </c>
       <c r="K38" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L38" s="52" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="M38" s="60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N38" s="25">
         <v>45915</v>
@@ -4995,7 +5002,7 @@
         <v>2025</v>
       </c>
       <c r="B39" s="49" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C39" s="44" t="s">
         <v>25</v>
@@ -5004,7 +5011,7 @@
         <v>0</v>
       </c>
       <c r="E39" s="38" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="F39" s="38" t="s">
         <v>27</v>
@@ -5013,7 +5020,7 @@
         <v>2025003050035</v>
       </c>
       <c r="H39" s="38" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I39" s="3">
         <v>5248430707.1999998</v>
@@ -5028,13 +5035,13 @@
         <v>30</v>
       </c>
       <c r="M39" s="60" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="N39" s="25">
         <v>45967</v>
       </c>
       <c r="O39" s="68" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="P39" s="47">
         <v>0</v>
@@ -5064,7 +5071,7 @@
         <v>0</v>
       </c>
       <c r="Y39" s="47" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="Z39" s="43"/>
       <c r="AA39" s="43"/>
@@ -5081,7 +5088,7 @@
         <v>2025</v>
       </c>
       <c r="B40" s="49" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C40" s="44" t="s">
         <v>25</v>
@@ -5091,7 +5098,7 @@
         <v>1.63</v>
       </c>
       <c r="E40" s="38" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="F40" s="38" t="s">
         <v>27</v>
@@ -5100,7 +5107,7 @@
         <v>2025003050026</v>
       </c>
       <c r="H40" s="38" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="I40" s="3">
         <v>3715229969</v>
@@ -5115,7 +5122,7 @@
         <v>30</v>
       </c>
       <c r="M40" s="60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N40" s="25">
         <v>45968</v>
@@ -5166,7 +5173,7 @@
         <v>2025</v>
       </c>
       <c r="B41" s="49" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C41" s="44" t="s">
         <v>25</v>
@@ -5176,16 +5183,16 @@
         <v>2</v>
       </c>
       <c r="E41" s="38" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="F41" s="38" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G41" s="50">
         <v>2025003050034</v>
       </c>
       <c r="H41" s="38" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="I41" s="3">
         <v>4782821867</v>
@@ -5200,7 +5207,7 @@
         <v>30</v>
       </c>
       <c r="M41" s="60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N41" s="25">
         <v>45973</v>
@@ -5251,7 +5258,7 @@
         <v>2025</v>
       </c>
       <c r="B42" s="49" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C42" s="44" t="s">
         <v>33</v>
@@ -5261,7 +5268,7 @@
         <v>1</v>
       </c>
       <c r="E42" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F42" s="38" t="s">
         <v>27</v>
@@ -5270,7 +5277,7 @@
         <v>2025003050031</v>
       </c>
       <c r="H42" s="38" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="I42" s="3">
         <v>2267187134</v>
@@ -5285,7 +5292,7 @@
         <v>30</v>
       </c>
       <c r="M42" s="62" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="N42" s="46">
         <v>45971</v>
@@ -5338,17 +5345,17 @@
         <v>2025</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D43" s="74">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E43" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F43" s="38" t="s">
         <v>27</v>
@@ -5357,7 +5364,7 @@
         <v>2025003050032</v>
       </c>
       <c r="H43" s="38" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="I43" s="3">
         <v>2068919343</v>
@@ -5366,13 +5373,13 @@
         <v>1654822441</v>
       </c>
       <c r="K43" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L43" s="52" t="s">
         <v>30</v>
       </c>
       <c r="M43" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N43" s="25">
         <v>46015</v>
@@ -5423,17 +5430,17 @@
         <v>2025</v>
       </c>
       <c r="B44" s="49" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C44" s="44" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D44" s="74">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E44" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F44" s="38" t="s">
         <v>27</v>
@@ -5442,7 +5449,7 @@
         <v>2025003050038</v>
       </c>
       <c r="H44" s="38" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="I44" s="3">
         <v>2138705796</v>
@@ -5451,13 +5458,13 @@
         <v>1500000000</v>
       </c>
       <c r="K44" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L44" s="52" t="s">
         <v>30</v>
       </c>
       <c r="M44" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N44" s="25">
         <v>46001</v>
@@ -5510,7 +5517,7 @@
         <v>2025</v>
       </c>
       <c r="B45" s="49" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C45" s="44" t="s">
         <v>25</v>
@@ -5529,7 +5536,7 @@
         <v>2025003050046</v>
       </c>
       <c r="H45" s="38" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I45" s="3">
         <v>4319392762</v>
@@ -5544,7 +5551,7 @@
         <v>30</v>
       </c>
       <c r="M45" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N45" s="25">
         <v>46014</v>
@@ -5577,7 +5584,7 @@
         <v>100</v>
       </c>
       <c r="X45" s="60" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="Y45" s="52"/>
       <c r="Z45" s="43"/>
@@ -5595,17 +5602,17 @@
         <v>2025</v>
       </c>
       <c r="B46" s="49" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C46" s="44" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D46" s="74">
         <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F46" s="38" t="s">
         <v>27</v>
@@ -5614,7 +5621,7 @@
         <v>2025003050043</v>
       </c>
       <c r="H46" s="38" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="I46" s="3">
         <v>2387040561</v>
@@ -5623,13 +5630,13 @@
         <v>1500000000</v>
       </c>
       <c r="K46" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L46" s="52" t="s">
         <v>30</v>
       </c>
       <c r="M46" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N46" s="25">
         <v>46011</v>
@@ -5680,26 +5687,26 @@
         <v>2025</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D47" s="75">
         <f t="shared" si="0"/>
         <v>9.1999999999999993</v>
       </c>
       <c r="E47" s="38" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G47" s="50">
         <v>2025003050027</v>
       </c>
       <c r="H47" s="38" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="I47" s="3">
         <v>27387320782</v>
@@ -5711,10 +5718,10 @@
         <v>29</v>
       </c>
       <c r="L47" s="52" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="M47" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N47" s="25">
         <v>46013</v>
@@ -5747,7 +5754,7 @@
         <v>89</v>
       </c>
       <c r="X47" s="60" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="Y47" s="47"/>
       <c r="Z47" s="43"/>
@@ -5765,7 +5772,7 @@
         <v>2025</v>
       </c>
       <c r="B48" s="49" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C48" s="44" t="s">
         <v>42</v>
@@ -5775,7 +5782,7 @@
         <v>1</v>
       </c>
       <c r="E48" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F48" s="38" t="s">
         <v>27</v>
@@ -5784,7 +5791,7 @@
         <v>2025003050053</v>
       </c>
       <c r="H48" s="38" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I48" s="3">
         <v>2149409352</v>
@@ -5793,7 +5800,7 @@
         <v>1500000000</v>
       </c>
       <c r="K48" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L48" s="52" t="s">
         <v>30</v>
@@ -5852,7 +5859,7 @@
         <v>2025</v>
       </c>
       <c r="B49" s="49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C49" s="44" t="s">
         <v>42</v>
@@ -5862,7 +5869,7 @@
         <v>1</v>
       </c>
       <c r="E49" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F49" s="38" t="s">
         <v>27</v>
@@ -5871,7 +5878,7 @@
         <v>2025003050051</v>
       </c>
       <c r="H49" s="38" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I49" s="3">
         <v>2264647460</v>
@@ -5880,7 +5887,7 @@
         <v>1750000000</v>
       </c>
       <c r="K49" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L49" s="52" t="s">
         <v>30</v>
@@ -5939,7 +5946,7 @@
         <v>2025</v>
       </c>
       <c r="B50" s="38" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C50" s="48" t="s">
         <v>25</v>
@@ -5949,7 +5956,7 @@
         <v>1.73</v>
       </c>
       <c r="E50" s="38" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F50" s="38" t="s">
         <v>27</v>
@@ -5958,7 +5965,7 @@
         <v>2025003050056</v>
       </c>
       <c r="H50" s="38" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I50" s="4">
         <v>4431237626</v>
@@ -5973,7 +5980,7 @@
         <v>30</v>
       </c>
       <c r="M50" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N50" s="25">
         <v>46014</v>
@@ -6006,7 +6013,7 @@
         <v>100</v>
       </c>
       <c r="X50" s="60" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="Y50" s="47"/>
       <c r="Z50" s="43"/>
@@ -6024,17 +6031,17 @@
         <v>2025</v>
       </c>
       <c r="B51" s="49" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C51" s="44" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D51" s="74">
         <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="E51" s="38" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F51" s="38" t="s">
         <v>27</v>
@@ -6043,7 +6050,7 @@
         <v>2025003050044</v>
       </c>
       <c r="H51" s="38" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="I51" s="3">
         <v>2808881690</v>
@@ -6052,7 +6059,7 @@
         <v>2708881690</v>
       </c>
       <c r="K51" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L51" s="52" t="s">
         <v>30</v>
@@ -6111,7 +6118,7 @@
         <v>2025</v>
       </c>
       <c r="B52" s="49" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C52" s="44" t="s">
         <v>25</v>
@@ -6121,7 +6128,7 @@
         <v>1</v>
       </c>
       <c r="E52" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F52" s="38" t="s">
         <v>27</v>
@@ -6130,7 +6137,7 @@
         <v>2025003050045</v>
       </c>
       <c r="H52" s="38" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="I52" s="3">
         <v>2357899973</v>
@@ -6139,13 +6146,13 @@
         <v>1680000000</v>
       </c>
       <c r="K52" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L52" s="52" t="s">
         <v>30</v>
       </c>
       <c r="M52" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N52" s="25">
         <v>46013</v>
@@ -6196,17 +6203,17 @@
         <v>2025</v>
       </c>
       <c r="B53" s="49" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C53" s="44" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D53" s="74">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E53" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F53" s="38" t="s">
         <v>27</v>
@@ -6215,7 +6222,7 @@
         <v>2025003050050</v>
       </c>
       <c r="H53" s="38" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I53" s="3">
         <v>1879328482</v>
@@ -6224,7 +6231,7 @@
         <v>1500000000</v>
       </c>
       <c r="K53" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L53" s="52" t="s">
         <v>30</v>
@@ -6283,7 +6290,7 @@
         <v>2025</v>
       </c>
       <c r="B54" s="49" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C54" s="44" t="s">
         <v>42</v>
@@ -6293,7 +6300,7 @@
         <v>1</v>
       </c>
       <c r="E54" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F54" s="38" t="s">
         <v>27</v>
@@ -6302,7 +6309,7 @@
         <v>2025003050049</v>
       </c>
       <c r="H54" s="38" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I54" s="3">
         <v>2156349509</v>
@@ -6311,7 +6318,7 @@
         <v>1500000000</v>
       </c>
       <c r="K54" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L54" s="52" t="s">
         <v>30</v>
@@ -6370,26 +6377,26 @@
         <v>2026</v>
       </c>
       <c r="B55" s="38" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C55" s="48" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D55" s="75">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E55" s="38" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F55" s="38" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G55" s="50">
         <v>2025003050036</v>
       </c>
       <c r="H55" s="38" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I55" s="3">
         <v>14202451801</v>
@@ -6404,7 +6411,7 @@
         <v>30</v>
       </c>
       <c r="M55" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N55" s="25">
         <v>46031</v>
@@ -6431,13 +6438,13 @@
         <v>38.06</v>
       </c>
       <c r="V55" s="47" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="W55" s="47" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="X55" s="60" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="Y55" s="47"/>
       <c r="Z55" s="43"/>
@@ -6455,26 +6462,26 @@
         <v>2026</v>
       </c>
       <c r="B56" s="38" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C56" s="48" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D56" s="75">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E56" s="38" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F56" s="38" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G56" s="50">
         <v>2025003050040</v>
       </c>
       <c r="H56" s="38" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I56" s="3">
         <v>2540216819</v>
@@ -6483,13 +6490,13 @@
         <v>2540216819</v>
       </c>
       <c r="K56" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L56" s="52" t="s">
         <v>30</v>
       </c>
       <c r="M56" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N56" s="25">
         <v>46031</v>
@@ -6498,10 +6505,10 @@
         <v>46335</v>
       </c>
       <c r="P56" s="54" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Q56" s="54" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R56" s="63">
         <v>19</v>
@@ -6540,26 +6547,26 @@
         <v>2026</v>
       </c>
       <c r="B57" s="38" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C57" s="48" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D57" s="75">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E57" s="38" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F57" s="38" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G57" s="50">
         <v>2025003050039</v>
       </c>
       <c r="H57" s="38" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I57" s="51">
         <v>9381110055</v>
@@ -6574,7 +6581,7 @@
         <v>30</v>
       </c>
       <c r="M57" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N57" s="25">
         <v>46031</v>
@@ -6583,10 +6590,10 @@
         <v>46505</v>
       </c>
       <c r="P57" s="47" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Q57" s="47" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R57" s="63" t="s">
         <v>40</v>
@@ -6625,26 +6632,26 @@
         <v>2026</v>
       </c>
       <c r="B58" s="38" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C58" s="48" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D58" s="75">
         <f t="shared" si="0"/>
         <v>1.07</v>
       </c>
       <c r="E58" s="38" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="F58" s="38" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G58" s="50">
         <v>2025003050060</v>
       </c>
       <c r="H58" s="38" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="I58" s="4">
         <v>5567719862</v>
@@ -6653,13 +6660,13 @@
         <v>2783859931</v>
       </c>
       <c r="K58" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L58" s="52" t="s">
         <v>30</v>
       </c>
       <c r="M58" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N58" s="25">
         <v>46048</v>
@@ -6689,7 +6696,7 @@
         <v>0</v>
       </c>
       <c r="W58" s="47" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="X58" s="60">
         <v>0</v>
@@ -6710,7 +6717,7 @@
         <v>2026</v>
       </c>
       <c r="B59" s="38" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C59" s="48" t="s">
         <v>25</v>
@@ -6720,7 +6727,7 @@
         <v>1</v>
       </c>
       <c r="E59" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F59" s="38" t="s">
         <v>27</v>
@@ -6729,7 +6736,7 @@
         <v>2025003050047</v>
       </c>
       <c r="H59" s="38" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="I59" s="51">
         <v>2577210949</v>
@@ -6738,13 +6745,13 @@
         <v>2557210949</v>
       </c>
       <c r="K59" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L59" s="52" t="s">
         <v>30</v>
       </c>
       <c r="M59" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N59" s="25">
         <v>46072</v>
@@ -6777,7 +6784,7 @@
         <v>40</v>
       </c>
       <c r="X59" s="60" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="Y59" s="47"/>
       <c r="Z59" s="43"/>
@@ -6795,26 +6802,26 @@
         <v>2026</v>
       </c>
       <c r="B60" s="38" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C60" s="48" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D60" s="75">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E60" s="38" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F60" s="38" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G60" s="50">
         <v>2025003050059</v>
       </c>
       <c r="H60" s="38" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="I60" s="3">
         <v>6759815490</v>
@@ -6823,13 +6830,13 @@
         <v>6759815490</v>
       </c>
       <c r="K60" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L60" s="28" t="s">
         <v>30</v>
       </c>
       <c r="M60" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N60" s="25">
         <v>46077</v>
@@ -6880,26 +6887,26 @@
         <v>2026</v>
       </c>
       <c r="B61" s="38" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C61" s="48" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D61" s="75">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E61" s="38" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F61" s="38" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G61" s="50">
         <v>2025003050058</v>
       </c>
       <c r="H61" s="38" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="I61" s="51">
         <v>1956028276</v>
@@ -6908,13 +6915,13 @@
         <v>1956028276</v>
       </c>
       <c r="K61" s="48" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L61" s="29" t="s">
         <v>30</v>
       </c>
       <c r="M61" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N61" s="25">
         <v>46073</v>
@@ -6944,7 +6951,7 @@
         <v>0</v>
       </c>
       <c r="W61" s="47" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="X61" s="60">
         <v>60</v>
@@ -6965,7 +6972,7 @@
         <v>2026</v>
       </c>
       <c r="B62" s="38" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C62" s="53" t="s">
         <v>25</v>
@@ -6975,16 +6982,16 @@
         <v>1</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F62" s="18" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G62" s="73">
         <v>2025003050037</v>
       </c>
       <c r="H62" s="38" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="I62" s="3">
         <v>4919153330</v>
@@ -6999,7 +7006,7 @@
         <v>30</v>
       </c>
       <c r="M62" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N62" s="25">
         <v>46073</v>
@@ -7050,7 +7057,7 @@
         <v>2026</v>
       </c>
       <c r="B63" s="38" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C63" s="53" t="s">
         <v>33</v>
@@ -7060,16 +7067,16 @@
         <v>1</v>
       </c>
       <c r="E63" s="18" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F63" s="18" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G63" s="73">
         <v>2025003050037</v>
       </c>
       <c r="H63" s="38" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="I63" s="3">
         <v>4814470012</v>
@@ -7084,7 +7091,7 @@
         <v>30</v>
       </c>
       <c r="M63" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N63" s="25">
         <v>46073</v>
@@ -7135,26 +7142,26 @@
         <v>2026</v>
       </c>
       <c r="B64" s="38" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C64" s="48" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D64" s="75">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="E64" s="38" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="F64" s="18" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G64" s="50">
         <v>2026003050010</v>
       </c>
       <c r="H64" s="38" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="I64" s="51">
         <v>8659084152</v>
@@ -7169,7 +7176,7 @@
         <v>30</v>
       </c>
       <c r="M64" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N64" s="25">
         <v>46105</v>
@@ -7220,7 +7227,7 @@
         <v>2026</v>
       </c>
       <c r="B65" s="38" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C65" s="48" t="s">
         <v>25</v>
@@ -7239,7 +7246,7 @@
         <v>2026003050009</v>
       </c>
       <c r="H65" s="38" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="I65" s="51">
         <v>5112178665</v>
@@ -7254,7 +7261,7 @@
         <v>30</v>
       </c>
       <c r="M65" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N65" s="25">
         <v>46107</v>
@@ -7305,7 +7312,7 @@
         <v>2026</v>
       </c>
       <c r="B66" s="38" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C66" s="48" t="s">
         <v>42</v>
@@ -7315,7 +7322,7 @@
         <v>1</v>
       </c>
       <c r="E66" s="18" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F66" s="18" t="s">
         <v>27</v>
@@ -7324,7 +7331,7 @@
         <v>2025003050057</v>
       </c>
       <c r="H66" s="38" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I66" s="3">
         <v>2205897938</v>
@@ -7333,13 +7340,13 @@
         <v>1500000000</v>
       </c>
       <c r="K66" s="48" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L66" s="52" t="s">
         <v>30</v>
       </c>
       <c r="M66" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N66" s="25">
         <v>46299</v>
@@ -7386,7 +7393,7 @@
         <v>2026</v>
       </c>
       <c r="B67" s="38" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C67" s="48" t="s">
         <v>25</v>
@@ -7396,7 +7403,7 @@
         <v>1</v>
       </c>
       <c r="E67" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F67" s="18" t="s">
         <v>27</v>
@@ -7405,7 +7412,7 @@
         <v>2025003050052</v>
       </c>
       <c r="H67" s="38" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="I67" s="3">
         <v>1865730932</v>
@@ -7414,19 +7421,19 @@
         <v>1500000000</v>
       </c>
       <c r="K67" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L67" s="52" t="s">
         <v>30</v>
       </c>
       <c r="M67" s="63" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="N67" s="25">
         <v>46132</v>
       </c>
       <c r="O67" s="68" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="P67" s="47" t="s">
         <v>40</v>
@@ -7467,17 +7474,17 @@
         <v>2026</v>
       </c>
       <c r="B68" s="38" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C68" s="48" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D68" s="74">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E68" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F68" s="18" t="s">
         <v>27</v>
@@ -7486,7 +7493,7 @@
         <v>2026003050017</v>
       </c>
       <c r="H68" s="38" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="I68" s="4">
         <v>2177276654</v>
@@ -7495,19 +7502,19 @@
         <v>1677276654</v>
       </c>
       <c r="K68" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L68" s="47" t="s">
         <v>30</v>
       </c>
       <c r="M68" s="63" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="N68" s="25">
         <v>46147</v>
       </c>
       <c r="O68" s="68" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="P68" s="47" t="s">
         <v>40</v>
@@ -7531,10 +7538,10 @@
         <v>0</v>
       </c>
       <c r="W68" s="47" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="X68" s="60" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="Y68" s="47"/>
       <c r="Z68" s="43"/>
@@ -7552,7 +7559,7 @@
         <v>2026</v>
       </c>
       <c r="B69" s="38" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C69" s="48" t="s">
         <v>25</v>
@@ -7562,7 +7569,7 @@
         <v>3</v>
       </c>
       <c r="E69" s="38" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F69" s="18" t="s">
         <v>27</v>
@@ -7571,7 +7578,7 @@
         <v>2026003050018</v>
       </c>
       <c r="H69" s="38" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="I69" s="51">
         <v>8022406899</v>
@@ -7586,7 +7593,7 @@
         <v>30</v>
       </c>
       <c r="M69" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N69" s="25">
         <v>46129</v>
@@ -7616,7 +7623,7 @@
         <v>40</v>
       </c>
       <c r="W69" s="47" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="X69" s="60">
         <v>100</v>
@@ -7637,7 +7644,7 @@
         <v>2026</v>
       </c>
       <c r="B70" s="38" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C70" s="48" t="s">
         <v>33</v>
@@ -7647,7 +7654,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F70" s="38" t="s">
         <v>27</v>
@@ -7656,7 +7663,7 @@
         <v>2026003050021</v>
       </c>
       <c r="H70" s="38" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="I70" s="3">
         <v>2356550945</v>
@@ -7665,19 +7672,19 @@
         <v>1768550945</v>
       </c>
       <c r="K70" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L70" s="52" t="s">
         <v>30</v>
       </c>
       <c r="M70" s="63" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="N70" s="25">
         <v>46149</v>
       </c>
       <c r="O70" s="68" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="P70" s="47" t="s">
         <v>40</v>
@@ -7701,7 +7708,7 @@
         <v>0</v>
       </c>
       <c r="W70" s="47" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="X70" s="60">
         <v>75</v>
@@ -7722,17 +7729,17 @@
         <v>2026</v>
       </c>
       <c r="B71" s="49" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C71" s="44" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D71" s="74">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E71" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F71" s="38" t="s">
         <v>27</v>
@@ -7741,7 +7748,7 @@
         <v>2026003050005</v>
       </c>
       <c r="H71" s="38" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I71" s="45">
         <v>2126428620</v>
@@ -7750,13 +7757,13 @@
         <v>1821081885</v>
       </c>
       <c r="K71" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L71" s="52" t="s">
         <v>30</v>
       </c>
       <c r="M71" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N71" s="25">
         <v>46191</v>
@@ -7786,7 +7793,7 @@
         <v>40</v>
       </c>
       <c r="W71" s="47" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="X71" s="60">
         <v>100</v>
@@ -7807,7 +7814,7 @@
         <v>2026</v>
       </c>
       <c r="B72" s="38" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C72" s="48" t="s">
         <v>42</v>
@@ -7817,7 +7824,7 @@
         <v>1</v>
       </c>
       <c r="E72" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F72" s="38" t="s">
         <v>27</v>
@@ -7826,7 +7833,7 @@
         <v>2026003050006</v>
       </c>
       <c r="H72" s="38" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="I72" s="3">
         <v>2495192913</v>
@@ -7835,19 +7842,19 @@
         <v>2490192913</v>
       </c>
       <c r="K72" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L72" s="52" t="s">
         <v>30</v>
       </c>
       <c r="M72" s="63" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="N72" s="25">
         <v>46170</v>
       </c>
       <c r="O72" s="68" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="P72" s="47" t="s">
         <v>40</v>
@@ -7888,17 +7895,17 @@
         <v>2026</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D73" s="74">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="F73" s="7" t="s">
         <v>27</v>
@@ -7907,7 +7914,7 @@
         <v>2026003050011</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I73" s="16">
         <v>2095882218</v>
@@ -7916,13 +7923,13 @@
         <v>1995882218</v>
       </c>
       <c r="K73" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L73" s="52" t="s">
         <v>30</v>
       </c>
       <c r="M73" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N73" s="25">
         <v>46132</v>
@@ -7952,7 +7959,7 @@
         <v>0</v>
       </c>
       <c r="W73" s="47" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="X73" s="60">
         <v>40</v>
@@ -7973,26 +7980,26 @@
         <v>2026</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D74" s="75">
+        <v>58</v>
+      </c>
+      <c r="D74" s="74">
         <f t="shared" si="1"/>
         <v>0.98</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G74" s="58">
         <v>2026003050014</v>
       </c>
       <c r="H74" s="7" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="I74" s="11">
         <v>5482855957</v>
@@ -8007,13 +8014,13 @@
         <v>30</v>
       </c>
       <c r="M74" s="63" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="N74" s="25">
         <v>46189</v>
       </c>
       <c r="O74" s="68" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="P74" s="47" t="s">
         <v>40</v>
@@ -8034,10 +8041,10 @@
         <v>40</v>
       </c>
       <c r="V74" s="46" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="W74" s="46" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="X74" s="60">
         <v>100</v>
@@ -8058,26 +8065,26 @@
         <v>2026</v>
       </c>
       <c r="B75" s="38" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C75" s="48" t="s">
-        <v>69</v>
-      </c>
-      <c r="D75" s="75">
+        <v>66</v>
+      </c>
+      <c r="D75" s="74">
         <f t="shared" si="1"/>
         <v>0.54</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G75" s="50">
         <v>2026003050008</v>
       </c>
       <c r="H75" s="38" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I75" s="3">
         <v>2300078297</v>
@@ -8086,13 +8093,13 @@
         <v>2250078297</v>
       </c>
       <c r="K75" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L75" s="52" t="s">
         <v>30</v>
       </c>
       <c r="M75" s="63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N75" s="25">
         <v>46175</v>
@@ -8119,10 +8126,10 @@
         <v>0</v>
       </c>
       <c r="V75" s="46" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="W75" s="46" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="X75" s="60">
         <v>100</v>
@@ -8143,26 +8150,26 @@
         <v>2026</v>
       </c>
       <c r="B76" s="38" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C76" s="48" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D76" s="75">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E76" s="38" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F76" s="18" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G76" s="50">
         <v>2026003050002</v>
       </c>
       <c r="H76" s="38" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="I76" s="51">
         <v>1408385533</v>
@@ -8171,19 +8178,19 @@
         <v>1408385533</v>
       </c>
       <c r="K76" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L76" s="52" t="s">
         <v>30</v>
       </c>
       <c r="M76" s="63" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="N76" s="25">
         <v>46185</v>
       </c>
       <c r="O76" s="68" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="P76" s="47" t="s">
         <v>40</v>
@@ -8204,10 +8211,10 @@
         <v>40</v>
       </c>
       <c r="V76" s="46" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="W76" s="46" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="X76" s="60">
         <v>100</v>
@@ -8228,26 +8235,26 @@
         <v>2026</v>
       </c>
       <c r="B77" s="38" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C77" s="53" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D77" s="75">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F77" s="18" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G77" s="73">
         <v>2026003050020</v>
       </c>
       <c r="H77" s="38" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="I77" s="51">
         <v>8105380232</v>
@@ -8262,13 +8269,13 @@
         <v>30</v>
       </c>
       <c r="M77" s="63" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="N77" s="25">
         <v>46185</v>
       </c>
       <c r="O77" s="68" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="P77" s="47" t="s">
         <v>40</v>
@@ -8289,10 +8296,10 @@
         <v>40</v>
       </c>
       <c r="V77" s="46" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="W77" s="46" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="X77" s="60">
         <v>100</v>
@@ -8313,26 +8320,26 @@
         <v>2026</v>
       </c>
       <c r="B78" s="38" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C78" s="53" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D78" s="75">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="F78" s="18" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G78" s="73">
         <v>2026003050020</v>
       </c>
       <c r="H78" s="38" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="I78" s="3">
         <v>4333614485</v>
@@ -8347,13 +8354,13 @@
         <v>30</v>
       </c>
       <c r="M78" s="63" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="N78" s="25">
         <v>46185</v>
       </c>
       <c r="O78" s="68" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="P78" s="47" t="s">
         <v>40</v>
@@ -8374,10 +8381,10 @@
         <v>40</v>
       </c>
       <c r="V78" s="46" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="W78" s="46" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="X78" s="60">
         <v>100</v>
@@ -8398,7 +8405,7 @@
         <v>2026</v>
       </c>
       <c r="B79" s="38" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C79" s="53" t="s">
         <v>42</v>
@@ -8408,16 +8415,16 @@
         <v>1</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="F79" s="18" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G79" s="73">
         <v>2026003050015</v>
       </c>
       <c r="H79" s="38" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I79" s="3">
         <v>3806958402</v>
@@ -8432,13 +8439,13 @@
         <v>30</v>
       </c>
       <c r="M79" s="63" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="N79" s="25">
         <v>46185</v>
       </c>
       <c r="O79" s="68" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="P79" s="47" t="s">
         <v>40</v>
@@ -8459,10 +8466,10 @@
         <v>40</v>
       </c>
       <c r="V79" s="46" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="W79" s="46" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="X79" s="60">
         <v>100</v>
@@ -8483,26 +8490,26 @@
         <v>2026</v>
       </c>
       <c r="B80" s="38" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C80" s="53" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D80" s="75">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F80" s="18" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G80" s="73">
         <v>2026003050015</v>
       </c>
       <c r="H80" s="38" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I80" s="3">
         <v>2044483403</v>
@@ -8517,13 +8524,13 @@
         <v>30</v>
       </c>
       <c r="M80" s="63" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="N80" s="25">
         <v>46185</v>
       </c>
       <c r="O80" s="68" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="P80" s="47" t="s">
         <v>40</v>
@@ -8544,10 +8551,10 @@
         <v>40</v>
       </c>
       <c r="V80" s="46" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="W80" s="46" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="X80" s="60">
         <v>100</v>
@@ -8568,26 +8575,26 @@
         <v>2026</v>
       </c>
       <c r="B81" s="38" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C81" s="48" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D81" s="75">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="F81" s="18" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G81" s="50">
         <v>2026003050025</v>
       </c>
       <c r="H81" s="38" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="I81" s="3">
         <v>3738220582</v>
@@ -8602,13 +8609,13 @@
         <v>30</v>
       </c>
       <c r="M81" s="63" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="N81" s="25">
         <v>46185</v>
       </c>
       <c r="O81" s="68" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="P81" s="47" t="s">
         <v>40</v>
@@ -8629,10 +8636,10 @@
         <v>40</v>
       </c>
       <c r="V81" s="46" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="W81" s="46" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="X81" s="60">
         <v>100</v>
@@ -8653,17 +8660,17 @@
         <v>2026</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C82" s="48" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D82" s="74">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E82" s="38" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="F82" s="38" t="s">
         <v>27</v>
@@ -8672,7 +8679,7 @@
         <v>2026003050016</v>
       </c>
       <c r="H82" s="38" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I82" s="4">
         <v>2343812951</v>
@@ -8681,17 +8688,17 @@
         <v>1875050361</v>
       </c>
       <c r="K82" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L82" s="47" t="s">
         <v>30</v>
       </c>
       <c r="M82" s="63" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N82" s="25"/>
       <c r="O82" s="68" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="P82" s="47" t="s">
         <v>40</v>
@@ -8736,26 +8743,26 @@
         <v>2026</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C83" s="48" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D83" s="75">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E83" s="38" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F83" s="38" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="G83" s="50">
         <v>2026003050022</v>
       </c>
       <c r="H83" s="38" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I83" s="51">
         <v>6654540000</v>
@@ -8770,13 +8777,13 @@
         <v>30</v>
       </c>
       <c r="M83" s="63" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="N83" s="69">
         <v>46239</v>
       </c>
       <c r="O83" s="68" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="P83" s="47" t="s">
         <v>40</v>
@@ -8821,26 +8828,26 @@
         <v>2026</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C84" s="48" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D84" s="75">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E84" s="38" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F84" s="38" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="G84" s="50">
         <v>2026003050019</v>
       </c>
       <c r="H84" s="38" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="I84" s="51">
         <v>8154980500</v>
@@ -8855,13 +8862,13 @@
         <v>30</v>
       </c>
       <c r="M84" s="63" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="N84" s="69">
         <v>46212</v>
       </c>
       <c r="O84" s="68" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="P84" s="47" t="s">
         <v>40</v>
@@ -10287,7 +10294,7 @@
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="T1:U1"/>
   </mergeCells>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="41" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OACEVEDOD\Desktop\Jefe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{019826CA-4825-4B33-B533-4F25D8B12F1D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296EA0E7-BAF4-437C-9FB5-89B629B30D8A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,10 +99,6 @@
     <t>Subregión</t>
   </si>
   <si>
-    <t>Alcance 
-#</t>
-  </si>
-  <si>
     <t>Alcance</t>
   </si>
   <si>
@@ -906,6 +902,10 @@
   </si>
   <si>
     <t>Construcción de Alcantarillado Residual Vía Centro de Salud Don Bosco de Currulao en el Distrito de Turbo, Antioquia</t>
+  </si>
+  <si>
+    <t>Alcance
+Valor</t>
   </si>
 </sst>
 </file>
@@ -916,8 +916,8 @@
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$$-240A]\ #,##0.00"/>
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="170" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -1298,10 +1298,10 @@
     <xf numFmtId="1" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1412,7 +1412,7 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1825,73 +1825,73 @@
         <v>7</v>
       </c>
       <c r="D2" s="31" t="s">
+        <v>276</v>
+      </c>
+      <c r="E2" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="F2" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="G2" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="H2" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="I2" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="32" t="s">
+      <c r="J2" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="32" t="s">
+      <c r="K2" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="32" t="s">
+      <c r="L2" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="31" t="s">
+      <c r="M2" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="33" t="s">
+      <c r="N2" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="33" t="s">
+      <c r="O2" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="34" t="s">
+      <c r="P2" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="35" t="s">
+      <c r="Q2" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="Q2" s="33" t="s">
+      <c r="R2" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="R2" s="33" t="s">
+      <c r="S2" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="T2" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="U2" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="V2" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="W2" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="X2" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="S2" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="T2" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="U2" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="V2" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="W2" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="X2" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y2" s="33" t="s">
+      <c r="Z2" s="36" t="s">
         <v>23</v>
-      </c>
-      <c r="Z2" s="36" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="36.75" customHeight="1">
@@ -1899,26 +1899,26 @@
         <v>2024</v>
       </c>
       <c r="B3" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="43" t="s">
         <v>25</v>
-      </c>
-      <c r="C3" s="43" t="s">
-        <v>26</v>
       </c>
       <c r="D3" s="65">
         <f>IF(ISNUMBER(E3),E3,IFERROR(VALUE(LEFT(E3,FIND(" ",E3)-1)),1))</f>
         <v>4</v>
       </c>
       <c r="E3" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="38" t="s">
         <v>27</v>
-      </c>
-      <c r="F3" s="38" t="s">
-        <v>28</v>
       </c>
       <c r="G3" s="1">
         <v>2024003050239</v>
       </c>
       <c r="H3" s="38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I3" s="3">
         <v>7046140299</v>
@@ -1930,13 +1930,13 @@
         <v>5636912239</v>
       </c>
       <c r="L3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="23" t="s">
+      <c r="N3" s="58" t="s">
         <v>31</v>
-      </c>
-      <c r="N3" s="58" t="s">
-        <v>32</v>
       </c>
       <c r="O3" s="45">
         <v>45635</v>
@@ -1969,7 +1969,7 @@
         <v>99.87</v>
       </c>
       <c r="Y3" s="58" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Z3" s="23">
         <v>100</v>
@@ -1989,26 +1989,26 @@
         <v>2024</v>
       </c>
       <c r="B4" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="43" t="s">
         <v>33</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>34</v>
       </c>
       <c r="D4" s="65">
         <f t="shared" ref="D4:D68" si="0">IF(ISNUMBER(E4),E4,IFERROR(VALUE(LEFT(E4,FIND(" ",E4)-1)),1))</f>
         <v>2</v>
       </c>
       <c r="E4" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4" s="39">
         <v>2024003050246</v>
       </c>
       <c r="H4" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I4" s="3">
         <v>4078127896</v>
@@ -2020,19 +2020,19 @@
         <v>3262502317</v>
       </c>
       <c r="L4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="M4" s="23" t="s">
-        <v>31</v>
-      </c>
       <c r="N4" s="59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O4" s="45">
         <v>45637</v>
       </c>
       <c r="P4" s="45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q4" s="24">
         <v>100</v>
@@ -2079,26 +2079,26 @@
         <v>2024</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" s="65">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E5" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5" s="1">
         <v>2024003050243</v>
       </c>
       <c r="H5" s="38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I5" s="3">
         <v>4907167940</v>
@@ -2110,13 +2110,13 @@
         <v>4047973265</v>
       </c>
       <c r="L5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="23" t="s">
+      <c r="N5" s="59" t="s">
         <v>31</v>
-      </c>
-      <c r="N5" s="59" t="s">
-        <v>32</v>
       </c>
       <c r="O5" s="45">
         <v>45635</v>
@@ -2149,7 +2149,7 @@
         <v>100</v>
       </c>
       <c r="Y5" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z5" s="23">
         <v>100</v>
@@ -2169,26 +2169,26 @@
         <v>2024</v>
       </c>
       <c r="B6" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="47" t="s">
         <v>43</v>
-      </c>
-      <c r="C6" s="47" t="s">
-        <v>44</v>
       </c>
       <c r="D6" s="65">
         <f>IF(ISNUMBER(E6),E6,IFERROR(VALUE(LEFT(E6,FIND(" ",E6)-1)),1))</f>
         <v>1866</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6" s="1">
         <v>2024053150037</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I6" s="3">
         <v>3945999620</v>
@@ -2200,13 +2200,13 @@
         <v>3156799696</v>
       </c>
       <c r="L6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="23" t="s">
+      <c r="N6" s="59" t="s">
         <v>31</v>
-      </c>
-      <c r="N6" s="59" t="s">
-        <v>32</v>
       </c>
       <c r="O6" s="45">
         <v>45635</v>
@@ -2239,7 +2239,7 @@
         <v>100</v>
       </c>
       <c r="Y6" s="59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Z6" s="23">
         <v>100</v>
@@ -2259,26 +2259,26 @@
         <v>2024</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" s="65">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E7" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7" s="39">
         <v>2024003050241</v>
       </c>
       <c r="H7" s="38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I7" s="3">
         <v>4232130933</v>
@@ -2290,13 +2290,13 @@
         <v>3385704746</v>
       </c>
       <c r="L7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="M7" s="23" t="s">
-        <v>31</v>
-      </c>
       <c r="N7" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O7" s="25">
         <v>45636</v>
@@ -2349,26 +2349,26 @@
         <v>2024</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E8" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G8" s="1">
         <v>2024051070040</v>
       </c>
       <c r="H8" s="38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I8" s="3">
         <v>1645755840</v>
@@ -2380,13 +2380,13 @@
         <v>1316604672</v>
       </c>
       <c r="L8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="M8" s="26" t="s">
+      <c r="N8" s="59" t="s">
         <v>31</v>
-      </c>
-      <c r="N8" s="59" t="s">
-        <v>32</v>
       </c>
       <c r="O8" s="45">
         <v>45636</v>
@@ -2419,7 +2419,7 @@
         <v>100</v>
       </c>
       <c r="Y8" s="59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Z8" s="23">
         <v>100</v>
@@ -2439,26 +2439,26 @@
         <v>2024</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9" s="65">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E9" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G9" s="39">
         <v>2024057560039</v>
       </c>
       <c r="H9" s="38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I9" s="3">
         <v>5459298912.8900003</v>
@@ -2470,19 +2470,19 @@
         <v>4319322167.8900003</v>
       </c>
       <c r="L9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="M9" s="23" t="s">
-        <v>31</v>
-      </c>
       <c r="N9" s="59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O9" s="25">
         <v>45636</v>
       </c>
       <c r="P9" s="45" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q9" s="23">
         <v>90.52</v>
@@ -2529,26 +2529,26 @@
         <v>2024</v>
       </c>
       <c r="B10" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="43" t="s">
         <v>57</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>58</v>
       </c>
       <c r="D10" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G10" s="39">
         <v>2024057890040</v>
       </c>
       <c r="H10" s="38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I10" s="3">
         <v>3035607509</v>
@@ -2560,19 +2560,19 @@
         <v>2428486007.1999998</v>
       </c>
       <c r="L10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M10" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="M10" s="23" t="s">
-        <v>31</v>
-      </c>
       <c r="N10" s="59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O10" s="45">
         <v>45628</v>
       </c>
       <c r="P10" s="45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q10" s="23">
         <v>98.69</v>
@@ -2599,7 +2599,7 @@
         <v>100</v>
       </c>
       <c r="Y10" s="59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z10" s="23">
         <v>100</v>
@@ -2619,26 +2619,26 @@
         <v>2024</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C11" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E11" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G11" s="39">
         <v>2024054830016</v>
       </c>
       <c r="H11" s="38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I11" s="3">
         <v>2596905323</v>
@@ -2650,13 +2650,13 @@
         <v>2077524258</v>
       </c>
       <c r="L11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M11" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="M11" s="23" t="s">
-        <v>31</v>
-      </c>
       <c r="N11" s="59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O11" s="45">
         <v>45636</v>
@@ -2689,7 +2689,7 @@
         <v>98.41</v>
       </c>
       <c r="Y11" s="59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z11" s="23">
         <v>100</v>
@@ -2709,26 +2709,26 @@
         <v>2024</v>
       </c>
       <c r="B12" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="43" t="s">
         <v>65</v>
-      </c>
-      <c r="C12" s="43" t="s">
-        <v>66</v>
       </c>
       <c r="D12" s="65">
         <f>IF(ISNUMBER(E12),E12,IFERROR(VALUE(LEFT(E12,FIND(" ",E12)-1)),1))</f>
         <v>1</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G12" s="39">
         <v>2024003050236</v>
       </c>
       <c r="H12" s="38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I12" s="3">
         <v>1513619665</v>
@@ -2740,13 +2740,13 @@
         <v>1210895732</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M12" s="23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N12" s="59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O12" s="45">
         <v>45618</v>
@@ -2799,26 +2799,26 @@
         <v>2024</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" s="65">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E13" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G13" s="39">
         <v>2024003050238</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I13" s="3">
         <v>4622246270</v>
@@ -2830,13 +2830,13 @@
         <v>3697797016</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M13" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="N13" s="59" t="s">
         <v>31</v>
-      </c>
-      <c r="N13" s="59" t="s">
-        <v>32</v>
       </c>
       <c r="O13" s="45">
         <v>45635</v>
@@ -2869,7 +2869,7 @@
         <v>100</v>
       </c>
       <c r="Y13" s="59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Z13" s="23">
         <v>100</v>
@@ -2889,26 +2889,26 @@
         <v>2024</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G14" s="39">
         <v>2024003050244</v>
       </c>
       <c r="H14" s="38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I14" s="4">
         <v>2241815667.6000004</v>
@@ -2920,19 +2920,19 @@
         <v>1742094798.4000001</v>
       </c>
       <c r="L14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M14" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="M14" s="24" t="s">
-        <v>31</v>
-      </c>
       <c r="N14" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O14" s="25">
         <v>45636</v>
       </c>
       <c r="P14" s="45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q14" s="27">
         <v>0</v>
@@ -2959,7 +2959,7 @@
         <v>96.99</v>
       </c>
       <c r="Y14" s="59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z14" s="24">
         <v>100</v>
@@ -2979,26 +2979,26 @@
         <v>2024</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" s="65">
         <f>IF(ISNUMBER(E15),E15,IFERROR(VALUE(LEFT(E15,FIND(" ",E15)-1)),1))</f>
         <v>1</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G15" s="1">
         <v>2024003050242</v>
       </c>
       <c r="H15" s="38" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I15" s="3">
         <v>2688840891</v>
@@ -3010,13 +3010,13 @@
         <v>2151072713</v>
       </c>
       <c r="L15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="M15" s="23" t="s">
+      <c r="N15" s="59" t="s">
         <v>31</v>
-      </c>
-      <c r="N15" s="59" t="s">
-        <v>32</v>
       </c>
       <c r="O15" s="45">
         <v>45637</v>
@@ -3049,7 +3049,7 @@
         <v>99.99</v>
       </c>
       <c r="Y15" s="59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Z15" s="23">
         <v>100</v>
@@ -3069,26 +3069,26 @@
         <v>2024</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D16" s="65">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G16" s="39">
         <v>2024003050245</v>
       </c>
       <c r="H16" s="38" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I16" s="3">
         <v>6076769979</v>
@@ -3100,19 +3100,19 @@
         <v>4861415983</v>
       </c>
       <c r="L16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M16" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="M16" s="23" t="s">
-        <v>31</v>
-      </c>
       <c r="N16" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O16" s="25">
         <v>45635</v>
       </c>
       <c r="P16" s="45" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q16" s="23">
         <v>71.45</v>
@@ -3159,26 +3159,26 @@
         <v>2024</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C17" s="43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17" s="65">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G17" s="39">
         <v>2024003050237</v>
       </c>
       <c r="H17" s="38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I17" s="3">
         <v>5449013722</v>
@@ -3190,13 +3190,13 @@
         <v>4359210977.6000004</v>
       </c>
       <c r="L17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M17" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="M17" s="23" t="s">
-        <v>31</v>
-      </c>
       <c r="N17" s="59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O17" s="25">
         <v>45635</v>
@@ -3249,26 +3249,26 @@
         <v>2024</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D18" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E18" s="38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F18" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G18" s="39">
         <v>2024051970041</v>
       </c>
       <c r="H18" s="38" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I18" s="3">
         <v>3445926513</v>
@@ -3280,13 +3280,13 @@
         <v>2756741210</v>
       </c>
       <c r="L18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M18" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="M18" s="23" t="s">
+      <c r="N18" s="59" t="s">
         <v>31</v>
-      </c>
-      <c r="N18" s="59" t="s">
-        <v>32</v>
       </c>
       <c r="O18" s="45">
         <v>45636</v>
@@ -3319,7 +3319,7 @@
         <v>99.99</v>
       </c>
       <c r="Y18" s="59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Z18" s="23">
         <v>100</v>
@@ -3339,26 +3339,26 @@
         <v>2024</v>
       </c>
       <c r="B19" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="43" t="s">
         <v>87</v>
-      </c>
-      <c r="C19" s="43" t="s">
-        <v>88</v>
       </c>
       <c r="D19" s="65">
         <f t="shared" si="0"/>
         <v>320</v>
       </c>
       <c r="E19" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" s="38" t="s">
         <v>89</v>
-      </c>
-      <c r="F19" s="38" t="s">
-        <v>90</v>
       </c>
       <c r="G19" s="39">
         <v>20243201010075</v>
       </c>
       <c r="H19" s="38" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I19" s="3">
         <v>15664988520</v>
@@ -3373,10 +3373,10 @@
         <v>0.2</v>
       </c>
       <c r="M19" s="23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N19" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O19" s="45">
         <v>45652</v>
@@ -3423,26 +3423,26 @@
         <v>2025</v>
       </c>
       <c r="B20" s="48" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C20" s="43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D20" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E20" s="38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F20" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G20" s="39">
         <v>2025003050003</v>
       </c>
       <c r="H20" s="38" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I20" s="3">
         <v>5581655075</v>
@@ -3454,13 +3454,13 @@
         <v>4519742225</v>
       </c>
       <c r="L20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M20" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="M20" s="23" t="s">
-        <v>31</v>
-      </c>
       <c r="N20" s="59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O20" s="25">
         <v>45768</v>
@@ -3511,26 +3511,26 @@
         <v>2025</v>
       </c>
       <c r="B21" s="48" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C21" s="43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D21" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E21" s="38" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F21" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G21" s="39">
         <v>2025003050008</v>
       </c>
       <c r="H21" s="38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I21" s="3">
         <v>2661301362</v>
@@ -3542,19 +3542,19 @@
         <v>2129041089.5999999</v>
       </c>
       <c r="L21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M21" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="M21" s="23" t="s">
-        <v>31</v>
-      </c>
       <c r="N21" s="59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O21" s="45">
         <v>45818</v>
       </c>
       <c r="P21" s="45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q21" s="46">
         <v>100</v>
@@ -3581,7 +3581,7 @@
         <v>100</v>
       </c>
       <c r="Y21" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z21" s="46">
         <v>100</v>
@@ -3601,26 +3601,26 @@
         <v>2025</v>
       </c>
       <c r="B22" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="43" t="s">
         <v>57</v>
-      </c>
-      <c r="C22" s="43" t="s">
-        <v>58</v>
       </c>
       <c r="D22" s="66">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G22" s="39">
         <v>2025003050002</v>
       </c>
       <c r="H22" s="38" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I22" s="3">
         <v>24272420632</v>
@@ -3632,19 +3632,19 @@
         <v>24272420632</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M22" s="23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N22" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O22" s="25">
         <v>45805</v>
       </c>
       <c r="P22" s="45" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q22" s="23">
         <v>7.59</v>
@@ -3689,26 +3689,26 @@
         <v>2025</v>
       </c>
       <c r="B23" s="48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C23" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D23" s="66">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E23" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="F23" s="38" t="s">
         <v>105</v>
-      </c>
-      <c r="F23" s="38" t="s">
-        <v>106</v>
       </c>
       <c r="G23" s="49">
         <v>2025003050005</v>
       </c>
       <c r="H23" s="38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I23" s="3">
         <v>13746524997</v>
@@ -3720,13 +3720,13 @@
         <v>12746524997</v>
       </c>
       <c r="L23" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M23" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M23" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N23" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O23" s="25">
         <v>45811</v>
@@ -3762,7 +3762,7 @@
         <v>90</v>
       </c>
       <c r="Z23" s="46" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AA23" s="42"/>
       <c r="AB23" s="42"/>
@@ -3779,26 +3779,26 @@
         <v>2025</v>
       </c>
       <c r="B24" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" s="43" t="s">
         <v>109</v>
-      </c>
-      <c r="C24" s="43" t="s">
-        <v>110</v>
       </c>
       <c r="D24" s="65">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G24" s="39">
         <v>2025003050011</v>
       </c>
       <c r="H24" s="38" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I24" s="3">
         <v>4237507648</v>
@@ -3810,13 +3810,13 @@
         <v>3390006119</v>
       </c>
       <c r="L24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M24" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="M24" s="23" t="s">
+      <c r="N24" s="59" t="s">
         <v>31</v>
-      </c>
-      <c r="N24" s="59" t="s">
-        <v>32</v>
       </c>
       <c r="O24" s="45">
         <v>45813</v>
@@ -3869,26 +3869,26 @@
         <v>2025</v>
       </c>
       <c r="B25" s="48" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C25" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D25" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E25" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F25" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G25" s="37">
         <v>2025003050014</v>
       </c>
       <c r="H25" s="38" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I25" s="3">
         <v>1811206529</v>
@@ -3900,13 +3900,13 @@
         <v>1448965223</v>
       </c>
       <c r="L25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M25" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="M25" s="23" t="s">
+      <c r="N25" s="59" t="s">
         <v>31</v>
-      </c>
-      <c r="N25" s="59" t="s">
-        <v>32</v>
       </c>
       <c r="O25" s="45">
         <v>45825</v>
@@ -3939,7 +3939,7 @@
         <v>100</v>
       </c>
       <c r="Y25" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z25" s="46">
         <v>100</v>
@@ -3959,26 +3959,26 @@
         <v>2025</v>
       </c>
       <c r="B26" s="48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C26" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D26" s="65">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E26" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G26" s="39">
         <v>2025003050012</v>
       </c>
       <c r="H26" s="38" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I26" s="3">
         <v>4812305821</v>
@@ -3990,13 +3990,13 @@
         <v>3849844657</v>
       </c>
       <c r="L26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M26" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="M26" s="23" t="s">
-        <v>31</v>
-      </c>
       <c r="N26" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O26" s="25">
         <v>45826</v>
@@ -4047,26 +4047,26 @@
         <v>2025</v>
       </c>
       <c r="B27" s="48" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C27" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D27" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E27" s="38" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G27" s="37">
         <v>2025003050015</v>
       </c>
       <c r="H27" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I27" s="3">
         <v>4294044919</v>
@@ -4078,13 +4078,13 @@
         <v>3435235935.1999998</v>
       </c>
       <c r="L27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M27" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="M27" s="23" t="s">
+      <c r="N27" s="59" t="s">
         <v>31</v>
-      </c>
-      <c r="N27" s="59" t="s">
-        <v>32</v>
       </c>
       <c r="O27" s="45">
         <v>45824</v>
@@ -4117,7 +4117,7 @@
         <v>100</v>
       </c>
       <c r="Y27" s="59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Z27" s="23">
         <v>100</v>
@@ -4137,26 +4137,26 @@
         <v>2025</v>
       </c>
       <c r="B28" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="C28" s="43" t="s">
         <v>120</v>
-      </c>
-      <c r="C28" s="43" t="s">
-        <v>121</v>
       </c>
       <c r="D28" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G28" s="49">
         <v>2025003050013</v>
       </c>
       <c r="H28" s="38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I28" s="3">
         <v>1999756329</v>
@@ -4168,19 +4168,19 @@
         <v>1599805063</v>
       </c>
       <c r="L28" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M28" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M28" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N28" s="59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O28" s="25">
         <v>45853</v>
       </c>
       <c r="P28" s="45" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q28" s="24">
         <v>100</v>
@@ -4227,26 +4227,26 @@
         <v>2025</v>
       </c>
       <c r="B29" s="48" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C29" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D29" s="65">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E29" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F29" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G29" s="49">
         <v>2025003050022</v>
       </c>
       <c r="H29" s="38" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I29" s="3">
         <v>5799983707</v>
@@ -4258,13 +4258,13 @@
         <v>3866655805</v>
       </c>
       <c r="L29" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M29" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M29" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N29" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O29" s="25">
         <v>45874</v>
@@ -4315,26 +4315,26 @@
         <v>2025</v>
       </c>
       <c r="B30" s="48" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C30" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D30" s="66">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E30" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="F30" s="38" t="s">
         <v>127</v>
-      </c>
-      <c r="F30" s="38" t="s">
-        <v>128</v>
       </c>
       <c r="G30" s="49">
         <v>2025003050017</v>
       </c>
       <c r="H30" s="38" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I30" s="3">
         <v>5922191430</v>
@@ -4346,19 +4346,19 @@
         <v>4922191430</v>
       </c>
       <c r="L30" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M30" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M30" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N30" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O30" s="25">
         <v>45854</v>
       </c>
       <c r="P30" s="45" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q30" s="24">
         <v>97.87</v>
@@ -4405,26 +4405,26 @@
         <v>2025</v>
       </c>
       <c r="B31" s="48" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C31" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D31" s="65">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E31" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G31" s="49">
         <v>2025003050020</v>
       </c>
       <c r="H31" s="38" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I31" s="3">
         <v>4797586284</v>
@@ -4436,19 +4436,19 @@
         <v>3838069027</v>
       </c>
       <c r="L31" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M31" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M31" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N31" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O31" s="25">
         <v>45874</v>
       </c>
       <c r="P31" s="45" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q31" s="46">
         <v>95.44</v>
@@ -4493,26 +4493,26 @@
         <v>2025</v>
       </c>
       <c r="B32" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="C32" s="43" t="s">
         <v>134</v>
-      </c>
-      <c r="C32" s="43" t="s">
-        <v>135</v>
       </c>
       <c r="D32" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E32" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F32" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G32" s="49">
         <v>2025003050010</v>
       </c>
       <c r="H32" s="38" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I32" s="3">
         <v>2479887333</v>
@@ -4524,19 +4524,19 @@
         <v>1983909866</v>
       </c>
       <c r="L32" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M32" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M32" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N32" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O32" s="25">
         <v>45874</v>
       </c>
       <c r="P32" s="45" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q32" s="23">
         <v>37.270000000000003</v>
@@ -4583,26 +4583,26 @@
         <v>2025</v>
       </c>
       <c r="B33" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C33" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D33" s="65">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E33" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G33" s="49">
         <v>2025003050021</v>
       </c>
       <c r="H33" s="38" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I33" s="3">
         <v>4847192489</v>
@@ -4614,13 +4614,13 @@
         <v>3877753992</v>
       </c>
       <c r="L33" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M33" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M33" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N33" s="59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O33" s="25">
         <v>45909</v>
@@ -4673,26 +4673,26 @@
         <v>2025</v>
       </c>
       <c r="B34" s="48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D34" s="66">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E34" s="38" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G34" s="49">
         <v>2025003050018</v>
       </c>
       <c r="H34" s="38" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I34" s="3">
         <v>2786298806</v>
@@ -4704,46 +4704,46 @@
         <v>2786298806</v>
       </c>
       <c r="L34" s="43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M34" s="51" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N34" s="59" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O34" s="25">
         <v>45903</v>
       </c>
       <c r="P34" s="45" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q34" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R34" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S34" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T34" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U34" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V34" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W34" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X34" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y34" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z34" s="46"/>
       <c r="AA34" s="42"/>
@@ -4761,26 +4761,26 @@
         <v>2025</v>
       </c>
       <c r="B35" s="48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C35" s="43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D35" s="65">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E35" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G35" s="49">
         <v>2025003050023</v>
       </c>
       <c r="H35" s="38" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I35" s="3">
         <v>4842926067</v>
@@ -4792,19 +4792,19 @@
         <v>4842926067</v>
       </c>
       <c r="L35" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M35" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M35" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N35" s="59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O35" s="25">
         <v>45944</v>
       </c>
       <c r="P35" s="45" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q35" s="46">
         <v>93.11</v>
@@ -4849,26 +4849,26 @@
         <v>2025</v>
       </c>
       <c r="B36" s="48" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C36" s="43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D36" s="65">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E36" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F36" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G36" s="49">
         <v>2025003050028</v>
       </c>
       <c r="H36" s="38" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I36" s="3">
         <v>4663630855</v>
@@ -4880,19 +4880,19 @@
         <v>3730904684</v>
       </c>
       <c r="L36" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M36" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M36" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N36" s="59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O36" s="25">
         <v>45936</v>
       </c>
       <c r="P36" s="45" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q36" s="46">
         <v>78.69</v>
@@ -4937,26 +4937,26 @@
         <v>2025</v>
       </c>
       <c r="B37" s="48" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C37" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D37" s="66">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="E37" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="F37" s="38" t="s">
         <v>151</v>
-      </c>
-      <c r="F37" s="38" t="s">
-        <v>152</v>
       </c>
       <c r="G37" s="49">
         <v>2025003050024</v>
       </c>
       <c r="H37" s="38" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I37" s="3">
         <v>14688946853</v>
@@ -4968,19 +4968,19 @@
         <v>14688946853</v>
       </c>
       <c r="L37" s="43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M37" s="51" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N37" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O37" s="25">
         <v>45938</v>
       </c>
       <c r="P37" s="45" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q37" s="46">
         <v>0</v>
@@ -5025,26 +5025,26 @@
         <v>2025</v>
       </c>
       <c r="B38" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" s="43" t="s">
         <v>87</v>
-      </c>
-      <c r="C38" s="43" t="s">
-        <v>88</v>
       </c>
       <c r="D38" s="66">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E38" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="F38" s="38" t="s">
         <v>154</v>
-      </c>
-      <c r="F38" s="38" t="s">
-        <v>155</v>
       </c>
       <c r="G38" s="49">
         <v>2025003050025</v>
       </c>
       <c r="H38" s="38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I38" s="3">
         <v>5913699663</v>
@@ -5056,19 +5056,19 @@
         <v>5913699663</v>
       </c>
       <c r="L38" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M38" s="51" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N38" s="59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O38" s="25">
         <v>45915</v>
       </c>
       <c r="P38" s="45" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q38" s="46">
         <v>82.86</v>
@@ -5113,25 +5113,25 @@
         <v>2025</v>
       </c>
       <c r="B39" s="48" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C39" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D39" s="65">
         <v>0</v>
       </c>
       <c r="E39" s="38" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G39" s="49">
         <v>2025003050035</v>
       </c>
       <c r="H39" s="38" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I39" s="3">
         <v>5248430707.1999998</v>
@@ -5143,13 +5143,13 @@
         <v>4198744565.5999999</v>
       </c>
       <c r="L39" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M39" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M39" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N39" s="59" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O39" s="25">
         <v>45967</v>
@@ -5183,7 +5183,7 @@
         <v>0</v>
       </c>
       <c r="Z39" s="46" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AA39" s="42"/>
       <c r="AB39" s="42"/>
@@ -5200,26 +5200,26 @@
         <v>2025</v>
       </c>
       <c r="B40" s="48" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C40" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D40" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E40" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G40" s="49">
         <v>2025003050026</v>
       </c>
       <c r="H40" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I40" s="3">
         <v>4458275963</v>
@@ -5231,13 +5231,13 @@
         <v>2972183975</v>
       </c>
       <c r="L40" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M40" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M40" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N40" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O40" s="25">
         <v>45968</v>
@@ -5288,26 +5288,26 @@
         <v>2025</v>
       </c>
       <c r="B41" s="48" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C41" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D41" s="66">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E41" s="38" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F41" s="38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G41" s="49">
         <v>2025003050034</v>
       </c>
       <c r="H41" s="38" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I41" s="3">
         <v>4782821867</v>
@@ -5319,13 +5319,13 @@
         <v>4682821867</v>
       </c>
       <c r="L41" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M41" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M41" s="51" t="s">
+      <c r="N41" s="59" t="s">
         <v>31</v>
-      </c>
-      <c r="N41" s="59" t="s">
-        <v>32</v>
       </c>
       <c r="O41" s="25">
         <v>45973</v>
@@ -5376,26 +5376,26 @@
         <v>2025</v>
       </c>
       <c r="B42" s="48" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C42" s="43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D42" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E42" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F42" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G42" s="49">
         <v>2025003050031</v>
       </c>
       <c r="H42" s="38" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I42" s="3">
         <v>2267187134</v>
@@ -5407,13 +5407,13 @@
         <v>1500000000</v>
       </c>
       <c r="L42" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M42" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M42" s="51" t="s">
+      <c r="N42" s="59" t="s">
         <v>31</v>
-      </c>
-      <c r="N42" s="59" t="s">
-        <v>32</v>
       </c>
       <c r="O42" s="45">
         <v>45971</v>
@@ -5466,26 +5466,26 @@
         <v>2025</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D43" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E43" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F43" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G43" s="49">
         <v>2025003050032</v>
       </c>
       <c r="H43" s="38" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I43" s="3">
         <v>2068919343</v>
@@ -5497,19 +5497,19 @@
         <v>1654822441</v>
       </c>
       <c r="L43" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M43" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N43" s="59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O43" s="25">
         <v>46015</v>
       </c>
       <c r="P43" s="45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q43" s="46">
         <v>45.41</v>
@@ -5554,26 +5554,26 @@
         <v>2025</v>
       </c>
       <c r="B44" s="48" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C44" s="43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D44" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E44" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G44" s="49">
         <v>2025003050038</v>
       </c>
       <c r="H44" s="38" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I44" s="3">
         <v>2138705796</v>
@@ -5585,19 +5585,19 @@
         <v>1500000000</v>
       </c>
       <c r="L44" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M44" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N44" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O44" s="25">
         <v>46001</v>
       </c>
       <c r="P44" s="45" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q44" s="46">
         <v>23.44</v>
@@ -5644,26 +5644,26 @@
         <v>2025</v>
       </c>
       <c r="B45" s="48" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C45" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D45" s="65">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E45" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F45" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G45" s="49">
         <v>2025003050046</v>
       </c>
       <c r="H45" s="38" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I45" s="3">
         <v>4319392762</v>
@@ -5675,19 +5675,19 @@
         <v>3414414209</v>
       </c>
       <c r="L45" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M45" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M45" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N45" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O45" s="25">
         <v>46014</v>
       </c>
       <c r="P45" s="45" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q45" s="46">
         <v>26.14</v>
@@ -5732,26 +5732,26 @@
         <v>2025</v>
       </c>
       <c r="B46" s="48" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C46" s="43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D46" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G46" s="49">
         <v>2025003050043</v>
       </c>
       <c r="H46" s="38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I46" s="3">
         <v>2387040561</v>
@@ -5763,13 +5763,13 @@
         <v>1500000000</v>
       </c>
       <c r="L46" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M46" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N46" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O46" s="25">
         <v>46011</v>
@@ -5820,26 +5820,26 @@
         <v>2025</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D47" s="66">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E47" s="38" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G47" s="49">
         <v>2025003050027</v>
       </c>
       <c r="H47" s="38" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I47" s="3">
         <v>27387320782</v>
@@ -5851,13 +5851,13 @@
         <v>27387320782</v>
       </c>
       <c r="L47" s="43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M47" s="51" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N47" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O47" s="25">
         <v>46013</v>
@@ -5908,26 +5908,26 @@
         <v>2025</v>
       </c>
       <c r="B48" s="48" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C48" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D48" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E48" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G48" s="49">
         <v>2025003050053</v>
       </c>
       <c r="H48" s="38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I48" s="3">
         <v>2149409352</v>
@@ -5939,13 +5939,13 @@
         <v>1500000000</v>
       </c>
       <c r="L48" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M48" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N48" s="59" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O48" s="25">
         <v>46014</v>
@@ -5998,26 +5998,26 @@
         <v>2025</v>
       </c>
       <c r="B49" s="48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C49" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D49" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E49" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G49" s="49">
         <v>2025003050051</v>
       </c>
       <c r="H49" s="38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I49" s="3">
         <v>2264647460</v>
@@ -6029,13 +6029,13 @@
         <v>1750000000</v>
       </c>
       <c r="L49" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M49" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N49" s="59" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O49" s="25">
         <v>46014</v>
@@ -6088,26 +6088,26 @@
         <v>2025</v>
       </c>
       <c r="B50" s="38" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C50" s="47" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D50" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E50" s="38" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F50" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G50" s="49">
         <v>2025003050056</v>
       </c>
       <c r="H50" s="38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I50" s="4">
         <v>4431237626</v>
@@ -6119,19 +6119,19 @@
         <v>4431237626</v>
       </c>
       <c r="L50" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="M50" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="M50" s="46" t="s">
-        <v>31</v>
-      </c>
       <c r="N50" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O50" s="25">
         <v>46014</v>
       </c>
       <c r="P50" s="45" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q50" s="46">
         <v>28.94</v>
@@ -6176,26 +6176,26 @@
         <v>2025</v>
       </c>
       <c r="B51" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C51" s="43" t="s">
         <v>57</v>
-      </c>
-      <c r="C51" s="43" t="s">
-        <v>58</v>
       </c>
       <c r="D51" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E51" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F51" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G51" s="49">
         <v>2025003050044</v>
       </c>
       <c r="H51" s="38" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I51" s="3">
         <v>2808881690</v>
@@ -6207,19 +6207,19 @@
         <v>2708881690</v>
       </c>
       <c r="L51" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M51" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N51" s="59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O51" s="25">
         <v>46014</v>
       </c>
       <c r="P51" s="45" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q51" s="46">
         <v>100</v>
@@ -6266,26 +6266,26 @@
         <v>2025</v>
       </c>
       <c r="B52" s="48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D52" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E52" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F52" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G52" s="49">
         <v>2025003050045</v>
       </c>
       <c r="H52" s="38" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I52" s="3">
         <v>2357899973</v>
@@ -6297,19 +6297,19 @@
         <v>1680000000</v>
       </c>
       <c r="L52" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M52" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N52" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O52" s="25">
         <v>46013</v>
       </c>
       <c r="P52" s="45" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="46">
         <v>5.64</v>
@@ -6354,26 +6354,26 @@
         <v>2025</v>
       </c>
       <c r="B53" s="48" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C53" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D53" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E53" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F53" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G53" s="49">
         <v>2025003050050</v>
       </c>
       <c r="H53" s="38" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I53" s="3">
         <v>1879328482</v>
@@ -6385,13 +6385,13 @@
         <v>1500000000</v>
       </c>
       <c r="L53" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M53" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N53" s="59" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O53" s="25">
         <v>46014</v>
@@ -6444,26 +6444,26 @@
         <v>2025</v>
       </c>
       <c r="B54" s="48" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C54" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D54" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E54" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F54" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G54" s="49">
         <v>2025003050049</v>
       </c>
       <c r="H54" s="38" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I54" s="3">
         <v>2156349509</v>
@@ -6475,13 +6475,13 @@
         <v>1500000000</v>
       </c>
       <c r="L54" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M54" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N54" s="59" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O54" s="25">
         <v>46014</v>
@@ -6534,26 +6534,26 @@
         <v>2026</v>
       </c>
       <c r="B55" s="38" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C55" s="47" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D55" s="66">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E55" s="38" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F55" s="38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G55" s="49">
         <v>2025003050036</v>
       </c>
       <c r="H55" s="38" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I55" s="3">
         <v>14202451801</v>
@@ -6565,19 +6565,19 @@
         <v>14202451801</v>
       </c>
       <c r="L55" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M55" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M55" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N55" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O55" s="25">
         <v>46031</v>
       </c>
       <c r="P55" s="45" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q55" s="46">
         <v>13.9</v>
@@ -6622,26 +6622,26 @@
         <v>2026</v>
       </c>
       <c r="B56" s="38" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C56" s="47" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D56" s="66">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E56" s="38" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F56" s="38" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G56" s="49">
         <v>2025003050040</v>
       </c>
       <c r="H56" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I56" s="3">
         <v>2540216819</v>
@@ -6653,13 +6653,13 @@
         <v>2540216819</v>
       </c>
       <c r="L56" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M56" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N56" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O56" s="25">
         <v>46031</v>
@@ -6668,10 +6668,10 @@
         <v>46335</v>
       </c>
       <c r="Q56" s="53" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R56" s="53" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S56" s="60">
         <v>19</v>
@@ -6710,26 +6710,26 @@
         <v>2026</v>
       </c>
       <c r="B57" s="38" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C57" s="47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D57" s="66">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E57" s="38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F57" s="38" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G57" s="49">
         <v>2025003050039</v>
       </c>
       <c r="H57" s="38" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I57" s="50">
         <v>9381110055</v>
@@ -6741,34 +6741,34 @@
         <v>9381110055</v>
       </c>
       <c r="L57" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M57" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M57" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N57" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O57" s="25">
         <v>46031</v>
       </c>
       <c r="P57" s="45" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q57" s="46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R57" s="46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S57" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T57" s="61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U57" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V57" s="61">
         <v>35.840000000000003</v>
@@ -6780,7 +6780,7 @@
         <v>35.840000000000003</v>
       </c>
       <c r="Y57" s="59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z57" s="46"/>
       <c r="AA57" s="42"/>
@@ -6798,26 +6798,26 @@
         <v>2026</v>
       </c>
       <c r="B58" s="38" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C58" s="47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D58" s="66">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E58" s="38" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F58" s="38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G58" s="49">
         <v>2025003050060</v>
       </c>
       <c r="H58" s="38" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I58" s="4">
         <v>5567719862</v>
@@ -6829,19 +6829,19 @@
         <v>2783859931</v>
       </c>
       <c r="L58" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M58" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N58" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O58" s="25">
         <v>46048</v>
       </c>
       <c r="P58" s="45" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q58" s="46">
         <v>15.02</v>
@@ -6886,26 +6886,26 @@
         <v>2026</v>
       </c>
       <c r="B59" s="38" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C59" s="47" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D59" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E59" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F59" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G59" s="49">
         <v>2025003050047</v>
       </c>
       <c r="H59" s="38" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I59" s="50">
         <v>2577210949</v>
@@ -6917,13 +6917,13 @@
         <v>2557210949.52</v>
       </c>
       <c r="L59" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M59" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N59" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O59" s="25">
         <v>46072</v>
@@ -6974,26 +6974,26 @@
         <v>2026</v>
       </c>
       <c r="B60" s="38" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C60" s="47" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D60" s="66">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E60" s="38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F60" s="38" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G60" s="49">
         <v>2025003050059</v>
       </c>
       <c r="H60" s="38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I60" s="3">
         <v>6759815490</v>
@@ -7005,19 +7005,19 @@
         <v>6759815490</v>
       </c>
       <c r="L60" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M60" s="28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N60" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O60" s="25">
         <v>46077</v>
       </c>
       <c r="P60" s="45" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="46">
         <v>39.979999999999997</v>
@@ -7062,26 +7062,26 @@
         <v>2026</v>
       </c>
       <c r="B61" s="38" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C61" s="47" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D61" s="66">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E61" s="38" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F61" s="38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G61" s="49">
         <v>2025003050058</v>
       </c>
       <c r="H61" s="38" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I61" s="50">
         <v>1956028276</v>
@@ -7093,19 +7093,19 @@
         <v>1956028276</v>
       </c>
       <c r="L61" s="47" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M61" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N61" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O61" s="25">
         <v>46073</v>
       </c>
       <c r="P61" s="45" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q61" s="46">
         <v>6.94</v>
@@ -7150,26 +7150,26 @@
         <v>2026</v>
       </c>
       <c r="B62" s="38" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C62" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D62" s="66">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F62" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G62" s="64">
         <v>2025003050037</v>
       </c>
       <c r="H62" s="38" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I62" s="3">
         <v>4919153330</v>
@@ -7181,13 +7181,13 @@
         <v>4919153330</v>
       </c>
       <c r="L62" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M62" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="M62" s="29" t="s">
-        <v>31</v>
-      </c>
       <c r="N62" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O62" s="25">
         <v>46073</v>
@@ -7238,26 +7238,26 @@
         <v>2026</v>
       </c>
       <c r="B63" s="38" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C63" s="52" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D63" s="66">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E63" s="18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F63" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G63" s="64">
         <v>2025003050037</v>
       </c>
       <c r="H63" s="38" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I63" s="3">
         <v>4814470012</v>
@@ -7269,13 +7269,13 @@
         <v>4814470012</v>
       </c>
       <c r="L63" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M63" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="M63" s="29" t="s">
-        <v>31</v>
-      </c>
       <c r="N63" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O63" s="25">
         <v>46073</v>
@@ -7326,26 +7326,26 @@
         <v>2026</v>
       </c>
       <c r="B64" s="38" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C64" s="47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D64" s="66">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E64" s="38" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F64" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G64" s="49">
         <v>2026003050010</v>
       </c>
       <c r="H64" s="38" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I64" s="50">
         <v>8659084152</v>
@@ -7357,13 +7357,13 @@
         <v>7659084152</v>
       </c>
       <c r="L64" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M64" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M64" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N64" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O64" s="25">
         <v>46105</v>
@@ -7414,26 +7414,26 @@
         <v>2026</v>
       </c>
       <c r="B65" s="38" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C65" s="47" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D65" s="65">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E65" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F65" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G65" s="49">
         <v>2026003050009</v>
       </c>
       <c r="H65" s="38" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I65" s="50">
         <v>5112178665</v>
@@ -7445,13 +7445,13 @@
         <v>4500000000</v>
       </c>
       <c r="L65" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M65" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M65" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N65" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O65" s="25">
         <v>46107</v>
@@ -7502,26 +7502,26 @@
         <v>2026</v>
       </c>
       <c r="B66" s="38" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C66" s="47" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D66" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E66" s="18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F66" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G66" s="49">
         <v>2025003050057</v>
       </c>
       <c r="H66" s="38" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I66" s="3">
         <v>2205897938</v>
@@ -7533,13 +7533,13 @@
         <v>1500000000</v>
       </c>
       <c r="L66" s="47" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M66" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N66" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O66" s="25">
         <v>46299</v>
@@ -7548,10 +7548,10 @@
         <v>46334</v>
       </c>
       <c r="Q66" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R66" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S66" s="60">
         <v>19.09</v>
@@ -7590,26 +7590,26 @@
         <v>2026</v>
       </c>
       <c r="B67" s="38" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C67" s="47" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D67" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E67" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F67" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G67" s="49">
         <v>2025003050052</v>
       </c>
       <c r="H67" s="38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I67" s="3">
         <v>1727008802</v>
@@ -7621,37 +7621,37 @@
         <v>1500000000</v>
       </c>
       <c r="L67" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M67" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N67" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O67" s="25">
         <v>46132</v>
       </c>
       <c r="P67" s="45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q67" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R67" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S67" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T67" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U67" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V67" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W67" s="61">
         <v>0</v>
@@ -7678,26 +7678,26 @@
         <v>2026</v>
       </c>
       <c r="B68" s="38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C68" s="47" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D68" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E68" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F68" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G68" s="49">
         <v>2026003050017</v>
       </c>
       <c r="H68" s="38" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I68" s="4">
         <v>2177276654</v>
@@ -7709,40 +7709,40 @@
         <v>1677276654</v>
       </c>
       <c r="L68" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M68" s="46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N68" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O68" s="25">
         <v>46147</v>
       </c>
       <c r="P68" s="45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q68" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R68" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S68" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T68" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U68" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V68" s="46">
         <v>45.33</v>
       </c>
       <c r="W68" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X68" s="61">
         <v>45.33</v>
@@ -7766,26 +7766,26 @@
         <v>2026</v>
       </c>
       <c r="B69" s="38" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C69" s="47" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D69" s="65">
         <f t="shared" ref="D69:D84" si="1">IF(ISNUMBER(E69),E69,IFERROR(VALUE(LEFT(E69,FIND(" ",E69)-1)),1))</f>
         <v>3</v>
       </c>
       <c r="E69" s="38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F69" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G69" s="49">
         <v>2026003050018</v>
       </c>
       <c r="H69" s="38" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I69" s="50">
         <v>8022406899</v>
@@ -7797,19 +7797,19 @@
         <v>8022406899</v>
       </c>
       <c r="L69" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="M69" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M69" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N69" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O69" s="25">
         <v>46129</v>
       </c>
       <c r="P69" s="45" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q69" s="46">
         <v>15.5</v>
@@ -7854,26 +7854,26 @@
         <v>2026</v>
       </c>
       <c r="B70" s="38" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C70" s="47" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D70" s="65">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E70" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F70" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G70" s="49">
         <v>2026003050021</v>
       </c>
       <c r="H70" s="38" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I70" s="3">
         <v>2356550945</v>
@@ -7885,13 +7885,13 @@
         <v>1768550945</v>
       </c>
       <c r="L70" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M70" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N70" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O70" s="25">
         <v>46149</v>
@@ -7900,22 +7900,22 @@
         <v>46427</v>
       </c>
       <c r="Q70" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R70" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S70" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T70" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U70" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V70" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W70" s="61">
         <v>32.200000000000003</v>
@@ -7942,26 +7942,26 @@
         <v>2026</v>
       </c>
       <c r="B71" s="48" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C71" s="43" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D71" s="65">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E71" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F71" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G71" s="49">
         <v>2026003050005</v>
       </c>
       <c r="H71" s="38" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I71" s="44">
         <v>2126428620</v>
@@ -7973,13 +7973,13 @@
         <v>1821081885</v>
       </c>
       <c r="L71" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M71" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N71" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O71" s="25">
         <v>46191</v>
@@ -7988,10 +7988,10 @@
         <v>46371</v>
       </c>
       <c r="Q71" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R71" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S71" s="60">
         <v>11</v>
@@ -8030,26 +8030,26 @@
         <v>2026</v>
       </c>
       <c r="B72" s="38" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C72" s="47" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D72" s="65">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E72" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F72" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G72" s="49">
         <v>2026003050006</v>
       </c>
       <c r="H72" s="38" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I72" s="3">
         <v>2495192913</v>
@@ -8061,43 +8061,43 @@
         <v>2490192913</v>
       </c>
       <c r="L72" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M72" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N72" s="59" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O72" s="25">
         <v>46170</v>
       </c>
       <c r="P72" s="45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q72" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R72" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S72" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T72" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U72" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V72" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W72" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X72" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y72" s="59">
         <v>100</v>
@@ -8118,26 +8118,26 @@
         <v>2026</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D73" s="65">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G73" s="57">
         <v>2026003050011</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I73" s="16">
         <v>2095882218</v>
@@ -8149,13 +8149,13 @@
         <v>1995882218</v>
       </c>
       <c r="L73" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M73" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N73" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O73" s="25">
         <v>46132</v>
@@ -8164,10 +8164,10 @@
         <v>46289</v>
       </c>
       <c r="Q73" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R73" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S73" s="60">
         <v>0</v>
@@ -8206,26 +8206,26 @@
         <v>2026</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D74" s="66">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G74" s="57">
         <v>2026003050014</v>
       </c>
       <c r="H74" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I74" s="11">
         <v>5482855957</v>
@@ -8237,43 +8237,43 @@
         <v>4386284766</v>
       </c>
       <c r="L74" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M74" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M74" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N74" s="59" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O74" s="25">
         <v>46189</v>
       </c>
       <c r="P74" s="45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q74" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R74" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S74" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T74" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U74" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V74" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W74" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X74" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y74" s="59">
         <v>100</v>
@@ -8294,26 +8294,26 @@
         <v>2026</v>
       </c>
       <c r="B75" s="38" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C75" s="47" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D75" s="66">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G75" s="49">
         <v>2026003050008</v>
       </c>
       <c r="H75" s="38" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I75" s="3">
         <v>2300078297</v>
@@ -8325,25 +8325,25 @@
         <v>2250078297</v>
       </c>
       <c r="L75" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M75" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N75" s="59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O75" s="25">
         <v>46175</v>
       </c>
       <c r="P75" s="45" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q75" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R75" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S75" s="60">
         <v>0</v>
@@ -8382,26 +8382,26 @@
         <v>2026</v>
       </c>
       <c r="B76" s="38" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C76" s="47" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D76" s="66">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E76" s="38" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F76" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G76" s="49">
         <v>2026003050002</v>
       </c>
       <c r="H76" s="38" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I76" s="50">
         <v>1408385533</v>
@@ -8413,43 +8413,43 @@
         <v>1408385533</v>
       </c>
       <c r="L76" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M76" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N76" s="59" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O76" s="25">
         <v>46185</v>
       </c>
       <c r="P76" s="45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q76" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R76" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S76" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T76" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U76" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V76" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W76" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X76" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y76" s="59">
         <v>100</v>
@@ -8470,26 +8470,26 @@
         <v>2026</v>
       </c>
       <c r="B77" s="38" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C77" s="52" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D77" s="66">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F77" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G77" s="64">
         <v>2026003050020</v>
       </c>
       <c r="H77" s="38" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I77" s="50">
         <v>8105380232</v>
@@ -8501,43 +8501,43 @@
         <v>8105380232</v>
       </c>
       <c r="L77" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M77" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M77" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N77" s="59" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O77" s="25">
         <v>46185</v>
       </c>
       <c r="P77" s="45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q77" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R77" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S77" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T77" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U77" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V77" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W77" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X77" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y77" s="59">
         <v>100</v>
@@ -8558,26 +8558,26 @@
         <v>2026</v>
       </c>
       <c r="B78" s="38" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C78" s="52" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D78" s="66">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F78" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G78" s="64">
         <v>2026003050020</v>
       </c>
       <c r="H78" s="38" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I78" s="3">
         <v>4333614485</v>
@@ -8589,43 +8589,43 @@
         <v>4333614485</v>
       </c>
       <c r="L78" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M78" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M78" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N78" s="59" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O78" s="25">
         <v>46185</v>
       </c>
       <c r="P78" s="45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q78" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R78" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S78" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T78" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U78" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V78" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W78" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X78" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y78" s="59">
         <v>100</v>
@@ -8646,26 +8646,26 @@
         <v>2026</v>
       </c>
       <c r="B79" s="38" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C79" s="52" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D79" s="66">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F79" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G79" s="64">
         <v>2026003050015</v>
       </c>
       <c r="H79" s="38" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I79" s="3">
         <v>3806958402</v>
@@ -8677,43 +8677,43 @@
         <v>3806958402</v>
       </c>
       <c r="L79" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M79" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M79" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N79" s="59" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O79" s="25">
         <v>46185</v>
       </c>
       <c r="P79" s="45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q79" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R79" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S79" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T79" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U79" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V79" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W79" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X79" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y79" s="59">
         <v>100</v>
@@ -8734,26 +8734,26 @@
         <v>2026</v>
       </c>
       <c r="B80" s="38" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C80" s="52" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D80" s="66">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F80" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G80" s="64">
         <v>2026003050015</v>
       </c>
       <c r="H80" s="38" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I80" s="3">
         <v>2044483403</v>
@@ -8765,43 +8765,43 @@
         <v>2044483403</v>
       </c>
       <c r="L80" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M80" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M80" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N80" s="59" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O80" s="25">
         <v>46185</v>
       </c>
       <c r="P80" s="45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q80" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R80" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S80" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T80" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U80" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V80" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W80" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X80" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y80" s="59">
         <v>100</v>
@@ -8822,26 +8822,26 @@
         <v>2026</v>
       </c>
       <c r="B81" s="38" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C81" s="47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D81" s="66">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F81" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G81" s="49">
         <v>2026003050025</v>
       </c>
       <c r="H81" s="38" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I81" s="3">
         <v>3738220582</v>
@@ -8853,43 +8853,43 @@
         <v>3738220582</v>
       </c>
       <c r="L81" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M81" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M81" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N81" s="59" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O81" s="25">
         <v>46185</v>
       </c>
       <c r="P81" s="45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q81" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R81" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S81" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T81" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U81" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V81" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W81" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X81" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y81" s="59">
         <v>100</v>
@@ -8910,26 +8910,26 @@
         <v>2026</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C82" s="47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D82" s="65">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E82" s="38" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F82" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G82" s="49">
         <v>2026003050016</v>
       </c>
       <c r="H82" s="38" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I82" s="4">
         <v>1875050361</v>
@@ -8941,46 +8941,46 @@
         <v>1875050361</v>
       </c>
       <c r="L82" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M82" s="46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N82" s="59" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O82" s="25">
         <v>46212</v>
       </c>
       <c r="P82" s="45" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q82" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R82" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S82" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T82" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U82" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V82" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W82" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X82" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y82" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z82" s="46"/>
       <c r="AA82" s="42"/>
@@ -8998,26 +8998,26 @@
         <v>2026</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C83" s="47" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D83" s="66">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E83" s="38" t="s">
+        <v>270</v>
+      </c>
+      <c r="F83" s="38" t="s">
         <v>271</v>
-      </c>
-      <c r="F83" s="38" t="s">
-        <v>272</v>
       </c>
       <c r="G83" s="49">
         <v>2026003050022</v>
       </c>
       <c r="H83" s="38" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I83" s="50">
         <v>6654540000</v>
@@ -9029,46 +9029,46 @@
         <v>6654540000</v>
       </c>
       <c r="L83" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="M83" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M83" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N83" s="59" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O83" s="62">
         <v>46239</v>
       </c>
       <c r="P83" s="45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q83" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R83" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S83" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T83" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U83" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V83" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W83" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X83" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y83" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z83" s="46"/>
       <c r="AA83" s="42"/>
@@ -9086,26 +9086,26 @@
         <v>2026</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C84" s="47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D84" s="66">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E84" s="38" t="s">
+        <v>273</v>
+      </c>
+      <c r="F84" s="38" t="s">
         <v>274</v>
-      </c>
-      <c r="F84" s="38" t="s">
-        <v>275</v>
       </c>
       <c r="G84" s="49">
         <v>2026003050019</v>
       </c>
       <c r="H84" s="38" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I84" s="50">
         <v>8054980500</v>
@@ -9117,46 +9117,46 @@
         <v>8054980500</v>
       </c>
       <c r="L84" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="M84" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M84" s="51" t="s">
-        <v>31</v>
-      </c>
       <c r="N84" s="59" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O84" s="62">
         <v>46212</v>
       </c>
       <c r="P84" s="45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q84" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R84" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S84" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T84" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U84" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V84" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W84" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X84" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y84" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z84" s="46"/>
       <c r="AA84" s="42"/>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OACEVEDOD\Desktop\Jefe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296EA0E7-BAF4-437C-9FB5-89B629B30D8A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F438B7EE-653C-47E4-B4A6-E0757D5AA5BE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -208,9 +208,6 @@
     <t>Norte</t>
   </si>
   <si>
-    <t>1.866 KM PLACA HUELLA</t>
-  </si>
-  <si>
     <t>Mejoramiento de vías terciarias en el municipio de Guadalupe Antioquia</t>
   </si>
   <si>
@@ -226,9 +223,6 @@
     <t>BRICEÑO</t>
   </si>
   <si>
-    <t>0.782 KM PLACA HUELLA</t>
-  </si>
-  <si>
     <t>Mejoramiento de la vía terciaria que comunica la vereda El Roblal y el Sector la Ye en el municipio de Briceño Antioquia</t>
   </si>
   <si>
@@ -250,9 +244,6 @@
     <t>Suroeste</t>
   </si>
   <si>
-    <t>1.3 KM PLACA HUELLA</t>
-  </si>
-  <si>
     <t>Construcción de placa huella de la vía terciaria El Hacha - La Alacena en el Municipio de Támesis del departamento de Antioquia</t>
   </si>
   <si>
@@ -274,9 +265,6 @@
     <t>Occidente</t>
   </si>
   <si>
-    <t>0.95 KM PLACA HUELLA</t>
-  </si>
-  <si>
     <t>Construcción de placa huella productiva en la vía terciaria Águila-Roblar del municipio de Giraldo</t>
   </si>
   <si>
@@ -301,9 +289,6 @@
     <t>ENTRERRÍOS</t>
   </si>
   <si>
-    <t>1.1 KM PLACA HUELLA</t>
-  </si>
-  <si>
     <t>Pavimentación tipo placa huella en vías rurales del municipio de Entrerríos Antioquia</t>
   </si>
   <si>
@@ -328,9 +313,6 @@
     <t>COCORNÁ</t>
   </si>
   <si>
-    <t>1.5 KM PLACA HUELLA</t>
-  </si>
-  <si>
     <t>Mejoramiento de vías terciarías del Municipio de Cocorná Antioquia</t>
   </si>
   <si>
@@ -355,27 +337,18 @@
     <t>AMAGÁ</t>
   </si>
   <si>
-    <t>3.5 KM PLACA HUELLA</t>
-  </si>
-  <si>
     <t>Mejoramiento de vías terciarias en las veredas Pueblitos la Delgadita Malabrigo y Maní del Cardal del municipio de Amagá Antioquia</t>
   </si>
   <si>
     <t>TITIRIBÍ</t>
   </si>
   <si>
-    <t>1.2 KM PLACA HUELLA</t>
-  </si>
-  <si>
     <t>Construcción de placa huella de la vía terciaria Vereda La Meseta sector El Corcovado en el municipio de Titiribí Antioquia</t>
   </si>
   <si>
     <t>24/12/2025</t>
   </si>
   <si>
-    <t>6.9 KM PAVIMENTO FLEXIBLE</t>
-  </si>
-  <si>
     <t>PAVIMENTO</t>
   </si>
   <si>
@@ -388,9 +361,6 @@
     <t>SOPETRÁN</t>
   </si>
   <si>
-    <t>1 PUENTE Y  1.5 KM VÍA</t>
-  </si>
-  <si>
     <t>PUENTE</t>
   </si>
   <si>
@@ -412,9 +382,6 @@
     <t>SAN JOSÉ DE LA MONTAÑA</t>
   </si>
   <si>
-    <t>0.75 KM PLACA HUELLA</t>
-  </si>
-  <si>
     <t>Mejoramiento de la vía de acceso a la vereda Potrerito municipio de San José de la Montaña Antioquia</t>
   </si>
   <si>
@@ -427,9 +394,6 @@
     <t>GÓMEZ PLATA</t>
   </si>
   <si>
-    <t>1.9 KM PLACA HUELLA</t>
-  </si>
-  <si>
     <t>Pavimentación de vías en sistemas constructivo placa huella para las veredas La Angostura Chilimaco sectores rurales del municipio de Gómez Plata Antioquia</t>
   </si>
   <si>
@@ -454,9 +418,6 @@
     <t>DONMATÍAS</t>
   </si>
   <si>
-    <t>1.95 KM PAVIMENTACION</t>
-  </si>
-  <si>
     <t xml:space="preserve">PAVIMENTO </t>
   </si>
   <si>
@@ -553,9 +514,6 @@
     <t>RIONEGRO</t>
   </si>
   <si>
-    <t>2.65 KM PLACA HUELLA</t>
-  </si>
-  <si>
     <t>Mejoramiento de las vías rurales del municipio de Rionegro, Antioquia</t>
   </si>
   <si>
@@ -568,9 +526,6 @@
     <t>GRANADA</t>
   </si>
   <si>
-    <t>1.63 KM PLACA HUELLA</t>
-  </si>
-  <si>
     <t>Mejoramiento de la vía vereda Quebradona Arriba en el municipio de Granada Antioquia</t>
   </si>
   <si>
@@ -619,9 +574,6 @@
     <t>Pavimentación mediante el sistema constructivo placa huella via terciaria San Juaquin vereda La Palamira del municipio de Hispania, Antioquía</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2 KM PAVIMENTO </t>
-  </si>
-  <si>
     <t>Mejoramientode la via de tercer orden Ye a La Bodega (Andes)-Buenas Aires-Puente Lata-Jericó en la subregión Suroeste del departamento de Antioquia</t>
   </si>
   <si>
@@ -637,9 +589,6 @@
     <t>GUATAPÉ</t>
   </si>
   <si>
-    <t>1.73 KM PLACA HUELLA</t>
-  </si>
-  <si>
     <t>Mejoramiento de la vía-Granada-Guatapé sector la Sonadora y la Peña, del municipio de Guatape, Antioquia</t>
   </si>
   <si>
@@ -706,9 +655,6 @@
     <t>CHIGORODÓ</t>
   </si>
   <si>
-    <t>1.07 PAV URBANA CALLE 97</t>
-  </si>
-  <si>
     <t>Transformación Urbanística de la Calle 97 y Vías Conexas para una Movilidad Segura en el Municipio de Chigorodó Antioquia</t>
   </si>
   <si>
@@ -748,9 +694,6 @@
     <t>PUENTE VEHICULAR</t>
   </si>
   <si>
-    <t>0.8 KM PAV VIAS URB PARQUE TERM TTE</t>
-  </si>
-  <si>
     <t>Construcción de pavimento rígido, urbanismo y obras complementarias para el desarrollo en el municipio de Chigorodó, Antioquia</t>
   </si>
   <si>
@@ -814,16 +757,10 @@
     <t>PUEBLORRICO</t>
   </si>
   <si>
-    <t>0.980 KM PAVIMENTO FLEXIBLE</t>
-  </si>
-  <si>
     <t>Mejoramiento de la Red Vial de Tercer Orden del Municipio de Pueblorrico Antioquia</t>
   </si>
   <si>
     <t>URAMITA</t>
-  </si>
-  <si>
-    <t>0.54 KM DE PAVIMENTACIÓN URBANA</t>
   </si>
   <si>
     <t>Pavimentación y Adecuación de Vía en el Barrio el Socorro y La Copa en la Zona Urbana del Municipio de Uramita Antioquia</t>
@@ -906,18 +843,82 @@
   <si>
     <t>Alcance
 Valor</t>
+  </si>
+  <si>
+    <t>1,866 KM PLACA HUELLA</t>
+  </si>
+  <si>
+    <t>0,782 KM PLACA HUELLA</t>
+  </si>
+  <si>
+    <t>1,3 KM PLACA HUELLA</t>
+  </si>
+  <si>
+    <t>0,95 KM PLACA HUELLA</t>
+  </si>
+  <si>
+    <t>1,1 KM PLACA HUELLA</t>
+  </si>
+  <si>
+    <t>1,5 KM PLACA HUELLA</t>
+  </si>
+  <si>
+    <t>3,5 KM PLACA HUELLA</t>
+  </si>
+  <si>
+    <t>1,2 KM PLACA HUELLA</t>
+  </si>
+  <si>
+    <t>6,9 KM PAVIMENTO FLEXIBLE</t>
+  </si>
+  <si>
+    <t>1 PUENTE Y  1,5 KM VÍA</t>
+  </si>
+  <si>
+    <t>0,75 KM PLACA HUELLA</t>
+  </si>
+  <si>
+    <t>1,9 KM PLACA HUELLA</t>
+  </si>
+  <si>
+    <t>1,95 KM PAVIMENTACION</t>
+  </si>
+  <si>
+    <t>2,65 KM PLACA HUELLA</t>
+  </si>
+  <si>
+    <t>1,63 KM PLACA HUELLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,2 KM PAVIMENTO </t>
+  </si>
+  <si>
+    <t>1,73 KM PLACA HUELLA</t>
+  </si>
+  <si>
+    <t>1,07 PAV URBANA CALLE 97</t>
+  </si>
+  <si>
+    <t>0,8 KM PAV VIAS URB PARQUE TERM TTE</t>
+  </si>
+  <si>
+    <t>0,980 KM PAVIMENTO FLEXIBLE</t>
+  </si>
+  <si>
+    <t>0,54 KM DE PAVIMENTACIÓN URBANA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$$-240A]\ #,##0.00"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -1215,7 +1216,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
     <xf numFmtId="9" fontId="22" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1426,6 +1427,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -1825,7 +1829,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="E2" s="31" t="s">
         <v>8</v>
@@ -2176,10 +2180,10 @@
       </c>
       <c r="D6" s="65">
         <f>IF(ISNUMBER(E6),E6,IFERROR(VALUE(LEFT(E6,FIND(" ",E6)-1)),1))</f>
-        <v>1866</v>
+        <v>1.8660000000000001</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>44</v>
+        <v>256</v>
       </c>
       <c r="F6" s="38" t="s">
         <v>27</v>
@@ -2188,7 +2192,7 @@
         <v>2024053150037</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I6" s="3">
         <v>3945999620</v>
@@ -2259,7 +2263,7 @@
         <v>2024</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" s="43" t="s">
         <v>33</v>
@@ -2278,7 +2282,7 @@
         <v>2024003050241</v>
       </c>
       <c r="H7" s="38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I7" s="3">
         <v>4232130933</v>
@@ -2296,7 +2300,7 @@
         <v>30</v>
       </c>
       <c r="N7" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O7" s="25">
         <v>45636</v>
@@ -2349,17 +2353,17 @@
         <v>2024</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8" s="43" t="s">
         <v>43</v>
       </c>
       <c r="D8" s="65">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.78200000000000003</v>
       </c>
       <c r="E8" s="38" t="s">
-        <v>50</v>
+        <v>257</v>
       </c>
       <c r="F8" s="38" t="s">
         <v>27</v>
@@ -2368,7 +2372,7 @@
         <v>2024051070040</v>
       </c>
       <c r="H8" s="38" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I8" s="3">
         <v>1645755840</v>
@@ -2439,7 +2443,7 @@
         <v>2024</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" s="43" t="s">
         <v>25</v>
@@ -2458,7 +2462,7 @@
         <v>2024057560039</v>
       </c>
       <c r="H9" s="38" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I9" s="3">
         <v>5459298912.8900003</v>
@@ -2482,7 +2486,7 @@
         <v>45636</v>
       </c>
       <c r="P9" s="45" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q9" s="23">
         <v>90.52</v>
@@ -2529,17 +2533,17 @@
         <v>2024</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C10" s="43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D10" s="65">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>58</v>
+        <v>258</v>
       </c>
       <c r="F10" s="38" t="s">
         <v>27</v>
@@ -2548,7 +2552,7 @@
         <v>2024057890040</v>
       </c>
       <c r="H10" s="38" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I10" s="3">
         <v>3035607509</v>
@@ -2572,7 +2576,7 @@
         <v>45628</v>
       </c>
       <c r="P10" s="45" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="Q10" s="23">
         <v>98.69</v>
@@ -2619,7 +2623,7 @@
         <v>2024</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C11" s="43" t="s">
         <v>25</v>
@@ -2629,7 +2633,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F11" s="38" t="s">
         <v>27</v>
@@ -2638,7 +2642,7 @@
         <v>2024054830016</v>
       </c>
       <c r="H11" s="38" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I11" s="3">
         <v>2596905323</v>
@@ -2709,17 +2713,17 @@
         <v>2024</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C12" s="43" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D12" s="65">
         <f>IF(ISNUMBER(E12),E12,IFERROR(VALUE(LEFT(E12,FIND(" ",E12)-1)),1))</f>
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>66</v>
+        <v>259</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>27</v>
@@ -2728,7 +2732,7 @@
         <v>2024003050236</v>
       </c>
       <c r="H12" s="38" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="I12" s="3">
         <v>1513619665</v>
@@ -2740,7 +2744,7 @@
         <v>1210895732</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="M12" s="23" t="s">
         <v>30</v>
@@ -2799,7 +2803,7 @@
         <v>2024</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C13" s="47" t="s">
         <v>43</v>
@@ -2818,7 +2822,7 @@
         <v>2024003050238</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I13" s="3">
         <v>4622246270</v>
@@ -2830,7 +2834,7 @@
         <v>3697797016</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="M13" s="23" t="s">
         <v>30</v>
@@ -2889,17 +2893,17 @@
         <v>2024</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>27</v>
@@ -2908,7 +2912,7 @@
         <v>2024003050244</v>
       </c>
       <c r="H14" s="38" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I14" s="4">
         <v>2241815667.6000004</v>
@@ -2926,13 +2930,13 @@
         <v>30</v>
       </c>
       <c r="N14" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O14" s="25">
         <v>45636</v>
       </c>
       <c r="P14" s="45" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="Q14" s="27">
         <v>0</v>
@@ -2979,17 +2983,17 @@
         <v>2024</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C15" s="43" t="s">
         <v>43</v>
       </c>
       <c r="D15" s="65">
         <f>IF(ISNUMBER(E15),E15,IFERROR(VALUE(LEFT(E15,FIND(" ",E15)-1)),1))</f>
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>75</v>
+        <v>260</v>
       </c>
       <c r="F15" s="38" t="s">
         <v>27</v>
@@ -2998,7 +3002,7 @@
         <v>2024003050242</v>
       </c>
       <c r="H15" s="38" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="I15" s="3">
         <v>2688840891</v>
@@ -3069,7 +3073,7 @@
         <v>2024</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C16" s="43" t="s">
         <v>43</v>
@@ -3079,7 +3083,7 @@
         <v>3</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>27</v>
@@ -3088,7 +3092,7 @@
         <v>2024003050245</v>
       </c>
       <c r="H16" s="38" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="I16" s="3">
         <v>6076769979</v>
@@ -3106,13 +3110,13 @@
         <v>30</v>
       </c>
       <c r="N16" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O16" s="25">
         <v>45635</v>
       </c>
       <c r="P16" s="45" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="Q16" s="23">
         <v>71.45</v>
@@ -3159,17 +3163,17 @@
         <v>2024</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C17" s="43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D17" s="65">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F17" s="38" t="s">
         <v>27</v>
@@ -3178,7 +3182,7 @@
         <v>2024003050237</v>
       </c>
       <c r="H17" s="38" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I17" s="3">
         <v>5449013722</v>
@@ -3249,17 +3253,17 @@
         <v>2024</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C18" s="47" t="s">
         <v>25</v>
       </c>
       <c r="D18" s="65">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E18" s="38" t="s">
-        <v>84</v>
+        <v>261</v>
       </c>
       <c r="F18" s="38" t="s">
         <v>27</v>
@@ -3268,7 +3272,7 @@
         <v>2024051970041</v>
       </c>
       <c r="H18" s="38" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="I18" s="3">
         <v>3445926513</v>
@@ -3339,26 +3343,26 @@
         <v>2024</v>
       </c>
       <c r="B19" s="48" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C19" s="43" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D19" s="65">
         <f t="shared" si="0"/>
         <v>320</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F19" s="38" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G19" s="39">
         <v>20243201010075</v>
       </c>
       <c r="H19" s="38" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I19" s="3">
         <v>15664988520</v>
@@ -3373,10 +3377,10 @@
         <v>0.2</v>
       </c>
       <c r="M19" s="23" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="N19" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O19" s="45">
         <v>45652</v>
@@ -3423,17 +3427,17 @@
         <v>2025</v>
       </c>
       <c r="B20" s="48" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C20" s="43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D20" s="65">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="E20" s="38" t="s">
-        <v>93</v>
+        <v>262</v>
       </c>
       <c r="F20" s="38" t="s">
         <v>27</v>
@@ -3442,7 +3446,7 @@
         <v>2025003050003</v>
       </c>
       <c r="H20" s="38" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I20" s="3">
         <v>5581655075</v>
@@ -3511,17 +3515,17 @@
         <v>2025</v>
       </c>
       <c r="B21" s="48" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C21" s="43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D21" s="65">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E21" s="38" t="s">
-        <v>96</v>
+        <v>263</v>
       </c>
       <c r="F21" s="38" t="s">
         <v>27</v>
@@ -3530,7 +3534,7 @@
         <v>2025003050008</v>
       </c>
       <c r="H21" s="38" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="I21" s="3">
         <v>2661301362</v>
@@ -3554,7 +3558,7 @@
         <v>45818</v>
       </c>
       <c r="P21" s="45" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="Q21" s="46">
         <v>100</v>
@@ -3601,26 +3605,26 @@
         <v>2025</v>
       </c>
       <c r="B22" s="48" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C22" s="43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D22" s="66">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>6.9</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>99</v>
+        <v>264</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="G22" s="39">
         <v>2025003050002</v>
       </c>
       <c r="H22" s="38" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="I22" s="3">
         <v>24272420632</v>
@@ -3635,16 +3639,16 @@
         <v>29</v>
       </c>
       <c r="M22" s="23" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="N22" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O22" s="25">
         <v>45805</v>
       </c>
       <c r="P22" s="45" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="Q22" s="23">
         <v>7.59</v>
@@ -3689,26 +3693,26 @@
         <v>2025</v>
       </c>
       <c r="B23" s="48" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C23" s="43" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D23" s="66">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E23" s="38" t="s">
-        <v>104</v>
+        <v>265</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="G23" s="49">
         <v>2025003050005</v>
       </c>
       <c r="H23" s="38" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="I23" s="3">
         <v>13746524997</v>
@@ -3726,7 +3730,7 @@
         <v>30</v>
       </c>
       <c r="N23" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O23" s="25">
         <v>45811</v>
@@ -3762,7 +3766,7 @@
         <v>90</v>
       </c>
       <c r="Z23" s="46" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="AA23" s="42"/>
       <c r="AB23" s="42"/>
@@ -3779,10 +3783,10 @@
         <v>2025</v>
       </c>
       <c r="B24" s="48" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C24" s="43" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D24" s="65">
         <f t="shared" si="0"/>
@@ -3798,7 +3802,7 @@
         <v>2025003050011</v>
       </c>
       <c r="H24" s="38" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="I24" s="3">
         <v>4237507648</v>
@@ -3869,17 +3873,17 @@
         <v>2025</v>
       </c>
       <c r="B25" s="48" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C25" s="43" t="s">
         <v>43</v>
       </c>
       <c r="D25" s="65">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E25" s="38" t="s">
-        <v>112</v>
+        <v>266</v>
       </c>
       <c r="F25" s="38" t="s">
         <v>27</v>
@@ -3888,7 +3892,7 @@
         <v>2025003050014</v>
       </c>
       <c r="H25" s="38" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="I25" s="3">
         <v>1811206529</v>
@@ -3959,7 +3963,7 @@
         <v>2025</v>
       </c>
       <c r="B26" s="48" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C26" s="43" t="s">
         <v>25</v>
@@ -3978,7 +3982,7 @@
         <v>2025003050012</v>
       </c>
       <c r="H26" s="38" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="I26" s="3">
         <v>4812305821</v>
@@ -3996,7 +4000,7 @@
         <v>30</v>
       </c>
       <c r="N26" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O26" s="25">
         <v>45826</v>
@@ -4047,17 +4051,17 @@
         <v>2025</v>
       </c>
       <c r="B27" s="48" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C27" s="43" t="s">
         <v>43</v>
       </c>
       <c r="D27" s="65">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="E27" s="38" t="s">
-        <v>117</v>
+        <v>267</v>
       </c>
       <c r="F27" s="38" t="s">
         <v>27</v>
@@ -4066,7 +4070,7 @@
         <v>2025003050015</v>
       </c>
       <c r="H27" s="38" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="I27" s="3">
         <v>4294044919</v>
@@ -4137,17 +4141,17 @@
         <v>2025</v>
       </c>
       <c r="B28" s="48" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C28" s="43" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D28" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F28" s="38" t="s">
         <v>27</v>
@@ -4156,7 +4160,7 @@
         <v>2025003050013</v>
       </c>
       <c r="H28" s="38" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="I28" s="3">
         <v>1999756329</v>
@@ -4180,7 +4184,7 @@
         <v>45853</v>
       </c>
       <c r="P28" s="45" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="Q28" s="24">
         <v>100</v>
@@ -4227,7 +4231,7 @@
         <v>2025</v>
       </c>
       <c r="B29" s="48" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C29" s="43" t="s">
         <v>25</v>
@@ -4246,7 +4250,7 @@
         <v>2025003050022</v>
       </c>
       <c r="H29" s="38" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="I29" s="3">
         <v>5799983707</v>
@@ -4264,7 +4268,7 @@
         <v>30</v>
       </c>
       <c r="N29" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O29" s="25">
         <v>45874</v>
@@ -4315,26 +4319,26 @@
         <v>2025</v>
       </c>
       <c r="B30" s="48" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C30" s="43" t="s">
         <v>43</v>
       </c>
       <c r="D30" s="66">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.95</v>
       </c>
       <c r="E30" s="38" t="s">
-        <v>126</v>
+        <v>268</v>
       </c>
       <c r="F30" s="38" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="G30" s="49">
         <v>2025003050017</v>
       </c>
       <c r="H30" s="38" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="I30" s="3">
         <v>5922191430</v>
@@ -4352,13 +4356,13 @@
         <v>30</v>
       </c>
       <c r="N30" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O30" s="25">
         <v>45854</v>
       </c>
       <c r="P30" s="45" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="Q30" s="24">
         <v>97.87</v>
@@ -4405,7 +4409,7 @@
         <v>2025</v>
       </c>
       <c r="B31" s="48" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="C31" s="43" t="s">
         <v>25</v>
@@ -4424,7 +4428,7 @@
         <v>2025003050020</v>
       </c>
       <c r="H31" s="38" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="I31" s="3">
         <v>4797586284</v>
@@ -4442,13 +4446,13 @@
         <v>30</v>
       </c>
       <c r="N31" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O31" s="25">
         <v>45874</v>
       </c>
       <c r="P31" s="45" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="Q31" s="46">
         <v>95.44</v>
@@ -4493,17 +4497,17 @@
         <v>2025</v>
       </c>
       <c r="B32" s="48" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="C32" s="43" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="D32" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E32" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F32" s="38" t="s">
         <v>27</v>
@@ -4512,7 +4516,7 @@
         <v>2025003050010</v>
       </c>
       <c r="H32" s="38" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="I32" s="3">
         <v>2479887333</v>
@@ -4530,13 +4534,13 @@
         <v>30</v>
       </c>
       <c r="N32" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O32" s="25">
         <v>45874</v>
       </c>
       <c r="P32" s="45" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="Q32" s="23">
         <v>37.270000000000003</v>
@@ -4583,7 +4587,7 @@
         <v>2025</v>
       </c>
       <c r="B33" s="48" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="C33" s="43" t="s">
         <v>25</v>
@@ -4602,7 +4606,7 @@
         <v>2025003050021</v>
       </c>
       <c r="H33" s="38" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="I33" s="3">
         <v>4847192489</v>
@@ -4673,7 +4677,7 @@
         <v>2025</v>
       </c>
       <c r="B34" s="48" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C34" s="43" t="s">
         <v>43</v>
@@ -4683,16 +4687,16 @@
         <v>1</v>
       </c>
       <c r="E34" s="38" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="G34" s="49">
         <v>2025003050018</v>
       </c>
       <c r="H34" s="38" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="I34" s="3">
         <v>2786298806</v>
@@ -4707,16 +4711,16 @@
         <v>29</v>
       </c>
       <c r="M34" s="51" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="N34" s="59" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="O34" s="25">
         <v>45903</v>
       </c>
       <c r="P34" s="45" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="Q34" s="46" t="s">
         <v>41</v>
@@ -4761,10 +4765,10 @@
         <v>2025</v>
       </c>
       <c r="B35" s="48" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="C35" s="43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D35" s="65">
         <f t="shared" si="0"/>
@@ -4780,7 +4784,7 @@
         <v>2025003050023</v>
       </c>
       <c r="H35" s="38" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="I35" s="3">
         <v>4842926067</v>
@@ -4804,7 +4808,7 @@
         <v>45944</v>
       </c>
       <c r="P35" s="45" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="Q35" s="46">
         <v>93.11</v>
@@ -4849,7 +4853,7 @@
         <v>2025</v>
       </c>
       <c r="B36" s="48" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="C36" s="43" t="s">
         <v>33</v>
@@ -4868,7 +4872,7 @@
         <v>2025003050028</v>
       </c>
       <c r="H36" s="38" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="I36" s="3">
         <v>4663630855</v>
@@ -4892,7 +4896,7 @@
         <v>45936</v>
       </c>
       <c r="P36" s="45" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="Q36" s="46">
         <v>78.69</v>
@@ -4937,7 +4941,7 @@
         <v>2025</v>
       </c>
       <c r="B37" s="48" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="C37" s="43" t="s">
         <v>43</v>
@@ -4947,16 +4951,16 @@
         <v>4</v>
       </c>
       <c r="E37" s="38" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="F37" s="38" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="G37" s="49">
         <v>2025003050024</v>
       </c>
       <c r="H37" s="38" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="I37" s="3">
         <v>14688946853</v>
@@ -4971,16 +4975,16 @@
         <v>29</v>
       </c>
       <c r="M37" s="51" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="N37" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O37" s="25">
         <v>45938</v>
       </c>
       <c r="P37" s="45" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="Q37" s="46">
         <v>0</v>
@@ -5025,26 +5029,26 @@
         <v>2025</v>
       </c>
       <c r="B38" s="48" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C38" s="43" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D38" s="66">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E38" s="38" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="F38" s="38" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="G38" s="49">
         <v>2025003050025</v>
       </c>
       <c r="H38" s="38" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="I38" s="3">
         <v>5913699663</v>
@@ -5056,10 +5060,10 @@
         <v>5913699663</v>
       </c>
       <c r="L38" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M38" s="51" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="N38" s="59" t="s">
         <v>36</v>
@@ -5068,7 +5072,7 @@
         <v>45915</v>
       </c>
       <c r="P38" s="45" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="46">
         <v>82.86</v>
@@ -5113,7 +5117,7 @@
         <v>2025</v>
       </c>
       <c r="B39" s="48" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C39" s="43" t="s">
         <v>25</v>
@@ -5122,7 +5126,7 @@
         <v>0</v>
       </c>
       <c r="E39" s="38" t="s">
-        <v>159</v>
+        <v>269</v>
       </c>
       <c r="F39" s="38" t="s">
         <v>27</v>
@@ -5131,7 +5135,7 @@
         <v>2025003050035</v>
       </c>
       <c r="H39" s="38" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="I39" s="3">
         <v>5248430707.1999998</v>
@@ -5149,7 +5153,7 @@
         <v>30</v>
       </c>
       <c r="N39" s="59" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="O39" s="25">
         <v>45967</v>
@@ -5183,7 +5187,7 @@
         <v>0</v>
       </c>
       <c r="Z39" s="46" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="AA39" s="42"/>
       <c r="AB39" s="42"/>
@@ -5200,17 +5204,17 @@
         <v>2025</v>
       </c>
       <c r="B40" s="48" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="C40" s="43" t="s">
         <v>25</v>
       </c>
       <c r="D40" s="65">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.63</v>
       </c>
       <c r="E40" s="38" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="F40" s="38" t="s">
         <v>27</v>
@@ -5219,7 +5223,7 @@
         <v>2025003050026</v>
       </c>
       <c r="H40" s="38" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="I40" s="3">
         <v>4458275963</v>
@@ -5237,7 +5241,7 @@
         <v>30</v>
       </c>
       <c r="N40" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O40" s="25">
         <v>45968</v>
@@ -5288,7 +5292,7 @@
         <v>2025</v>
       </c>
       <c r="B41" s="48" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C41" s="43" t="s">
         <v>25</v>
@@ -5298,16 +5302,16 @@
         <v>2</v>
       </c>
       <c r="E41" s="38" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="F41" s="38" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="G41" s="49">
         <v>2025003050034</v>
       </c>
       <c r="H41" s="38" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="I41" s="3">
         <v>4782821867</v>
@@ -5376,7 +5380,7 @@
         <v>2025</v>
       </c>
       <c r="B42" s="48" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C42" s="43" t="s">
         <v>33</v>
@@ -5386,7 +5390,7 @@
         <v>1</v>
       </c>
       <c r="E42" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F42" s="38" t="s">
         <v>27</v>
@@ -5395,7 +5399,7 @@
         <v>2025003050031</v>
       </c>
       <c r="H42" s="38" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="I42" s="3">
         <v>2267187134</v>
@@ -5466,17 +5470,17 @@
         <v>2025</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D43" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E43" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F43" s="38" t="s">
         <v>27</v>
@@ -5485,7 +5489,7 @@
         <v>2025003050032</v>
       </c>
       <c r="H43" s="38" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="I43" s="3">
         <v>2068919343</v>
@@ -5497,7 +5501,7 @@
         <v>1654822441</v>
       </c>
       <c r="L43" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M43" s="51" t="s">
         <v>30</v>
@@ -5509,7 +5513,7 @@
         <v>46015</v>
       </c>
       <c r="P43" s="45" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="Q43" s="46">
         <v>45.41</v>
@@ -5554,17 +5558,17 @@
         <v>2025</v>
       </c>
       <c r="B44" s="48" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="C44" s="43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D44" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E44" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F44" s="38" t="s">
         <v>27</v>
@@ -5573,7 +5577,7 @@
         <v>2025003050038</v>
       </c>
       <c r="H44" s="38" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="I44" s="3">
         <v>2138705796</v>
@@ -5585,19 +5589,19 @@
         <v>1500000000</v>
       </c>
       <c r="L44" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M44" s="51" t="s">
         <v>30</v>
       </c>
       <c r="N44" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O44" s="25">
         <v>46001</v>
       </c>
       <c r="P44" s="45" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="Q44" s="46">
         <v>23.44</v>
@@ -5644,7 +5648,7 @@
         <v>2025</v>
       </c>
       <c r="B45" s="48" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C45" s="43" t="s">
         <v>25</v>
@@ -5663,7 +5667,7 @@
         <v>2025003050046</v>
       </c>
       <c r="H45" s="38" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="I45" s="3">
         <v>4319392762</v>
@@ -5681,13 +5685,13 @@
         <v>30</v>
       </c>
       <c r="N45" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O45" s="25">
         <v>46014</v>
       </c>
       <c r="P45" s="45" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="Q45" s="46">
         <v>26.14</v>
@@ -5732,17 +5736,17 @@
         <v>2025</v>
       </c>
       <c r="B46" s="48" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="C46" s="43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D46" s="65">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>84</v>
+        <v>261</v>
       </c>
       <c r="F46" s="38" t="s">
         <v>27</v>
@@ -5751,7 +5755,7 @@
         <v>2025003050043</v>
       </c>
       <c r="H46" s="38" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I46" s="3">
         <v>2387040561</v>
@@ -5763,13 +5767,13 @@
         <v>1500000000</v>
       </c>
       <c r="L46" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M46" s="51" t="s">
         <v>30</v>
       </c>
       <c r="N46" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O46" s="25">
         <v>46011</v>
@@ -5820,26 +5824,26 @@
         <v>2025</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D47" s="66">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="E47" s="38" t="s">
-        <v>181</v>
+        <v>271</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="G47" s="49">
         <v>2025003050027</v>
       </c>
       <c r="H47" s="38" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="I47" s="3">
         <v>27387320782</v>
@@ -5854,10 +5858,10 @@
         <v>29</v>
       </c>
       <c r="M47" s="51" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="N47" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O47" s="25">
         <v>46013</v>
@@ -5908,7 +5912,7 @@
         <v>2025</v>
       </c>
       <c r="B48" s="48" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="C48" s="43" t="s">
         <v>43</v>
@@ -5918,7 +5922,7 @@
         <v>1</v>
       </c>
       <c r="E48" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F48" s="38" t="s">
         <v>27</v>
@@ -5927,7 +5931,7 @@
         <v>2025003050053</v>
       </c>
       <c r="H48" s="38" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="I48" s="3">
         <v>2149409352</v>
@@ -5939,7 +5943,7 @@
         <v>1500000000</v>
       </c>
       <c r="L48" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M48" s="51" t="s">
         <v>30</v>
@@ -5998,7 +6002,7 @@
         <v>2025</v>
       </c>
       <c r="B49" s="48" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C49" s="43" t="s">
         <v>43</v>
@@ -6008,7 +6012,7 @@
         <v>1</v>
       </c>
       <c r="E49" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F49" s="38" t="s">
         <v>27</v>
@@ -6017,7 +6021,7 @@
         <v>2025003050051</v>
       </c>
       <c r="H49" s="38" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="I49" s="3">
         <v>2264647460</v>
@@ -6029,7 +6033,7 @@
         <v>1750000000</v>
       </c>
       <c r="L49" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M49" s="51" t="s">
         <v>30</v>
@@ -6088,17 +6092,17 @@
         <v>2025</v>
       </c>
       <c r="B50" s="38" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="C50" s="47" t="s">
         <v>25</v>
       </c>
       <c r="D50" s="65">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.73</v>
       </c>
       <c r="E50" s="38" t="s">
-        <v>187</v>
+        <v>272</v>
       </c>
       <c r="F50" s="38" t="s">
         <v>27</v>
@@ -6107,7 +6111,7 @@
         <v>2025003050056</v>
       </c>
       <c r="H50" s="38" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="I50" s="4">
         <v>4431237626</v>
@@ -6125,13 +6129,13 @@
         <v>30</v>
       </c>
       <c r="N50" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O50" s="25">
         <v>46014</v>
       </c>
       <c r="P50" s="45" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="Q50" s="46">
         <v>28.94</v>
@@ -6176,17 +6180,17 @@
         <v>2025</v>
       </c>
       <c r="B51" s="48" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C51" s="43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D51" s="65">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E51" s="38" t="s">
-        <v>75</v>
+        <v>260</v>
       </c>
       <c r="F51" s="38" t="s">
         <v>27</v>
@@ -6195,7 +6199,7 @@
         <v>2025003050044</v>
       </c>
       <c r="H51" s="38" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="I51" s="3">
         <v>2808881690</v>
@@ -6207,7 +6211,7 @@
         <v>2708881690</v>
       </c>
       <c r="L51" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M51" s="51" t="s">
         <v>30</v>
@@ -6219,7 +6223,7 @@
         <v>46014</v>
       </c>
       <c r="P51" s="45" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="Q51" s="46">
         <v>100</v>
@@ -6266,7 +6270,7 @@
         <v>2025</v>
       </c>
       <c r="B52" s="48" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C52" s="43" t="s">
         <v>25</v>
@@ -6276,7 +6280,7 @@
         <v>1</v>
       </c>
       <c r="E52" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F52" s="38" t="s">
         <v>27</v>
@@ -6285,7 +6289,7 @@
         <v>2025003050045</v>
       </c>
       <c r="H52" s="38" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="I52" s="3">
         <v>2357899973</v>
@@ -6297,19 +6301,19 @@
         <v>1680000000</v>
       </c>
       <c r="L52" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M52" s="51" t="s">
         <v>30</v>
       </c>
       <c r="N52" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O52" s="25">
         <v>46013</v>
       </c>
       <c r="P52" s="45" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="Q52" s="46">
         <v>5.64</v>
@@ -6354,17 +6358,17 @@
         <v>2025</v>
       </c>
       <c r="B53" s="48" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="C53" s="43" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D53" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E53" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F53" s="38" t="s">
         <v>27</v>
@@ -6373,7 +6377,7 @@
         <v>2025003050050</v>
       </c>
       <c r="H53" s="38" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="I53" s="3">
         <v>1879328482</v>
@@ -6385,7 +6389,7 @@
         <v>1500000000</v>
       </c>
       <c r="L53" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M53" s="51" t="s">
         <v>30</v>
@@ -6444,7 +6448,7 @@
         <v>2025</v>
       </c>
       <c r="B54" s="48" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="C54" s="43" t="s">
         <v>43</v>
@@ -6454,7 +6458,7 @@
         <v>1</v>
       </c>
       <c r="E54" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F54" s="38" t="s">
         <v>27</v>
@@ -6463,7 +6467,7 @@
         <v>2025003050049</v>
       </c>
       <c r="H54" s="38" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="I54" s="3">
         <v>2156349509</v>
@@ -6475,7 +6479,7 @@
         <v>1500000000</v>
       </c>
       <c r="L54" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M54" s="51" t="s">
         <v>30</v>
@@ -6534,26 +6538,26 @@
         <v>2026</v>
       </c>
       <c r="B55" s="38" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="C55" s="47" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D55" s="66">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E55" s="38" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="F55" s="38" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="G55" s="49">
         <v>2025003050036</v>
       </c>
       <c r="H55" s="38" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="I55" s="3">
         <v>14202451801</v>
@@ -6571,13 +6575,13 @@
         <v>30</v>
       </c>
       <c r="N55" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O55" s="25">
         <v>46031</v>
       </c>
       <c r="P55" s="45" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="Q55" s="46">
         <v>13.9</v>
@@ -6622,26 +6626,26 @@
         <v>2026</v>
       </c>
       <c r="B56" s="38" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="C56" s="47" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D56" s="66">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E56" s="38" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="F56" s="38" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="G56" s="49">
         <v>2025003050040</v>
       </c>
       <c r="H56" s="38" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="I56" s="3">
         <v>2540216819</v>
@@ -6653,13 +6657,13 @@
         <v>2540216819</v>
       </c>
       <c r="L56" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M56" s="51" t="s">
         <v>30</v>
       </c>
       <c r="N56" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O56" s="25">
         <v>46031</v>
@@ -6668,10 +6672,10 @@
         <v>46335</v>
       </c>
       <c r="Q56" s="53" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R56" s="53" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S56" s="60">
         <v>19</v>
@@ -6710,26 +6714,26 @@
         <v>2026</v>
       </c>
       <c r="B57" s="38" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="C57" s="47" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="D57" s="66">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E57" s="38" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="F57" s="38" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="G57" s="49">
         <v>2025003050039</v>
       </c>
       <c r="H57" s="38" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="I57" s="50">
         <v>9381110055</v>
@@ -6747,19 +6751,19 @@
         <v>30</v>
       </c>
       <c r="N57" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O57" s="25">
         <v>46031</v>
       </c>
       <c r="P57" s="45" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="Q57" s="46" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R57" s="46" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S57" s="60" t="s">
         <v>41</v>
@@ -6798,26 +6802,26 @@
         <v>2026</v>
       </c>
       <c r="B58" s="38" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="C58" s="47" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="D58" s="66">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="E58" s="38" t="s">
-        <v>210</v>
+        <v>273</v>
       </c>
       <c r="F58" s="38" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="G58" s="49">
         <v>2025003050060</v>
       </c>
       <c r="H58" s="38" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="I58" s="4">
         <v>5567719862</v>
@@ -6829,19 +6833,19 @@
         <v>2783859931</v>
       </c>
       <c r="L58" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M58" s="51" t="s">
         <v>30</v>
       </c>
       <c r="N58" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O58" s="25">
         <v>46048</v>
       </c>
       <c r="P58" s="45" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="Q58" s="46">
         <v>15.02</v>
@@ -6886,7 +6890,7 @@
         <v>2026</v>
       </c>
       <c r="B59" s="38" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="C59" s="47" t="s">
         <v>25</v>
@@ -6896,7 +6900,7 @@
         <v>1</v>
       </c>
       <c r="E59" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F59" s="38" t="s">
         <v>27</v>
@@ -6905,7 +6909,7 @@
         <v>2025003050047</v>
       </c>
       <c r="H59" s="38" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="I59" s="50">
         <v>2577210949</v>
@@ -6917,13 +6921,13 @@
         <v>2557210949.52</v>
       </c>
       <c r="L59" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M59" s="51" t="s">
         <v>30</v>
       </c>
       <c r="N59" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O59" s="25">
         <v>46072</v>
@@ -6974,26 +6978,26 @@
         <v>2026</v>
       </c>
       <c r="B60" s="38" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="C60" s="47" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D60" s="66">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E60" s="38" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="F60" s="38" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="G60" s="49">
         <v>2025003050059</v>
       </c>
       <c r="H60" s="38" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="I60" s="3">
         <v>6759815490</v>
@@ -7005,19 +7009,19 @@
         <v>6759815490</v>
       </c>
       <c r="L60" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M60" s="28" t="s">
         <v>30</v>
       </c>
       <c r="N60" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O60" s="25">
         <v>46077</v>
       </c>
       <c r="P60" s="45" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="Q60" s="46">
         <v>39.979999999999997</v>
@@ -7062,26 +7066,26 @@
         <v>2026</v>
       </c>
       <c r="B61" s="38" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="C61" s="47" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D61" s="66">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E61" s="38" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="F61" s="38" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="G61" s="49">
         <v>2025003050058</v>
       </c>
       <c r="H61" s="38" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="I61" s="50">
         <v>1956028276</v>
@@ -7093,19 +7097,19 @@
         <v>1956028276</v>
       </c>
       <c r="L61" s="47" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M61" s="29" t="s">
         <v>30</v>
       </c>
       <c r="N61" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O61" s="25">
         <v>46073</v>
       </c>
       <c r="P61" s="45" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="Q61" s="46">
         <v>6.94</v>
@@ -7150,7 +7154,7 @@
         <v>2026</v>
       </c>
       <c r="B62" s="38" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C62" s="52" t="s">
         <v>25</v>
@@ -7160,16 +7164,16 @@
         <v>1</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="F62" s="18" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="G62" s="64">
         <v>2025003050037</v>
       </c>
       <c r="H62" s="38" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="I62" s="3">
         <v>4919153330</v>
@@ -7187,7 +7191,7 @@
         <v>30</v>
       </c>
       <c r="N62" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O62" s="25">
         <v>46073</v>
@@ -7238,7 +7242,7 @@
         <v>2026</v>
       </c>
       <c r="B63" s="38" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="C63" s="52" t="s">
         <v>33</v>
@@ -7248,16 +7252,16 @@
         <v>1</v>
       </c>
       <c r="E63" s="18" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="F63" s="18" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="G63" s="64">
         <v>2025003050037</v>
       </c>
       <c r="H63" s="38" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="I63" s="3">
         <v>4814470012</v>
@@ -7275,7 +7279,7 @@
         <v>30</v>
       </c>
       <c r="N63" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O63" s="25">
         <v>46073</v>
@@ -7326,26 +7330,26 @@
         <v>2026</v>
       </c>
       <c r="B64" s="38" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="C64" s="47" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="D64" s="66">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E64" s="38" t="s">
-        <v>224</v>
+        <v>274</v>
       </c>
       <c r="F64" s="18" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="G64" s="49">
         <v>2026003050010</v>
       </c>
       <c r="H64" s="38" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="I64" s="50">
         <v>8659084152</v>
@@ -7363,7 +7367,7 @@
         <v>30</v>
       </c>
       <c r="N64" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O64" s="25">
         <v>46105</v>
@@ -7414,7 +7418,7 @@
         <v>2026</v>
       </c>
       <c r="B65" s="38" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="C65" s="47" t="s">
         <v>25</v>
@@ -7433,7 +7437,7 @@
         <v>2026003050009</v>
       </c>
       <c r="H65" s="38" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="I65" s="50">
         <v>5112178665</v>
@@ -7451,7 +7455,7 @@
         <v>30</v>
       </c>
       <c r="N65" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O65" s="25">
         <v>46107</v>
@@ -7502,7 +7506,7 @@
         <v>2026</v>
       </c>
       <c r="B66" s="38" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="C66" s="47" t="s">
         <v>43</v>
@@ -7512,7 +7516,7 @@
         <v>1</v>
       </c>
       <c r="E66" s="18" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F66" s="18" t="s">
         <v>27</v>
@@ -7521,7 +7525,7 @@
         <v>2025003050057</v>
       </c>
       <c r="H66" s="38" t="s">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="I66" s="3">
         <v>2205897938</v>
@@ -7533,13 +7537,13 @@
         <v>1500000000</v>
       </c>
       <c r="L66" s="47" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M66" s="51" t="s">
         <v>30</v>
       </c>
       <c r="N66" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O66" s="25">
         <v>46299</v>
@@ -7590,7 +7594,7 @@
         <v>2026</v>
       </c>
       <c r="B67" s="38" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="C67" s="47" t="s">
         <v>25</v>
@@ -7600,7 +7604,7 @@
         <v>1</v>
       </c>
       <c r="E67" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F67" s="18" t="s">
         <v>27</v>
@@ -7609,7 +7613,7 @@
         <v>2025003050052</v>
       </c>
       <c r="H67" s="38" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="I67" s="3">
         <v>1727008802</v>
@@ -7621,19 +7625,19 @@
         <v>1500000000</v>
       </c>
       <c r="L67" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M67" s="51" t="s">
         <v>30</v>
       </c>
       <c r="N67" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O67" s="25">
         <v>46132</v>
       </c>
       <c r="P67" s="45" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="Q67" s="46" t="s">
         <v>41</v>
@@ -7678,17 +7682,17 @@
         <v>2026</v>
       </c>
       <c r="B68" s="38" t="s">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="C68" s="47" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D68" s="65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E68" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F68" s="18" t="s">
         <v>27</v>
@@ -7697,7 +7701,7 @@
         <v>2026003050017</v>
       </c>
       <c r="H68" s="38" t="s">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="I68" s="4">
         <v>2177276654</v>
@@ -7709,19 +7713,19 @@
         <v>1677276654</v>
       </c>
       <c r="L68" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M68" s="46" t="s">
         <v>30</v>
       </c>
       <c r="N68" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O68" s="25">
         <v>46147</v>
       </c>
       <c r="P68" s="45" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="Q68" s="46" t="s">
         <v>41</v>
@@ -7766,7 +7770,7 @@
         <v>2026</v>
       </c>
       <c r="B69" s="38" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="C69" s="47" t="s">
         <v>25</v>
@@ -7776,7 +7780,7 @@
         <v>3</v>
       </c>
       <c r="E69" s="38" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F69" s="18" t="s">
         <v>27</v>
@@ -7785,7 +7789,7 @@
         <v>2026003050018</v>
       </c>
       <c r="H69" s="38" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="I69" s="50">
         <v>8022406899</v>
@@ -7803,13 +7807,13 @@
         <v>30</v>
       </c>
       <c r="N69" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O69" s="25">
         <v>46129</v>
       </c>
       <c r="P69" s="45" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="Q69" s="46">
         <v>15.5</v>
@@ -7854,7 +7858,7 @@
         <v>2026</v>
       </c>
       <c r="B70" s="38" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="C70" s="47" t="s">
         <v>33</v>
@@ -7864,7 +7868,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F70" s="38" t="s">
         <v>27</v>
@@ -7873,7 +7877,7 @@
         <v>2026003050021</v>
       </c>
       <c r="H70" s="38" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="I70" s="3">
         <v>2356550945</v>
@@ -7885,13 +7889,13 @@
         <v>1768550945</v>
       </c>
       <c r="L70" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M70" s="51" t="s">
         <v>30</v>
       </c>
       <c r="N70" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O70" s="25">
         <v>46149</v>
@@ -7942,17 +7946,17 @@
         <v>2026</v>
       </c>
       <c r="B71" s="48" t="s">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="C71" s="43" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D71" s="65">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E71" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F71" s="38" t="s">
         <v>27</v>
@@ -7961,7 +7965,7 @@
         <v>2026003050005</v>
       </c>
       <c r="H71" s="38" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="I71" s="44">
         <v>2126428620</v>
@@ -7973,13 +7977,13 @@
         <v>1821081885</v>
       </c>
       <c r="L71" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M71" s="51" t="s">
         <v>30</v>
       </c>
       <c r="N71" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O71" s="25">
         <v>46191</v>
@@ -8030,7 +8034,7 @@
         <v>2026</v>
       </c>
       <c r="B72" s="38" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="C72" s="47" t="s">
         <v>43</v>
@@ -8040,7 +8044,7 @@
         <v>1</v>
       </c>
       <c r="E72" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F72" s="38" t="s">
         <v>27</v>
@@ -8049,7 +8053,7 @@
         <v>2026003050006</v>
       </c>
       <c r="H72" s="38" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="I72" s="3">
         <v>2495192913</v>
@@ -8061,19 +8065,19 @@
         <v>2490192913</v>
       </c>
       <c r="L72" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M72" s="51" t="s">
         <v>30</v>
       </c>
       <c r="N72" s="59" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="O72" s="25">
         <v>46170</v>
       </c>
       <c r="P72" s="45" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="Q72" s="46" t="s">
         <v>41</v>
@@ -8118,17 +8122,17 @@
         <v>2026</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="D73" s="65">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="F73" s="7" t="s">
         <v>27</v>
@@ -8137,7 +8141,7 @@
         <v>2026003050011</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="I73" s="16">
         <v>2095882218</v>
@@ -8149,13 +8153,13 @@
         <v>1995882218</v>
       </c>
       <c r="L73" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M73" s="51" t="s">
         <v>30</v>
       </c>
       <c r="N73" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O73" s="25">
         <v>46132</v>
@@ -8206,26 +8210,26 @@
         <v>2026</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D74" s="66">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="G74" s="57">
         <v>2026003050014</v>
       </c>
       <c r="H74" s="7" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="I74" s="11">
         <v>5482855957</v>
@@ -8243,13 +8247,13 @@
         <v>30</v>
       </c>
       <c r="N74" s="59" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="O74" s="25">
         <v>46189</v>
       </c>
       <c r="P74" s="45" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="Q74" s="46" t="s">
         <v>41</v>
@@ -8294,26 +8298,26 @@
         <v>2026</v>
       </c>
       <c r="B75" s="38" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="C75" s="47" t="s">
-        <v>65</v>
-      </c>
-      <c r="D75" s="66">
+        <v>62</v>
+      </c>
+      <c r="D75" s="71">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="G75" s="49">
         <v>2026003050008</v>
       </c>
       <c r="H75" s="38" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="I75" s="3">
         <v>2300078297</v>
@@ -8325,19 +8329,19 @@
         <v>2250078297</v>
       </c>
       <c r="L75" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M75" s="51" t="s">
         <v>30</v>
       </c>
       <c r="N75" s="59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O75" s="25">
         <v>46175</v>
       </c>
       <c r="P75" s="45" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="Q75" s="46" t="s">
         <v>41</v>
@@ -8382,26 +8386,26 @@
         <v>2026</v>
       </c>
       <c r="B76" s="38" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="C76" s="47" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D76" s="66">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E76" s="38" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="F76" s="18" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="G76" s="49">
         <v>2026003050002</v>
       </c>
       <c r="H76" s="38" t="s">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="I76" s="50">
         <v>1408385533</v>
@@ -8413,19 +8417,19 @@
         <v>1408385533</v>
       </c>
       <c r="L76" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M76" s="51" t="s">
         <v>30</v>
       </c>
       <c r="N76" s="59" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="O76" s="25">
         <v>46185</v>
       </c>
       <c r="P76" s="45" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="Q76" s="46" t="s">
         <v>41</v>
@@ -8470,26 +8474,26 @@
         <v>2026</v>
       </c>
       <c r="B77" s="38" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="C77" s="52" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D77" s="66">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="F77" s="18" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="G77" s="64">
         <v>2026003050020</v>
       </c>
       <c r="H77" s="38" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
       <c r="I77" s="50">
         <v>8105380232</v>
@@ -8507,13 +8511,13 @@
         <v>30</v>
       </c>
       <c r="N77" s="59" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="O77" s="25">
         <v>46185</v>
       </c>
       <c r="P77" s="45" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="Q77" s="46" t="s">
         <v>41</v>
@@ -8558,26 +8562,26 @@
         <v>2026</v>
       </c>
       <c r="B78" s="38" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C78" s="52" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D78" s="66">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="F78" s="18" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="G78" s="64">
         <v>2026003050020</v>
       </c>
       <c r="H78" s="38" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
       <c r="I78" s="3">
         <v>4333614485</v>
@@ -8595,13 +8599,13 @@
         <v>30</v>
       </c>
       <c r="N78" s="59" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="O78" s="25">
         <v>46185</v>
       </c>
       <c r="P78" s="45" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="Q78" s="46" t="s">
         <v>41</v>
@@ -8646,7 +8650,7 @@
         <v>2026</v>
       </c>
       <c r="B79" s="38" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="C79" s="52" t="s">
         <v>43</v>
@@ -8656,16 +8660,16 @@
         <v>1</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="F79" s="18" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="G79" s="64">
         <v>2026003050015</v>
       </c>
       <c r="H79" s="38" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="I79" s="3">
         <v>3806958402</v>
@@ -8683,13 +8687,13 @@
         <v>30</v>
       </c>
       <c r="N79" s="59" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="O79" s="25">
         <v>46185</v>
       </c>
       <c r="P79" s="45" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="Q79" s="46" t="s">
         <v>41</v>
@@ -8734,26 +8738,26 @@
         <v>2026</v>
       </c>
       <c r="B80" s="38" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="C80" s="52" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D80" s="66">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="F80" s="18" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="G80" s="64">
         <v>2026003050015</v>
       </c>
       <c r="H80" s="38" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="I80" s="3">
         <v>2044483403</v>
@@ -8771,13 +8775,13 @@
         <v>30</v>
       </c>
       <c r="N80" s="59" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="O80" s="25">
         <v>46185</v>
       </c>
       <c r="P80" s="45" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="Q80" s="46" t="s">
         <v>41</v>
@@ -8822,26 +8826,26 @@
         <v>2026</v>
       </c>
       <c r="B81" s="38" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="C81" s="47" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="D81" s="66">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="F81" s="18" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="G81" s="49">
         <v>2026003050025</v>
       </c>
       <c r="H81" s="38" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="I81" s="3">
         <v>3738220582</v>
@@ -8859,13 +8863,13 @@
         <v>30</v>
       </c>
       <c r="N81" s="59" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="O81" s="25">
         <v>46185</v>
       </c>
       <c r="P81" s="45" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="Q81" s="46" t="s">
         <v>41</v>
@@ -8910,17 +8914,17 @@
         <v>2026</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="C82" s="47" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="D82" s="65">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E82" s="38" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="F82" s="38" t="s">
         <v>27</v>
@@ -8929,7 +8933,7 @@
         <v>2026003050016</v>
       </c>
       <c r="H82" s="38" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="I82" s="4">
         <v>1875050361</v>
@@ -8941,19 +8945,19 @@
         <v>1875050361</v>
       </c>
       <c r="L82" s="43" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="M82" s="46" t="s">
         <v>30</v>
       </c>
       <c r="N82" s="59" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="O82" s="25">
         <v>46212</v>
       </c>
       <c r="P82" s="45" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q82" s="46" t="s">
         <v>41</v>
@@ -8998,26 +9002,26 @@
         <v>2026</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="C83" s="47" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D83" s="66">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E83" s="38" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="F83" s="38" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="G83" s="49">
         <v>2026003050022</v>
       </c>
       <c r="H83" s="38" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="I83" s="50">
         <v>6654540000</v>
@@ -9035,13 +9039,13 @@
         <v>30</v>
       </c>
       <c r="N83" s="59" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="O83" s="62">
         <v>46239</v>
       </c>
       <c r="P83" s="45" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="Q83" s="46" t="s">
         <v>41</v>
@@ -9086,26 +9090,26 @@
         <v>2026</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="C84" s="47" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="D84" s="66">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E84" s="38" t="s">
-        <v>273</v>
+        <v>252</v>
       </c>
       <c r="F84" s="38" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="G84" s="49">
         <v>2026003050019</v>
       </c>
       <c r="H84" s="38" t="s">
-        <v>275</v>
+        <v>254</v>
       </c>
       <c r="I84" s="50">
         <v>8054980500</v>
@@ -9123,13 +9127,13 @@
         <v>30</v>
       </c>
       <c r="N84" s="59" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="O84" s="62">
         <v>46212</v>
       </c>
       <c r="P84" s="45" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="Q84" s="46" t="s">
         <v>41</v>
